--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A4FF693C-FE01-4724-8304-5E2C05CD45CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE2F694-97AF-4E01-8160-9D27BD61659A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="51">
   <si>
     <t>Presupuesto</t>
   </si>
@@ -146,6 +146,9 @@
   </si>
   <si>
     <t>Deposita Nico</t>
+  </si>
+  <si>
+    <t>Banco compartido</t>
   </si>
   <si>
     <t>Mayo</t>
@@ -688,9 +691,7 @@
     <col min="25" max="25" width="13" style="4" customWidth="1"/>
     <col min="26" max="26" width="9.140625" style="4"/>
     <col min="27" max="27" width="12" style="4" customWidth="1"/>
-    <col min="28" max="33" width="9.140625" style="4"/>
-    <col min="34" max="34" width="9" style="4" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="4"/>
+    <col min="28" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -825,12 +826,12 @@
         <v>33</v>
       </c>
       <c r="AH2" s="7" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3" s="4">
         <v>15500</v>
@@ -928,7 +929,7 @@
     </row>
     <row r="4" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" s="4">
         <v>15500</v>
@@ -1029,7 +1030,7 @@
     </row>
     <row r="5" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C5" s="4">
         <v>4369</v>
@@ -1130,7 +1131,7 @@
     </row>
     <row r="6" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D6" s="4">
         <v>15500</v>
@@ -1225,7 +1226,7 @@
     </row>
     <row r="7" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" s="4">
         <v>25000</v>
@@ -1326,7 +1327,7 @@
     </row>
     <row r="8" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D8" s="4">
         <v>15500</v>
@@ -1424,7 +1425,7 @@
     </row>
     <row r="9" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C9" s="4">
         <v>4369</v>
@@ -1525,7 +1526,7 @@
     </row>
     <row r="10" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" s="4">
         <v>15500</v>
@@ -1620,7 +1621,7 @@
     </row>
     <row r="12" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -1708,7 +1709,7 @@
         <v>19</v>
       </c>
       <c r="T13" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="U13" s="4" t="s">
         <v>21</v>
@@ -1717,7 +1718,7 @@
         <v>22</v>
       </c>
       <c r="W13" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X13" s="4" t="s">
         <v>24</v>
@@ -1734,7 +1735,7 @@
     </row>
     <row r="14" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B14" s="4" t="str">
         <f>IF(Mayo!B33&gt;0,Mayo!B33,"")</f>
@@ -1760,13 +1761,13 @@
         <f>IF(Mayo!G33&gt;0,Mayo!G33,"")</f>
         <v>980</v>
       </c>
-      <c r="H14" s="4" t="str">
+      <c r="H14" s="4">
         <f>IF(Mayo!H33&gt;0,Mayo!H33,"")</f>
-        <v/>
-      </c>
-      <c r="I14" s="4" t="str">
+        <v>3291.56</v>
+      </c>
+      <c r="I14" s="4">
         <f>IF(Mayo!I33&gt;0,Mayo!I33,"")</f>
-        <v/>
+        <v>2144.2600000000002</v>
       </c>
       <c r="J14" s="4" t="str">
         <f>IF(Mayo!J33&gt;0,Mayo!J33,"")</f>
@@ -1838,12 +1839,12 @@
       </c>
       <c r="AA14" s="4">
         <f>IF(Mayo!AA33&gt;0,Mayo!AA33,"")</f>
-        <v>22170.41</v>
+        <v>27606.23</v>
       </c>
     </row>
     <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B15" s="4" t="str">
         <f>IF(Junio!B32&gt;0,Junio!B32,"")</f>
@@ -1952,7 +1953,7 @@
     </row>
     <row r="16" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B16" s="4" t="str">
         <f>IF(Julio!B33&gt;0,Julio!B33,"")</f>
@@ -2061,7 +2062,7 @@
     </row>
     <row r="17" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17" s="4" t="str">
         <f>IF(Agosto!B33&gt;0,Agosto!B33,"")</f>
@@ -2170,7 +2171,7 @@
     </row>
     <row r="18" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" s="4" t="str">
         <f>IF(Setiembre!B32&gt;0,Setiembre!B32,"")</f>
@@ -2279,7 +2280,7 @@
     </row>
     <row r="19" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B19" s="4" t="str">
         <f>IF(Octubre!B33&gt;0,Octubre!B33,"")</f>
@@ -2388,7 +2389,7 @@
     </row>
     <row r="20" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B20" s="4" t="str">
         <f>IF(Noviembre!B32&gt;0,Noviembre!B32,"")</f>
@@ -2497,7 +2498,7 @@
     </row>
     <row r="21" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B21" s="4" t="str">
         <f>IF(Diciembre!B33&gt;0,Diciembre!B33,"")</f>
@@ -2606,7 +2607,7 @@
     </row>
     <row r="23" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -2694,7 +2695,7 @@
         <v>19</v>
       </c>
       <c r="T24" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="U24" s="4" t="s">
         <v>21</v>
@@ -2703,7 +2704,7 @@
         <v>22</v>
       </c>
       <c r="W24" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X24" s="4" t="s">
         <v>24</v>
@@ -2715,12 +2716,12 @@
         <v>26</v>
       </c>
       <c r="AA24" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25" s="4" t="str">
         <f>IF(ISNUMBER(Mayo!B33),B3-Mayo!B33,"")</f>
@@ -2746,13 +2747,13 @@
         <f>IF(ISNUMBER(Mayo!G33),G3-Mayo!G33,"")</f>
         <v>20</v>
       </c>
-      <c r="H25" s="4" t="str">
+      <c r="H25" s="4">
         <f>IF(ISNUMBER(Mayo!H33),H3-Mayo!H33,"")</f>
-        <v/>
-      </c>
-      <c r="I25" s="4" t="str">
+        <v>208.44000000000005</v>
+      </c>
+      <c r="I25" s="4">
         <f>IF(ISNUMBER(Mayo!I33),I3-Mayo!I33,"")</f>
-        <v/>
+        <v>855.73999999999978</v>
       </c>
       <c r="J25" s="4" t="str">
         <f>IF(ISNUMBER(Mayo!J33),J3-Mayo!J33,"")</f>
@@ -2824,12 +2825,12 @@
       </c>
       <c r="AA25" s="13">
         <f t="shared" ref="AA25:AA33" si="6">SUMIF(B25:Z25,"&lt;&gt;"&amp;"")</f>
-        <v>26329.59</v>
+        <v>27393.77</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26" s="4" t="str">
         <f>IF(ISNUMBER(Junio!B32),B4-Junio!B32,"")</f>
@@ -2938,7 +2939,7 @@
     </row>
     <row r="27" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27" s="4" t="str">
         <f>IF(ISNUMBER(Julio!B33),B5-Julio!B33,"")</f>
@@ -3047,7 +3048,7 @@
     </row>
     <row r="28" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28" s="4" t="str">
         <f>IF(ISNUMBER(Agosto!B33),B6-Agosto!B33,"")</f>
@@ -3156,7 +3157,7 @@
     </row>
     <row r="29" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29" s="4" t="str">
         <f>IF(ISNUMBER(Setiembre!B32),B7-Setiembre!B32,"")</f>
@@ -3265,7 +3266,7 @@
     </row>
     <row r="30" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30" s="4" t="str">
         <f>IF(ISNUMBER(Octubre!B33),B8-Octubre!B33,"")</f>
@@ -3374,7 +3375,7 @@
     </row>
     <row r="31" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31" s="4" t="str">
         <f>IF(ISNUMBER(Noviembre!B32),B9-Noviembre!B32,"")</f>
@@ -3483,7 +3484,7 @@
     </row>
     <row r="32" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B32" s="4" t="str">
         <f>IF(ISNUMBER(Diciembre!B33),B10-Diciembre!B33,"")</f>
@@ -3592,7 +3593,7 @@
     </row>
     <row r="33" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B33" s="13">
         <f t="shared" ref="B33:Z33" si="7">SUMIF(B25:B32,"&lt;&gt;"&amp;"")</f>
@@ -3620,11 +3621,11 @@
       </c>
       <c r="H33" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>208.44000000000005</v>
       </c>
       <c r="I33" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>855.73999999999978</v>
       </c>
       <c r="J33" s="13">
         <f t="shared" si="7"/>
@@ -3696,7 +3697,7 @@
       </c>
       <c r="AA33" s="13">
         <f t="shared" si="6"/>
-        <v>26329.59</v>
+        <v>27393.77</v>
       </c>
     </row>
   </sheetData>
@@ -3728,12 +3729,29 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="26" width="13" customWidth="1"/>
-    <col min="27" max="27" width="14" customWidth="1"/>
+    <col min="2" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="21.140625" customWidth="1"/>
+    <col min="5" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="12.28515625" customWidth="1"/>
+    <col min="10" max="10" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.42578125" customWidth="1"/>
+    <col min="12" max="12" width="22.42578125" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="22.28515625" customWidth="1"/>
+    <col min="15" max="16" width="13" customWidth="1"/>
+    <col min="17" max="18" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="20.140625" customWidth="1"/>
+    <col min="21" max="22" width="13" customWidth="1"/>
+    <col min="23" max="23" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>1</v>
       </c>
@@ -3816,7 +3834,7 @@
         <v>27</v>
       </c>
       <c r="AB1" s="15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4014,8 +4032,14 @@
       <c r="E7" s="17"/>
       <c r="F7" s="17"/>
       <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
+      <c r="H7" s="17">
+        <f>3327-35.44</f>
+        <v>3291.56</v>
+      </c>
+      <c r="I7" s="17">
+        <f>2180-35.74</f>
+        <v>2144.2600000000002</v>
+      </c>
       <c r="J7" s="17"/>
       <c r="K7" s="17"/>
       <c r="L7" s="17"/>
@@ -4035,7 +4059,7 @@
       <c r="Z7" s="17"/>
       <c r="AA7" s="17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5435.82</v>
       </c>
       <c r="AB7" s="17"/>
     </row>
@@ -4916,7 +4940,7 @@
     </row>
     <row r="33" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B33" s="13" t="str">
         <f t="shared" ref="B33:AA33" si="1">IF(COUNTA(B2:B32)&gt;0,SUM(B2:B32),"")</f>
@@ -4942,13 +4966,13 @@
         <f t="shared" si="1"/>
         <v>980</v>
       </c>
-      <c r="H33" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I33" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="H33" s="13">
+        <f t="shared" si="1"/>
+        <v>3291.56</v>
+      </c>
+      <c r="I33" s="13">
+        <f t="shared" si="1"/>
+        <v>2144.2600000000002</v>
       </c>
       <c r="J33" s="13" t="str">
         <f t="shared" si="1"/>
@@ -5020,7 +5044,7 @@
       </c>
       <c r="AA33" s="13">
         <f t="shared" si="1"/>
-        <v>22170.41</v>
+        <v>27606.23</v>
       </c>
       <c r="AB33" s="18"/>
     </row>
@@ -5124,7 +5148,7 @@
         <v>27</v>
       </c>
       <c r="AB1" s="15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6179,7 +6203,7 @@
     </row>
     <row r="32" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B32" s="13" t="str">
         <f t="shared" ref="B32:AA32" si="1">IF(COUNTA(B2:B31)&gt;0,SUM(B2:B31),"")</f>
@@ -6387,7 +6411,7 @@
         <v>27</v>
       </c>
       <c r="AB1" s="15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7477,7 +7501,7 @@
     </row>
     <row r="33" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B33" s="13" t="str">
         <f t="shared" ref="B33:AA33" si="1">IF(COUNTA(B2:B32)&gt;0,SUM(B2:B32),"")</f>
@@ -7685,7 +7709,7 @@
         <v>27</v>
       </c>
       <c r="AB1" s="15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8775,7 +8799,7 @@
     </row>
     <row r="33" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B33" s="13" t="str">
         <f t="shared" ref="B33:AA33" si="1">IF(COUNTA(B2:B32)&gt;0,SUM(B2:B32),"")</f>
@@ -8983,7 +9007,7 @@
         <v>27</v>
       </c>
       <c r="AB1" s="15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10038,7 +10062,7 @@
     </row>
     <row r="32" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B32" s="13" t="str">
         <f t="shared" ref="B32:AA32" si="1">IF(COUNTA(B2:B31)&gt;0,SUM(B2:B31),"")</f>
@@ -10246,7 +10270,7 @@
         <v>27</v>
       </c>
       <c r="AB1" s="15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11336,7 +11360,7 @@
     </row>
     <row r="33" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B33" s="13" t="str">
         <f t="shared" ref="B33:AA33" si="1">IF(COUNTA(B2:B32)&gt;0,SUM(B2:B32),"")</f>
@@ -11544,7 +11568,7 @@
         <v>27</v>
       </c>
       <c r="AB1" s="15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12599,7 +12623,7 @@
     </row>
     <row r="32" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B32" s="13" t="str">
         <f t="shared" ref="B32:AA32" si="1">IF(COUNTA(B2:B31)&gt;0,SUM(B2:B31),"")</f>
@@ -12807,7 +12831,7 @@
         <v>27</v>
       </c>
       <c r="AB1" s="15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13897,7 +13921,7 @@
     </row>
     <row r="33" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B33" s="13" t="str">
         <f t="shared" ref="B33:AA33" si="1">IF(COUNTA(B2:B32)&gt;0,SUM(B2:B32),"")</f>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42D45407-6470-4E15-AF69-014C33C07B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38529319-E284-4F54-997E-64DA84AD1025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="62">
   <si>
     <t>Presupuesto</t>
   </si>
@@ -198,12 +198,49 @@
   <si>
     <t>Total</t>
   </si>
+  <si>
+    <t>Objetivo</t>
+  </si>
+  <si>
+    <t>Sofi</t>
+  </si>
+  <si>
+    <t>Nico</t>
+  </si>
+  <si>
+    <t>Fondo</t>
+  </si>
+  <si>
+    <t>% completado</t>
+  </si>
+  <si>
+    <t>Gastos del fondo</t>
+  </si>
+  <si>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
+    <t>Monto</t>
+  </si>
+  <si>
+    <t>Total gastos</t>
+  </si>
+  <si>
+    <t>Saldo neto</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+  </numFmts>
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,8 +282,42 @@
       <name val="Cambria"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Cambria"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0284C7"/>
+      <name val="Cambria"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF555555"/>
+      <name val="Cambria"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC62828"/>
+      <name val="Cambria"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1B5E20"/>
+      <name val="Cambria"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -301,6 +372,36 @@
         <bgColor rgb="FF666699"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E7D32"/>
+        <bgColor rgb="FF276221"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFE8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2FE"/>
+        <bgColor rgb="FFE3F2FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E6C9"/>
+        <bgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF388E3C"/>
+        <bgColor rgb="FF2E7D32"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -329,7 +430,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -364,6 +465,19 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="7" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -373,6 +487,22 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="9" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -668,16 +798,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH33"/>
+  <dimension ref="A1:AH54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.28515625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8" style="1" customWidth="1"/>
     <col min="4" max="4" width="13.5703125" style="1" customWidth="1"/>
-    <col min="5" max="9" width="9.140625" style="1"/>
-    <col min="10" max="10" width="14" style="1" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="1"/>
+    <col min="7" max="7" width="12" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="1"/>
+    <col min="9" max="10" width="14" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" customWidth="1"/>
     <col min="12" max="12" width="18.5703125" style="1" customWidth="1"/>
     <col min="13" max="13" width="10.42578125" style="1" customWidth="1"/>
     <col min="14" max="14" width="12.7109375" style="1" customWidth="1"/>
@@ -695,35 +828,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
-      <c r="S1" s="16"/>
-      <c r="T1" s="16"/>
-      <c r="U1" s="16"/>
-      <c r="V1" s="16"/>
-      <c r="W1" s="16"/>
-      <c r="X1" s="16"/>
-      <c r="Y1" s="16"/>
-      <c r="Z1" s="16"/>
-      <c r="AA1" s="16"/>
+      <c r="A1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
+      <c r="R1" s="25"/>
+      <c r="S1" s="25"/>
+      <c r="T1" s="25"/>
+      <c r="U1" s="25"/>
+      <c r="V1" s="25"/>
+      <c r="W1" s="25"/>
+      <c r="X1" s="25"/>
+      <c r="Y1" s="25"/>
+      <c r="Z1" s="25"/>
+      <c r="AA1" s="25"/>
     </row>
     <row r="2" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1620,35 +1753,35 @@
       </c>
     </row>
     <row r="12" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="17"/>
-      <c r="R12" s="17"/>
-      <c r="S12" s="17"/>
-      <c r="T12" s="17"/>
-      <c r="U12" s="17"/>
-      <c r="V12" s="17"/>
-      <c r="W12" s="17"/>
-      <c r="X12" s="17"/>
-      <c r="Y12" s="17"/>
-      <c r="Z12" s="17"/>
-      <c r="AA12" s="17"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="26"/>
+      <c r="M12" s="26"/>
+      <c r="N12" s="26"/>
+      <c r="O12" s="26"/>
+      <c r="P12" s="26"/>
+      <c r="Q12" s="26"/>
+      <c r="R12" s="26"/>
+      <c r="S12" s="26"/>
+      <c r="T12" s="26"/>
+      <c r="U12" s="26"/>
+      <c r="V12" s="26"/>
+      <c r="W12" s="26"/>
+      <c r="X12" s="26"/>
+      <c r="Y12" s="26"/>
+      <c r="Z12" s="26"/>
+      <c r="AA12" s="26"/>
     </row>
     <row r="13" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -2606,35 +2739,35 @@
       </c>
     </row>
     <row r="23" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="18"/>
-      <c r="K23" s="18"/>
-      <c r="L23" s="18"/>
-      <c r="M23" s="18"/>
-      <c r="N23" s="18"/>
-      <c r="O23" s="18"/>
-      <c r="P23" s="18"/>
-      <c r="Q23" s="18"/>
-      <c r="R23" s="18"/>
-      <c r="S23" s="18"/>
-      <c r="T23" s="18"/>
-      <c r="U23" s="18"/>
-      <c r="V23" s="18"/>
-      <c r="W23" s="18"/>
-      <c r="X23" s="18"/>
-      <c r="Y23" s="18"/>
-      <c r="Z23" s="18"/>
-      <c r="AA23" s="18"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="27"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="27"/>
+      <c r="N23" s="27"/>
+      <c r="O23" s="27"/>
+      <c r="P23" s="27"/>
+      <c r="Q23" s="27"/>
+      <c r="R23" s="27"/>
+      <c r="S23" s="27"/>
+      <c r="T23" s="27"/>
+      <c r="U23" s="27"/>
+      <c r="V23" s="27"/>
+      <c r="W23" s="27"/>
+      <c r="X23" s="27"/>
+      <c r="Y23" s="27"/>
+      <c r="Z23" s="27"/>
+      <c r="AA23" s="27"/>
     </row>
     <row r="24" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
@@ -3698,6 +3831,173 @@
       <c r="AA33" s="10">
         <f t="shared" si="6"/>
         <v>27411.759999999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A37" s="17"/>
+      <c r="B37" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="F37" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="G37" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="H37" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="I37" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="J37" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="K37" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="L37" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="M37" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A38" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B38" s="19">
+        <v>500000</v>
+      </c>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
+      <c r="H38" s="20"/>
+      <c r="I38" s="20"/>
+      <c r="J38" s="20"/>
+      <c r="K38" s="21">
+        <f>SUM(C38:J38)</f>
+        <v>0</v>
+      </c>
+      <c r="L38" s="22">
+        <f>K38/2</f>
+        <v>0</v>
+      </c>
+      <c r="M38" s="22">
+        <f>K38/2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A39" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="K39" s="24">
+        <f>K38/B38</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A41" s="28" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A42" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="B42" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" s="29" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A43" s="30"/>
+      <c r="B43" s="31"/>
+      <c r="C43" s="32"/>
+    </row>
+    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A44" s="30"/>
+      <c r="B44" s="31"/>
+      <c r="C44" s="32"/>
+    </row>
+    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A45" s="30"/>
+      <c r="B45" s="31"/>
+      <c r="C45" s="32"/>
+    </row>
+    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A46" s="30"/>
+      <c r="B46" s="31"/>
+      <c r="C46" s="32"/>
+    </row>
+    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A47" s="30"/>
+      <c r="B47" s="31"/>
+      <c r="C47" s="32"/>
+    </row>
+    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A48" s="30"/>
+      <c r="B48" s="31"/>
+      <c r="C48" s="32"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="30"/>
+      <c r="B49" s="31"/>
+      <c r="C49" s="32"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="30"/>
+      <c r="B50" s="31"/>
+      <c r="C50" s="32"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="30"/>
+      <c r="B51" s="31"/>
+      <c r="C51" s="32"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="30"/>
+      <c r="B52" s="31"/>
+      <c r="C52" s="32"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="34"/>
+      <c r="C53" s="35">
+        <f>SUM(C43:C52)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="36"/>
+      <c r="C54" s="37">
+        <f>K38-C53</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38529319-E284-4F54-997E-64DA84AD1025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF5816E9-2059-428C-BC21-C464E9A04280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="63">
   <si>
     <t>Presupuesto</t>
   </si>
@@ -230,6 +230,9 @@
   </si>
   <si>
     <t>Saldo neto</t>
+  </si>
+  <si>
+    <t>Uniforme Roci</t>
   </si>
 </sst>
 </file>
@@ -478,15 +481,6 @@
     <xf numFmtId="3" fontId="7" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -503,6 +497,15 @@
     <xf numFmtId="3" fontId="9" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -828,35 +831,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="25"/>
-      <c r="Z1" s="25"/>
-      <c r="AA1" s="25"/>
+      <c r="A1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="35"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="35"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="35"/>
+      <c r="AA1" s="35"/>
     </row>
     <row r="2" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -970,10 +973,10 @@
         <v>15500</v>
       </c>
       <c r="E3" s="1">
-        <v>9500</v>
+        <v>10600</v>
       </c>
       <c r="F3" s="1">
-        <v>26000</v>
+        <v>26100</v>
       </c>
       <c r="G3" s="1">
         <v>1000</v>
@@ -1031,33 +1034,33 @@
       </c>
       <c r="AA3" s="1">
         <f t="shared" ref="AA3:AA10" si="0">SUM(B3:Z3)</f>
-        <v>150500</v>
+        <v>151700</v>
       </c>
       <c r="AB3" s="5">
         <f t="shared" ref="AB3:AB10" si="1">+AA3/2</f>
-        <v>75250</v>
+        <v>75850</v>
       </c>
       <c r="AC3" s="1">
         <v>10000</v>
       </c>
       <c r="AD3" s="5">
         <f t="shared" ref="AD3:AD10" si="2">+AE3-AB3-AC3</f>
-        <v>9750</v>
+        <v>9150</v>
       </c>
       <c r="AE3" s="1">
         <v>95000</v>
       </c>
       <c r="AF3" s="6">
-        <f t="shared" ref="AF3:AF10" si="3">AA3/2-L3</f>
-        <v>56250</v>
+        <f>AA3/2-L3</f>
+        <v>56850</v>
       </c>
       <c r="AG3" s="7">
-        <f t="shared" ref="AG3:AG10" si="4">AA3/2-D3</f>
-        <v>59750</v>
+        <f t="shared" ref="AG3:AG10" si="3">AA3/2-D3</f>
+        <v>60350</v>
       </c>
       <c r="AH3" s="8">
-        <f t="shared" ref="AH3:AH10" si="5">AF3+AG3</f>
-        <v>116000</v>
+        <f t="shared" ref="AH3:AH10" si="4">AF3+AG3</f>
+        <v>117200</v>
       </c>
     </row>
     <row r="4" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1068,10 +1071,10 @@
         <v>15500</v>
       </c>
       <c r="E4" s="1">
-        <v>9500</v>
+        <v>10600</v>
       </c>
       <c r="F4" s="1">
-        <v>35000</v>
+        <v>35500</v>
       </c>
       <c r="G4" s="1">
         <v>1000</v>
@@ -1132,33 +1135,33 @@
       </c>
       <c r="AA4" s="1">
         <f t="shared" si="0"/>
-        <v>146400</v>
+        <v>148000</v>
       </c>
       <c r="AB4" s="5">
         <f t="shared" si="1"/>
-        <v>73200</v>
+        <v>74000</v>
       </c>
       <c r="AC4" s="1">
         <v>10000</v>
       </c>
       <c r="AD4" s="5">
         <f t="shared" si="2"/>
-        <v>11800</v>
+        <v>11000</v>
       </c>
       <c r="AE4" s="1">
         <v>95000</v>
       </c>
       <c r="AF4" s="6">
+        <f t="shared" ref="AF3:AF10" si="5">AA4/2-L4</f>
+        <v>66500</v>
+      </c>
+      <c r="AG4" s="7">
         <f t="shared" si="3"/>
-        <v>65700</v>
-      </c>
-      <c r="AG4" s="7">
+        <v>58500</v>
+      </c>
+      <c r="AH4" s="8">
         <f t="shared" si="4"/>
-        <v>57700</v>
-      </c>
-      <c r="AH4" s="8">
-        <f t="shared" si="5"/>
-        <v>123400</v>
+        <v>125000</v>
       </c>
     </row>
     <row r="5" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1172,10 +1175,10 @@
         <v>15500</v>
       </c>
       <c r="E5" s="1">
-        <v>9500</v>
+        <v>10600</v>
       </c>
       <c r="F5" s="1">
-        <v>26000</v>
+        <v>26100</v>
       </c>
       <c r="G5" s="1">
         <v>1000</v>
@@ -1233,33 +1236,33 @@
       </c>
       <c r="AA5" s="1">
         <f t="shared" si="0"/>
-        <v>133419</v>
+        <v>134619</v>
       </c>
       <c r="AB5" s="5">
         <f t="shared" si="1"/>
-        <v>66709.5</v>
+        <v>67309.5</v>
       </c>
       <c r="AC5" s="1">
         <v>10000</v>
       </c>
       <c r="AD5" s="5">
         <f t="shared" si="2"/>
-        <v>18290.5</v>
+        <v>17690.5</v>
       </c>
       <c r="AE5" s="1">
         <v>95000</v>
       </c>
       <c r="AF5" s="6">
+        <f t="shared" si="5"/>
+        <v>59809.5</v>
+      </c>
+      <c r="AG5" s="7">
         <f t="shared" si="3"/>
-        <v>59209.5</v>
-      </c>
-      <c r="AG5" s="7">
+        <v>51809.5</v>
+      </c>
+      <c r="AH5" s="8">
         <f t="shared" si="4"/>
-        <v>51209.5</v>
-      </c>
-      <c r="AH5" s="8">
-        <f t="shared" si="5"/>
-        <v>110419</v>
+        <v>111619</v>
       </c>
     </row>
     <row r="6" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1270,10 +1273,10 @@
         <v>15500</v>
       </c>
       <c r="E6" s="1">
-        <v>9500</v>
+        <v>10600</v>
       </c>
       <c r="F6" s="1">
-        <v>26000</v>
+        <v>26100</v>
       </c>
       <c r="G6" s="1">
         <v>1000</v>
@@ -1328,33 +1331,33 @@
       </c>
       <c r="AA6" s="1">
         <f t="shared" si="0"/>
-        <v>127550</v>
+        <v>128750</v>
       </c>
       <c r="AB6" s="5">
         <f t="shared" si="1"/>
-        <v>63775</v>
+        <v>64375</v>
       </c>
       <c r="AC6" s="1">
         <v>10000</v>
       </c>
       <c r="AD6" s="5">
         <f t="shared" si="2"/>
-        <v>21225</v>
+        <v>20625</v>
       </c>
       <c r="AE6" s="1">
         <v>95000</v>
       </c>
       <c r="AF6" s="6">
+        <f t="shared" si="5"/>
+        <v>56875</v>
+      </c>
+      <c r="AG6" s="7">
         <f t="shared" si="3"/>
-        <v>56275</v>
-      </c>
-      <c r="AG6" s="7">
+        <v>48875</v>
+      </c>
+      <c r="AH6" s="8">
         <f t="shared" si="4"/>
-        <v>48275</v>
-      </c>
-      <c r="AH6" s="8">
-        <f t="shared" si="5"/>
-        <v>104550</v>
+        <v>105750</v>
       </c>
     </row>
     <row r="7" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1371,10 +1374,10 @@
         <v>15500</v>
       </c>
       <c r="E7" s="1">
-        <v>9500</v>
+        <v>10600</v>
       </c>
       <c r="F7" s="1">
-        <v>26000</v>
+        <v>26100</v>
       </c>
       <c r="G7" s="1">
         <v>1000</v>
@@ -1429,33 +1432,33 @@
       </c>
       <c r="AA7" s="1">
         <f t="shared" si="0"/>
-        <v>156919</v>
+        <v>158119</v>
       </c>
       <c r="AB7" s="5">
         <f t="shared" si="1"/>
-        <v>78459.5</v>
+        <v>79059.5</v>
       </c>
       <c r="AC7" s="1">
         <v>10000</v>
       </c>
       <c r="AD7" s="5">
         <f t="shared" si="2"/>
-        <v>6540.5</v>
+        <v>5940.5</v>
       </c>
       <c r="AE7" s="1">
         <v>95000</v>
       </c>
       <c r="AF7" s="6">
+        <f t="shared" si="5"/>
+        <v>71559.5</v>
+      </c>
+      <c r="AG7" s="7">
         <f t="shared" si="3"/>
-        <v>70959.5</v>
-      </c>
-      <c r="AG7" s="7">
+        <v>63559.5</v>
+      </c>
+      <c r="AH7" s="8">
         <f t="shared" si="4"/>
-        <v>62959.5</v>
-      </c>
-      <c r="AH7" s="8">
-        <f t="shared" si="5"/>
-        <v>133919</v>
+        <v>135119</v>
       </c>
     </row>
     <row r="8" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1466,10 +1469,10 @@
         <v>15500</v>
       </c>
       <c r="E8" s="1">
-        <v>9500</v>
+        <v>10600</v>
       </c>
       <c r="F8" s="1">
-        <v>26000</v>
+        <v>26100</v>
       </c>
       <c r="G8" s="1">
         <v>1000</v>
@@ -1527,33 +1530,33 @@
       </c>
       <c r="AA8" s="1">
         <f t="shared" si="0"/>
-        <v>130850</v>
+        <v>132050</v>
       </c>
       <c r="AB8" s="5">
         <f t="shared" si="1"/>
-        <v>65425</v>
+        <v>66025</v>
       </c>
       <c r="AC8" s="1">
         <v>10000</v>
       </c>
       <c r="AD8" s="5">
         <f t="shared" si="2"/>
-        <v>19575</v>
+        <v>18975</v>
       </c>
       <c r="AE8" s="1">
         <v>95000</v>
       </c>
       <c r="AF8" s="6">
+        <f t="shared" si="5"/>
+        <v>58525</v>
+      </c>
+      <c r="AG8" s="7">
         <f t="shared" si="3"/>
-        <v>57925</v>
-      </c>
-      <c r="AG8" s="7">
+        <v>50525</v>
+      </c>
+      <c r="AH8" s="8">
         <f t="shared" si="4"/>
-        <v>49925</v>
-      </c>
-      <c r="AH8" s="8">
-        <f t="shared" si="5"/>
-        <v>107850</v>
+        <v>109050</v>
       </c>
     </row>
     <row r="9" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1567,10 +1570,10 @@
         <v>15500</v>
       </c>
       <c r="E9" s="1">
-        <v>9500</v>
+        <v>10600</v>
       </c>
       <c r="F9" s="1">
-        <v>26000</v>
+        <v>26100</v>
       </c>
       <c r="G9" s="1">
         <v>1000</v>
@@ -1628,33 +1631,33 @@
       </c>
       <c r="AA9" s="1">
         <f t="shared" si="0"/>
-        <v>145719</v>
+        <v>146919</v>
       </c>
       <c r="AB9" s="5">
         <f t="shared" si="1"/>
-        <v>72859.5</v>
+        <v>73459.5</v>
       </c>
       <c r="AC9" s="1">
         <v>10000</v>
       </c>
       <c r="AD9" s="5">
         <f t="shared" si="2"/>
-        <v>12140.5</v>
+        <v>11540.5</v>
       </c>
       <c r="AE9" s="1">
         <v>95000</v>
       </c>
       <c r="AF9" s="6">
+        <f t="shared" si="5"/>
+        <v>65959.5</v>
+      </c>
+      <c r="AG9" s="7">
         <f t="shared" si="3"/>
-        <v>65359.5</v>
-      </c>
-      <c r="AG9" s="7">
+        <v>57959.5</v>
+      </c>
+      <c r="AH9" s="8">
         <f t="shared" si="4"/>
-        <v>57359.5</v>
-      </c>
-      <c r="AH9" s="8">
-        <f t="shared" si="5"/>
-        <v>122719</v>
+        <v>123919</v>
       </c>
     </row>
     <row r="10" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1665,10 +1668,10 @@
         <v>15500</v>
       </c>
       <c r="E10" s="1">
-        <v>9500</v>
+        <v>10600</v>
       </c>
       <c r="F10" s="1">
-        <v>35000</v>
+        <v>45000</v>
       </c>
       <c r="G10" s="1">
         <v>1000</v>
@@ -1723,65 +1726,65 @@
       </c>
       <c r="AA10" s="1">
         <f t="shared" si="0"/>
-        <v>138350</v>
+        <v>149450</v>
       </c>
       <c r="AB10" s="5">
         <f t="shared" si="1"/>
-        <v>69175</v>
+        <v>74725</v>
       </c>
       <c r="AC10" s="1">
         <v>10000</v>
       </c>
       <c r="AD10" s="5">
         <f t="shared" si="2"/>
-        <v>15825</v>
+        <v>10275</v>
       </c>
       <c r="AE10" s="1">
         <v>95000</v>
       </c>
       <c r="AF10" s="6">
+        <f t="shared" si="5"/>
+        <v>67225</v>
+      </c>
+      <c r="AG10" s="7">
         <f t="shared" si="3"/>
-        <v>61675</v>
-      </c>
-      <c r="AG10" s="7">
+        <v>59225</v>
+      </c>
+      <c r="AH10" s="8">
         <f t="shared" si="4"/>
-        <v>53675</v>
-      </c>
-      <c r="AH10" s="8">
-        <f t="shared" si="5"/>
-        <v>115350</v>
+        <v>126450</v>
       </c>
     </row>
     <row r="12" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
-      <c r="K12" s="26"/>
-      <c r="L12" s="26"/>
-      <c r="M12" s="26"/>
-      <c r="N12" s="26"/>
-      <c r="O12" s="26"/>
-      <c r="P12" s="26"/>
-      <c r="Q12" s="26"/>
-      <c r="R12" s="26"/>
-      <c r="S12" s="26"/>
-      <c r="T12" s="26"/>
-      <c r="U12" s="26"/>
-      <c r="V12" s="26"/>
-      <c r="W12" s="26"/>
-      <c r="X12" s="26"/>
-      <c r="Y12" s="26"/>
-      <c r="Z12" s="26"/>
-      <c r="AA12" s="26"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="36"/>
+      <c r="K12" s="36"/>
+      <c r="L12" s="36"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
+      <c r="S12" s="36"/>
+      <c r="T12" s="36"/>
+      <c r="U12" s="36"/>
+      <c r="V12" s="36"/>
+      <c r="W12" s="36"/>
+      <c r="X12" s="36"/>
+      <c r="Y12" s="36"/>
+      <c r="Z12" s="36"/>
+      <c r="AA12" s="36"/>
     </row>
     <row r="13" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -1882,13 +1885,13 @@
         <f>IF(Mayo!D33&gt;0,Mayo!D33,"")</f>
         <v/>
       </c>
-      <c r="E14" s="1" t="str">
+      <c r="E14" s="1">
         <f>IF(Mayo!E33&gt;0,Mayo!E33,"")</f>
-        <v/>
+        <v>10570</v>
       </c>
       <c r="F14" s="1">
         <f>IF(Mayo!F33&gt;0,Mayo!F33,"")</f>
-        <v>17944</v>
+        <v>26054</v>
       </c>
       <c r="G14" s="1">
         <f>IF(Mayo!G33&gt;0,Mayo!G33,"")</f>
@@ -1932,7 +1935,7 @@
       </c>
       <c r="Q14" s="1">
         <f>IF(Mayo!Q33&gt;0,Mayo!Q33,"")</f>
-        <v>3177.77</v>
+        <v>3312.77</v>
       </c>
       <c r="R14" s="1" t="str">
         <f>IF(Mayo!R33&gt;0,Mayo!R33,"")</f>
@@ -1966,13 +1969,13 @@
         <f>IF(Mayo!Y33&gt;0,Mayo!Y33,"")</f>
         <v/>
       </c>
-      <c r="Z14" s="1" t="str">
+      <c r="Z14" s="1">
         <f>IF(Mayo!Z33&gt;0,Mayo!Z33,"")</f>
-        <v/>
+        <v>2258.36</v>
       </c>
       <c r="AA14" s="1">
         <f>IF(Mayo!AA33&gt;0,Mayo!AA33,"")</f>
-        <v>45688.240000000005</v>
+        <v>66761.600000000006</v>
       </c>
     </row>
     <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2739,35 +2742,35 @@
       </c>
     </row>
     <row r="23" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="27" t="s">
+      <c r="A23" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="27"/>
-      <c r="L23" s="27"/>
-      <c r="M23" s="27"/>
-      <c r="N23" s="27"/>
-      <c r="O23" s="27"/>
-      <c r="P23" s="27"/>
-      <c r="Q23" s="27"/>
-      <c r="R23" s="27"/>
-      <c r="S23" s="27"/>
-      <c r="T23" s="27"/>
-      <c r="U23" s="27"/>
-      <c r="V23" s="27"/>
-      <c r="W23" s="27"/>
-      <c r="X23" s="27"/>
-      <c r="Y23" s="27"/>
-      <c r="Z23" s="27"/>
-      <c r="AA23" s="27"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="37"/>
+      <c r="L23" s="37"/>
+      <c r="M23" s="37"/>
+      <c r="N23" s="37"/>
+      <c r="O23" s="37"/>
+      <c r="P23" s="37"/>
+      <c r="Q23" s="37"/>
+      <c r="R23" s="37"/>
+      <c r="S23" s="37"/>
+      <c r="T23" s="37"/>
+      <c r="U23" s="37"/>
+      <c r="V23" s="37"/>
+      <c r="W23" s="37"/>
+      <c r="X23" s="37"/>
+      <c r="Y23" s="37"/>
+      <c r="Z23" s="37"/>
+      <c r="AA23" s="37"/>
     </row>
     <row r="24" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
@@ -2868,13 +2871,13 @@
         <f>IF(ISNUMBER(Mayo!D33),D3-Mayo!D33,"")</f>
         <v/>
       </c>
-      <c r="E25" s="1" t="str">
+      <c r="E25" s="1">
         <f>IF(ISNUMBER(Mayo!E33),E3-Mayo!E33,"")</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="F25" s="1">
         <f>IF(ISNUMBER(Mayo!F33),F3-Mayo!F33,"")</f>
-        <v>8056</v>
+        <v>46</v>
       </c>
       <c r="G25" s="1">
         <f>IF(ISNUMBER(Mayo!G33),G3-Mayo!G33,"")</f>
@@ -2918,7 +2921,7 @@
       </c>
       <c r="Q25" s="1">
         <f>IF(ISNUMBER(Mayo!Q33),Q3-Mayo!Q33,"")</f>
-        <v>16822.23</v>
+        <v>16687.23</v>
       </c>
       <c r="R25" s="1" t="str">
         <f>IF(ISNUMBER(Mayo!R33),R3-Mayo!R33,"")</f>
@@ -2952,13 +2955,13 @@
         <f>IF(ISNUMBER(Mayo!Y33),Y3-Mayo!Y33,"")</f>
         <v/>
       </c>
-      <c r="Z25" s="1" t="str">
+      <c r="Z25" s="1">
         <f>IF(ISNUMBER(Mayo!Z33),Z3-Mayo!Z33,"")</f>
-        <v/>
+        <v>1741.6399999999999</v>
       </c>
       <c r="AA25" s="10">
         <f t="shared" ref="AA25:AA33" si="6">SUMIF(B25:Z25,"&lt;&gt;"&amp;"")</f>
-        <v>27411.759999999998</v>
+        <v>21038.399999999998</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3742,11 +3745,11 @@
       </c>
       <c r="E33" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F33" s="10">
         <f t="shared" si="7"/>
-        <v>8056</v>
+        <v>46</v>
       </c>
       <c r="G33" s="10">
         <f t="shared" si="7"/>
@@ -3790,7 +3793,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="7"/>
-        <v>16822.23</v>
+        <v>16687.23</v>
       </c>
       <c r="R33" s="10">
         <f t="shared" si="7"/>
@@ -3826,11 +3829,11 @@
       </c>
       <c r="Z33" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1741.6399999999999</v>
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="6"/>
-        <v>27411.759999999998</v>
+        <v>21038.399999999998</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
@@ -3915,77 +3918,77 @@
       </c>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A41" s="28" t="s">
+      <c r="A41" s="25" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A42" s="29" t="s">
+      <c r="A42" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="B42" s="29" t="s">
+      <c r="B42" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="C42" s="29" t="s">
+      <c r="C42" s="26" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A43" s="30"/>
-      <c r="B43" s="31"/>
-      <c r="C43" s="32"/>
+      <c r="A43" s="27"/>
+      <c r="B43" s="28"/>
+      <c r="C43" s="29"/>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A44" s="30"/>
-      <c r="B44" s="31"/>
-      <c r="C44" s="32"/>
+      <c r="A44" s="27"/>
+      <c r="B44" s="28"/>
+      <c r="C44" s="29"/>
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A45" s="30"/>
-      <c r="B45" s="31"/>
-      <c r="C45" s="32"/>
+      <c r="A45" s="27"/>
+      <c r="B45" s="28"/>
+      <c r="C45" s="29"/>
     </row>
     <row r="46" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A46" s="30"/>
-      <c r="B46" s="31"/>
-      <c r="C46" s="32"/>
+      <c r="A46" s="27"/>
+      <c r="B46" s="28"/>
+      <c r="C46" s="29"/>
     </row>
     <row r="47" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A47" s="30"/>
-      <c r="B47" s="31"/>
-      <c r="C47" s="32"/>
+      <c r="A47" s="27"/>
+      <c r="B47" s="28"/>
+      <c r="C47" s="29"/>
     </row>
     <row r="48" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A48" s="30"/>
-      <c r="B48" s="31"/>
-      <c r="C48" s="32"/>
+      <c r="A48" s="27"/>
+      <c r="B48" s="28"/>
+      <c r="C48" s="29"/>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="30"/>
-      <c r="B49" s="31"/>
-      <c r="C49" s="32"/>
+      <c r="A49" s="27"/>
+      <c r="B49" s="28"/>
+      <c r="C49" s="29"/>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="30"/>
-      <c r="B50" s="31"/>
-      <c r="C50" s="32"/>
+      <c r="A50" s="27"/>
+      <c r="B50" s="28"/>
+      <c r="C50" s="29"/>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="30"/>
-      <c r="B51" s="31"/>
-      <c r="C51" s="32"/>
+      <c r="A51" s="27"/>
+      <c r="B51" s="28"/>
+      <c r="C51" s="29"/>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="30"/>
-      <c r="B52" s="31"/>
-      <c r="C52" s="32"/>
+      <c r="A52" s="27"/>
+      <c r="B52" s="28"/>
+      <c r="C52" s="29"/>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="33" t="s">
+      <c r="A53" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="B53" s="34"/>
-      <c r="C53" s="35">
+      <c r="B53" s="31"/>
+      <c r="C53" s="32">
         <f>SUM(C43:C52)</f>
         <v>0</v>
       </c>
@@ -3994,8 +3997,8 @@
       <c r="A54" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="B54" s="36"/>
-      <c r="C54" s="37">
+      <c r="B54" s="33"/>
+      <c r="C54" s="34">
         <f>K38-C53</f>
         <v>0</v>
       </c>
@@ -4329,8 +4332,12 @@
       <c r="B7" s="14"/>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
+      <c r="E7" s="14">
+        <v>10570</v>
+      </c>
+      <c r="F7" s="14">
+        <v>8110</v>
+      </c>
       <c r="G7" s="14"/>
       <c r="H7" s="14">
         <f>3327-35.44</f>
@@ -4350,7 +4357,9 @@
       <c r="N7" s="14"/>
       <c r="O7" s="14"/>
       <c r="P7" s="14"/>
-      <c r="Q7" s="14"/>
+      <c r="Q7" s="14">
+        <v>135</v>
+      </c>
       <c r="R7" s="14"/>
       <c r="S7" s="14"/>
       <c r="T7" s="14"/>
@@ -4359,12 +4368,16 @@
       <c r="W7" s="14"/>
       <c r="X7" s="14"/>
       <c r="Y7" s="14"/>
-      <c r="Z7" s="14"/>
+      <c r="Z7" s="14">
+        <v>2258.36</v>
+      </c>
       <c r="AA7" s="14">
         <f t="shared" si="0"/>
-        <v>23517.83</v>
-      </c>
-      <c r="AB7" s="14"/>
+        <v>44591.19</v>
+      </c>
+      <c r="AB7" s="14" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="8" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13">
@@ -5257,13 +5270,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E33" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="E33" s="10">
+        <f t="shared" si="1"/>
+        <v>10570</v>
       </c>
       <c r="F33" s="10">
         <f t="shared" si="1"/>
-        <v>17944</v>
+        <v>26054</v>
       </c>
       <c r="G33" s="10">
         <f t="shared" si="1"/>
@@ -5307,7 +5320,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="1"/>
-        <v>3177.77</v>
+        <v>3312.77</v>
       </c>
       <c r="R33" s="10" t="str">
         <f t="shared" si="1"/>
@@ -5341,13 +5354,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Z33" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="Z33" s="10">
+        <f t="shared" si="1"/>
+        <v>2258.36</v>
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="1"/>
-        <v>45688.240000000005</v>
+        <v>66761.600000000006</v>
       </c>
       <c r="AB33" s="15"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF5816E9-2059-428C-BC21-C464E9A04280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{275F9326-FFEB-484A-AAC8-58D15BA5B292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -994,7 +994,7 @@
         <v>18100</v>
       </c>
       <c r="L3" s="1">
-        <v>19000</v>
+        <v>10000</v>
       </c>
       <c r="M3" s="1">
         <v>850</v>
@@ -1034,29 +1034,29 @@
       </c>
       <c r="AA3" s="1">
         <f t="shared" ref="AA3:AA10" si="0">SUM(B3:Z3)</f>
-        <v>151700</v>
+        <v>142700</v>
       </c>
       <c r="AB3" s="5">
         <f t="shared" ref="AB3:AB10" si="1">+AA3/2</f>
-        <v>75850</v>
+        <v>71350</v>
       </c>
       <c r="AC3" s="1">
         <v>10000</v>
       </c>
       <c r="AD3" s="5">
         <f t="shared" ref="AD3:AD10" si="2">+AE3-AB3-AC3</f>
-        <v>9150</v>
+        <v>13650</v>
       </c>
       <c r="AE3" s="1">
         <v>95000</v>
       </c>
       <c r="AF3" s="6">
         <f>AA3/2-L3</f>
-        <v>56850</v>
+        <v>61350</v>
       </c>
       <c r="AG3" s="7">
         <f t="shared" ref="AG3:AG10" si="3">AA3/2-D3</f>
-        <v>60350</v>
+        <v>55850</v>
       </c>
       <c r="AH3" s="8">
         <f t="shared" ref="AH3:AH10" si="4">AF3+AG3</f>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{275F9326-FFEB-484A-AAC8-58D15BA5B292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0122C2DF-60FF-4BEF-805F-DA9045674AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1152,7 +1152,7 @@
         <v>95000</v>
       </c>
       <c r="AF4" s="6">
-        <f t="shared" ref="AF3:AF10" si="5">AA4/2-L4</f>
+        <f t="shared" ref="AF4:AF10" si="5">AA4/2-L4</f>
         <v>66500</v>
       </c>
       <c r="AG4" s="7">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="Q14" s="1">
         <f>IF(Mayo!Q33&gt;0,Mayo!Q33,"")</f>
-        <v>3312.77</v>
+        <v>3758.51</v>
       </c>
       <c r="R14" s="1" t="str">
         <f>IF(Mayo!R33&gt;0,Mayo!R33,"")</f>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="AA14" s="1">
         <f>IF(Mayo!AA33&gt;0,Mayo!AA33,"")</f>
-        <v>66761.600000000006</v>
+        <v>67207.340000000011</v>
       </c>
     </row>
     <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="Q25" s="1">
         <f>IF(ISNUMBER(Mayo!Q33),Q3-Mayo!Q33,"")</f>
-        <v>16687.23</v>
+        <v>16241.49</v>
       </c>
       <c r="R25" s="1" t="str">
         <f>IF(ISNUMBER(Mayo!R33),R3-Mayo!R33,"")</f>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="AA25" s="10">
         <f t="shared" ref="AA25:AA33" si="6">SUMIF(B25:Z25,"&lt;&gt;"&amp;"")</f>
-        <v>21038.399999999998</v>
+        <v>20592.659999999996</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="7"/>
-        <v>16687.23</v>
+        <v>16241.49</v>
       </c>
       <c r="R33" s="10">
         <f t="shared" si="7"/>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="6"/>
-        <v>21038.399999999998</v>
+        <v>20592.659999999996</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
@@ -4398,7 +4398,10 @@
       <c r="N8" s="14"/>
       <c r="O8" s="14"/>
       <c r="P8" s="14"/>
-      <c r="Q8" s="14"/>
+      <c r="Q8" s="14">
+        <f>454-8.26</f>
+        <v>445.74</v>
+      </c>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
       <c r="T8" s="14"/>
@@ -4410,7 +4413,7 @@
       <c r="Z8" s="14"/>
       <c r="AA8" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>445.74</v>
       </c>
       <c r="AB8" s="14"/>
     </row>
@@ -5320,7 +5323,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="1"/>
-        <v>3312.77</v>
+        <v>3758.51</v>
       </c>
       <c r="R33" s="10" t="str">
         <f t="shared" si="1"/>
@@ -5360,7 +5363,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="1"/>
-        <v>66761.600000000006</v>
+        <v>67207.340000000011</v>
       </c>
       <c r="AB33" s="15"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0122C2DF-60FF-4BEF-805F-DA9045674AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACC81601-4A60-4670-8C3B-04F08BB15D74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="W14" s="1">
         <f>IF(Mayo!W33&gt;0,Mayo!W33,"")</f>
-        <v>68.64</v>
+        <v>494.09</v>
       </c>
       <c r="X14" s="1" t="str">
         <f>IF(Mayo!X33&gt;0,Mayo!X33,"")</f>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="AA14" s="1">
         <f>IF(Mayo!AA33&gt;0,Mayo!AA33,"")</f>
-        <v>67207.340000000011</v>
+        <v>67632.789999999994</v>
       </c>
     </row>
     <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="W25" s="1">
         <f>IF(ISNUMBER(Mayo!W33),W3-Mayo!W33,"")</f>
-        <v>1431.36</v>
+        <v>1005.9100000000001</v>
       </c>
       <c r="X25" s="1" t="str">
         <f>IF(ISNUMBER(Mayo!X33),X3-Mayo!X33,"")</f>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="AA25" s="10">
         <f t="shared" ref="AA25:AA33" si="6">SUMIF(B25:Z25,"&lt;&gt;"&amp;"")</f>
-        <v>20592.659999999996</v>
+        <v>20167.209999999995</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="W33" s="10">
         <f t="shared" si="7"/>
-        <v>1431.36</v>
+        <v>1005.9100000000001</v>
       </c>
       <c r="X33" s="10">
         <f t="shared" si="7"/>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="6"/>
-        <v>20592.659999999996</v>
+        <v>20167.209999999995</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
@@ -4365,7 +4365,9 @@
       <c r="T7" s="14"/>
       <c r="U7" s="14"/>
       <c r="V7" s="14"/>
-      <c r="W7" s="14"/>
+      <c r="W7" s="14">
+        <v>334.65</v>
+      </c>
       <c r="X7" s="14"/>
       <c r="Y7" s="14"/>
       <c r="Z7" s="14">
@@ -4373,7 +4375,7 @@
       </c>
       <c r="AA7" s="14">
         <f t="shared" si="0"/>
-        <v>44591.19</v>
+        <v>44925.840000000004</v>
       </c>
       <c r="AB7" s="14" t="s">
         <v>62</v>
@@ -4407,13 +4409,16 @@
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <f>2.27*40</f>
+        <v>90.8</v>
+      </c>
       <c r="X8" s="14"/>
       <c r="Y8" s="14"/>
       <c r="Z8" s="14"/>
       <c r="AA8" s="14">
         <f t="shared" si="0"/>
-        <v>445.74</v>
+        <v>536.54</v>
       </c>
       <c r="AB8" s="14"/>
     </row>
@@ -5347,7 +5352,7 @@
       </c>
       <c r="W33" s="10">
         <f t="shared" si="1"/>
-        <v>68.64</v>
+        <v>494.09</v>
       </c>
       <c r="X33" s="10" t="str">
         <f t="shared" si="1"/>
@@ -5363,7 +5368,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="1"/>
-        <v>67207.340000000011</v>
+        <v>67632.789999999994</v>
       </c>
       <c r="AB33" s="15"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACC81601-4A60-4670-8C3B-04F08BB15D74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F068D295-57F9-466D-B092-E430F91BA03E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="Q14" s="1">
         <f>IF(Mayo!Q33&gt;0,Mayo!Q33,"")</f>
-        <v>3758.51</v>
+        <v>4256.21</v>
       </c>
       <c r="R14" s="1" t="str">
         <f>IF(Mayo!R33&gt;0,Mayo!R33,"")</f>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="AA14" s="1">
         <f>IF(Mayo!AA33&gt;0,Mayo!AA33,"")</f>
-        <v>67632.789999999994</v>
+        <v>68130.490000000005</v>
       </c>
     </row>
     <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="Q25" s="1">
         <f>IF(ISNUMBER(Mayo!Q33),Q3-Mayo!Q33,"")</f>
-        <v>16241.49</v>
+        <v>15743.79</v>
       </c>
       <c r="R25" s="1" t="str">
         <f>IF(ISNUMBER(Mayo!R33),R3-Mayo!R33,"")</f>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="AA25" s="10">
         <f t="shared" ref="AA25:AA33" si="6">SUMIF(B25:Z25,"&lt;&gt;"&amp;"")</f>
-        <v>20167.209999999995</v>
+        <v>19669.509999999998</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="7"/>
-        <v>16241.49</v>
+        <v>15743.79</v>
       </c>
       <c r="R33" s="10">
         <f t="shared" si="7"/>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="6"/>
-        <v>20167.209999999995</v>
+        <v>19669.509999999998</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
@@ -3885,7 +3885,7 @@
         <v>54</v>
       </c>
       <c r="B38" s="19">
-        <v>500000</v>
+        <v>400000</v>
       </c>
       <c r="C38" s="20"/>
       <c r="D38" s="20"/>
@@ -4401,8 +4401,8 @@
       <c r="O8" s="14"/>
       <c r="P8" s="14"/>
       <c r="Q8" s="14">
-        <f>454-8.26</f>
-        <v>445.74</v>
+        <f>454-8.26+506-8.3</f>
+        <v>943.44</v>
       </c>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
@@ -4418,7 +4418,7 @@
       <c r="Z8" s="14"/>
       <c r="AA8" s="14">
         <f t="shared" si="0"/>
-        <v>536.54</v>
+        <v>1034.24</v>
       </c>
       <c r="AB8" s="14"/>
     </row>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="1"/>
-        <v>3758.51</v>
+        <v>4256.21</v>
       </c>
       <c r="R33" s="10" t="str">
         <f t="shared" si="1"/>
@@ -5368,7 +5368,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="1"/>
-        <v>67632.789999999994</v>
+        <v>68130.490000000005</v>
       </c>
       <c r="AB33" s="15"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F068D295-57F9-466D-B092-E430F91BA03E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D38BC12-90EE-4E12-AC57-DB5E006EC5DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -255,69 +255,69 @@
       <b/>
       <sz val="11"/>
       <name val="Cambria"/>
-      <charset val="1"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFAD1457"/>
       <name val="Cambria"/>
-      <charset val="1"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF1565C0"/>
       <name val="Cambria"/>
-      <charset val="1"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF2E7D32"/>
       <name val="Cambria"/>
-      <charset val="1"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Cambria"/>
-      <charset val="1"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="Cambria"/>
-      <charset val="1"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF0284C7"/>
       <name val="Cambria"/>
-      <charset val="1"/>
+      <family val="1"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF555555"/>
       <name val="Cambria"/>
-      <charset val="1"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFC62828"/>
       <name val="Cambria"/>
-      <charset val="1"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF1B5E20"/>
       <name val="Cambria"/>
-      <charset val="1"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="15">
@@ -1905,9 +1905,9 @@
         <f>IF(Mayo!I33&gt;0,Mayo!I33,"")</f>
         <v>2144.2600000000002</v>
       </c>
-      <c r="J14" s="1" t="str">
+      <c r="J14" s="1">
         <f>IF(Mayo!J33&gt;0,Mayo!J33,"")</f>
-        <v/>
+        <v>700</v>
       </c>
       <c r="K14" s="1">
         <f>IF(Mayo!K33&gt;0,Mayo!K33,"")</f>
@@ -1917,9 +1917,9 @@
         <f>IF(Mayo!L33&gt;0,Mayo!L33,"")</f>
         <v/>
       </c>
-      <c r="M14" s="1" t="str">
+      <c r="M14" s="1">
         <f>IF(Mayo!M33&gt;0,Mayo!M33,"")</f>
-        <v/>
+        <v>810</v>
       </c>
       <c r="N14" s="1" t="str">
         <f>IF(Mayo!N33&gt;0,Mayo!N33,"")</f>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="AA14" s="1">
         <f>IF(Mayo!AA33&gt;0,Mayo!AA33,"")</f>
-        <v>68130.490000000005</v>
+        <v>69640.490000000005</v>
       </c>
     </row>
     <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2891,9 +2891,9 @@
         <f>IF(ISNUMBER(Mayo!I33),I3-Mayo!I33,"")</f>
         <v>855.73999999999978</v>
       </c>
-      <c r="J25" s="1" t="str">
+      <c r="J25" s="1">
         <f>IF(ISNUMBER(Mayo!J33),J3-Mayo!J33,"")</f>
-        <v/>
+        <v>300</v>
       </c>
       <c r="K25" s="1">
         <f>IF(ISNUMBER(Mayo!K33),K3-Mayo!K33,"")</f>
@@ -2903,9 +2903,9 @@
         <f>IF(ISNUMBER(Mayo!L33),L3-Mayo!L33,"")</f>
         <v/>
       </c>
-      <c r="M25" s="1" t="str">
+      <c r="M25" s="1">
         <f>IF(ISNUMBER(Mayo!M33),M3-Mayo!M33,"")</f>
-        <v/>
+        <v>40</v>
       </c>
       <c r="N25" s="1" t="str">
         <f>IF(ISNUMBER(Mayo!N33),N3-Mayo!N33,"")</f>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="AA25" s="10">
         <f t="shared" ref="AA25:AA33" si="6">SUMIF(B25:Z25,"&lt;&gt;"&amp;"")</f>
-        <v>19669.509999999998</v>
+        <v>20009.509999999998</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="J33" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K33" s="10">
         <f t="shared" si="7"/>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="M33" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="N33" s="10">
         <f t="shared" si="7"/>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="6"/>
-        <v>19669.509999999998</v>
+        <v>20009.509999999998</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
@@ -4434,10 +4434,14 @@
       <c r="G9" s="14"/>
       <c r="H9" s="14"/>
       <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
+      <c r="J9" s="14">
+        <v>700</v>
+      </c>
       <c r="K9" s="14"/>
       <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
+      <c r="M9" s="14">
+        <v>810</v>
+      </c>
       <c r="N9" s="14"/>
       <c r="O9" s="14"/>
       <c r="P9" s="14"/>
@@ -4453,7 +4457,7 @@
       <c r="Z9" s="14"/>
       <c r="AA9" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1510</v>
       </c>
       <c r="AB9" s="14"/>
     </row>
@@ -5298,9 +5302,9 @@
         <f t="shared" si="1"/>
         <v>2144.2600000000002</v>
       </c>
-      <c r="J33" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="J33" s="10">
+        <f t="shared" si="1"/>
+        <v>700</v>
       </c>
       <c r="K33" s="10">
         <f t="shared" si="1"/>
@@ -5310,9 +5314,9 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="M33" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="M33" s="10">
+        <f t="shared" si="1"/>
+        <v>810</v>
       </c>
       <c r="N33" s="10" t="str">
         <f t="shared" si="1"/>
@@ -5368,7 +5372,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="1"/>
-        <v>68130.490000000005</v>
+        <v>69640.490000000005</v>
       </c>
       <c r="AB33" s="15"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D38BC12-90EE-4E12-AC57-DB5E006EC5DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C03A509-63A4-4D06-A724-F5B44EEF83AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="64">
   <si>
     <t>Presupuesto</t>
   </si>
@@ -233,6 +233,9 @@
   </si>
   <si>
     <t>Uniforme Roci</t>
+  </si>
+  <si>
+    <t>Botas Roci</t>
   </si>
 </sst>
 </file>
@@ -1935,15 +1938,15 @@
       </c>
       <c r="Q14" s="1">
         <f>IF(Mayo!Q33&gt;0,Mayo!Q33,"")</f>
-        <v>4256.21</v>
+        <v>4879.43</v>
       </c>
       <c r="R14" s="1" t="str">
         <f>IF(Mayo!R33&gt;0,Mayo!R33,"")</f>
         <v/>
       </c>
-      <c r="S14" s="1" t="str">
+      <c r="S14" s="1">
         <f>IF(Mayo!S33&gt;0,Mayo!S33,"")</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="T14" s="1" t="str">
         <f>IF(Mayo!T33&gt;0,Mayo!T33,"")</f>
@@ -1971,11 +1974,11 @@
       </c>
       <c r="Z14" s="1">
         <f>IF(Mayo!Z33&gt;0,Mayo!Z33,"")</f>
-        <v>2258.36</v>
+        <v>3142.62</v>
       </c>
       <c r="AA14" s="1">
         <f>IF(Mayo!AA33&gt;0,Mayo!AA33,"")</f>
-        <v>69640.490000000005</v>
+        <v>71647.97</v>
       </c>
     </row>
     <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2921,15 +2924,15 @@
       </c>
       <c r="Q25" s="1">
         <f>IF(ISNUMBER(Mayo!Q33),Q3-Mayo!Q33,"")</f>
-        <v>15743.79</v>
+        <v>15120.57</v>
       </c>
       <c r="R25" s="1" t="str">
         <f>IF(ISNUMBER(Mayo!R33),R3-Mayo!R33,"")</f>
         <v/>
       </c>
-      <c r="S25" s="1" t="str">
+      <c r="S25" s="1">
         <f>IF(ISNUMBER(Mayo!S33),S3-Mayo!S33,"")</f>
-        <v/>
+        <v>4500</v>
       </c>
       <c r="T25" s="1" t="str">
         <f>IF(ISNUMBER(Mayo!T33),T3-Mayo!T33,"")</f>
@@ -2957,11 +2960,11 @@
       </c>
       <c r="Z25" s="1">
         <f>IF(ISNUMBER(Mayo!Z33),Z3-Mayo!Z33,"")</f>
-        <v>1741.6399999999999</v>
+        <v>857.38000000000011</v>
       </c>
       <c r="AA25" s="10">
         <f t="shared" ref="AA25:AA33" si="6">SUMIF(B25:Z25,"&lt;&gt;"&amp;"")</f>
-        <v>20009.509999999998</v>
+        <v>23002.03</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3793,7 +3796,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="7"/>
-        <v>15743.79</v>
+        <v>15120.57</v>
       </c>
       <c r="R33" s="10">
         <f t="shared" si="7"/>
@@ -3801,7 +3804,7 @@
       </c>
       <c r="S33" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="T33" s="10">
         <f t="shared" si="7"/>
@@ -3829,11 +3832,11 @@
       </c>
       <c r="Z33" s="10">
         <f t="shared" si="7"/>
-        <v>1741.6399999999999</v>
+        <v>857.38000000000011</v>
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="6"/>
-        <v>20009.509999999998</v>
+        <v>23002.03</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
@@ -4445,21 +4448,31 @@
       <c r="N9" s="14"/>
       <c r="O9" s="14"/>
       <c r="P9" s="14"/>
-      <c r="Q9" s="14"/>
+      <c r="Q9" s="14">
+        <f>452-2.93+179-4.85</f>
+        <v>623.21999999999991</v>
+      </c>
       <c r="R9" s="14"/>
-      <c r="S9" s="14"/>
+      <c r="S9" s="14">
+        <v>500</v>
+      </c>
       <c r="T9" s="14"/>
       <c r="U9" s="14"/>
       <c r="V9" s="14"/>
       <c r="W9" s="14"/>
       <c r="X9" s="14"/>
       <c r="Y9" s="14"/>
-      <c r="Z9" s="14"/>
+      <c r="Z9" s="14">
+        <f>899-14.74</f>
+        <v>884.26</v>
+      </c>
       <c r="AA9" s="14">
         <f t="shared" si="0"/>
-        <v>1510</v>
-      </c>
-      <c r="AB9" s="14"/>
+        <v>3517.4799999999996</v>
+      </c>
+      <c r="AB9" s="14" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="10" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13">
@@ -5332,15 +5345,15 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="1"/>
-        <v>4256.21</v>
+        <v>4879.43</v>
       </c>
       <c r="R33" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="S33" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="S33" s="10">
+        <f t="shared" si="1"/>
+        <v>500</v>
       </c>
       <c r="T33" s="10" t="str">
         <f t="shared" si="1"/>
@@ -5368,11 +5381,11 @@
       </c>
       <c r="Z33" s="10">
         <f t="shared" si="1"/>
-        <v>2258.36</v>
+        <v>3142.62</v>
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="1"/>
-        <v>69640.490000000005</v>
+        <v>71647.97</v>
       </c>
       <c r="AB33" s="15"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C03A509-63A4-4D06-A724-F5B44EEF83AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6040322-8A25-43C9-894E-F054740ED69F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1924,9 +1924,9 @@
         <f>IF(Mayo!M33&gt;0,Mayo!M33,"")</f>
         <v>810</v>
       </c>
-      <c r="N14" s="1" t="str">
+      <c r="N14" s="1">
         <f>IF(Mayo!N33&gt;0,Mayo!N33,"")</f>
-        <v/>
+        <v>6292.6100000000006</v>
       </c>
       <c r="O14" s="1" t="str">
         <f>IF(Mayo!O33&gt;0,Mayo!O33,"")</f>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="S14" s="1">
         <f>IF(Mayo!S33&gt;0,Mayo!S33,"")</f>
-        <v>500</v>
+        <v>3261.5</v>
       </c>
       <c r="T14" s="1" t="str">
         <f>IF(Mayo!T33&gt;0,Mayo!T33,"")</f>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AA14" s="1">
         <f>IF(Mayo!AA33&gt;0,Mayo!AA33,"")</f>
-        <v>71647.97</v>
+        <v>80702.080000000002</v>
       </c>
     </row>
     <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2910,9 +2910,9 @@
         <f>IF(ISNUMBER(Mayo!M33),M3-Mayo!M33,"")</f>
         <v>40</v>
       </c>
-      <c r="N25" s="1" t="str">
+      <c r="N25" s="1">
         <f>IF(ISNUMBER(Mayo!N33),N3-Mayo!N33,"")</f>
-        <v/>
+        <v>3707.3899999999994</v>
       </c>
       <c r="O25" s="1" t="str">
         <f>IF(ISNUMBER(Mayo!O33),O3-Mayo!O33,"")</f>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="S25" s="1">
         <f>IF(ISNUMBER(Mayo!S33),S3-Mayo!S33,"")</f>
-        <v>4500</v>
+        <v>1738.5</v>
       </c>
       <c r="T25" s="1" t="str">
         <f>IF(ISNUMBER(Mayo!T33),T3-Mayo!T33,"")</f>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AA25" s="10">
         <f t="shared" ref="AA25:AA33" si="6">SUMIF(B25:Z25,"&lt;&gt;"&amp;"")</f>
-        <v>23002.03</v>
+        <v>23947.919999999998</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="N33" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3707.3899999999994</v>
       </c>
       <c r="O33" s="10">
         <f t="shared" si="7"/>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="S33" s="10">
         <f t="shared" si="7"/>
-        <v>4500</v>
+        <v>1738.5</v>
       </c>
       <c r="T33" s="10">
         <f t="shared" si="7"/>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="6"/>
-        <v>23002.03</v>
+        <v>23947.919999999998</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
@@ -4400,7 +4400,9 @@
       <c r="K8" s="14"/>
       <c r="L8" s="14"/>
       <c r="M8" s="14"/>
-      <c r="N8" s="14"/>
+      <c r="N8" s="14">
+        <v>351</v>
+      </c>
       <c r="O8" s="14"/>
       <c r="P8" s="14"/>
       <c r="Q8" s="14">
@@ -4408,7 +4410,9 @@
         <v>943.44</v>
       </c>
       <c r="R8" s="14"/>
-      <c r="S8" s="14"/>
+      <c r="S8" s="14">
+        <v>1540</v>
+      </c>
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
@@ -4421,7 +4425,7 @@
       <c r="Z8" s="14"/>
       <c r="AA8" s="14">
         <f t="shared" si="0"/>
-        <v>1034.24</v>
+        <v>2925.2400000000002</v>
       </c>
       <c r="AB8" s="14"/>
     </row>
@@ -4445,7 +4449,10 @@
       <c r="M9" s="14">
         <v>810</v>
       </c>
-      <c r="N9" s="14"/>
+      <c r="N9" s="14">
+        <f>1000-16.39</f>
+        <v>983.61</v>
+      </c>
       <c r="O9" s="14"/>
       <c r="P9" s="14"/>
       <c r="Q9" s="14">
@@ -4468,7 +4475,7 @@
       </c>
       <c r="AA9" s="14">
         <f t="shared" si="0"/>
-        <v>3517.4799999999996</v>
+        <v>4501.09</v>
       </c>
       <c r="AB9" s="14" t="s">
         <v>63</v>
@@ -4490,12 +4497,17 @@
       <c r="K10" s="14"/>
       <c r="L10" s="14"/>
       <c r="M10" s="14"/>
-      <c r="N10" s="14"/>
+      <c r="N10" s="14">
+        <v>1321</v>
+      </c>
       <c r="O10" s="14"/>
       <c r="P10" s="14"/>
       <c r="Q10" s="14"/>
       <c r="R10" s="14"/>
-      <c r="S10" s="14"/>
+      <c r="S10" s="14">
+        <f>1037-17</f>
+        <v>1020</v>
+      </c>
       <c r="T10" s="14"/>
       <c r="U10" s="14"/>
       <c r="V10" s="14"/>
@@ -4505,7 +4517,7 @@
       <c r="Z10" s="14"/>
       <c r="AA10" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2341</v>
       </c>
       <c r="AB10" s="14"/>
     </row>
@@ -4525,12 +4537,17 @@
       <c r="K11" s="14"/>
       <c r="L11" s="14"/>
       <c r="M11" s="14"/>
-      <c r="N11" s="14"/>
+      <c r="N11" s="14">
+        <v>3637</v>
+      </c>
       <c r="O11" s="14"/>
       <c r="P11" s="14"/>
       <c r="Q11" s="14"/>
       <c r="R11" s="14"/>
-      <c r="S11" s="14"/>
+      <c r="S11" s="14">
+        <f>205-3.5</f>
+        <v>201.5</v>
+      </c>
       <c r="T11" s="14"/>
       <c r="U11" s="14"/>
       <c r="V11" s="14"/>
@@ -4540,7 +4557,7 @@
       <c r="Z11" s="14"/>
       <c r="AA11" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3838.5</v>
       </c>
       <c r="AB11" s="14"/>
     </row>
@@ -5331,9 +5348,9 @@
         <f t="shared" si="1"/>
         <v>810</v>
       </c>
-      <c r="N33" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="N33" s="10">
+        <f t="shared" si="1"/>
+        <v>6292.6100000000006</v>
       </c>
       <c r="O33" s="10" t="str">
         <f t="shared" si="1"/>
@@ -5353,7 +5370,7 @@
       </c>
       <c r="S33" s="10">
         <f t="shared" si="1"/>
-        <v>500</v>
+        <v>3261.5</v>
       </c>
       <c r="T33" s="10" t="str">
         <f t="shared" si="1"/>
@@ -5385,7 +5402,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="1"/>
-        <v>71647.97</v>
+        <v>80702.080000000002</v>
       </c>
       <c r="AB33" s="15"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6040322-8A25-43C9-894E-F054740ED69F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{692F5B54-11B9-4ACB-B234-475E6D3F2917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1020,6 +1020,9 @@
       <c r="S3" s="1">
         <v>5000</v>
       </c>
+      <c r="T3" s="1">
+        <v>9000</v>
+      </c>
       <c r="V3" s="1">
         <v>3000</v>
       </c>
@@ -1037,33 +1040,33 @@
       </c>
       <c r="AA3" s="1">
         <f t="shared" ref="AA3:AA10" si="0">SUM(B3:Z3)</f>
-        <v>142700</v>
+        <v>151700</v>
       </c>
       <c r="AB3" s="5">
         <f t="shared" ref="AB3:AB10" si="1">+AA3/2</f>
-        <v>71350</v>
+        <v>75850</v>
       </c>
       <c r="AC3" s="1">
         <v>10000</v>
       </c>
       <c r="AD3" s="5">
         <f t="shared" ref="AD3:AD10" si="2">+AE3-AB3-AC3</f>
-        <v>13650</v>
+        <v>9150</v>
       </c>
       <c r="AE3" s="1">
         <v>95000</v>
       </c>
       <c r="AF3" s="6">
         <f>AA3/2-L3</f>
-        <v>61350</v>
+        <v>65850</v>
       </c>
       <c r="AG3" s="7">
         <f t="shared" ref="AG3:AG10" si="3">AA3/2-D3</f>
-        <v>55850</v>
+        <v>60350</v>
       </c>
       <c r="AH3" s="8">
         <f t="shared" ref="AH3:AH10" si="4">AF3+AG3</f>
-        <v>117200</v>
+        <v>126200</v>
       </c>
     </row>
     <row r="4" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1118,9 +1121,6 @@
       <c r="S4" s="1">
         <v>5000</v>
       </c>
-      <c r="T4" s="1">
-        <v>9000</v>
-      </c>
       <c r="V4" s="1">
         <v>3000</v>
       </c>
@@ -1138,33 +1138,33 @@
       </c>
       <c r="AA4" s="1">
         <f t="shared" si="0"/>
-        <v>148000</v>
+        <v>139000</v>
       </c>
       <c r="AB4" s="5">
         <f t="shared" si="1"/>
-        <v>74000</v>
+        <v>69500</v>
       </c>
       <c r="AC4" s="1">
         <v>10000</v>
       </c>
       <c r="AD4" s="5">
         <f t="shared" si="2"/>
-        <v>11000</v>
+        <v>15500</v>
       </c>
       <c r="AE4" s="1">
         <v>95000</v>
       </c>
       <c r="AF4" s="6">
         <f t="shared" ref="AF4:AF10" si="5">AA4/2-L4</f>
-        <v>66500</v>
+        <v>62000</v>
       </c>
       <c r="AG4" s="7">
         <f t="shared" si="3"/>
-        <v>58500</v>
+        <v>54000</v>
       </c>
       <c r="AH4" s="8">
         <f t="shared" si="4"/>
-        <v>125000</v>
+        <v>116000</v>
       </c>
     </row>
     <row r="5" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1513,6 +1513,9 @@
       <c r="S8" s="1">
         <v>5000</v>
       </c>
+      <c r="T8" s="1">
+        <v>12000</v>
+      </c>
       <c r="U8" s="1">
         <v>1500</v>
       </c>
@@ -1533,33 +1536,33 @@
       </c>
       <c r="AA8" s="1">
         <f t="shared" si="0"/>
-        <v>132050</v>
+        <v>144050</v>
       </c>
       <c r="AB8" s="5">
         <f t="shared" si="1"/>
-        <v>66025</v>
+        <v>72025</v>
       </c>
       <c r="AC8" s="1">
         <v>10000</v>
       </c>
       <c r="AD8" s="5">
         <f t="shared" si="2"/>
-        <v>18975</v>
+        <v>12975</v>
       </c>
       <c r="AE8" s="1">
         <v>95000</v>
       </c>
       <c r="AF8" s="6">
         <f t="shared" si="5"/>
-        <v>58525</v>
+        <v>64525</v>
       </c>
       <c r="AG8" s="7">
         <f t="shared" si="3"/>
-        <v>50525</v>
+        <v>56525</v>
       </c>
       <c r="AH8" s="8">
         <f t="shared" si="4"/>
-        <v>109050</v>
+        <v>121050</v>
       </c>
     </row>
     <row r="9" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1614,9 +1617,6 @@
       <c r="S9" s="1">
         <v>5000</v>
       </c>
-      <c r="T9" s="1">
-        <v>12000</v>
-      </c>
       <c r="V9" s="1">
         <v>3000</v>
       </c>
@@ -1634,33 +1634,33 @@
       </c>
       <c r="AA9" s="1">
         <f t="shared" si="0"/>
-        <v>146919</v>
+        <v>134919</v>
       </c>
       <c r="AB9" s="5">
         <f t="shared" si="1"/>
-        <v>73459.5</v>
+        <v>67459.5</v>
       </c>
       <c r="AC9" s="1">
         <v>10000</v>
       </c>
       <c r="AD9" s="5">
         <f t="shared" si="2"/>
-        <v>11540.5</v>
+        <v>17540.5</v>
       </c>
       <c r="AE9" s="1">
         <v>95000</v>
       </c>
       <c r="AF9" s="6">
         <f t="shared" si="5"/>
-        <v>65959.5</v>
+        <v>59959.5</v>
       </c>
       <c r="AG9" s="7">
         <f t="shared" si="3"/>
-        <v>57959.5</v>
+        <v>51959.5</v>
       </c>
       <c r="AH9" s="8">
         <f t="shared" si="4"/>
-        <v>123919</v>
+        <v>111919</v>
       </c>
     </row>
     <row r="10" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{692F5B54-11B9-4ACB-B234-475E6D3F2917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{899DD884-CEF8-43C5-B438-4E617E4A4F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -997,7 +997,7 @@
         <v>18100</v>
       </c>
       <c r="L3" s="1">
-        <v>10000</v>
+        <v>22200</v>
       </c>
       <c r="M3" s="1">
         <v>850</v>
@@ -1021,7 +1021,7 @@
         <v>5000</v>
       </c>
       <c r="T3" s="1">
-        <v>9000</v>
+        <v>15000</v>
       </c>
       <c r="V3" s="1">
         <v>3000</v>
@@ -1040,33 +1040,33 @@
       </c>
       <c r="AA3" s="1">
         <f t="shared" ref="AA3:AA10" si="0">SUM(B3:Z3)</f>
-        <v>151700</v>
+        <v>169900</v>
       </c>
       <c r="AB3" s="5">
         <f t="shared" ref="AB3:AB10" si="1">+AA3/2</f>
-        <v>75850</v>
+        <v>84950</v>
       </c>
       <c r="AC3" s="1">
         <v>10000</v>
       </c>
       <c r="AD3" s="5">
         <f t="shared" ref="AD3:AD10" si="2">+AE3-AB3-AC3</f>
-        <v>9150</v>
+        <v>50</v>
       </c>
       <c r="AE3" s="1">
         <v>95000</v>
       </c>
       <c r="AF3" s="6">
         <f>AA3/2-L3</f>
-        <v>65850</v>
+        <v>62750</v>
       </c>
       <c r="AG3" s="7">
         <f t="shared" ref="AG3:AG10" si="3">AA3/2-D3</f>
-        <v>60350</v>
+        <v>69450</v>
       </c>
       <c r="AH3" s="8">
         <f t="shared" ref="AH3:AH10" si="4">AF3+AG3</f>
-        <v>126200</v>
+        <v>132200</v>
       </c>
     </row>
     <row r="4" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1884,9 +1884,9 @@
         <f>IF(Mayo!C33&gt;0,Mayo!C33,"")</f>
         <v/>
       </c>
-      <c r="D14" s="1" t="str">
+      <c r="D14" s="1">
         <f>IF(Mayo!D33&gt;0,Mayo!D33,"")</f>
-        <v/>
+        <v>15452.77</v>
       </c>
       <c r="E14" s="1">
         <f>IF(Mayo!E33&gt;0,Mayo!E33,"")</f>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="N14" s="1">
         <f>IF(Mayo!N33&gt;0,Mayo!N33,"")</f>
-        <v>6292.6100000000006</v>
+        <v>6239.9600000000009</v>
       </c>
       <c r="O14" s="1" t="str">
         <f>IF(Mayo!O33&gt;0,Mayo!O33,"")</f>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="Q14" s="1">
         <f>IF(Mayo!Q33&gt;0,Mayo!Q33,"")</f>
-        <v>4879.43</v>
+        <v>7418.32</v>
       </c>
       <c r="R14" s="1" t="str">
         <f>IF(Mayo!R33&gt;0,Mayo!R33,"")</f>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="AA14" s="1">
         <f>IF(Mayo!AA33&gt;0,Mayo!AA33,"")</f>
-        <v>80702.080000000002</v>
+        <v>98641.09</v>
       </c>
     </row>
     <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2870,9 +2870,9 @@
         <f>IF(ISNUMBER(Mayo!C33),C3-Mayo!C33,"")</f>
         <v/>
       </c>
-      <c r="D25" s="1" t="str">
+      <c r="D25" s="1">
         <f>IF(ISNUMBER(Mayo!D33),D3-Mayo!D33,"")</f>
-        <v/>
+        <v>47.229999999999563</v>
       </c>
       <c r="E25" s="1">
         <f>IF(ISNUMBER(Mayo!E33),E3-Mayo!E33,"")</f>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="N25" s="1">
         <f>IF(ISNUMBER(Mayo!N33),N3-Mayo!N33,"")</f>
-        <v>3707.3899999999994</v>
+        <v>3760.0399999999991</v>
       </c>
       <c r="O25" s="1" t="str">
         <f>IF(ISNUMBER(Mayo!O33),O3-Mayo!O33,"")</f>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="Q25" s="1">
         <f>IF(ISNUMBER(Mayo!Q33),Q3-Mayo!Q33,"")</f>
-        <v>15120.57</v>
+        <v>12581.68</v>
       </c>
       <c r="R25" s="1" t="str">
         <f>IF(ISNUMBER(Mayo!R33),R3-Mayo!R33,"")</f>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AA25" s="10">
         <f t="shared" ref="AA25:AA33" si="6">SUMIF(B25:Z25,"&lt;&gt;"&amp;"")</f>
-        <v>23947.919999999998</v>
+        <v>21508.909999999996</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="D33" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>47.229999999999563</v>
       </c>
       <c r="E33" s="10">
         <f t="shared" si="7"/>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="N33" s="10">
         <f t="shared" si="7"/>
-        <v>3707.3899999999994</v>
+        <v>3760.0399999999991</v>
       </c>
       <c r="O33" s="10">
         <f t="shared" si="7"/>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="7"/>
-        <v>15120.57</v>
+        <v>12581.68</v>
       </c>
       <c r="R33" s="10">
         <f t="shared" si="7"/>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="6"/>
-        <v>23947.919999999998</v>
+        <v>21508.909999999996</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
@@ -4542,7 +4542,10 @@
       </c>
       <c r="O11" s="14"/>
       <c r="P11" s="14"/>
-      <c r="Q11" s="14"/>
+      <c r="Q11" s="14">
+        <f>205-3.5</f>
+        <v>201.5</v>
+      </c>
       <c r="R11" s="14"/>
       <c r="S11" s="14">
         <f>205-3.5</f>
@@ -4557,7 +4560,7 @@
       <c r="Z11" s="14"/>
       <c r="AA11" s="14">
         <f t="shared" si="0"/>
-        <v>3838.5</v>
+        <v>4040</v>
       </c>
       <c r="AB11" s="14"/>
     </row>
@@ -4567,7 +4570,9 @@
       </c>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
+      <c r="D12" s="14">
+        <v>15452.77</v>
+      </c>
       <c r="E12" s="14"/>
       <c r="F12" s="14"/>
       <c r="G12" s="14"/>
@@ -4577,10 +4582,15 @@
       <c r="K12" s="14"/>
       <c r="L12" s="14"/>
       <c r="M12" s="14"/>
-      <c r="N12" s="14"/>
+      <c r="N12" s="14">
+        <v>-52.65</v>
+      </c>
       <c r="O12" s="14"/>
       <c r="P12" s="14"/>
-      <c r="Q12" s="14"/>
+      <c r="Q12" s="14">
+        <f>709-15.08+920-6.49+396-1.39+347-11.65</f>
+        <v>2337.39</v>
+      </c>
       <c r="R12" s="14"/>
       <c r="S12" s="14"/>
       <c r="T12" s="14"/>
@@ -4592,7 +4602,7 @@
       <c r="Z12" s="14"/>
       <c r="AA12" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>17737.510000000002</v>
       </c>
       <c r="AB12" s="14"/>
     </row>
@@ -5308,9 +5318,9 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D33" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="D33" s="10">
+        <f t="shared" si="1"/>
+        <v>15452.77</v>
       </c>
       <c r="E33" s="10">
         <f t="shared" si="1"/>
@@ -5350,7 +5360,7 @@
       </c>
       <c r="N33" s="10">
         <f t="shared" si="1"/>
-        <v>6292.6100000000006</v>
+        <v>6239.9600000000009</v>
       </c>
       <c r="O33" s="10" t="str">
         <f t="shared" si="1"/>
@@ -5362,7 +5372,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="1"/>
-        <v>4879.43</v>
+        <v>7418.32</v>
       </c>
       <c r="R33" s="10" t="str">
         <f t="shared" si="1"/>
@@ -5402,7 +5412,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="1"/>
-        <v>80702.080000000002</v>
+        <v>98641.09</v>
       </c>
       <c r="AB33" s="15"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{899DD884-CEF8-43C5-B438-4E617E4A4F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{386491B2-2B49-474F-8BBC-AE3FF33F64AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="65">
   <si>
     <t>Presupuesto</t>
   </si>
@@ -236,6 +236,9 @@
   </si>
   <si>
     <t>Botas Roci</t>
+  </si>
+  <si>
+    <t>2 cubiertas chery</t>
   </si>
 </sst>
 </file>
@@ -1926,7 +1929,7 @@
       </c>
       <c r="N14" s="1">
         <f>IF(Mayo!N33&gt;0,Mayo!N33,"")</f>
-        <v>6239.9600000000009</v>
+        <v>5694.4100000000008</v>
       </c>
       <c r="O14" s="1" t="str">
         <f>IF(Mayo!O33&gt;0,Mayo!O33,"")</f>
@@ -1938,7 +1941,7 @@
       </c>
       <c r="Q14" s="1">
         <f>IF(Mayo!Q33&gt;0,Mayo!Q33,"")</f>
-        <v>7418.32</v>
+        <v>7815.94</v>
       </c>
       <c r="R14" s="1" t="str">
         <f>IF(Mayo!R33&gt;0,Mayo!R33,"")</f>
@@ -1948,17 +1951,17 @@
         <f>IF(Mayo!S33&gt;0,Mayo!S33,"")</f>
         <v>3261.5</v>
       </c>
-      <c r="T14" s="1" t="str">
+      <c r="T14" s="1">
         <f>IF(Mayo!T33&gt;0,Mayo!T33,"")</f>
-        <v/>
+        <v>5803.28</v>
       </c>
       <c r="U14" s="1" t="str">
         <f>IF(Mayo!U33&gt;0,Mayo!U33,"")</f>
         <v/>
       </c>
-      <c r="V14" s="1" t="str">
+      <c r="V14" s="1">
         <f>IF(Mayo!V33&gt;0,Mayo!V33,"")</f>
-        <v/>
+        <v>285.25</v>
       </c>
       <c r="W14" s="1">
         <f>IF(Mayo!W33&gt;0,Mayo!W33,"")</f>
@@ -1978,7 +1981,7 @@
       </c>
       <c r="AA14" s="1">
         <f>IF(Mayo!AA33&gt;0,Mayo!AA33,"")</f>
-        <v>98641.09</v>
+        <v>104581.69</v>
       </c>
     </row>
     <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2862,13 +2865,13 @@
       <c r="A25" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B25" s="1" t="str">
+      <c r="B25" s="1">
         <f>IF(ISNUMBER(Mayo!B33),B3-Mayo!B33,"")</f>
-        <v/>
-      </c>
-      <c r="C25" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="C25" s="1">
         <f>IF(ISNUMBER(Mayo!C33),C3-Mayo!C33,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D25" s="1">
         <f>IF(ISNUMBER(Mayo!D33),D3-Mayo!D33,"")</f>
@@ -2912,7 +2915,7 @@
       </c>
       <c r="N25" s="1">
         <f>IF(ISNUMBER(Mayo!N33),N3-Mayo!N33,"")</f>
-        <v>3760.0399999999991</v>
+        <v>4305.5899999999992</v>
       </c>
       <c r="O25" s="1" t="str">
         <f>IF(ISNUMBER(Mayo!O33),O3-Mayo!O33,"")</f>
@@ -2924,7 +2927,7 @@
       </c>
       <c r="Q25" s="1">
         <f>IF(ISNUMBER(Mayo!Q33),Q3-Mayo!Q33,"")</f>
-        <v>12581.68</v>
+        <v>12184.060000000001</v>
       </c>
       <c r="R25" s="1" t="str">
         <f>IF(ISNUMBER(Mayo!R33),R3-Mayo!R33,"")</f>
@@ -2934,17 +2937,17 @@
         <f>IF(ISNUMBER(Mayo!S33),S3-Mayo!S33,"")</f>
         <v>1738.5</v>
       </c>
-      <c r="T25" s="1" t="str">
+      <c r="T25" s="1">
         <f>IF(ISNUMBER(Mayo!T33),T3-Mayo!T33,"")</f>
-        <v/>
-      </c>
-      <c r="U25" s="1" t="str">
+        <v>9196.7200000000012</v>
+      </c>
+      <c r="U25" s="1">
         <f>IF(ISNUMBER(Mayo!U33),U3-Mayo!U33,"")</f>
-        <v/>
-      </c>
-      <c r="V25" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="V25" s="1">
         <f>IF(ISNUMBER(Mayo!V33),V3-Mayo!V33,"")</f>
-        <v/>
+        <v>2714.75</v>
       </c>
       <c r="W25" s="1">
         <f>IF(ISNUMBER(Mayo!W33),W3-Mayo!W33,"")</f>
@@ -2964,7 +2967,7 @@
       </c>
       <c r="AA25" s="10">
         <f t="shared" ref="AA25:AA33" si="6">SUMIF(B25:Z25,"&lt;&gt;"&amp;"")</f>
-        <v>21508.909999999996</v>
+        <v>33568.31</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3784,7 +3787,7 @@
       </c>
       <c r="N33" s="10">
         <f t="shared" si="7"/>
-        <v>3760.0399999999991</v>
+        <v>4305.5899999999992</v>
       </c>
       <c r="O33" s="10">
         <f t="shared" si="7"/>
@@ -3796,7 +3799,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="7"/>
-        <v>12581.68</v>
+        <v>12184.060000000001</v>
       </c>
       <c r="R33" s="10">
         <f t="shared" si="7"/>
@@ -3808,7 +3811,7 @@
       </c>
       <c r="T33" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9196.7200000000012</v>
       </c>
       <c r="U33" s="10">
         <f t="shared" si="7"/>
@@ -3816,7 +3819,7 @@
       </c>
       <c r="V33" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2714.75</v>
       </c>
       <c r="W33" s="10">
         <f t="shared" si="7"/>
@@ -3836,7 +3839,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="6"/>
-        <v>21508.909999999996</v>
+        <v>33568.31</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
@@ -4622,24 +4625,37 @@
       <c r="K13" s="14"/>
       <c r="L13" s="14"/>
       <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
+      <c r="N13" s="14">
+        <v>-545.54999999999995</v>
+      </c>
       <c r="O13" s="14"/>
       <c r="P13" s="14"/>
-      <c r="Q13" s="14"/>
+      <c r="Q13" s="14">
+        <f>404.98-7.36</f>
+        <v>397.62</v>
+      </c>
       <c r="R13" s="14"/>
       <c r="S13" s="14"/>
-      <c r="T13" s="14"/>
+      <c r="T13" s="14">
+        <f>5900-96.72</f>
+        <v>5803.28</v>
+      </c>
       <c r="U13" s="14"/>
-      <c r="V13" s="14"/>
+      <c r="V13" s="14">
+        <f>290-4.75</f>
+        <v>285.25</v>
+      </c>
       <c r="W13" s="14"/>
       <c r="X13" s="14"/>
       <c r="Y13" s="14"/>
       <c r="Z13" s="14"/>
       <c r="AA13" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AB13" s="14"/>
+        <v>5940.5999999999995</v>
+      </c>
+      <c r="AB13" s="14" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="14" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13">
@@ -5275,8 +5291,12 @@
       <c r="A32" s="13">
         <v>31</v>
       </c>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
+      <c r="B32" s="14">
+        <v>0</v>
+      </c>
+      <c r="C32" s="14">
+        <v>0</v>
+      </c>
       <c r="D32" s="14"/>
       <c r="E32" s="14"/>
       <c r="F32" s="14"/>
@@ -5294,7 +5314,9 @@
       <c r="R32" s="14"/>
       <c r="S32" s="14"/>
       <c r="T32" s="14"/>
-      <c r="U32" s="14"/>
+      <c r="U32" s="14">
+        <v>0</v>
+      </c>
       <c r="V32" s="14"/>
       <c r="W32" s="14"/>
       <c r="X32" s="14"/>
@@ -5310,13 +5332,13 @@
       <c r="A33" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B33" s="10" t="str">
+      <c r="B33" s="10">
         <f t="shared" ref="B33:AA33" si="1">IF(COUNTA(B2:B32)&gt;0,SUM(B2:B32),"")</f>
-        <v/>
-      </c>
-      <c r="C33" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="C33" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="D33" s="10">
         <f t="shared" si="1"/>
@@ -5360,7 +5382,7 @@
       </c>
       <c r="N33" s="10">
         <f t="shared" si="1"/>
-        <v>6239.9600000000009</v>
+        <v>5694.4100000000008</v>
       </c>
       <c r="O33" s="10" t="str">
         <f t="shared" si="1"/>
@@ -5372,7 +5394,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="1"/>
-        <v>7418.32</v>
+        <v>7815.94</v>
       </c>
       <c r="R33" s="10" t="str">
         <f t="shared" si="1"/>
@@ -5382,17 +5404,17 @@
         <f t="shared" si="1"/>
         <v>3261.5</v>
       </c>
-      <c r="T33" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="U33" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="V33" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="T33" s="10">
+        <f t="shared" si="1"/>
+        <v>5803.28</v>
+      </c>
+      <c r="U33" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="10">
+        <f t="shared" si="1"/>
+        <v>285.25</v>
       </c>
       <c r="W33" s="10">
         <f t="shared" si="1"/>
@@ -5412,7 +5434,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="1"/>
-        <v>98641.09</v>
+        <v>104581.69</v>
       </c>
       <c r="AB33" s="15"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{386491B2-2B49-474F-8BBC-AE3FF33F64AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BAC2F67-4A4F-44C6-9684-F11F731C087D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -326,7 +326,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -411,6 +411,12 @@
         <bgColor rgb="FF2E7D32"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -439,7 +445,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -512,6 +518,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1935,9 +1942,9 @@
         <f>IF(Mayo!O33&gt;0,Mayo!O33,"")</f>
         <v/>
       </c>
-      <c r="P14" s="1" t="str">
+      <c r="P14" s="1">
         <f>IF(Mayo!P33&gt;0,Mayo!P33,"")</f>
-        <v/>
+        <v>2449.1799999999998</v>
       </c>
       <c r="Q14" s="1">
         <f>IF(Mayo!Q33&gt;0,Mayo!Q33,"")</f>
@@ -1981,7 +1988,7 @@
       </c>
       <c r="AA14" s="1">
         <f>IF(Mayo!AA33&gt;0,Mayo!AA33,"")</f>
-        <v>104581.69</v>
+        <v>107030.87</v>
       </c>
     </row>
     <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2921,9 +2928,9 @@
         <f>IF(ISNUMBER(Mayo!O33),O3-Mayo!O33,"")</f>
         <v/>
       </c>
-      <c r="P25" s="1" t="str">
+      <c r="P25" s="1">
         <f>IF(ISNUMBER(Mayo!P33),P3-Mayo!P33,"")</f>
-        <v/>
+        <v>50.820000000000164</v>
       </c>
       <c r="Q25" s="1">
         <f>IF(ISNUMBER(Mayo!Q33),Q3-Mayo!Q33,"")</f>
@@ -2967,7 +2974,7 @@
       </c>
       <c r="AA25" s="10">
         <f t="shared" ref="AA25:AA33" si="6">SUMIF(B25:Z25,"&lt;&gt;"&amp;"")</f>
-        <v>33568.31</v>
+        <v>33619.129999999997</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3795,7 +3802,7 @@
       </c>
       <c r="P33" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>50.820000000000164</v>
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="7"/>
@@ -3839,7 +3846,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="6"/>
-        <v>33568.31</v>
+        <v>33619.129999999997</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
@@ -4452,7 +4459,7 @@
       <c r="M9" s="14">
         <v>810</v>
       </c>
-      <c r="N9" s="14">
+      <c r="N9" s="38">
         <f>1000-16.39</f>
         <v>983.61</v>
       </c>
@@ -4675,7 +4682,10 @@
       <c r="M14" s="14"/>
       <c r="N14" s="14"/>
       <c r="O14" s="14"/>
-      <c r="P14" s="14"/>
+      <c r="P14" s="14">
+        <f>2490-40.82</f>
+        <v>2449.1799999999998</v>
+      </c>
       <c r="Q14" s="14"/>
       <c r="R14" s="14"/>
       <c r="S14" s="14"/>
@@ -4688,7 +4698,7 @@
       <c r="Z14" s="14"/>
       <c r="AA14" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2449.1799999999998</v>
       </c>
       <c r="AB14" s="14"/>
     </row>
@@ -5388,9 +5398,9 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="P33" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="P33" s="10">
+        <f t="shared" si="1"/>
+        <v>2449.1799999999998</v>
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="1"/>
@@ -5434,7 +5444,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="1"/>
-        <v>104581.69</v>
+        <v>107030.87</v>
       </c>
       <c r="AB33" s="15"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BAC2F67-4A4F-44C6-9684-F11F731C087D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4CA0A5E-0967-4A44-8A7B-644B116796BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -509,6 +509,7 @@
     <xf numFmtId="3" fontId="9" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -518,7 +519,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -844,35 +844,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
-      <c r="W1" s="35"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="35"/>
-      <c r="AA1" s="35"/>
+      <c r="A1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="36"/>
+      <c r="R1" s="36"/>
+      <c r="S1" s="36"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="36"/>
+      <c r="V1" s="36"/>
+      <c r="W1" s="36"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="36"/>
+      <c r="Z1" s="36"/>
+      <c r="AA1" s="36"/>
     </row>
     <row r="2" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1769,35 +1769,35 @@
       </c>
     </row>
     <row r="12" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="36" t="s">
+      <c r="A12" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="36"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="36"/>
-      <c r="J12" s="36"/>
-      <c r="K12" s="36"/>
-      <c r="L12" s="36"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
-      <c r="P12" s="36"/>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="36"/>
-      <c r="S12" s="36"/>
-      <c r="T12" s="36"/>
-      <c r="U12" s="36"/>
-      <c r="V12" s="36"/>
-      <c r="W12" s="36"/>
-      <c r="X12" s="36"/>
-      <c r="Y12" s="36"/>
-      <c r="Z12" s="36"/>
-      <c r="AA12" s="36"/>
+      <c r="B12" s="37"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="37"/>
+      <c r="G12" s="37"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="37"/>
+      <c r="K12" s="37"/>
+      <c r="L12" s="37"/>
+      <c r="M12" s="37"/>
+      <c r="N12" s="37"/>
+      <c r="O12" s="37"/>
+      <c r="P12" s="37"/>
+      <c r="Q12" s="37"/>
+      <c r="R12" s="37"/>
+      <c r="S12" s="37"/>
+      <c r="T12" s="37"/>
+      <c r="U12" s="37"/>
+      <c r="V12" s="37"/>
+      <c r="W12" s="37"/>
+      <c r="X12" s="37"/>
+      <c r="Y12" s="37"/>
+      <c r="Z12" s="37"/>
+      <c r="AA12" s="37"/>
     </row>
     <row r="13" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="T14" s="1">
         <f>IF(Mayo!T33&gt;0,Mayo!T33,"")</f>
-        <v>5803.28</v>
+        <v>14385.25</v>
       </c>
       <c r="U14" s="1" t="str">
         <f>IF(Mayo!U33&gt;0,Mayo!U33,"")</f>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="AA14" s="1">
         <f>IF(Mayo!AA33&gt;0,Mayo!AA33,"")</f>
-        <v>107030.87</v>
+        <v>115612.84</v>
       </c>
     </row>
     <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2755,35 +2755,35 @@
       </c>
     </row>
     <row r="23" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="37" t="s">
+      <c r="A23" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="37"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="37"/>
-      <c r="L23" s="37"/>
-      <c r="M23" s="37"/>
-      <c r="N23" s="37"/>
-      <c r="O23" s="37"/>
-      <c r="P23" s="37"/>
-      <c r="Q23" s="37"/>
-      <c r="R23" s="37"/>
-      <c r="S23" s="37"/>
-      <c r="T23" s="37"/>
-      <c r="U23" s="37"/>
-      <c r="V23" s="37"/>
-      <c r="W23" s="37"/>
-      <c r="X23" s="37"/>
-      <c r="Y23" s="37"/>
-      <c r="Z23" s="37"/>
-      <c r="AA23" s="37"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="38"/>
+      <c r="L23" s="38"/>
+      <c r="M23" s="38"/>
+      <c r="N23" s="38"/>
+      <c r="O23" s="38"/>
+      <c r="P23" s="38"/>
+      <c r="Q23" s="38"/>
+      <c r="R23" s="38"/>
+      <c r="S23" s="38"/>
+      <c r="T23" s="38"/>
+      <c r="U23" s="38"/>
+      <c r="V23" s="38"/>
+      <c r="W23" s="38"/>
+      <c r="X23" s="38"/>
+      <c r="Y23" s="38"/>
+      <c r="Z23" s="38"/>
+      <c r="AA23" s="38"/>
     </row>
     <row r="24" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="T25" s="1">
         <f>IF(ISNUMBER(Mayo!T33),T3-Mayo!T33,"")</f>
-        <v>9196.7200000000012</v>
+        <v>614.75</v>
       </c>
       <c r="U25" s="1">
         <f>IF(ISNUMBER(Mayo!U33),U3-Mayo!U33,"")</f>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AA25" s="10">
         <f t="shared" ref="AA25:AA33" si="6">SUMIF(B25:Z25,"&lt;&gt;"&amp;"")</f>
-        <v>33619.129999999997</v>
+        <v>25037.159999999996</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="T33" s="10">
         <f t="shared" si="7"/>
-        <v>9196.7200000000012</v>
+        <v>614.75</v>
       </c>
       <c r="U33" s="10">
         <f t="shared" si="7"/>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="6"/>
-        <v>33619.129999999997</v>
+        <v>25037.159999999996</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
@@ -4459,7 +4459,7 @@
       <c r="M9" s="14">
         <v>810</v>
       </c>
-      <c r="N9" s="38">
+      <c r="N9" s="35">
         <f>1000-16.39</f>
         <v>983.61</v>
       </c>
@@ -4689,7 +4689,10 @@
       <c r="Q14" s="14"/>
       <c r="R14" s="14"/>
       <c r="S14" s="14"/>
-      <c r="T14" s="14"/>
+      <c r="T14" s="14">
+        <f>8725-143.03</f>
+        <v>8581.9699999999993</v>
+      </c>
       <c r="U14" s="14"/>
       <c r="V14" s="14"/>
       <c r="W14" s="14"/>
@@ -4698,7 +4701,7 @@
       <c r="Z14" s="14"/>
       <c r="AA14" s="14">
         <f t="shared" si="0"/>
-        <v>2449.1799999999998</v>
+        <v>11031.15</v>
       </c>
       <c r="AB14" s="14"/>
     </row>
@@ -5416,7 +5419,7 @@
       </c>
       <c r="T33" s="10">
         <f t="shared" si="1"/>
-        <v>5803.28</v>
+        <v>14385.25</v>
       </c>
       <c r="U33" s="10">
         <f t="shared" si="1"/>
@@ -5444,7 +5447,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="1"/>
-        <v>107030.87</v>
+        <v>115612.84</v>
       </c>
       <c r="AB33" s="15"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4CA0A5E-0967-4A44-8A7B-644B116796BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4472E7A-DDB9-4B06-958C-6522F314D5A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="Q14" s="1">
         <f>IF(Mayo!Q33&gt;0,Mayo!Q33,"")</f>
-        <v>7815.94</v>
+        <v>8258.56</v>
       </c>
       <c r="R14" s="1" t="str">
         <f>IF(Mayo!R33&gt;0,Mayo!R33,"")</f>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="W14" s="1">
         <f>IF(Mayo!W33&gt;0,Mayo!W33,"")</f>
-        <v>494.09</v>
+        <v>709.08999999999992</v>
       </c>
       <c r="X14" s="1" t="str">
         <f>IF(Mayo!X33&gt;0,Mayo!X33,"")</f>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="AA14" s="1">
         <f>IF(Mayo!AA33&gt;0,Mayo!AA33,"")</f>
-        <v>115612.84</v>
+        <v>116270.45999999999</v>
       </c>
     </row>
     <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="Q25" s="1">
         <f>IF(ISNUMBER(Mayo!Q33),Q3-Mayo!Q33,"")</f>
-        <v>12184.060000000001</v>
+        <v>11741.44</v>
       </c>
       <c r="R25" s="1" t="str">
         <f>IF(ISNUMBER(Mayo!R33),R3-Mayo!R33,"")</f>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="W25" s="1">
         <f>IF(ISNUMBER(Mayo!W33),W3-Mayo!W33,"")</f>
-        <v>1005.9100000000001</v>
+        <v>790.91000000000008</v>
       </c>
       <c r="X25" s="1" t="str">
         <f>IF(ISNUMBER(Mayo!X33),X3-Mayo!X33,"")</f>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AA25" s="10">
         <f t="shared" ref="AA25:AA33" si="6">SUMIF(B25:Z25,"&lt;&gt;"&amp;"")</f>
-        <v>25037.159999999996</v>
+        <v>24379.539999999997</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="7"/>
-        <v>12184.060000000001</v>
+        <v>11741.44</v>
       </c>
       <c r="R33" s="10">
         <f t="shared" si="7"/>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="W33" s="10">
         <f t="shared" si="7"/>
-        <v>1005.9100000000001</v>
+        <v>790.91000000000008</v>
       </c>
       <c r="X33" s="10">
         <f t="shared" si="7"/>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="6"/>
-        <v>25037.159999999996</v>
+        <v>24379.539999999997</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
@@ -4759,19 +4759,24 @@
       <c r="N16" s="14"/>
       <c r="O16" s="14"/>
       <c r="P16" s="14"/>
-      <c r="Q16" s="14"/>
+      <c r="Q16" s="14">
+        <f>450-7.38</f>
+        <v>442.62</v>
+      </c>
       <c r="R16" s="14"/>
       <c r="S16" s="14"/>
       <c r="T16" s="14"/>
       <c r="U16" s="14"/>
       <c r="V16" s="14"/>
-      <c r="W16" s="14"/>
+      <c r="W16" s="14">
+        <v>215</v>
+      </c>
       <c r="X16" s="14"/>
       <c r="Y16" s="14"/>
       <c r="Z16" s="14"/>
       <c r="AA16" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>657.62</v>
       </c>
       <c r="AB16" s="14"/>
     </row>
@@ -5407,7 +5412,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="1"/>
-        <v>7815.94</v>
+        <v>8258.56</v>
       </c>
       <c r="R33" s="10" t="str">
         <f t="shared" si="1"/>
@@ -5431,7 +5436,7 @@
       </c>
       <c r="W33" s="10">
         <f t="shared" si="1"/>
-        <v>494.09</v>
+        <v>709.08999999999992</v>
       </c>
       <c r="X33" s="10" t="str">
         <f t="shared" si="1"/>
@@ -5447,7 +5452,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="1"/>
-        <v>115612.84</v>
+        <v>116270.45999999999</v>
       </c>
       <c r="AB33" s="15"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4472E7A-DDB9-4B06-958C-6522F314D5A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76EF92A1-6B97-4ED8-8639-A220A6053ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="Q14" s="1">
         <f>IF(Mayo!Q33&gt;0,Mayo!Q33,"")</f>
-        <v>8258.56</v>
+        <v>10340.66</v>
       </c>
       <c r="R14" s="1" t="str">
         <f>IF(Mayo!R33&gt;0,Mayo!R33,"")</f>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="AA14" s="1">
         <f>IF(Mayo!AA33&gt;0,Mayo!AA33,"")</f>
-        <v>116270.45999999999</v>
+        <v>118352.56</v>
       </c>
     </row>
     <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="Q25" s="1">
         <f>IF(ISNUMBER(Mayo!Q33),Q3-Mayo!Q33,"")</f>
-        <v>11741.44</v>
+        <v>9659.34</v>
       </c>
       <c r="R25" s="1" t="str">
         <f>IF(ISNUMBER(Mayo!R33),R3-Mayo!R33,"")</f>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AA25" s="10">
         <f t="shared" ref="AA25:AA33" si="6">SUMIF(B25:Z25,"&lt;&gt;"&amp;"")</f>
-        <v>24379.539999999997</v>
+        <v>22297.439999999995</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="7"/>
-        <v>11741.44</v>
+        <v>9659.34</v>
       </c>
       <c r="R33" s="10">
         <f t="shared" si="7"/>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="6"/>
-        <v>24379.539999999997</v>
+        <v>22297.439999999995</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
@@ -4799,7 +4799,10 @@
       <c r="N17" s="14"/>
       <c r="O17" s="14"/>
       <c r="P17" s="14"/>
-      <c r="Q17" s="14"/>
+      <c r="Q17" s="14">
+        <f>682-11.38+1322-21.67+113-1.85</f>
+        <v>2082.1</v>
+      </c>
       <c r="R17" s="14"/>
       <c r="S17" s="14"/>
       <c r="T17" s="14"/>
@@ -4811,7 +4814,7 @@
       <c r="Z17" s="14"/>
       <c r="AA17" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2082.1</v>
       </c>
       <c r="AB17" s="14"/>
     </row>
@@ -5412,7 +5415,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="1"/>
-        <v>8258.56</v>
+        <v>10340.66</v>
       </c>
       <c r="R33" s="10" t="str">
         <f t="shared" si="1"/>
@@ -5452,7 +5455,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="1"/>
-        <v>116270.45999999999</v>
+        <v>118352.56</v>
       </c>
       <c r="AB33" s="15"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76EF92A1-6B97-4ED8-8639-A220A6053ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8250CAB7-9D61-475A-BB20-D97C93FDE9D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="Q14" s="1">
         <f>IF(Mayo!Q33&gt;0,Mayo!Q33,"")</f>
-        <v>10340.66</v>
+        <v>10714.43</v>
       </c>
       <c r="R14" s="1" t="str">
         <f>IF(Mayo!R33&gt;0,Mayo!R33,"")</f>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="AA14" s="1">
         <f>IF(Mayo!AA33&gt;0,Mayo!AA33,"")</f>
-        <v>118352.56</v>
+        <v>118726.33</v>
       </c>
     </row>
     <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="Q25" s="1">
         <f>IF(ISNUMBER(Mayo!Q33),Q3-Mayo!Q33,"")</f>
-        <v>9659.34</v>
+        <v>9285.57</v>
       </c>
       <c r="R25" s="1" t="str">
         <f>IF(ISNUMBER(Mayo!R33),R3-Mayo!R33,"")</f>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AA25" s="10">
         <f t="shared" ref="AA25:AA33" si="6">SUMIF(B25:Z25,"&lt;&gt;"&amp;"")</f>
-        <v>22297.439999999995</v>
+        <v>21923.67</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="7"/>
-        <v>9659.34</v>
+        <v>9285.57</v>
       </c>
       <c r="R33" s="10">
         <f t="shared" si="7"/>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="6"/>
-        <v>22297.439999999995</v>
+        <v>21923.67</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
@@ -4872,7 +4872,10 @@
       <c r="N19" s="14"/>
       <c r="O19" s="14"/>
       <c r="P19" s="14"/>
-      <c r="Q19" s="14"/>
+      <c r="Q19" s="14">
+        <f>380-6.23</f>
+        <v>373.77</v>
+      </c>
       <c r="R19" s="14"/>
       <c r="S19" s="14"/>
       <c r="T19" s="14"/>
@@ -4884,7 +4887,7 @@
       <c r="Z19" s="14"/>
       <c r="AA19" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>373.77</v>
       </c>
       <c r="AB19" s="14"/>
     </row>
@@ -5415,7 +5418,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="1"/>
-        <v>10340.66</v>
+        <v>10714.43</v>
       </c>
       <c r="R33" s="10" t="str">
         <f t="shared" si="1"/>
@@ -5455,7 +5458,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="1"/>
-        <v>118352.56</v>
+        <v>118726.33</v>
       </c>
       <c r="AB33" s="15"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8250CAB7-9D61-475A-BB20-D97C93FDE9D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D06438F6-C541-4A0D-BE4D-836ACE5BCA55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="Q14" s="1">
         <f>IF(Mayo!Q33&gt;0,Mayo!Q33,"")</f>
-        <v>10714.43</v>
+        <v>10818.69</v>
       </c>
       <c r="R14" s="1" t="str">
         <f>IF(Mayo!R33&gt;0,Mayo!R33,"")</f>
@@ -1984,11 +1984,11 @@
       </c>
       <c r="Z14" s="1">
         <f>IF(Mayo!Z33&gt;0,Mayo!Z33,"")</f>
-        <v>3142.62</v>
+        <v>3909.3399999999997</v>
       </c>
       <c r="AA14" s="1">
         <f>IF(Mayo!AA33&gt;0,Mayo!AA33,"")</f>
-        <v>118726.33</v>
+        <v>119597.31</v>
       </c>
     </row>
     <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="Q25" s="1">
         <f>IF(ISNUMBER(Mayo!Q33),Q3-Mayo!Q33,"")</f>
-        <v>9285.57</v>
+        <v>9181.31</v>
       </c>
       <c r="R25" s="1" t="str">
         <f>IF(ISNUMBER(Mayo!R33),R3-Mayo!R33,"")</f>
@@ -2970,11 +2970,11 @@
       </c>
       <c r="Z25" s="1">
         <f>IF(ISNUMBER(Mayo!Z33),Z3-Mayo!Z33,"")</f>
-        <v>857.38000000000011</v>
+        <v>90.660000000000309</v>
       </c>
       <c r="AA25" s="10">
         <f t="shared" ref="AA25:AA33" si="6">SUMIF(B25:Z25,"&lt;&gt;"&amp;"")</f>
-        <v>21923.67</v>
+        <v>21052.689999999995</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="7"/>
-        <v>9285.57</v>
+        <v>9181.31</v>
       </c>
       <c r="R33" s="10">
         <f t="shared" si="7"/>
@@ -3842,11 +3842,11 @@
       </c>
       <c r="Z33" s="10">
         <f t="shared" si="7"/>
-        <v>857.38000000000011</v>
+        <v>90.660000000000309</v>
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="6"/>
-        <v>21923.67</v>
+        <v>21052.689999999995</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
@@ -4910,7 +4910,10 @@
       <c r="N20" s="14"/>
       <c r="O20" s="14"/>
       <c r="P20" s="14"/>
-      <c r="Q20" s="14"/>
+      <c r="Q20" s="14">
+        <f>106-1.74</f>
+        <v>104.26</v>
+      </c>
       <c r="R20" s="14"/>
       <c r="S20" s="14"/>
       <c r="T20" s="14"/>
@@ -4919,10 +4922,13 @@
       <c r="W20" s="14"/>
       <c r="X20" s="14"/>
       <c r="Y20" s="14"/>
-      <c r="Z20" s="14"/>
+      <c r="Z20" s="14">
+        <f>234+545-8.44-3.84</f>
+        <v>766.71999999999991</v>
+      </c>
       <c r="AA20" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>870.9799999999999</v>
       </c>
       <c r="AB20" s="14"/>
     </row>
@@ -5418,7 +5424,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="1"/>
-        <v>10714.43</v>
+        <v>10818.69</v>
       </c>
       <c r="R33" s="10" t="str">
         <f t="shared" si="1"/>
@@ -5454,11 +5460,11 @@
       </c>
       <c r="Z33" s="10">
         <f t="shared" si="1"/>
-        <v>3142.62</v>
+        <v>3909.3399999999997</v>
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="1"/>
-        <v>118726.33</v>
+        <v>119597.31</v>
       </c>
       <c r="AB33" s="15"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D06438F6-C541-4A0D-BE4D-836ACE5BCA55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5F628FC-6097-4848-8E56-37A57100EF32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="Q14" s="1">
         <f>IF(Mayo!Q33&gt;0,Mayo!Q33,"")</f>
-        <v>10818.69</v>
+        <v>12283.94</v>
       </c>
       <c r="R14" s="1" t="str">
         <f>IF(Mayo!R33&gt;0,Mayo!R33,"")</f>
@@ -1984,11 +1984,11 @@
       </c>
       <c r="Z14" s="1">
         <f>IF(Mayo!Z33&gt;0,Mayo!Z33,"")</f>
-        <v>3909.3399999999997</v>
+        <v>3879.3399999999997</v>
       </c>
       <c r="AA14" s="1">
         <f>IF(Mayo!AA33&gt;0,Mayo!AA33,"")</f>
-        <v>119597.31</v>
+        <v>121032.56</v>
       </c>
     </row>
     <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="Q25" s="1">
         <f>IF(ISNUMBER(Mayo!Q33),Q3-Mayo!Q33,"")</f>
-        <v>9181.31</v>
+        <v>7716.0599999999995</v>
       </c>
       <c r="R25" s="1" t="str">
         <f>IF(ISNUMBER(Mayo!R33),R3-Mayo!R33,"")</f>
@@ -2970,11 +2970,11 @@
       </c>
       <c r="Z25" s="1">
         <f>IF(ISNUMBER(Mayo!Z33),Z3-Mayo!Z33,"")</f>
-        <v>90.660000000000309</v>
+        <v>120.66000000000031</v>
       </c>
       <c r="AA25" s="10">
         <f t="shared" ref="AA25:AA33" si="6">SUMIF(B25:Z25,"&lt;&gt;"&amp;"")</f>
-        <v>21052.689999999995</v>
+        <v>19617.439999999995</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="7"/>
-        <v>9181.31</v>
+        <v>7716.0599999999995</v>
       </c>
       <c r="R33" s="10">
         <f t="shared" si="7"/>
@@ -3842,11 +3842,11 @@
       </c>
       <c r="Z33" s="10">
         <f t="shared" si="7"/>
-        <v>90.660000000000309</v>
+        <v>120.66000000000031</v>
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="6"/>
-        <v>21052.689999999995</v>
+        <v>19617.439999999995</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
@@ -4923,12 +4923,12 @@
       <c r="X20" s="14"/>
       <c r="Y20" s="14"/>
       <c r="Z20" s="14">
-        <f>234+545-8.44-3.84</f>
-        <v>766.71999999999991</v>
+        <f>234+515-8.44-3.84</f>
+        <v>736.71999999999991</v>
       </c>
       <c r="AA20" s="14">
         <f t="shared" si="0"/>
-        <v>870.9799999999999</v>
+        <v>840.9799999999999</v>
       </c>
       <c r="AB20" s="14"/>
     </row>
@@ -4951,7 +4951,10 @@
       <c r="N21" s="14"/>
       <c r="O21" s="14"/>
       <c r="P21" s="14"/>
-      <c r="Q21" s="14"/>
+      <c r="Q21" s="14">
+        <f>858+498-15.6-8.92+136-2.23</f>
+        <v>1465.25</v>
+      </c>
       <c r="R21" s="14"/>
       <c r="S21" s="14"/>
       <c r="T21" s="14"/>
@@ -4963,7 +4966,7 @@
       <c r="Z21" s="14"/>
       <c r="AA21" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1465.25</v>
       </c>
       <c r="AB21" s="14"/>
     </row>
@@ -5424,7 +5427,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="1"/>
-        <v>10818.69</v>
+        <v>12283.94</v>
       </c>
       <c r="R33" s="10" t="str">
         <f t="shared" si="1"/>
@@ -5460,11 +5463,11 @@
       </c>
       <c r="Z33" s="10">
         <f t="shared" si="1"/>
-        <v>3909.3399999999997</v>
+        <v>3879.3399999999997</v>
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="1"/>
-        <v>119597.31</v>
+        <v>121032.56</v>
       </c>
       <c r="AB33" s="15"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5F628FC-6097-4848-8E56-37A57100EF32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39F4BEB4-BBDD-4AB7-AF3D-7B06AE47E509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="66">
   <si>
     <t>Presupuesto</t>
   </si>
@@ -239,6 +239,9 @@
   </si>
   <si>
     <t>2 cubiertas chery</t>
+  </si>
+  <si>
+    <t>retiro cajero</t>
   </si>
 </sst>
 </file>
@@ -1926,9 +1929,9 @@
         <f>IF(Mayo!K33&gt;0,Mayo!K33,"")</f>
         <v>18082.010000000002</v>
       </c>
-      <c r="L14" s="1" t="str">
+      <c r="L14" s="1">
         <f>IF(Mayo!L33&gt;0,Mayo!L33,"")</f>
-        <v/>
+        <v>22127.68</v>
       </c>
       <c r="M14" s="1">
         <f>IF(Mayo!M33&gt;0,Mayo!M33,"")</f>
@@ -1948,7 +1951,7 @@
       </c>
       <c r="Q14" s="1">
         <f>IF(Mayo!Q33&gt;0,Mayo!Q33,"")</f>
-        <v>12283.94</v>
+        <v>13206.140000000001</v>
       </c>
       <c r="R14" s="1" t="str">
         <f>IF(Mayo!R33&gt;0,Mayo!R33,"")</f>
@@ -1984,11 +1987,11 @@
       </c>
       <c r="Z14" s="1">
         <f>IF(Mayo!Z33&gt;0,Mayo!Z33,"")</f>
-        <v>3879.3399999999997</v>
+        <v>4379.34</v>
       </c>
       <c r="AA14" s="1">
         <f>IF(Mayo!AA33&gt;0,Mayo!AA33,"")</f>
-        <v>121032.56</v>
+        <v>144582.44</v>
       </c>
     </row>
     <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2912,9 +2915,9 @@
         <f>IF(ISNUMBER(Mayo!K33),K3-Mayo!K33,"")</f>
         <v>17.989999999997963</v>
       </c>
-      <c r="L25" s="1" t="str">
+      <c r="L25" s="1">
         <f>IF(ISNUMBER(Mayo!L33),L3-Mayo!L33,"")</f>
-        <v/>
+        <v>72.319999999999709</v>
       </c>
       <c r="M25" s="1">
         <f>IF(ISNUMBER(Mayo!M33),M3-Mayo!M33,"")</f>
@@ -2934,7 +2937,7 @@
       </c>
       <c r="Q25" s="1">
         <f>IF(ISNUMBER(Mayo!Q33),Q3-Mayo!Q33,"")</f>
-        <v>7716.0599999999995</v>
+        <v>6793.8599999999988</v>
       </c>
       <c r="R25" s="1" t="str">
         <f>IF(ISNUMBER(Mayo!R33),R3-Mayo!R33,"")</f>
@@ -2970,11 +2973,11 @@
       </c>
       <c r="Z25" s="1">
         <f>IF(ISNUMBER(Mayo!Z33),Z3-Mayo!Z33,"")</f>
-        <v>120.66000000000031</v>
+        <v>-379.34000000000015</v>
       </c>
       <c r="AA25" s="10">
         <f t="shared" ref="AA25:AA33" si="6">SUMIF(B25:Z25,"&lt;&gt;"&amp;"")</f>
-        <v>19617.439999999995</v>
+        <v>18267.559999999994</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3786,7 +3789,7 @@
       </c>
       <c r="L33" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>72.319999999999709</v>
       </c>
       <c r="M33" s="10">
         <f t="shared" si="7"/>
@@ -3806,7 +3809,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="7"/>
-        <v>7716.0599999999995</v>
+        <v>6793.8599999999988</v>
       </c>
       <c r="R33" s="10">
         <f t="shared" si="7"/>
@@ -3842,11 +3845,11 @@
       </c>
       <c r="Z33" s="10">
         <f t="shared" si="7"/>
-        <v>120.66000000000031</v>
+        <v>-379.34000000000015</v>
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="6"/>
-        <v>19617.439999999995</v>
+        <v>18267.559999999994</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
@@ -4984,12 +4987,17 @@
       <c r="I22" s="14"/>
       <c r="J22" s="14"/>
       <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
+      <c r="L22" s="14">
+        <v>22127.68</v>
+      </c>
       <c r="M22" s="14"/>
       <c r="N22" s="14"/>
       <c r="O22" s="14"/>
       <c r="P22" s="14"/>
-      <c r="Q22" s="14"/>
+      <c r="Q22" s="14">
+        <f>524+414-8.59-7.21</f>
+        <v>922.19999999999993</v>
+      </c>
       <c r="R22" s="14"/>
       <c r="S22" s="14"/>
       <c r="T22" s="14"/>
@@ -4998,12 +5006,16 @@
       <c r="W22" s="14"/>
       <c r="X22" s="14"/>
       <c r="Y22" s="14"/>
-      <c r="Z22" s="14"/>
+      <c r="Z22" s="14">
+        <v>500</v>
+      </c>
       <c r="AA22" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AB22" s="14"/>
+        <v>23549.88</v>
+      </c>
+      <c r="AB22" s="14" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="23" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13">
@@ -5405,9 +5417,9 @@
         <f t="shared" si="1"/>
         <v>18082.010000000002</v>
       </c>
-      <c r="L33" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="L33" s="10">
+        <f t="shared" si="1"/>
+        <v>22127.68</v>
       </c>
       <c r="M33" s="10">
         <f t="shared" si="1"/>
@@ -5427,7 +5439,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="1"/>
-        <v>12283.94</v>
+        <v>13206.140000000001</v>
       </c>
       <c r="R33" s="10" t="str">
         <f t="shared" si="1"/>
@@ -5463,11 +5475,11 @@
       </c>
       <c r="Z33" s="10">
         <f t="shared" si="1"/>
-        <v>3879.3399999999997</v>
+        <v>4379.34</v>
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="1"/>
-        <v>121032.56</v>
+        <v>144582.44</v>
       </c>
       <c r="AB33" s="15"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39F4BEB4-BBDD-4AB7-AF3D-7B06AE47E509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54B8BE7F-2E5F-4F43-8621-0EA3FBED6045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="N14" s="1">
         <f>IF(Mayo!N33&gt;0,Mayo!N33,"")</f>
-        <v>5694.4100000000008</v>
+        <v>9325.41</v>
       </c>
       <c r="O14" s="1" t="str">
         <f>IF(Mayo!O33&gt;0,Mayo!O33,"")</f>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="Q14" s="1">
         <f>IF(Mayo!Q33&gt;0,Mayo!Q33,"")</f>
-        <v>13206.140000000001</v>
+        <v>14436.940000000002</v>
       </c>
       <c r="R14" s="1" t="str">
         <f>IF(Mayo!R33&gt;0,Mayo!R33,"")</f>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="AA14" s="1">
         <f>IF(Mayo!AA33&gt;0,Mayo!AA33,"")</f>
-        <v>144582.44</v>
+        <v>149444.24</v>
       </c>
     </row>
     <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="N25" s="1">
         <f>IF(ISNUMBER(Mayo!N33),N3-Mayo!N33,"")</f>
-        <v>4305.5899999999992</v>
+        <v>674.59000000000015</v>
       </c>
       <c r="O25" s="1" t="str">
         <f>IF(ISNUMBER(Mayo!O33),O3-Mayo!O33,"")</f>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="Q25" s="1">
         <f>IF(ISNUMBER(Mayo!Q33),Q3-Mayo!Q33,"")</f>
-        <v>6793.8599999999988</v>
+        <v>5563.0599999999977</v>
       </c>
       <c r="R25" s="1" t="str">
         <f>IF(ISNUMBER(Mayo!R33),R3-Mayo!R33,"")</f>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="AA25" s="10">
         <f t="shared" ref="AA25:AA33" si="6">SUMIF(B25:Z25,"&lt;&gt;"&amp;"")</f>
-        <v>18267.559999999994</v>
+        <v>13405.759999999995</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="N33" s="10">
         <f t="shared" si="7"/>
-        <v>4305.5899999999992</v>
+        <v>674.59000000000015</v>
       </c>
       <c r="O33" s="10">
         <f t="shared" si="7"/>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="7"/>
-        <v>6793.8599999999988</v>
+        <v>5563.0599999999977</v>
       </c>
       <c r="R33" s="10">
         <f t="shared" si="7"/>
@@ -3849,7 +3849,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="6"/>
-        <v>18267.559999999994</v>
+        <v>13405.759999999995</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
@@ -5036,7 +5036,10 @@
       <c r="N23" s="14"/>
       <c r="O23" s="14"/>
       <c r="P23" s="14"/>
-      <c r="Q23" s="14"/>
+      <c r="Q23" s="14">
+        <f>932.73+320.86-16.96-5.83</f>
+        <v>1230.8000000000002</v>
+      </c>
       <c r="R23" s="14"/>
       <c r="S23" s="14"/>
       <c r="T23" s="14"/>
@@ -5048,7 +5051,7 @@
       <c r="Z23" s="14"/>
       <c r="AA23" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1230.8000000000002</v>
       </c>
       <c r="AB23" s="14"/>
     </row>
@@ -5068,7 +5071,9 @@
       <c r="K24" s="14"/>
       <c r="L24" s="14"/>
       <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
+      <c r="N24" s="14">
+        <v>3631</v>
+      </c>
       <c r="O24" s="14"/>
       <c r="P24" s="14"/>
       <c r="Q24" s="14"/>
@@ -5083,7 +5088,7 @@
       <c r="Z24" s="14"/>
       <c r="AA24" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3631</v>
       </c>
       <c r="AB24" s="14"/>
     </row>
@@ -5427,7 +5432,7 @@
       </c>
       <c r="N33" s="10">
         <f t="shared" si="1"/>
-        <v>5694.4100000000008</v>
+        <v>9325.41</v>
       </c>
       <c r="O33" s="10" t="str">
         <f t="shared" si="1"/>
@@ -5439,7 +5444,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="1"/>
-        <v>13206.140000000001</v>
+        <v>14436.940000000002</v>
       </c>
       <c r="R33" s="10" t="str">
         <f t="shared" si="1"/>
@@ -5479,7 +5484,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="1"/>
-        <v>144582.44</v>
+        <v>149444.24</v>
       </c>
       <c r="AB33" s="15"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54B8BE7F-2E5F-4F43-8621-0EA3FBED6045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BBACBFF-BA33-4D10-8D75-BC4861ED8D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="68">
   <si>
     <t>Presupuesto</t>
   </si>
@@ -242,6 +242,12 @@
   </si>
   <si>
     <t>retiro cajero</t>
+  </si>
+  <si>
+    <t>Gas y calefaccion</t>
+  </si>
+  <si>
+    <t>Gas y calefacción</t>
   </si>
 </sst>
 </file>
@@ -840,7 +846,7 @@
     <col min="22" max="22" width="9.7109375" style="1" customWidth="1"/>
     <col min="23" max="23" width="15" style="1" customWidth="1"/>
     <col min="24" max="24" width="9.140625" style="1"/>
-    <col min="25" max="25" width="13" style="1" customWidth="1"/>
+    <col min="25" max="25" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="9.140625" style="1"/>
     <col min="27" max="27" width="12" style="1" customWidth="1"/>
     <col min="28" max="16384" width="9.140625" style="1"/>
@@ -951,7 +957,7 @@
         <v>24</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="Z2" s="1" t="s">
         <v>26</v>
@@ -1046,40 +1052,40 @@
         <v>2000</v>
       </c>
       <c r="Y3" s="1">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="Z3" s="1">
         <v>4000</v>
       </c>
       <c r="AA3" s="1">
         <f t="shared" ref="AA3:AA10" si="0">SUM(B3:Z3)</f>
-        <v>169900</v>
+        <v>169650</v>
       </c>
       <c r="AB3" s="5">
         <f t="shared" ref="AB3:AB10" si="1">+AA3/2</f>
-        <v>84950</v>
+        <v>84825</v>
       </c>
       <c r="AC3" s="1">
         <v>10000</v>
       </c>
       <c r="AD3" s="5">
         <f t="shared" ref="AD3:AD10" si="2">+AE3-AB3-AC3</f>
-        <v>50</v>
+        <v>175</v>
       </c>
       <c r="AE3" s="1">
         <v>95000</v>
       </c>
       <c r="AF3" s="6">
         <f>AA3/2-L3</f>
-        <v>62750</v>
+        <v>62625</v>
       </c>
       <c r="AG3" s="7">
         <f t="shared" ref="AG3:AG10" si="3">AA3/2-D3</f>
-        <v>69450</v>
+        <v>69325</v>
       </c>
       <c r="AH3" s="8">
         <f t="shared" ref="AH3:AH10" si="4">AF3+AG3</f>
-        <v>132200</v>
+        <v>131950</v>
       </c>
     </row>
     <row r="4" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1144,40 +1150,41 @@
         <v>2000</v>
       </c>
       <c r="Y4" s="1">
-        <v>750</v>
+        <f>1350+2500</f>
+        <v>3850</v>
       </c>
       <c r="Z4" s="1">
         <v>4000</v>
       </c>
       <c r="AA4" s="1">
         <f t="shared" si="0"/>
-        <v>139000</v>
+        <v>142100</v>
       </c>
       <c r="AB4" s="5">
         <f t="shared" si="1"/>
-        <v>69500</v>
+        <v>71050</v>
       </c>
       <c r="AC4" s="1">
         <v>10000</v>
       </c>
       <c r="AD4" s="5">
         <f t="shared" si="2"/>
-        <v>15500</v>
+        <v>13950</v>
       </c>
       <c r="AE4" s="1">
         <v>95000</v>
       </c>
       <c r="AF4" s="6">
         <f t="shared" ref="AF4:AF10" si="5">AA4/2-L4</f>
-        <v>62000</v>
+        <v>63550</v>
       </c>
       <c r="AG4" s="7">
         <f t="shared" si="3"/>
-        <v>54000</v>
+        <v>55550</v>
       </c>
       <c r="AH4" s="8">
         <f t="shared" si="4"/>
-        <v>116000</v>
+        <v>119100</v>
       </c>
     </row>
     <row r="5" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1244,41 +1251,38 @@
       <c r="X5" s="1">
         <v>2000</v>
       </c>
-      <c r="Y5" s="1">
-        <v>750</v>
-      </c>
       <c r="Z5" s="1">
         <v>4000</v>
       </c>
       <c r="AA5" s="1">
         <f t="shared" si="0"/>
-        <v>134619</v>
+        <v>133869</v>
       </c>
       <c r="AB5" s="5">
         <f t="shared" si="1"/>
-        <v>67309.5</v>
+        <v>66934.5</v>
       </c>
       <c r="AC5" s="1">
         <v>10000</v>
       </c>
       <c r="AD5" s="5">
         <f t="shared" si="2"/>
-        <v>17690.5</v>
+        <v>18065.5</v>
       </c>
       <c r="AE5" s="1">
         <v>95000</v>
       </c>
       <c r="AF5" s="6">
         <f t="shared" si="5"/>
-        <v>59809.5</v>
+        <v>59434.5</v>
       </c>
       <c r="AG5" s="7">
         <f t="shared" si="3"/>
-        <v>51809.5</v>
+        <v>51434.5</v>
       </c>
       <c r="AH5" s="8">
         <f t="shared" si="4"/>
-        <v>111619</v>
+        <v>110869</v>
       </c>
     </row>
     <row r="6" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1339,41 +1343,38 @@
       <c r="X6" s="1">
         <v>2000</v>
       </c>
-      <c r="Y6" s="1">
-        <v>750</v>
-      </c>
       <c r="Z6" s="1">
         <v>4000</v>
       </c>
       <c r="AA6" s="1">
         <f t="shared" si="0"/>
-        <v>128750</v>
+        <v>128000</v>
       </c>
       <c r="AB6" s="5">
         <f t="shared" si="1"/>
-        <v>64375</v>
+        <v>64000</v>
       </c>
       <c r="AC6" s="1">
         <v>10000</v>
       </c>
       <c r="AD6" s="5">
         <f t="shared" si="2"/>
-        <v>20625</v>
+        <v>21000</v>
       </c>
       <c r="AE6" s="1">
         <v>95000</v>
       </c>
       <c r="AF6" s="6">
         <f t="shared" si="5"/>
-        <v>56875</v>
+        <v>56500</v>
       </c>
       <c r="AG6" s="7">
         <f t="shared" si="3"/>
-        <v>48875</v>
+        <v>48500</v>
       </c>
       <c r="AH6" s="8">
         <f t="shared" si="4"/>
-        <v>105750</v>
+        <v>105000</v>
       </c>
     </row>
     <row r="7" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1441,40 +1442,40 @@
         <v>2000</v>
       </c>
       <c r="Y7" s="1">
-        <v>750</v>
+        <v>1350</v>
       </c>
       <c r="Z7" s="1">
         <v>4000</v>
       </c>
       <c r="AA7" s="1">
         <f t="shared" si="0"/>
-        <v>158119</v>
+        <v>158719</v>
       </c>
       <c r="AB7" s="5">
         <f t="shared" si="1"/>
-        <v>79059.5</v>
+        <v>79359.5</v>
       </c>
       <c r="AC7" s="1">
         <v>10000</v>
       </c>
       <c r="AD7" s="5">
         <f t="shared" si="2"/>
-        <v>5940.5</v>
+        <v>5640.5</v>
       </c>
       <c r="AE7" s="1">
         <v>95000</v>
       </c>
       <c r="AF7" s="6">
         <f t="shared" si="5"/>
-        <v>71559.5</v>
+        <v>71859.5</v>
       </c>
       <c r="AG7" s="7">
         <f t="shared" si="3"/>
-        <v>63559.5</v>
+        <v>63859.5</v>
       </c>
       <c r="AH7" s="8">
         <f t="shared" si="4"/>
-        <v>135119</v>
+        <v>135719</v>
       </c>
     </row>
     <row r="8" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1541,41 +1542,38 @@
       <c r="X8" s="1">
         <v>2000</v>
       </c>
-      <c r="Y8" s="1">
-        <v>750</v>
-      </c>
       <c r="Z8" s="1">
         <v>4000</v>
       </c>
       <c r="AA8" s="1">
         <f t="shared" si="0"/>
-        <v>144050</v>
+        <v>143300</v>
       </c>
       <c r="AB8" s="5">
         <f t="shared" si="1"/>
-        <v>72025</v>
+        <v>71650</v>
       </c>
       <c r="AC8" s="1">
         <v>10000</v>
       </c>
       <c r="AD8" s="5">
         <f t="shared" si="2"/>
-        <v>12975</v>
+        <v>13350</v>
       </c>
       <c r="AE8" s="1">
         <v>95000</v>
       </c>
       <c r="AF8" s="6">
         <f t="shared" si="5"/>
-        <v>64525</v>
+        <v>64150</v>
       </c>
       <c r="AG8" s="7">
         <f t="shared" si="3"/>
-        <v>56525</v>
+        <v>56150</v>
       </c>
       <c r="AH8" s="8">
         <f t="shared" si="4"/>
-        <v>121050</v>
+        <v>120300</v>
       </c>
     </row>
     <row r="9" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1639,41 +1637,38 @@
       <c r="X9" s="1">
         <v>2000</v>
       </c>
-      <c r="Y9" s="1">
-        <v>750</v>
-      </c>
       <c r="Z9" s="1">
         <v>4000</v>
       </c>
       <c r="AA9" s="1">
         <f t="shared" si="0"/>
-        <v>134919</v>
+        <v>134169</v>
       </c>
       <c r="AB9" s="5">
         <f t="shared" si="1"/>
-        <v>67459.5</v>
+        <v>67084.5</v>
       </c>
       <c r="AC9" s="1">
         <v>10000</v>
       </c>
       <c r="AD9" s="5">
         <f t="shared" si="2"/>
-        <v>17540.5</v>
+        <v>17915.5</v>
       </c>
       <c r="AE9" s="1">
         <v>95000</v>
       </c>
       <c r="AF9" s="6">
         <f t="shared" si="5"/>
-        <v>59959.5</v>
+        <v>59584.5</v>
       </c>
       <c r="AG9" s="7">
         <f t="shared" si="3"/>
-        <v>51959.5</v>
+        <v>51584.5</v>
       </c>
       <c r="AH9" s="8">
         <f t="shared" si="4"/>
-        <v>111919</v>
+        <v>111169</v>
       </c>
     </row>
     <row r="10" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1735,40 +1730,40 @@
         <v>2000</v>
       </c>
       <c r="Y10" s="1">
-        <v>750</v>
+        <v>1350</v>
       </c>
       <c r="Z10" s="1">
         <v>4000</v>
       </c>
       <c r="AA10" s="1">
         <f t="shared" si="0"/>
-        <v>149450</v>
+        <v>150050</v>
       </c>
       <c r="AB10" s="5">
         <f t="shared" si="1"/>
-        <v>74725</v>
+        <v>75025</v>
       </c>
       <c r="AC10" s="1">
         <v>10000</v>
       </c>
       <c r="AD10" s="5">
         <f t="shared" si="2"/>
-        <v>10275</v>
+        <v>9975</v>
       </c>
       <c r="AE10" s="1">
         <v>95000</v>
       </c>
       <c r="AF10" s="6">
         <f t="shared" si="5"/>
-        <v>67225</v>
+        <v>67525</v>
       </c>
       <c r="AG10" s="7">
         <f t="shared" si="3"/>
-        <v>59225</v>
+        <v>59525</v>
       </c>
       <c r="AH10" s="8">
         <f t="shared" si="4"/>
-        <v>126450</v>
+        <v>127050</v>
       </c>
     </row>
     <row r="12" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1876,7 +1871,7 @@
         <v>24</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="Z13" s="1" t="s">
         <v>26</v>
@@ -1981,13 +1976,13 @@
         <f>IF(Mayo!X33&gt;0,Mayo!X33,"")</f>
         <v/>
       </c>
-      <c r="Y14" s="1" t="str">
+      <c r="Y14" s="1">
         <f>IF(Mayo!Y33&gt;0,Mayo!Y33,"")</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="Z14" s="1">
         <f>IF(Mayo!Z33&gt;0,Mayo!Z33,"")</f>
-        <v>4379.34</v>
+        <v>3879.3399999999997</v>
       </c>
       <c r="AA14" s="1">
         <f>IF(Mayo!AA33&gt;0,Mayo!AA33,"")</f>
@@ -2862,7 +2857,7 @@
         <v>24</v>
       </c>
       <c r="Y24" s="1" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="Z24" s="1" t="s">
         <v>26</v>
@@ -2967,17 +2962,17 @@
         <f>IF(ISNUMBER(Mayo!X33),X3-Mayo!X33,"")</f>
         <v/>
       </c>
-      <c r="Y25" s="1" t="str">
+      <c r="Y25" s="1">
         <f>IF(ISNUMBER(Mayo!Y33),Y3-Mayo!Y33,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Z25" s="1">
         <f>IF(ISNUMBER(Mayo!Z33),Z3-Mayo!Z33,"")</f>
-        <v>-379.34000000000015</v>
+        <v>120.66000000000031</v>
       </c>
       <c r="AA25" s="10">
         <f t="shared" ref="AA25:AA33" si="6">SUMIF(B25:Z25,"&lt;&gt;"&amp;"")</f>
-        <v>13405.759999999995</v>
+        <v>13905.759999999995</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3845,11 +3840,11 @@
       </c>
       <c r="Z33" s="10">
         <f t="shared" si="7"/>
-        <v>-379.34000000000015</v>
+        <v>120.66000000000031</v>
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="6"/>
-        <v>13405.759999999995</v>
+        <v>13905.759999999995</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
@@ -4064,7 +4059,7 @@
     <col min="21" max="22" width="13" customWidth="1"/>
     <col min="23" max="23" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="6.5703125" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="25" customWidth="1"/>
@@ -4144,7 +4139,7 @@
         <v>24</v>
       </c>
       <c r="Y1" s="12" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="Z1" s="12" t="s">
         <v>26</v>
@@ -5005,10 +5000,10 @@
       <c r="V22" s="14"/>
       <c r="W22" s="14"/>
       <c r="X22" s="14"/>
-      <c r="Y22" s="14"/>
-      <c r="Z22" s="14">
+      <c r="Y22" s="14">
         <v>500</v>
       </c>
+      <c r="Z22" s="14"/>
       <c r="AA22" s="14">
         <f t="shared" si="0"/>
         <v>23549.88</v>
@@ -5474,13 +5469,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y33" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="Y33" s="10">
+        <f t="shared" si="1"/>
+        <v>500</v>
       </c>
       <c r="Z33" s="10">
         <f t="shared" si="1"/>
-        <v>4379.34</v>
+        <v>3879.3399999999997</v>
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="1"/>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BBACBFF-BA33-4D10-8D75-BC4861ED8D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCE24E6B-B628-4219-9A62-AD7D332AA049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="69">
   <si>
     <t>Presupuesto</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t>Gas y calefacción</t>
+  </si>
+  <si>
+    <t>China City</t>
   </si>
 </sst>
 </file>
@@ -1055,37 +1058,37 @@
         <v>500</v>
       </c>
       <c r="Z3" s="1">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="AA3" s="1">
         <f t="shared" ref="AA3:AA10" si="0">SUM(B3:Z3)</f>
-        <v>169650</v>
+        <v>170650</v>
       </c>
       <c r="AB3" s="5">
         <f t="shared" ref="AB3:AB10" si="1">+AA3/2</f>
-        <v>84825</v>
+        <v>85325</v>
       </c>
       <c r="AC3" s="1">
         <v>10000</v>
       </c>
       <c r="AD3" s="5">
         <f t="shared" ref="AD3:AD10" si="2">+AE3-AB3-AC3</f>
-        <v>175</v>
+        <v>-325</v>
       </c>
       <c r="AE3" s="1">
         <v>95000</v>
       </c>
       <c r="AF3" s="6">
         <f>AA3/2-L3</f>
-        <v>62625</v>
+        <v>63125</v>
       </c>
       <c r="AG3" s="7">
         <f t="shared" ref="AG3:AG10" si="3">AA3/2-D3</f>
-        <v>69325</v>
+        <v>69825</v>
       </c>
       <c r="AH3" s="8">
         <f t="shared" ref="AH3:AH10" si="4">AF3+AG3</f>
-        <v>131950</v>
+        <v>132950</v>
       </c>
     </row>
     <row r="4" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1154,37 +1157,37 @@
         <v>3850</v>
       </c>
       <c r="Z4" s="1">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="AA4" s="1">
         <f t="shared" si="0"/>
-        <v>142100</v>
+        <v>143100</v>
       </c>
       <c r="AB4" s="5">
         <f t="shared" si="1"/>
-        <v>71050</v>
+        <v>71550</v>
       </c>
       <c r="AC4" s="1">
         <v>10000</v>
       </c>
       <c r="AD4" s="5">
         <f t="shared" si="2"/>
-        <v>13950</v>
+        <v>13450</v>
       </c>
       <c r="AE4" s="1">
         <v>95000</v>
       </c>
       <c r="AF4" s="6">
         <f t="shared" ref="AF4:AF10" si="5">AA4/2-L4</f>
-        <v>63550</v>
+        <v>64050</v>
       </c>
       <c r="AG4" s="7">
         <f t="shared" si="3"/>
-        <v>55550</v>
+        <v>56050</v>
       </c>
       <c r="AH4" s="8">
         <f t="shared" si="4"/>
-        <v>119100</v>
+        <v>120100</v>
       </c>
     </row>
     <row r="5" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1252,37 +1255,37 @@
         <v>2000</v>
       </c>
       <c r="Z5" s="1">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="AA5" s="1">
         <f t="shared" si="0"/>
-        <v>133869</v>
+        <v>134869</v>
       </c>
       <c r="AB5" s="5">
         <f t="shared" si="1"/>
-        <v>66934.5</v>
+        <v>67434.5</v>
       </c>
       <c r="AC5" s="1">
         <v>10000</v>
       </c>
       <c r="AD5" s="5">
         <f t="shared" si="2"/>
-        <v>18065.5</v>
+        <v>17565.5</v>
       </c>
       <c r="AE5" s="1">
         <v>95000</v>
       </c>
       <c r="AF5" s="6">
         <f t="shared" si="5"/>
-        <v>59434.5</v>
+        <v>59934.5</v>
       </c>
       <c r="AG5" s="7">
         <f t="shared" si="3"/>
-        <v>51434.5</v>
+        <v>51934.5</v>
       </c>
       <c r="AH5" s="8">
         <f t="shared" si="4"/>
-        <v>110869</v>
+        <v>111869</v>
       </c>
     </row>
     <row r="6" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1344,37 +1347,37 @@
         <v>2000</v>
       </c>
       <c r="Z6" s="1">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="AA6" s="1">
         <f t="shared" si="0"/>
-        <v>128000</v>
+        <v>129000</v>
       </c>
       <c r="AB6" s="5">
         <f t="shared" si="1"/>
-        <v>64000</v>
+        <v>64500</v>
       </c>
       <c r="AC6" s="1">
         <v>10000</v>
       </c>
       <c r="AD6" s="5">
         <f t="shared" si="2"/>
-        <v>21000</v>
+        <v>20500</v>
       </c>
       <c r="AE6" s="1">
         <v>95000</v>
       </c>
       <c r="AF6" s="6">
         <f t="shared" si="5"/>
-        <v>56500</v>
+        <v>57000</v>
       </c>
       <c r="AG6" s="7">
         <f t="shared" si="3"/>
-        <v>48500</v>
+        <v>49000</v>
       </c>
       <c r="AH6" s="8">
         <f t="shared" si="4"/>
-        <v>105000</v>
+        <v>106000</v>
       </c>
     </row>
     <row r="7" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1445,37 +1448,37 @@
         <v>1350</v>
       </c>
       <c r="Z7" s="1">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="AA7" s="1">
         <f t="shared" si="0"/>
-        <v>158719</v>
+        <v>159719</v>
       </c>
       <c r="AB7" s="5">
         <f t="shared" si="1"/>
-        <v>79359.5</v>
+        <v>79859.5</v>
       </c>
       <c r="AC7" s="1">
         <v>10000</v>
       </c>
       <c r="AD7" s="5">
         <f t="shared" si="2"/>
-        <v>5640.5</v>
+        <v>5140.5</v>
       </c>
       <c r="AE7" s="1">
         <v>95000</v>
       </c>
       <c r="AF7" s="6">
         <f t="shared" si="5"/>
-        <v>71859.5</v>
+        <v>72359.5</v>
       </c>
       <c r="AG7" s="7">
         <f t="shared" si="3"/>
-        <v>63859.5</v>
+        <v>64359.5</v>
       </c>
       <c r="AH7" s="8">
         <f t="shared" si="4"/>
-        <v>135719</v>
+        <v>136719</v>
       </c>
     </row>
     <row r="8" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1543,37 +1546,37 @@
         <v>2000</v>
       </c>
       <c r="Z8" s="1">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="AA8" s="1">
         <f t="shared" si="0"/>
-        <v>143300</v>
+        <v>144300</v>
       </c>
       <c r="AB8" s="5">
         <f t="shared" si="1"/>
-        <v>71650</v>
+        <v>72150</v>
       </c>
       <c r="AC8" s="1">
         <v>10000</v>
       </c>
       <c r="AD8" s="5">
         <f t="shared" si="2"/>
-        <v>13350</v>
+        <v>12850</v>
       </c>
       <c r="AE8" s="1">
         <v>95000</v>
       </c>
       <c r="AF8" s="6">
         <f t="shared" si="5"/>
-        <v>64150</v>
+        <v>64650</v>
       </c>
       <c r="AG8" s="7">
         <f t="shared" si="3"/>
-        <v>56150</v>
+        <v>56650</v>
       </c>
       <c r="AH8" s="8">
         <f t="shared" si="4"/>
-        <v>120300</v>
+        <v>121300</v>
       </c>
     </row>
     <row r="9" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1638,37 +1641,37 @@
         <v>2000</v>
       </c>
       <c r="Z9" s="1">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="AA9" s="1">
         <f t="shared" si="0"/>
-        <v>134169</v>
+        <v>135169</v>
       </c>
       <c r="AB9" s="5">
         <f t="shared" si="1"/>
-        <v>67084.5</v>
+        <v>67584.5</v>
       </c>
       <c r="AC9" s="1">
         <v>10000</v>
       </c>
       <c r="AD9" s="5">
         <f t="shared" si="2"/>
-        <v>17915.5</v>
+        <v>17415.5</v>
       </c>
       <c r="AE9" s="1">
         <v>95000</v>
       </c>
       <c r="AF9" s="6">
         <f t="shared" si="5"/>
-        <v>59584.5</v>
+        <v>60084.5</v>
       </c>
       <c r="AG9" s="7">
         <f t="shared" si="3"/>
-        <v>51584.5</v>
+        <v>52084.5</v>
       </c>
       <c r="AH9" s="8">
         <f t="shared" si="4"/>
-        <v>111169</v>
+        <v>112169</v>
       </c>
     </row>
     <row r="10" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1733,37 +1736,37 @@
         <v>1350</v>
       </c>
       <c r="Z10" s="1">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="AA10" s="1">
         <f t="shared" si="0"/>
-        <v>150050</v>
+        <v>151050</v>
       </c>
       <c r="AB10" s="5">
         <f t="shared" si="1"/>
-        <v>75025</v>
+        <v>75525</v>
       </c>
       <c r="AC10" s="1">
         <v>10000</v>
       </c>
       <c r="AD10" s="5">
         <f t="shared" si="2"/>
-        <v>9975</v>
+        <v>9475</v>
       </c>
       <c r="AE10" s="1">
         <v>95000</v>
       </c>
       <c r="AF10" s="6">
         <f t="shared" si="5"/>
-        <v>67525</v>
+        <v>68025</v>
       </c>
       <c r="AG10" s="7">
         <f t="shared" si="3"/>
-        <v>59525</v>
+        <v>60025</v>
       </c>
       <c r="AH10" s="8">
         <f t="shared" si="4"/>
-        <v>127050</v>
+        <v>128050</v>
       </c>
     </row>
     <row r="12" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1946,7 +1949,7 @@
       </c>
       <c r="Q14" s="1">
         <f>IF(Mayo!Q33&gt;0,Mayo!Q33,"")</f>
-        <v>14436.940000000002</v>
+        <v>15286.480000000003</v>
       </c>
       <c r="R14" s="1" t="str">
         <f>IF(Mayo!R33&gt;0,Mayo!R33,"")</f>
@@ -1966,7 +1969,7 @@
       </c>
       <c r="V14" s="1">
         <f>IF(Mayo!V33&gt;0,Mayo!V33,"")</f>
-        <v>285.25</v>
+        <v>1268.8600000000001</v>
       </c>
       <c r="W14" s="1">
         <f>IF(Mayo!W33&gt;0,Mayo!W33,"")</f>
@@ -1982,11 +1985,11 @@
       </c>
       <c r="Z14" s="1">
         <f>IF(Mayo!Z33&gt;0,Mayo!Z33,"")</f>
-        <v>3879.3399999999997</v>
+        <v>4705.57</v>
       </c>
       <c r="AA14" s="1">
         <f>IF(Mayo!AA33&gt;0,Mayo!AA33,"")</f>
-        <v>149444.24</v>
+        <v>152103.62</v>
       </c>
     </row>
     <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2922,9 +2925,9 @@
         <f>IF(ISNUMBER(Mayo!N33),N3-Mayo!N33,"")</f>
         <v>674.59000000000015</v>
       </c>
-      <c r="O25" s="1" t="str">
+      <c r="O25" s="1">
         <f>IF(ISNUMBER(Mayo!O33),O3-Mayo!O33,"")</f>
-        <v/>
+        <v>1800</v>
       </c>
       <c r="P25" s="1">
         <f>IF(ISNUMBER(Mayo!P33),P3-Mayo!P33,"")</f>
@@ -2932,7 +2935,7 @@
       </c>
       <c r="Q25" s="1">
         <f>IF(ISNUMBER(Mayo!Q33),Q3-Mayo!Q33,"")</f>
-        <v>5563.0599999999977</v>
+        <v>4713.5199999999968</v>
       </c>
       <c r="R25" s="1" t="str">
         <f>IF(ISNUMBER(Mayo!R33),R3-Mayo!R33,"")</f>
@@ -2952,7 +2955,7 @@
       </c>
       <c r="V25" s="1">
         <f>IF(ISNUMBER(Mayo!V33),V3-Mayo!V33,"")</f>
-        <v>2714.75</v>
+        <v>1731.1399999999999</v>
       </c>
       <c r="W25" s="1">
         <f>IF(ISNUMBER(Mayo!W33),W3-Mayo!W33,"")</f>
@@ -2968,11 +2971,11 @@
       </c>
       <c r="Z25" s="1">
         <f>IF(ISNUMBER(Mayo!Z33),Z3-Mayo!Z33,"")</f>
-        <v>120.66000000000031</v>
+        <v>294.43000000000029</v>
       </c>
       <c r="AA25" s="10">
         <f t="shared" ref="AA25:AA33" si="6">SUMIF(B25:Z25,"&lt;&gt;"&amp;"")</f>
-        <v>13905.759999999995</v>
+        <v>14046.379999999994</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3796,7 +3799,7 @@
       </c>
       <c r="O33" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="P33" s="10">
         <f t="shared" si="7"/>
@@ -3804,7 +3807,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="7"/>
-        <v>5563.0599999999977</v>
+        <v>4713.5199999999968</v>
       </c>
       <c r="R33" s="10">
         <f t="shared" si="7"/>
@@ -3824,7 +3827,7 @@
       </c>
       <c r="V33" s="10">
         <f t="shared" si="7"/>
-        <v>2714.75</v>
+        <v>1731.1399999999999</v>
       </c>
       <c r="W33" s="10">
         <f t="shared" si="7"/>
@@ -3840,11 +3843,11 @@
       </c>
       <c r="Z33" s="10">
         <f t="shared" si="7"/>
-        <v>120.66000000000031</v>
+        <v>294.43000000000029</v>
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="6"/>
-        <v>13905.759999999995</v>
+        <v>14046.379999999994</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
@@ -5106,21 +5109,32 @@
       <c r="N25" s="14"/>
       <c r="O25" s="14"/>
       <c r="P25" s="14"/>
-      <c r="Q25" s="14"/>
+      <c r="Q25" s="14">
+        <f>862-12.46</f>
+        <v>849.54</v>
+      </c>
       <c r="R25" s="14"/>
       <c r="S25" s="14"/>
       <c r="T25" s="14"/>
       <c r="U25" s="14"/>
-      <c r="V25" s="14"/>
+      <c r="V25" s="14">
+        <f>1000-16.39</f>
+        <v>983.61</v>
+      </c>
       <c r="W25" s="14"/>
       <c r="X25" s="14"/>
       <c r="Y25" s="14"/>
-      <c r="Z25" s="14"/>
+      <c r="Z25" s="14">
+        <f>840-13.77</f>
+        <v>826.23</v>
+      </c>
       <c r="AA25" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AB25" s="14"/>
+        <v>2659.38</v>
+      </c>
+      <c r="AB25" s="14" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="26" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13">
@@ -5353,7 +5367,9 @@
       <c r="L32" s="14"/>
       <c r="M32" s="14"/>
       <c r="N32" s="14"/>
-      <c r="O32" s="14"/>
+      <c r="O32" s="14">
+        <v>0</v>
+      </c>
       <c r="P32" s="14"/>
       <c r="Q32" s="14"/>
       <c r="R32" s="14"/>
@@ -5429,9 +5445,9 @@
         <f t="shared" si="1"/>
         <v>9325.41</v>
       </c>
-      <c r="O33" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="O33" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="P33" s="10">
         <f t="shared" si="1"/>
@@ -5439,7 +5455,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="1"/>
-        <v>14436.940000000002</v>
+        <v>15286.480000000003</v>
       </c>
       <c r="R33" s="10" t="str">
         <f t="shared" si="1"/>
@@ -5459,7 +5475,7 @@
       </c>
       <c r="V33" s="10">
         <f t="shared" si="1"/>
-        <v>285.25</v>
+        <v>1268.8600000000001</v>
       </c>
       <c r="W33" s="10">
         <f t="shared" si="1"/>
@@ -5475,11 +5491,11 @@
       </c>
       <c r="Z33" s="10">
         <f t="shared" si="1"/>
-        <v>3879.3399999999997</v>
+        <v>4705.57</v>
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="1"/>
-        <v>149444.24</v>
+        <v>152103.62</v>
       </c>
       <c r="AB33" s="15"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCE24E6B-B628-4219-9A62-AD7D332AA049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C137722-6467-465E-9124-C7F521CE8A47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="Q14" s="1">
         <f>IF(Mayo!Q33&gt;0,Mayo!Q33,"")</f>
-        <v>15286.480000000003</v>
+        <v>15752.710000000003</v>
       </c>
       <c r="R14" s="1" t="str">
         <f>IF(Mayo!R33&gt;0,Mayo!R33,"")</f>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="AA14" s="1">
         <f>IF(Mayo!AA33&gt;0,Mayo!AA33,"")</f>
-        <v>152103.62</v>
+        <v>152569.84999999998</v>
       </c>
     </row>
     <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="Q25" s="1">
         <f>IF(ISNUMBER(Mayo!Q33),Q3-Mayo!Q33,"")</f>
-        <v>4713.5199999999968</v>
+        <v>4247.2899999999972</v>
       </c>
       <c r="R25" s="1" t="str">
         <f>IF(ISNUMBER(Mayo!R33),R3-Mayo!R33,"")</f>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="AA25" s="10">
         <f t="shared" ref="AA25:AA33" si="6">SUMIF(B25:Z25,"&lt;&gt;"&amp;"")</f>
-        <v>14046.379999999994</v>
+        <v>13580.149999999994</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="7"/>
-        <v>4713.5199999999968</v>
+        <v>4247.2899999999972</v>
       </c>
       <c r="R33" s="10">
         <f t="shared" si="7"/>
@@ -3847,7 +3847,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="6"/>
-        <v>14046.379999999994</v>
+        <v>13580.149999999994</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
@@ -5110,8 +5110,8 @@
       <c r="O25" s="14"/>
       <c r="P25" s="14"/>
       <c r="Q25" s="14">
-        <f>862-12.46</f>
-        <v>849.54</v>
+        <f>862-12.46+474-7.77</f>
+        <v>1315.77</v>
       </c>
       <c r="R25" s="14"/>
       <c r="S25" s="14"/>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AA25" s="14">
         <f t="shared" si="0"/>
-        <v>2659.38</v>
+        <v>3125.61</v>
       </c>
       <c r="AB25" s="14" t="s">
         <v>68</v>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="1"/>
-        <v>15286.480000000003</v>
+        <v>15752.710000000003</v>
       </c>
       <c r="R33" s="10" t="str">
         <f t="shared" si="1"/>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="1"/>
-        <v>152103.62</v>
+        <v>152569.84999999998</v>
       </c>
       <c r="AB33" s="15"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C137722-6467-465E-9124-C7F521CE8A47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD88361-6BA3-4D1B-B8C4-78FA7D7DF7F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="N14" s="1">
         <f>IF(Mayo!N33&gt;0,Mayo!N33,"")</f>
-        <v>9325.41</v>
+        <v>8780.76</v>
       </c>
       <c r="O14" s="1" t="str">
         <f>IF(Mayo!O33&gt;0,Mayo!O33,"")</f>
@@ -1949,11 +1949,11 @@
       </c>
       <c r="Q14" s="1">
         <f>IF(Mayo!Q33&gt;0,Mayo!Q33,"")</f>
-        <v>15752.710000000003</v>
-      </c>
-      <c r="R14" s="1" t="str">
+        <v>16345.570000000003</v>
+      </c>
+      <c r="R14" s="1">
         <f>IF(Mayo!R33&gt;0,Mayo!R33,"")</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="S14" s="1">
         <f>IF(Mayo!S33&gt;0,Mayo!S33,"")</f>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="AA14" s="1">
         <f>IF(Mayo!AA33&gt;0,Mayo!AA33,"")</f>
-        <v>152569.84999999998</v>
+        <v>152768.05999999997</v>
       </c>
     </row>
     <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="N25" s="1">
         <f>IF(ISNUMBER(Mayo!N33),N3-Mayo!N33,"")</f>
-        <v>674.59000000000015</v>
+        <v>1219.2399999999998</v>
       </c>
       <c r="O25" s="1">
         <f>IF(ISNUMBER(Mayo!O33),O3-Mayo!O33,"")</f>
@@ -2935,11 +2935,11 @@
       </c>
       <c r="Q25" s="1">
         <f>IF(ISNUMBER(Mayo!Q33),Q3-Mayo!Q33,"")</f>
-        <v>4247.2899999999972</v>
-      </c>
-      <c r="R25" s="1" t="str">
+        <v>3654.4299999999967</v>
+      </c>
+      <c r="R25" s="1">
         <f>IF(ISNUMBER(Mayo!R33),R3-Mayo!R33,"")</f>
-        <v/>
+        <v>2350</v>
       </c>
       <c r="S25" s="1">
         <f>IF(ISNUMBER(Mayo!S33),S3-Mayo!S33,"")</f>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="AA25" s="10">
         <f t="shared" ref="AA25:AA33" si="6">SUMIF(B25:Z25,"&lt;&gt;"&amp;"")</f>
-        <v>13580.149999999994</v>
+        <v>15881.939999999993</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="N33" s="10">
         <f t="shared" si="7"/>
-        <v>674.59000000000015</v>
+        <v>1219.2399999999998</v>
       </c>
       <c r="O33" s="10">
         <f t="shared" si="7"/>
@@ -3807,11 +3807,11 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="7"/>
-        <v>4247.2899999999972</v>
+        <v>3654.4299999999967</v>
       </c>
       <c r="R33" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2350</v>
       </c>
       <c r="S33" s="10">
         <f t="shared" si="7"/>
@@ -3847,7 +3847,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="6"/>
-        <v>13580.149999999994</v>
+        <v>15881.939999999993</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
@@ -5106,7 +5106,9 @@
       <c r="K25" s="14"/>
       <c r="L25" s="14"/>
       <c r="M25" s="14"/>
-      <c r="N25" s="14"/>
+      <c r="N25" s="14">
+        <v>-544.65</v>
+      </c>
       <c r="O25" s="14"/>
       <c r="P25" s="14"/>
       <c r="Q25" s="14">
@@ -5130,7 +5132,7 @@
       </c>
       <c r="AA25" s="14">
         <f t="shared" si="0"/>
-        <v>3125.61</v>
+        <v>2580.96</v>
       </c>
       <c r="AB25" s="14" t="s">
         <v>68</v>
@@ -5155,8 +5157,13 @@
       <c r="N26" s="14"/>
       <c r="O26" s="14"/>
       <c r="P26" s="14"/>
-      <c r="Q26" s="14"/>
-      <c r="R26" s="14"/>
+      <c r="Q26" s="14">
+        <f>606-13.14</f>
+        <v>592.86</v>
+      </c>
+      <c r="R26" s="14">
+        <v>150</v>
+      </c>
       <c r="S26" s="14"/>
       <c r="T26" s="14"/>
       <c r="U26" s="14"/>
@@ -5167,7 +5174,7 @@
       <c r="Z26" s="14"/>
       <c r="AA26" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>742.86</v>
       </c>
       <c r="AB26" s="14"/>
     </row>
@@ -5443,7 +5450,7 @@
       </c>
       <c r="N33" s="10">
         <f t="shared" si="1"/>
-        <v>9325.41</v>
+        <v>8780.76</v>
       </c>
       <c r="O33" s="10">
         <f t="shared" si="1"/>
@@ -5455,11 +5462,11 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="1"/>
-        <v>15752.710000000003</v>
-      </c>
-      <c r="R33" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+        <v>16345.570000000003</v>
+      </c>
+      <c r="R33" s="10">
+        <f t="shared" si="1"/>
+        <v>150</v>
       </c>
       <c r="S33" s="10">
         <f t="shared" si="1"/>
@@ -5495,7 +5502,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="1"/>
-        <v>152569.84999999998</v>
+        <v>152768.05999999997</v>
       </c>
       <c r="AB33" s="15"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD88361-6BA3-4D1B-B8C4-78FA7D7DF7F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6189D5F9-67AE-42C8-BABD-1145665BED0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="70">
   <si>
     <t>Presupuesto</t>
   </si>
@@ -251,6 +251,9 @@
   </si>
   <si>
     <t>China City</t>
+  </si>
+  <si>
+    <t>Pantalones Roci</t>
   </si>
 </sst>
 </file>
@@ -1949,7 +1952,7 @@
       </c>
       <c r="Q14" s="1">
         <f>IF(Mayo!Q33&gt;0,Mayo!Q33,"")</f>
-        <v>16345.570000000003</v>
+        <v>17091.590000000004</v>
       </c>
       <c r="R14" s="1">
         <f>IF(Mayo!R33&gt;0,Mayo!R33,"")</f>
@@ -1975,9 +1978,9 @@
         <f>IF(Mayo!W33&gt;0,Mayo!W33,"")</f>
         <v>709.08999999999992</v>
       </c>
-      <c r="X14" s="1" t="str">
+      <c r="X14" s="1">
         <f>IF(Mayo!X33&gt;0,Mayo!X33,"")</f>
-        <v/>
+        <v>1780.33</v>
       </c>
       <c r="Y14" s="1">
         <f>IF(Mayo!Y33&gt;0,Mayo!Y33,"")</f>
@@ -1989,7 +1992,7 @@
       </c>
       <c r="AA14" s="1">
         <f>IF(Mayo!AA33&gt;0,Mayo!AA33,"")</f>
-        <v>152768.05999999997</v>
+        <v>155294.40999999997</v>
       </c>
     </row>
     <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2935,7 +2938,7 @@
       </c>
       <c r="Q25" s="1">
         <f>IF(ISNUMBER(Mayo!Q33),Q3-Mayo!Q33,"")</f>
-        <v>3654.4299999999967</v>
+        <v>2908.4099999999962</v>
       </c>
       <c r="R25" s="1">
         <f>IF(ISNUMBER(Mayo!R33),R3-Mayo!R33,"")</f>
@@ -2961,9 +2964,9 @@
         <f>IF(ISNUMBER(Mayo!W33),W3-Mayo!W33,"")</f>
         <v>790.91000000000008</v>
       </c>
-      <c r="X25" s="1" t="str">
+      <c r="X25" s="1">
         <f>IF(ISNUMBER(Mayo!X33),X3-Mayo!X33,"")</f>
-        <v/>
+        <v>219.67000000000007</v>
       </c>
       <c r="Y25" s="1">
         <f>IF(ISNUMBER(Mayo!Y33),Y3-Mayo!Y33,"")</f>
@@ -2975,7 +2978,7 @@
       </c>
       <c r="AA25" s="10">
         <f t="shared" ref="AA25:AA33" si="6">SUMIF(B25:Z25,"&lt;&gt;"&amp;"")</f>
-        <v>15881.939999999993</v>
+        <v>15355.589999999993</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3807,7 +3810,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="7"/>
-        <v>3654.4299999999967</v>
+        <v>2908.4099999999962</v>
       </c>
       <c r="R33" s="10">
         <f t="shared" si="7"/>
@@ -3835,7 +3838,7 @@
       </c>
       <c r="X33" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>219.67000000000007</v>
       </c>
       <c r="Y33" s="10">
         <f t="shared" si="7"/>
@@ -3847,7 +3850,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="6"/>
-        <v>15881.939999999993</v>
+        <v>15355.589999999993</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
@@ -5197,21 +5200,29 @@
       <c r="N27" s="14"/>
       <c r="O27" s="14"/>
       <c r="P27" s="14"/>
-      <c r="Q27" s="14"/>
+      <c r="Q27" s="14">
+        <f>759-12.98</f>
+        <v>746.02</v>
+      </c>
       <c r="R27" s="14"/>
       <c r="S27" s="14"/>
       <c r="T27" s="14"/>
       <c r="U27" s="14"/>
       <c r="V27" s="14"/>
       <c r="W27" s="14"/>
-      <c r="X27" s="14"/>
+      <c r="X27" s="14">
+        <f>1810-29.67</f>
+        <v>1780.33</v>
+      </c>
       <c r="Y27" s="14"/>
       <c r="Z27" s="14"/>
       <c r="AA27" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AB27" s="14"/>
+        <v>2526.35</v>
+      </c>
+      <c r="AB27" s="14" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="28" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="13">
@@ -5462,7 +5473,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="1"/>
-        <v>16345.570000000003</v>
+        <v>17091.590000000004</v>
       </c>
       <c r="R33" s="10">
         <f t="shared" si="1"/>
@@ -5488,9 +5499,9 @@
         <f t="shared" si="1"/>
         <v>709.08999999999992</v>
       </c>
-      <c r="X33" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="X33" s="10">
+        <f t="shared" si="1"/>
+        <v>1780.33</v>
       </c>
       <c r="Y33" s="10">
         <f t="shared" si="1"/>
@@ -5502,7 +5513,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="1"/>
-        <v>152768.05999999997</v>
+        <v>155294.40999999997</v>
       </c>
       <c r="AB33" s="15"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6189D5F9-67AE-42C8-BABD-1145665BED0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14DF5E8-849D-49C0-B108-B62DD8C9D7DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="Q14" s="1">
         <f>IF(Mayo!Q33&gt;0,Mayo!Q33,"")</f>
-        <v>17091.590000000004</v>
+        <v>17742.730000000003</v>
       </c>
       <c r="R14" s="1">
         <f>IF(Mayo!R33&gt;0,Mayo!R33,"")</f>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AA14" s="1">
         <f>IF(Mayo!AA33&gt;0,Mayo!AA33,"")</f>
-        <v>155294.40999999997</v>
+        <v>155945.54999999999</v>
       </c>
     </row>
     <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="Q25" s="1">
         <f>IF(ISNUMBER(Mayo!Q33),Q3-Mayo!Q33,"")</f>
-        <v>2908.4099999999962</v>
+        <v>2257.2699999999968</v>
       </c>
       <c r="R25" s="1">
         <f>IF(ISNUMBER(Mayo!R33),R3-Mayo!R33,"")</f>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="AA25" s="10">
         <f t="shared" ref="AA25:AA33" si="6">SUMIF(B25:Z25,"&lt;&gt;"&amp;"")</f>
-        <v>15355.589999999993</v>
+        <v>14704.449999999993</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="7"/>
-        <v>2908.4099999999962</v>
+        <v>2257.2699999999968</v>
       </c>
       <c r="R33" s="10">
         <f t="shared" si="7"/>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="6"/>
-        <v>15355.589999999993</v>
+        <v>14704.449999999993</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
@@ -5243,7 +5243,10 @@
       <c r="N28" s="14"/>
       <c r="O28" s="14"/>
       <c r="P28" s="14"/>
-      <c r="Q28" s="14"/>
+      <c r="Q28" s="14">
+        <f>662-10.86</f>
+        <v>651.14</v>
+      </c>
       <c r="R28" s="14"/>
       <c r="S28" s="14"/>
       <c r="T28" s="14"/>
@@ -5255,7 +5258,7 @@
       <c r="Z28" s="14"/>
       <c r="AA28" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>651.14</v>
       </c>
       <c r="AB28" s="14"/>
     </row>
@@ -5473,7 +5476,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="1"/>
-        <v>17091.590000000004</v>
+        <v>17742.730000000003</v>
       </c>
       <c r="R33" s="10">
         <f t="shared" si="1"/>
@@ -5513,7 +5516,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="1"/>
-        <v>155294.40999999997</v>
+        <v>155945.54999999999</v>
       </c>
       <c r="AB33" s="15"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14DF5E8-849D-49C0-B108-B62DD8C9D7DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFBC3B49-17D0-4BC9-A938-1EEDA46E02EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="Q14" s="1">
         <f>IF(Mayo!Q33&gt;0,Mayo!Q33,"")</f>
-        <v>17742.730000000003</v>
+        <v>19619.210000000003</v>
       </c>
       <c r="R14" s="1">
         <f>IF(Mayo!R33&gt;0,Mayo!R33,"")</f>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AA14" s="1">
         <f>IF(Mayo!AA33&gt;0,Mayo!AA33,"")</f>
-        <v>155945.54999999999</v>
+        <v>157822.02999999997</v>
       </c>
     </row>
     <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="Q25" s="1">
         <f>IF(ISNUMBER(Mayo!Q33),Q3-Mayo!Q33,"")</f>
-        <v>2257.2699999999968</v>
+        <v>380.78999999999724</v>
       </c>
       <c r="R25" s="1">
         <f>IF(ISNUMBER(Mayo!R33),R3-Mayo!R33,"")</f>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="AA25" s="10">
         <f t="shared" ref="AA25:AA33" si="6">SUMIF(B25:Z25,"&lt;&gt;"&amp;"")</f>
-        <v>14704.449999999993</v>
+        <v>12827.969999999994</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="7"/>
-        <v>2257.2699999999968</v>
+        <v>380.78999999999724</v>
       </c>
       <c r="R33" s="10">
         <f t="shared" si="7"/>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="6"/>
-        <v>14704.449999999993</v>
+        <v>12827.969999999994</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
@@ -5281,7 +5281,10 @@
       <c r="N29" s="14"/>
       <c r="O29" s="14"/>
       <c r="P29" s="14"/>
-      <c r="Q29" s="14"/>
+      <c r="Q29" s="14">
+        <f>444-6.38+248-4.07</f>
+        <v>681.55</v>
+      </c>
       <c r="R29" s="14"/>
       <c r="S29" s="14"/>
       <c r="T29" s="14"/>
@@ -5293,7 +5296,7 @@
       <c r="Z29" s="14"/>
       <c r="AA29" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>681.55</v>
       </c>
       <c r="AB29" s="14"/>
     </row>
@@ -5316,7 +5319,10 @@
       <c r="N30" s="14"/>
       <c r="O30" s="14"/>
       <c r="P30" s="14"/>
-      <c r="Q30" s="14"/>
+      <c r="Q30" s="14">
+        <f>671.07-12.2+545-8.94</f>
+        <v>1194.9299999999998</v>
+      </c>
       <c r="R30" s="14"/>
       <c r="S30" s="14"/>
       <c r="T30" s="14"/>
@@ -5328,7 +5334,7 @@
       <c r="Z30" s="14"/>
       <c r="AA30" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1194.9299999999998</v>
       </c>
       <c r="AB30" s="14"/>
     </row>
@@ -5476,7 +5482,7 @@
       </c>
       <c r="Q33" s="10">
         <f t="shared" si="1"/>
-        <v>17742.730000000003</v>
+        <v>19619.210000000003</v>
       </c>
       <c r="R33" s="10">
         <f t="shared" si="1"/>
@@ -5516,7 +5522,7 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="1"/>
-        <v>155945.54999999999</v>
+        <v>157822.02999999997</v>
       </c>
       <c r="AB33" s="15"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFBC3B49-17D0-4BC9-A938-1EEDA46E02EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73DD0E1A-12CF-4B47-A791-AB611CF76D59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1120,10 +1120,10 @@
         <v>1000</v>
       </c>
       <c r="K4" s="1">
-        <v>7500</v>
+        <v>10000</v>
       </c>
       <c r="L4" s="1">
-        <v>7500</v>
+        <v>8000</v>
       </c>
       <c r="M4" s="1">
         <v>850</v>
@@ -1164,33 +1164,33 @@
       </c>
       <c r="AA4" s="1">
         <f t="shared" si="0"/>
-        <v>143100</v>
+        <v>146100</v>
       </c>
       <c r="AB4" s="5">
         <f t="shared" si="1"/>
-        <v>71550</v>
+        <v>73050</v>
       </c>
       <c r="AC4" s="1">
         <v>10000</v>
       </c>
       <c r="AD4" s="5">
         <f t="shared" si="2"/>
-        <v>13450</v>
+        <v>11950</v>
       </c>
       <c r="AE4" s="1">
         <v>95000</v>
       </c>
       <c r="AF4" s="6">
         <f t="shared" ref="AF4:AF10" si="5">AA4/2-L4</f>
-        <v>64050</v>
+        <v>65050</v>
       </c>
       <c r="AG4" s="7">
         <f t="shared" si="3"/>
-        <v>56050</v>
+        <v>57550</v>
       </c>
       <c r="AH4" s="8">
         <f t="shared" si="4"/>
-        <v>120100</v>
+        <v>122600</v>
       </c>
     </row>
     <row r="5" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1227,6 +1227,9 @@
       <c r="L5" s="1">
         <v>7500</v>
       </c>
+      <c r="M5" s="1">
+        <v>850</v>
+      </c>
       <c r="N5" s="1">
         <v>10000</v>
       </c>
@@ -1262,33 +1265,33 @@
       </c>
       <c r="AA5" s="1">
         <f t="shared" si="0"/>
-        <v>134869</v>
+        <v>135719</v>
       </c>
       <c r="AB5" s="5">
         <f t="shared" si="1"/>
-        <v>67434.5</v>
+        <v>67859.5</v>
       </c>
       <c r="AC5" s="1">
         <v>10000</v>
       </c>
       <c r="AD5" s="5">
         <f t="shared" si="2"/>
-        <v>17565.5</v>
+        <v>17140.5</v>
       </c>
       <c r="AE5" s="1">
         <v>95000</v>
       </c>
       <c r="AF5" s="6">
         <f t="shared" si="5"/>
-        <v>59934.5</v>
+        <v>60359.5</v>
       </c>
       <c r="AG5" s="7">
         <f t="shared" si="3"/>
-        <v>51934.5</v>
+        <v>52359.5</v>
       </c>
       <c r="AH5" s="8">
         <f t="shared" si="4"/>
-        <v>111869</v>
+        <v>112719</v>
       </c>
     </row>
     <row r="6" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1322,6 +1325,9 @@
       <c r="L6" s="1">
         <v>7500</v>
       </c>
+      <c r="M6" s="1">
+        <v>850</v>
+      </c>
       <c r="N6" s="1">
         <v>10000</v>
       </c>
@@ -1354,33 +1360,33 @@
       </c>
       <c r="AA6" s="1">
         <f t="shared" si="0"/>
-        <v>129000</v>
+        <v>129850</v>
       </c>
       <c r="AB6" s="5">
         <f t="shared" si="1"/>
-        <v>64500</v>
+        <v>64925</v>
       </c>
       <c r="AC6" s="1">
         <v>10000</v>
       </c>
       <c r="AD6" s="5">
         <f t="shared" si="2"/>
-        <v>20500</v>
+        <v>20075</v>
       </c>
       <c r="AE6" s="1">
         <v>95000</v>
       </c>
       <c r="AF6" s="6">
         <f t="shared" si="5"/>
-        <v>57000</v>
+        <v>57425</v>
       </c>
       <c r="AG6" s="7">
         <f t="shared" si="3"/>
-        <v>49000</v>
+        <v>49425</v>
       </c>
       <c r="AH6" s="8">
         <f t="shared" si="4"/>
-        <v>106000</v>
+        <v>106850</v>
       </c>
     </row>
     <row r="7" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1420,6 +1426,9 @@
       <c r="L7" s="1">
         <v>7500</v>
       </c>
+      <c r="M7" s="1">
+        <v>850</v>
+      </c>
       <c r="N7" s="1">
         <v>10000</v>
       </c>
@@ -1455,33 +1464,33 @@
       </c>
       <c r="AA7" s="1">
         <f t="shared" si="0"/>
-        <v>159719</v>
+        <v>160569</v>
       </c>
       <c r="AB7" s="5">
         <f t="shared" si="1"/>
-        <v>79859.5</v>
+        <v>80284.5</v>
       </c>
       <c r="AC7" s="1">
         <v>10000</v>
       </c>
       <c r="AD7" s="5">
         <f t="shared" si="2"/>
-        <v>5140.5</v>
+        <v>4715.5</v>
       </c>
       <c r="AE7" s="1">
         <v>95000</v>
       </c>
       <c r="AF7" s="6">
         <f t="shared" si="5"/>
-        <v>72359.5</v>
+        <v>72784.5</v>
       </c>
       <c r="AG7" s="7">
         <f t="shared" si="3"/>
-        <v>64359.5</v>
+        <v>64784.5</v>
       </c>
       <c r="AH7" s="8">
         <f t="shared" si="4"/>
-        <v>136719</v>
+        <v>137569</v>
       </c>
     </row>
     <row r="8" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1515,6 +1524,9 @@
       <c r="L8" s="1">
         <v>7500</v>
       </c>
+      <c r="M8" s="1">
+        <v>850</v>
+      </c>
       <c r="N8" s="1">
         <v>10000</v>
       </c>
@@ -1553,33 +1565,33 @@
       </c>
       <c r="AA8" s="1">
         <f t="shared" si="0"/>
-        <v>144300</v>
+        <v>145150</v>
       </c>
       <c r="AB8" s="5">
         <f t="shared" si="1"/>
-        <v>72150</v>
+        <v>72575</v>
       </c>
       <c r="AC8" s="1">
         <v>10000</v>
       </c>
       <c r="AD8" s="5">
         <f t="shared" si="2"/>
-        <v>12850</v>
+        <v>12425</v>
       </c>
       <c r="AE8" s="1">
         <v>95000</v>
       </c>
       <c r="AF8" s="6">
         <f t="shared" si="5"/>
-        <v>64650</v>
+        <v>65075</v>
       </c>
       <c r="AG8" s="7">
         <f t="shared" si="3"/>
-        <v>56650</v>
+        <v>57075</v>
       </c>
       <c r="AH8" s="8">
         <f t="shared" si="4"/>
-        <v>121300</v>
+        <v>122150</v>
       </c>
     </row>
     <row r="9" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1616,6 +1628,9 @@
       <c r="L9" s="1">
         <v>7500</v>
       </c>
+      <c r="M9" s="1">
+        <v>850</v>
+      </c>
       <c r="N9" s="1">
         <v>10000</v>
       </c>
@@ -1648,33 +1663,33 @@
       </c>
       <c r="AA9" s="1">
         <f t="shared" si="0"/>
-        <v>135169</v>
+        <v>136019</v>
       </c>
       <c r="AB9" s="5">
         <f t="shared" si="1"/>
-        <v>67584.5</v>
+        <v>68009.5</v>
       </c>
       <c r="AC9" s="1">
         <v>10000</v>
       </c>
       <c r="AD9" s="5">
         <f t="shared" si="2"/>
-        <v>17415.5</v>
+        <v>16990.5</v>
       </c>
       <c r="AE9" s="1">
         <v>95000</v>
       </c>
       <c r="AF9" s="6">
         <f t="shared" si="5"/>
-        <v>60084.5</v>
+        <v>60509.5</v>
       </c>
       <c r="AG9" s="7">
         <f t="shared" si="3"/>
-        <v>52084.5</v>
+        <v>52509.5</v>
       </c>
       <c r="AH9" s="8">
         <f t="shared" si="4"/>
-        <v>112169</v>
+        <v>113019</v>
       </c>
     </row>
     <row r="10" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1708,6 +1723,9 @@
       <c r="L10" s="1">
         <v>7500</v>
       </c>
+      <c r="M10" s="1">
+        <v>850</v>
+      </c>
       <c r="N10" s="1">
         <v>10000</v>
       </c>
@@ -1743,33 +1761,33 @@
       </c>
       <c r="AA10" s="1">
         <f t="shared" si="0"/>
-        <v>151050</v>
+        <v>151900</v>
       </c>
       <c r="AB10" s="5">
         <f t="shared" si="1"/>
-        <v>75525</v>
+        <v>75950</v>
       </c>
       <c r="AC10" s="1">
         <v>10000</v>
       </c>
       <c r="AD10" s="5">
         <f t="shared" si="2"/>
-        <v>9475</v>
+        <v>9050</v>
       </c>
       <c r="AE10" s="1">
         <v>95000</v>
       </c>
       <c r="AF10" s="6">
         <f t="shared" si="5"/>
-        <v>68025</v>
+        <v>68450</v>
       </c>
       <c r="AG10" s="7">
         <f t="shared" si="3"/>
-        <v>60025</v>
+        <v>60450</v>
       </c>
       <c r="AH10" s="8">
         <f t="shared" si="4"/>
-        <v>128050</v>
+        <v>128900</v>
       </c>
     </row>
     <row r="12" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17BD53A-37B7-4520-A69C-2F251DC2453C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE41313-2305-4AFC-B336-CCDC740148BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1145,7 +1145,7 @@
         <v>850</v>
       </c>
       <c r="O4" s="1">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="P4" s="1">
         <v>1800</v>
@@ -1180,33 +1180,33 @@
       </c>
       <c r="AB4" s="1">
         <f t="shared" si="0"/>
-        <v>147400</v>
+        <v>148400</v>
       </c>
       <c r="AC4" s="5">
         <f t="shared" si="1"/>
-        <v>73700</v>
+        <v>74200</v>
       </c>
       <c r="AD4" s="1">
         <v>10000</v>
       </c>
       <c r="AE4" s="5">
         <f t="shared" si="2"/>
-        <v>11300</v>
+        <v>10800</v>
       </c>
       <c r="AF4" s="1">
         <v>95000</v>
       </c>
       <c r="AG4" s="6">
         <f t="shared" ref="AG4:AG10" si="5">AB4/2-M4</f>
-        <v>65700</v>
+        <v>66200</v>
       </c>
       <c r="AH4" s="7">
         <f t="shared" si="3"/>
-        <v>58200</v>
+        <v>58700</v>
       </c>
       <c r="AI4" s="8">
         <f t="shared" si="4"/>
-        <v>123900</v>
+        <v>124900</v>
       </c>
     </row>
     <row r="5" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1238,8 +1238,8 @@
         <v>1000</v>
       </c>
       <c r="K5" s="1">
-        <f>1300+9800+6000</f>
-        <v>17100</v>
+        <f>1300+9800+6600</f>
+        <v>17700</v>
       </c>
       <c r="L5" s="1">
         <v>7500</v>
@@ -1251,7 +1251,7 @@
         <v>850</v>
       </c>
       <c r="O5" s="1">
-        <v>4000</v>
+        <v>4400</v>
       </c>
       <c r="P5" s="1">
         <v>1800</v>
@@ -1285,33 +1285,33 @@
       </c>
       <c r="AB5" s="1">
         <f t="shared" si="0"/>
-        <v>136219</v>
+        <v>137219</v>
       </c>
       <c r="AC5" s="5">
         <f t="shared" si="1"/>
-        <v>68109.5</v>
+        <v>68609.5</v>
       </c>
       <c r="AD5" s="1">
         <v>10000</v>
       </c>
       <c r="AE5" s="5">
         <f t="shared" si="2"/>
-        <v>16890.5</v>
+        <v>16390.5</v>
       </c>
       <c r="AF5" s="1">
         <v>95000</v>
       </c>
       <c r="AG5" s="6">
         <f t="shared" si="5"/>
-        <v>60609.5</v>
+        <v>61109.5</v>
       </c>
       <c r="AH5" s="7">
         <f t="shared" si="3"/>
-        <v>52609.5</v>
+        <v>53109.5</v>
       </c>
       <c r="AI5" s="8">
         <f t="shared" si="4"/>
-        <v>113219</v>
+        <v>114219</v>
       </c>
     </row>
     <row r="6" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1340,8 +1340,8 @@
         <v>1000</v>
       </c>
       <c r="K6" s="1">
-        <f t="shared" ref="K6:K10" si="6">1300+9800+6000</f>
-        <v>17100</v>
+        <f t="shared" ref="K6:K10" si="6">1300+9800+6600</f>
+        <v>17700</v>
       </c>
       <c r="L6" s="1">
         <v>7500</v>
@@ -1353,7 +1353,7 @@
         <v>850</v>
       </c>
       <c r="O6" s="1">
-        <v>4000</v>
+        <v>4400</v>
       </c>
       <c r="P6" s="1">
         <v>1800</v>
@@ -1384,33 +1384,33 @@
       </c>
       <c r="AB6" s="1">
         <f t="shared" si="0"/>
-        <v>130350</v>
+        <v>131350</v>
       </c>
       <c r="AC6" s="5">
         <f t="shared" si="1"/>
-        <v>65175</v>
+        <v>65675</v>
       </c>
       <c r="AD6" s="1">
         <v>10000</v>
       </c>
       <c r="AE6" s="5">
         <f t="shared" si="2"/>
-        <v>19825</v>
+        <v>19325</v>
       </c>
       <c r="AF6" s="1">
         <v>95000</v>
       </c>
       <c r="AG6" s="6">
         <f t="shared" si="5"/>
-        <v>57675</v>
+        <v>58175</v>
       </c>
       <c r="AH6" s="7">
         <f t="shared" si="3"/>
-        <v>49675</v>
+        <v>50175</v>
       </c>
       <c r="AI6" s="8">
         <f t="shared" si="4"/>
-        <v>107350</v>
+        <v>108350</v>
       </c>
     </row>
     <row r="7" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K7" s="1">
         <f t="shared" si="6"/>
-        <v>17100</v>
+        <v>17700</v>
       </c>
       <c r="L7" s="1">
         <v>7500</v>
@@ -1458,7 +1458,7 @@
         <v>850</v>
       </c>
       <c r="O7" s="1">
-        <v>4000</v>
+        <v>4400</v>
       </c>
       <c r="P7" s="1">
         <v>1800</v>
@@ -1492,33 +1492,33 @@
       </c>
       <c r="AB7" s="1">
         <f t="shared" si="0"/>
-        <v>161069</v>
+        <v>162069</v>
       </c>
       <c r="AC7" s="5">
         <f t="shared" si="1"/>
-        <v>80534.5</v>
+        <v>81034.5</v>
       </c>
       <c r="AD7" s="1">
         <v>10000</v>
       </c>
       <c r="AE7" s="5">
         <f t="shared" si="2"/>
-        <v>4465.5</v>
+        <v>3965.5</v>
       </c>
       <c r="AF7" s="1">
         <v>95000</v>
       </c>
       <c r="AG7" s="6">
         <f t="shared" si="5"/>
-        <v>73034.5</v>
+        <v>73534.5</v>
       </c>
       <c r="AH7" s="7">
         <f t="shared" si="3"/>
-        <v>65034.5</v>
+        <v>65534.5</v>
       </c>
       <c r="AI7" s="8">
         <f t="shared" si="4"/>
-        <v>138069</v>
+        <v>139069</v>
       </c>
     </row>
     <row r="8" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="K8" s="1">
         <f t="shared" si="6"/>
-        <v>17100</v>
+        <v>17700</v>
       </c>
       <c r="L8" s="1">
         <v>7500</v>
@@ -1560,7 +1560,7 @@
         <v>850</v>
       </c>
       <c r="O8" s="1">
-        <v>4000</v>
+        <v>4400</v>
       </c>
       <c r="P8" s="1">
         <v>3600</v>
@@ -1597,33 +1597,33 @@
       </c>
       <c r="AB8" s="1">
         <f t="shared" si="0"/>
-        <v>145650</v>
+        <v>146650</v>
       </c>
       <c r="AC8" s="5">
         <f t="shared" si="1"/>
-        <v>72825</v>
+        <v>73325</v>
       </c>
       <c r="AD8" s="1">
         <v>10000</v>
       </c>
       <c r="AE8" s="5">
         <f t="shared" si="2"/>
-        <v>12175</v>
+        <v>11675</v>
       </c>
       <c r="AF8" s="1">
         <v>95000</v>
       </c>
       <c r="AG8" s="6">
         <f t="shared" si="5"/>
-        <v>65325</v>
+        <v>65825</v>
       </c>
       <c r="AH8" s="7">
         <f t="shared" si="3"/>
-        <v>57325</v>
+        <v>57825</v>
       </c>
       <c r="AI8" s="8">
         <f t="shared" si="4"/>
-        <v>122650</v>
+        <v>123650</v>
       </c>
     </row>
     <row r="9" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="K9" s="1">
         <f t="shared" si="6"/>
-        <v>17100</v>
+        <v>17700</v>
       </c>
       <c r="L9" s="1">
         <v>7500</v>
@@ -1668,7 +1668,7 @@
         <v>850</v>
       </c>
       <c r="O9" s="1">
-        <v>4000</v>
+        <v>4400</v>
       </c>
       <c r="P9" s="1">
         <v>3600</v>
@@ -1699,33 +1699,33 @@
       </c>
       <c r="AB9" s="1">
         <f t="shared" si="0"/>
-        <v>136519</v>
+        <v>137519</v>
       </c>
       <c r="AC9" s="5">
         <f t="shared" si="1"/>
-        <v>68259.5</v>
+        <v>68759.5</v>
       </c>
       <c r="AD9" s="1">
         <v>10000</v>
       </c>
       <c r="AE9" s="5">
         <f t="shared" si="2"/>
-        <v>16740.5</v>
+        <v>16240.5</v>
       </c>
       <c r="AF9" s="1">
         <v>95000</v>
       </c>
       <c r="AG9" s="6">
         <f t="shared" si="5"/>
-        <v>60759.5</v>
+        <v>61259.5</v>
       </c>
       <c r="AH9" s="7">
         <f t="shared" si="3"/>
-        <v>52759.5</v>
+        <v>53259.5</v>
       </c>
       <c r="AI9" s="8">
         <f t="shared" si="4"/>
-        <v>113519</v>
+        <v>114519</v>
       </c>
     </row>
     <row r="10" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="K10" s="1">
         <f t="shared" si="6"/>
-        <v>17100</v>
+        <v>17700</v>
       </c>
       <c r="L10" s="1">
         <v>7500</v>
@@ -1767,7 +1767,7 @@
         <v>850</v>
       </c>
       <c r="O10" s="1">
-        <v>4000</v>
+        <v>4400</v>
       </c>
       <c r="P10" s="1">
         <v>3600</v>
@@ -1801,33 +1801,33 @@
       </c>
       <c r="AB10" s="1">
         <f t="shared" si="0"/>
-        <v>152400</v>
+        <v>153400</v>
       </c>
       <c r="AC10" s="5">
         <f t="shared" si="1"/>
-        <v>76200</v>
+        <v>76700</v>
       </c>
       <c r="AD10" s="1">
         <v>10000</v>
       </c>
       <c r="AE10" s="5">
         <f t="shared" si="2"/>
-        <v>8800</v>
+        <v>8300</v>
       </c>
       <c r="AF10" s="1">
         <v>95000</v>
       </c>
       <c r="AG10" s="6">
         <f t="shared" si="5"/>
-        <v>68700</v>
+        <v>69200</v>
       </c>
       <c r="AH10" s="7">
         <f t="shared" si="3"/>
-        <v>60700</v>
+        <v>61200</v>
       </c>
       <c r="AI10" s="8">
         <f t="shared" si="4"/>
-        <v>129400</v>
+        <v>130400</v>
       </c>
     </row>
     <row r="12" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2077,9 +2077,9 @@
         <f>IF(Junio!D32&gt;0,Junio!D32,"")</f>
         <v/>
       </c>
-      <c r="E15" s="1" t="str">
+      <c r="E15" s="1">
         <f>IF(Junio!E32&gt;0,Junio!E32,"")</f>
-        <v/>
+        <v>10990.82</v>
       </c>
       <c r="F15" s="1" t="str">
         <f>IF(Junio!F32&gt;0,Junio!F32,"")</f>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="R15" s="1">
         <f>IF(Junio!R32&gt;0,Junio!R32,"")</f>
-        <v>6825.82</v>
+        <v>7454.79</v>
       </c>
       <c r="S15" s="1" t="str">
         <f>IF(Junio!S32&gt;0,Junio!S32,"")</f>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="AB15" s="1">
         <f>IF(Junio!AB32&gt;0,Junio!AB32,"")</f>
-        <v>13163.619999999999</v>
+        <v>24783.41</v>
       </c>
     </row>
     <row r="16" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3071,9 +3071,9 @@
         <f>IF(ISNUMBER(Junio!D32),D4-Junio!D32,"")</f>
         <v/>
       </c>
-      <c r="E26" s="1" t="str">
+      <c r="E26" s="1">
         <f>IF(ISNUMBER(Junio!E32),E4-Junio!E32,"")</f>
-        <v/>
+        <v>-390.81999999999971</v>
       </c>
       <c r="F26" s="1" t="str">
         <f>IF(ISNUMBER(Junio!F32),F4-Junio!F32,"")</f>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="R26" s="1">
         <f>IF(ISNUMBER(Junio!R32),R4-Junio!R32,"")</f>
-        <v>13174.18</v>
+        <v>12545.21</v>
       </c>
       <c r="S26" s="1" t="str">
         <f>IF(ISNUMBER(Junio!S32),S4-Junio!S32,"")</f>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="AB26" s="10">
         <f t="shared" si="7"/>
-        <v>18336.38</v>
+        <v>17316.59</v>
       </c>
     </row>
     <row r="27" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="E33" s="10">
         <f t="shared" si="8"/>
-        <v>30</v>
+        <v>-360.81999999999971</v>
       </c>
       <c r="F33" s="10">
         <f t="shared" si="8"/>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="R33" s="10">
         <f t="shared" si="8"/>
-        <v>13554.969999999998</v>
+        <v>12925.999999999996</v>
       </c>
       <c r="S33" s="10">
         <f t="shared" si="8"/>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="AB33" s="10">
         <f t="shared" si="7"/>
-        <v>30503.349999999995</v>
+        <v>29483.559999999994</v>
       </c>
     </row>
     <row r="36" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
@@ -5818,7 +5818,9 @@
       <c r="B3" s="14"/>
       <c r="C3" s="14"/>
       <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
+      <c r="E3" s="14">
+        <v>10990.82</v>
+      </c>
       <c r="F3" s="14"/>
       <c r="G3" s="14"/>
       <c r="H3" s="14">
@@ -5852,7 +5854,7 @@
       <c r="AA3" s="14"/>
       <c r="AB3" s="14">
         <f t="shared" si="0"/>
-        <v>6524.6900000000005</v>
+        <v>17515.509999999998</v>
       </c>
       <c r="AC3" s="14"/>
     </row>
@@ -5876,7 +5878,10 @@
       <c r="O4" s="14"/>
       <c r="P4" s="14"/>
       <c r="Q4" s="14"/>
-      <c r="R4" s="14"/>
+      <c r="R4" s="14">
+        <f>640-11.03</f>
+        <v>628.97</v>
+      </c>
       <c r="S4" s="14"/>
       <c r="T4" s="14"/>
       <c r="U4" s="14"/>
@@ -5888,7 +5893,7 @@
       <c r="AA4" s="14"/>
       <c r="AB4" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>628.97</v>
       </c>
       <c r="AC4" s="14"/>
     </row>
@@ -6880,9 +6885,9 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E32" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="E32" s="10">
+        <f t="shared" si="1"/>
+        <v>10990.82</v>
       </c>
       <c r="F32" s="10" t="str">
         <f t="shared" si="1"/>
@@ -6934,7 +6939,7 @@
       </c>
       <c r="R32" s="10">
         <f t="shared" si="1"/>
-        <v>6825.82</v>
+        <v>7454.79</v>
       </c>
       <c r="S32" s="10" t="str">
         <f t="shared" si="1"/>
@@ -6974,7 +6979,7 @@
       </c>
       <c r="AB32" s="10">
         <f t="shared" si="1"/>
-        <v>13163.619999999999</v>
+        <v>24783.41</v>
       </c>
       <c r="AC32" s="15"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE41313-2305-4AFC-B336-CCDC740148BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AE13D05-EC16-414D-B6E0-6C9FE4ACCC55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="73">
   <si>
     <t>Presupuesto</t>
   </si>
@@ -260,6 +260,9 @@
   </si>
   <si>
     <t>Tarjeta CDE</t>
+  </si>
+  <si>
+    <t>Vidrio, silicona, pistola silicona</t>
   </si>
 </sst>
 </file>
@@ -2127,7 +2130,7 @@
       </c>
       <c r="R15" s="1">
         <f>IF(Junio!R32&gt;0,Junio!R32,"")</f>
-        <v>7454.79</v>
+        <v>7852.61</v>
       </c>
       <c r="S15" s="1" t="str">
         <f>IF(Junio!S32&gt;0,Junio!S32,"")</f>
@@ -2163,11 +2166,11 @@
       </c>
       <c r="AA15" s="1">
         <f>IF(Junio!AA32&gt;0,Junio!AA32,"")</f>
-        <v>204.59</v>
+        <v>1928.1899999999998</v>
       </c>
       <c r="AB15" s="1">
         <f>IF(Junio!AB32&gt;0,Junio!AB32,"")</f>
-        <v>24783.41</v>
+        <v>26904.83</v>
       </c>
     </row>
     <row r="16" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3121,7 +3124,7 @@
       </c>
       <c r="R26" s="1">
         <f>IF(ISNUMBER(Junio!R32),R4-Junio!R32,"")</f>
-        <v>12545.21</v>
+        <v>12147.39</v>
       </c>
       <c r="S26" s="1" t="str">
         <f>IF(ISNUMBER(Junio!S32),S4-Junio!S32,"")</f>
@@ -3157,11 +3160,11 @@
       </c>
       <c r="AA26" s="1">
         <f>IF(ISNUMBER(Junio!AA32),AA4-Junio!AA32,"")</f>
-        <v>4795.41</v>
+        <v>3071.8100000000004</v>
       </c>
       <c r="AB26" s="10">
         <f t="shared" si="7"/>
-        <v>17316.59</v>
+        <v>15195.170000000002</v>
       </c>
     </row>
     <row r="27" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3885,7 +3888,7 @@
       </c>
       <c r="R33" s="10">
         <f t="shared" si="8"/>
-        <v>12925.999999999996</v>
+        <v>12528.179999999997</v>
       </c>
       <c r="S33" s="10">
         <f t="shared" si="8"/>
@@ -3921,11 +3924,11 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="8"/>
-        <v>5089.84</v>
+        <v>3366.2400000000007</v>
       </c>
       <c r="AB33" s="10">
         <f t="shared" si="7"/>
-        <v>29483.559999999994</v>
+        <v>27362.139999999996</v>
       </c>
     </row>
     <row r="36" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
@@ -5917,7 +5920,10 @@
       <c r="O5" s="14"/>
       <c r="P5" s="14"/>
       <c r="Q5" s="14"/>
-      <c r="R5" s="14"/>
+      <c r="R5" s="14">
+        <f>405-7.18</f>
+        <v>397.82</v>
+      </c>
       <c r="S5" s="14"/>
       <c r="T5" s="14"/>
       <c r="U5" s="14"/>
@@ -5926,12 +5932,17 @@
       <c r="X5" s="14"/>
       <c r="Y5" s="14"/>
       <c r="Z5" s="14"/>
-      <c r="AA5" s="14"/>
+      <c r="AA5" s="14">
+        <f>980+500+256-8.2-4.2</f>
+        <v>1723.6</v>
+      </c>
       <c r="AB5" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AC5" s="14"/>
+        <v>2121.42</v>
+      </c>
+      <c r="AC5" s="14" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="6" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13">
@@ -6939,7 +6950,7 @@
       </c>
       <c r="R32" s="10">
         <f t="shared" si="1"/>
-        <v>7454.79</v>
+        <v>7852.61</v>
       </c>
       <c r="S32" s="10" t="str">
         <f t="shared" si="1"/>
@@ -6975,11 +6986,11 @@
       </c>
       <c r="AA32" s="10">
         <f t="shared" si="1"/>
-        <v>204.59</v>
+        <v>1928.1899999999998</v>
       </c>
       <c r="AB32" s="10">
         <f t="shared" si="1"/>
-        <v>24783.41</v>
+        <v>26904.83</v>
       </c>
       <c r="AC32" s="15"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AE13D05-EC16-414D-B6E0-6C9FE4ACCC55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3955CC5A-F107-40E9-BE5B-4EC0B5734A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="75">
   <si>
     <t>Presupuesto</t>
   </si>
@@ -264,6 +264,12 @@
   <si>
     <t>Vidrio, silicona, pistola silicona</t>
   </si>
+  <si>
+    <t>caravanas</t>
+  </si>
+  <si>
+    <t>luz spot</t>
+  </si>
 </sst>
 </file>
 
@@ -350,7 +356,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -441,6 +447,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -469,7 +481,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -543,6 +555,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1204,7 +1217,7 @@
         <v>66200</v>
       </c>
       <c r="AH4" s="7">
-        <f t="shared" si="3"/>
+        <f>AB4/2-D4</f>
         <v>58700</v>
       </c>
       <c r="AI4" s="8">
@@ -2084,9 +2097,9 @@
         <f>IF(Junio!E32&gt;0,Junio!E32,"")</f>
         <v>10990.82</v>
       </c>
-      <c r="F15" s="1" t="str">
+      <c r="F15" s="1">
         <f>IF(Junio!F32&gt;0,Junio!F32,"")</f>
-        <v/>
+        <v>17944</v>
       </c>
       <c r="G15" s="1" t="str">
         <f>IF(Junio!G32&gt;0,Junio!G32,"")</f>
@@ -2104,9 +2117,13 @@
         <f>IF(Junio!J32&gt;0,Junio!J32,"")</f>
         <v/>
       </c>
-      <c r="L15" s="1" t="str">
+      <c r="K15" s="1">
+        <f>IF(Junio!K32&gt;0,Junio!K32,"")</f>
+        <v>1286.19</v>
+      </c>
+      <c r="L15" s="1">
         <f>IF(Junio!L32&gt;0,Junio!L32,"")</f>
-        <v/>
+        <v>9690.8900000000012</v>
       </c>
       <c r="M15" s="1" t="str">
         <f>IF(Junio!M32&gt;0,Junio!M32,"")</f>
@@ -2130,7 +2147,7 @@
       </c>
       <c r="R15" s="1">
         <f>IF(Junio!R32&gt;0,Junio!R32,"")</f>
-        <v>7852.61</v>
+        <v>11114.54</v>
       </c>
       <c r="S15" s="1" t="str">
         <f>IF(Junio!S32&gt;0,Junio!S32,"")</f>
@@ -2166,11 +2183,11 @@
       </c>
       <c r="AA15" s="1">
         <f>IF(Junio!AA32&gt;0,Junio!AA32,"")</f>
-        <v>1928.1899999999998</v>
+        <v>4925.57</v>
       </c>
       <c r="AB15" s="1">
         <f>IF(Junio!AB32&gt;0,Junio!AB32,"")</f>
-        <v>26904.83</v>
+        <v>62085.220000000008</v>
       </c>
     </row>
     <row r="16" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2213,6 +2230,10 @@
         <f>IF(Julio!J33&gt;0,Julio!J33,"")</f>
         <v/>
       </c>
+      <c r="K16" s="1" t="str">
+        <f>IF(Julio!K33&gt;0,Julio!K33,"")</f>
+        <v/>
+      </c>
       <c r="L16" s="1" t="str">
         <f>IF(Julio!L33&gt;0,Julio!L33,"")</f>
         <v/>
@@ -2322,6 +2343,10 @@
         <f>IF(Agosto!J33&gt;0,Agosto!J33,"")</f>
         <v/>
       </c>
+      <c r="K17" s="1" t="str">
+        <f>IF(Agosto!K33&gt;0,Agosto!K33,"")</f>
+        <v/>
+      </c>
       <c r="L17" s="1" t="str">
         <f>IF(Agosto!L33&gt;0,Agosto!L33,"")</f>
         <v/>
@@ -2431,6 +2456,10 @@
         <f>IF(Setiembre!J32&gt;0,Setiembre!J32,"")</f>
         <v/>
       </c>
+      <c r="K18" s="1" t="str">
+        <f>IF(Setiembre!K32&gt;0,Setiembre!K32,"")</f>
+        <v/>
+      </c>
       <c r="L18" s="1" t="str">
         <f>IF(Setiembre!L32&gt;0,Setiembre!L32,"")</f>
         <v/>
@@ -2540,6 +2569,10 @@
         <f>IF(Octubre!J33&gt;0,Octubre!J33,"")</f>
         <v/>
       </c>
+      <c r="K19" s="1" t="str">
+        <f>IF(Octubre!K33&gt;0,Octubre!K33,"")</f>
+        <v/>
+      </c>
       <c r="L19" s="1" t="str">
         <f>IF(Octubre!L33&gt;0,Octubre!L33,"")</f>
         <v/>
@@ -2649,6 +2682,10 @@
         <f>IF(Noviembre!J32&gt;0,Noviembre!J32,"")</f>
         <v/>
       </c>
+      <c r="K20" s="1" t="str">
+        <f>IF(Noviembre!K32&gt;0,Noviembre!K32,"")</f>
+        <v/>
+      </c>
       <c r="L20" s="1" t="str">
         <f>IF(Noviembre!L32&gt;0,Noviembre!L32,"")</f>
         <v/>
@@ -2756,6 +2793,10 @@
       </c>
       <c r="J21" s="1" t="str">
         <f>IF(Diciembre!J33&gt;0,Diciembre!J33,"")</f>
+        <v/>
+      </c>
+      <c r="K21" s="1" t="str">
+        <f>IF(Diciembre!K33&gt;0,Diciembre!K33,"")</f>
         <v/>
       </c>
       <c r="L21" s="1" t="str">
@@ -3078,9 +3119,9 @@
         <f>IF(ISNUMBER(Junio!E32),E4-Junio!E32,"")</f>
         <v>-390.81999999999971</v>
       </c>
-      <c r="F26" s="1" t="str">
+      <c r="F26" s="1">
         <f>IF(ISNUMBER(Junio!F32),F4-Junio!F32,"")</f>
-        <v/>
+        <v>17556</v>
       </c>
       <c r="G26" s="1" t="str">
         <f>IF(ISNUMBER(Junio!G32),G4-Junio!G32,"")</f>
@@ -3098,9 +3139,13 @@
         <f>IF(ISNUMBER(Junio!J32),J4-Junio!J32,"")</f>
         <v/>
       </c>
-      <c r="L26" s="1" t="str">
+      <c r="K26" s="1">
+        <f>IF(ISNUMBER(Junio!K32),K4-Junio!K32,"")</f>
+        <v>13.809999999999945</v>
+      </c>
+      <c r="L26" s="1">
         <f>IF(ISNUMBER(Junio!L32),L4-Junio!L32,"")</f>
-        <v/>
+        <v>309.10999999999876</v>
       </c>
       <c r="M26" s="1" t="str">
         <f>IF(ISNUMBER(Junio!M32),M4-Junio!M32,"")</f>
@@ -3124,7 +3169,7 @@
       </c>
       <c r="R26" s="1">
         <f>IF(ISNUMBER(Junio!R32),R4-Junio!R32,"")</f>
-        <v>12147.39</v>
+        <v>8885.4599999999991</v>
       </c>
       <c r="S26" s="1" t="str">
         <f>IF(ISNUMBER(Junio!S32),S4-Junio!S32,"")</f>
@@ -3160,11 +3205,11 @@
       </c>
       <c r="AA26" s="1">
         <f>IF(ISNUMBER(Junio!AA32),AA4-Junio!AA32,"")</f>
-        <v>3071.8100000000004</v>
+        <v>74.430000000000291</v>
       </c>
       <c r="AB26" s="10">
         <f t="shared" si="7"/>
-        <v>15195.170000000002</v>
+        <v>26814.78</v>
       </c>
     </row>
     <row r="27" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3207,6 +3252,10 @@
         <f>IF(ISNUMBER(Julio!J33),J5-Julio!J33,"")</f>
         <v/>
       </c>
+      <c r="K27" s="1" t="str">
+        <f>IF(ISNUMBER(Julio!K33),K5-Julio!K33,"")</f>
+        <v/>
+      </c>
       <c r="L27" s="1" t="str">
         <f>IF(ISNUMBER(Julio!L33),L5-Julio!L33,"")</f>
         <v/>
@@ -3316,6 +3365,10 @@
         <f>IF(ISNUMBER(Agosto!J33),J6-Agosto!J33,"")</f>
         <v/>
       </c>
+      <c r="K28" s="1" t="str">
+        <f>IF(ISNUMBER(Agosto!K33),K6-Agosto!K33,"")</f>
+        <v/>
+      </c>
       <c r="L28" s="1" t="str">
         <f>IF(ISNUMBER(Agosto!L33),L6-Agosto!L33,"")</f>
         <v/>
@@ -3425,6 +3478,10 @@
         <f>IF(ISNUMBER(Setiembre!J32),J7-Setiembre!J32,"")</f>
         <v/>
       </c>
+      <c r="K29" s="1" t="str">
+        <f>IF(ISNUMBER(Setiembre!K32),K7-Setiembre!K32,"")</f>
+        <v/>
+      </c>
       <c r="L29" s="1" t="str">
         <f>IF(ISNUMBER(Setiembre!L32),L7-Setiembre!L32,"")</f>
         <v/>
@@ -3534,6 +3591,10 @@
         <f>IF(ISNUMBER(Octubre!J33),J8-Octubre!J33,"")</f>
         <v/>
       </c>
+      <c r="K30" s="1" t="str">
+        <f>IF(ISNUMBER(Octubre!K33),K8-Octubre!K33,"")</f>
+        <v/>
+      </c>
       <c r="L30" s="1" t="str">
         <f>IF(ISNUMBER(Octubre!L33),L8-Octubre!L33,"")</f>
         <v/>
@@ -3643,6 +3704,10 @@
         <f>IF(ISNUMBER(Noviembre!J32),J9-Noviembre!J32,"")</f>
         <v/>
       </c>
+      <c r="K31" s="1" t="str">
+        <f>IF(ISNUMBER(Noviembre!K32),K9-Noviembre!K32,"")</f>
+        <v/>
+      </c>
       <c r="L31" s="1" t="str">
         <f>IF(ISNUMBER(Noviembre!L32),L9-Noviembre!L32,"")</f>
         <v/>
@@ -3752,6 +3817,10 @@
         <f>IF(ISNUMBER(Diciembre!J33),J10-Diciembre!J33,"")</f>
         <v/>
       </c>
+      <c r="K32" s="1" t="str">
+        <f>IF(ISNUMBER(Diciembre!K33),K10-Diciembre!K33,"")</f>
+        <v/>
+      </c>
       <c r="L32" s="1" t="str">
         <f>IF(ISNUMBER(Diciembre!L33),L10-Diciembre!L33,"")</f>
         <v/>
@@ -3843,7 +3912,7 @@
       </c>
       <c r="F33" s="10">
         <f t="shared" si="8"/>
-        <v>46</v>
+        <v>17602</v>
       </c>
       <c r="G33" s="10">
         <f t="shared" si="8"/>
@@ -3861,10 +3930,13 @@
         <f t="shared" si="8"/>
         <v>300</v>
       </c>
-      <c r="K33" s="10"/>
+      <c r="K33" s="10">
+        <f t="shared" si="8"/>
+        <v>13.809999999999945</v>
+      </c>
       <c r="L33" s="10">
         <f t="shared" si="8"/>
-        <v>17.989999999997963</v>
+        <v>327.09999999999673</v>
       </c>
       <c r="M33" s="10">
         <f t="shared" si="8"/>
@@ -3888,7 +3960,7 @@
       </c>
       <c r="R33" s="10">
         <f t="shared" si="8"/>
-        <v>12528.179999999997</v>
+        <v>9266.2499999999964</v>
       </c>
       <c r="S33" s="10">
         <f t="shared" si="8"/>
@@ -3924,11 +3996,11 @@
       </c>
       <c r="AA33" s="10">
         <f t="shared" si="8"/>
-        <v>3366.2400000000007</v>
+        <v>368.86000000000058</v>
       </c>
       <c r="AB33" s="10">
         <f t="shared" si="7"/>
-        <v>27362.139999999996</v>
+        <v>38981.75</v>
       </c>
     </row>
     <row r="36" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
@@ -5821,7 +5893,7 @@
       <c r="B3" s="14"/>
       <c r="C3" s="14"/>
       <c r="D3" s="14"/>
-      <c r="E3" s="14">
+      <c r="E3" s="39">
         <v>10990.82</v>
       </c>
       <c r="F3" s="14"/>
@@ -5952,7 +6024,9 @@
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
       <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
+      <c r="F6" s="39">
+        <v>17944</v>
+      </c>
       <c r="G6" s="14"/>
       <c r="H6" s="14"/>
       <c r="I6" s="14"/>
@@ -5964,7 +6038,10 @@
       <c r="O6" s="14"/>
       <c r="P6" s="14"/>
       <c r="Q6" s="14"/>
-      <c r="R6" s="14"/>
+      <c r="R6" s="14">
+        <f>550+431-7.53+550+459-7.72-10-7.5</f>
+        <v>1957.25</v>
+      </c>
       <c r="S6" s="14"/>
       <c r="T6" s="14"/>
       <c r="U6" s="14"/>
@@ -5973,12 +6050,17 @@
       <c r="X6" s="14"/>
       <c r="Y6" s="14"/>
       <c r="Z6" s="14"/>
-      <c r="AA6" s="14"/>
+      <c r="AA6" s="14">
+        <f>99-1.62</f>
+        <v>97.38</v>
+      </c>
       <c r="AB6" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AC6" s="14"/>
+        <v>19998.63</v>
+      </c>
+      <c r="AC6" s="14" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="7" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13">
@@ -6036,7 +6118,10 @@
       <c r="O8" s="14"/>
       <c r="P8" s="14"/>
       <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
+      <c r="R8" s="39">
+        <f>670.25+634.43</f>
+        <v>1304.6799999999998</v>
+      </c>
       <c r="S8" s="14"/>
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
@@ -6048,7 +6133,7 @@
       <c r="AA8" s="14"/>
       <c r="AB8" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1304.6799999999998</v>
       </c>
       <c r="AC8" s="14"/>
     </row>
@@ -6065,7 +6150,10 @@
       <c r="H9" s="14"/>
       <c r="I9" s="14"/>
       <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
+      <c r="K9" s="14">
+        <f>1290.7-4.51</f>
+        <v>1286.19</v>
+      </c>
       <c r="L9" s="14"/>
       <c r="M9" s="14"/>
       <c r="N9" s="14"/>
@@ -6081,12 +6169,16 @@
       <c r="X9" s="14"/>
       <c r="Y9" s="14"/>
       <c r="Z9" s="14"/>
-      <c r="AA9" s="14"/>
+      <c r="AA9" s="14">
+        <v>2900</v>
+      </c>
       <c r="AB9" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AC9" s="14"/>
+        <v>4186.1900000000005</v>
+      </c>
+      <c r="AC9" s="14" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="10" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13">
@@ -6102,7 +6194,10 @@
       <c r="I10" s="14"/>
       <c r="J10" s="14"/>
       <c r="K10" s="14"/>
-      <c r="L10" s="14"/>
+      <c r="L10" s="14">
+        <f>14136.35-4704+258.54</f>
+        <v>9690.8900000000012</v>
+      </c>
       <c r="M10" s="14"/>
       <c r="N10" s="14"/>
       <c r="O10" s="14"/>
@@ -6120,7 +6215,7 @@
       <c r="AA10" s="14"/>
       <c r="AB10" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9690.8900000000012</v>
       </c>
       <c r="AC10" s="14"/>
     </row>
@@ -6900,9 +6995,9 @@
         <f t="shared" si="1"/>
         <v>10990.82</v>
       </c>
-      <c r="F32" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="F32" s="10">
+        <f t="shared" si="1"/>
+        <v>17944</v>
       </c>
       <c r="G32" s="10" t="str">
         <f t="shared" si="1"/>
@@ -6920,13 +7015,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K32" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="L32" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="K32" s="10">
+        <f t="shared" si="1"/>
+        <v>1286.19</v>
+      </c>
+      <c r="L32" s="10">
+        <f t="shared" si="1"/>
+        <v>9690.8900000000012</v>
       </c>
       <c r="M32" s="10" t="str">
         <f t="shared" si="1"/>
@@ -6950,7 +7045,7 @@
       </c>
       <c r="R32" s="10">
         <f t="shared" si="1"/>
-        <v>7852.61</v>
+        <v>11114.54</v>
       </c>
       <c r="S32" s="10" t="str">
         <f t="shared" si="1"/>
@@ -6986,11 +7081,11 @@
       </c>
       <c r="AA32" s="10">
         <f t="shared" si="1"/>
-        <v>1928.1899999999998</v>
+        <v>4925.57</v>
       </c>
       <c r="AB32" s="10">
         <f t="shared" si="1"/>
-        <v>26904.83</v>
+        <v>62085.220000000008</v>
       </c>
       <c r="AC32" s="15"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D91565-B68E-4E60-8334-449C91DE3F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F93048B-105C-409B-8E81-B96472EA3D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="77">
   <si>
     <t>Presupuesto</t>
   </si>
@@ -273,6 +273,9 @@
   <si>
     <t>caravanas</t>
   </si>
+  <si>
+    <t>materiales almohadones</t>
+  </si>
 </sst>
 </file>
 
@@ -295,7 +298,7 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Cambria"/>
-      <charset val="1"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
@@ -379,7 +382,7 @@
       <b/>
       <sz val="11"/>
       <name val="Cambria"/>
-      <charset val="1"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="18">
@@ -1172,7 +1175,7 @@
         <v>38</v>
       </c>
       <c r="D4" s="1">
-        <v>15500</v>
+        <v>15550</v>
       </c>
       <c r="E4" s="1">
         <v>10600</v>
@@ -1243,7 +1246,7 @@
       </c>
       <c r="AC4" s="1">
         <f t="shared" si="0"/>
-        <v>166400</v>
+        <v>166450</v>
       </c>
       <c r="AD4" s="7">
         <f t="shared" si="1"/>
@@ -1261,11 +1264,11 @@
       </c>
       <c r="AH4" s="8">
         <f t="shared" si="3"/>
-        <v>75200</v>
+        <v>75225</v>
       </c>
       <c r="AI4" s="9">
         <f t="shared" si="4"/>
-        <v>67700</v>
+        <v>67675</v>
       </c>
       <c r="AJ4" s="10">
         <f>AH4+AI4</f>
@@ -1280,7 +1283,7 @@
         <v>4369</v>
       </c>
       <c r="D5" s="1">
-        <v>15500</v>
+        <v>15600</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
@@ -1349,7 +1352,7 @@
       <c r="AB5" s="6"/>
       <c r="AC5" s="1">
         <f t="shared" si="0"/>
-        <v>137219</v>
+        <v>137319</v>
       </c>
       <c r="AD5" s="7">
         <f t="shared" si="1"/>
@@ -1367,11 +1370,11 @@
       </c>
       <c r="AH5" s="8">
         <f t="shared" si="3"/>
-        <v>61109.5</v>
+        <v>61159.5</v>
       </c>
       <c r="AI5" s="9">
         <f t="shared" si="4"/>
-        <v>53109.5</v>
+        <v>53059.5</v>
       </c>
       <c r="AJ5" s="10">
         <f t="shared" si="5"/>
@@ -1383,7 +1386,7 @@
         <v>40</v>
       </c>
       <c r="D6" s="1">
-        <v>15500</v>
+        <v>15600</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
@@ -1449,7 +1452,7 @@
       <c r="AB6" s="6"/>
       <c r="AC6" s="1">
         <f t="shared" si="0"/>
-        <v>131350</v>
+        <v>131450</v>
       </c>
       <c r="AD6" s="7">
         <f t="shared" si="1"/>
@@ -1467,11 +1470,11 @@
       </c>
       <c r="AH6" s="8">
         <f t="shared" si="3"/>
-        <v>58175</v>
+        <v>58225</v>
       </c>
       <c r="AI6" s="9">
         <f t="shared" si="4"/>
-        <v>50175</v>
+        <v>50125</v>
       </c>
       <c r="AJ6" s="10">
         <f t="shared" si="5"/>
@@ -1489,7 +1492,7 @@
         <v>4369</v>
       </c>
       <c r="D7" s="1">
-        <v>15500</v>
+        <v>15650</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
@@ -1558,7 +1561,7 @@
       <c r="AB7" s="6"/>
       <c r="AC7" s="1">
         <f t="shared" si="0"/>
-        <v>162069</v>
+        <v>162219</v>
       </c>
       <c r="AD7" s="7">
         <f t="shared" si="1"/>
@@ -1576,11 +1579,11 @@
       </c>
       <c r="AH7" s="8">
         <f t="shared" si="3"/>
-        <v>73534.5</v>
+        <v>73609.5</v>
       </c>
       <c r="AI7" s="9">
         <f t="shared" si="4"/>
-        <v>65534.5</v>
+        <v>65459.5</v>
       </c>
       <c r="AJ7" s="10">
         <f t="shared" si="5"/>
@@ -1592,7 +1595,7 @@
         <v>42</v>
       </c>
       <c r="D8" s="1">
-        <v>15500</v>
+        <v>15650</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
@@ -1664,7 +1667,7 @@
       <c r="AB8" s="6"/>
       <c r="AC8" s="1">
         <f t="shared" si="0"/>
-        <v>146650</v>
+        <v>146800</v>
       </c>
       <c r="AD8" s="7">
         <f t="shared" si="1"/>
@@ -1682,11 +1685,11 @@
       </c>
       <c r="AH8" s="8">
         <f t="shared" si="3"/>
-        <v>65825</v>
+        <v>65900</v>
       </c>
       <c r="AI8" s="9">
         <f t="shared" si="4"/>
-        <v>57825</v>
+        <v>57750</v>
       </c>
       <c r="AJ8" s="10">
         <f t="shared" si="5"/>
@@ -1701,7 +1704,7 @@
         <v>4369</v>
       </c>
       <c r="D9" s="1">
-        <v>15500</v>
+        <v>15700</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
@@ -1767,7 +1770,7 @@
       <c r="AB9" s="6"/>
       <c r="AC9" s="1">
         <f t="shared" si="0"/>
-        <v>137519</v>
+        <v>137719</v>
       </c>
       <c r="AD9" s="7">
         <f t="shared" si="1"/>
@@ -1785,11 +1788,11 @@
       </c>
       <c r="AH9" s="8">
         <f t="shared" si="3"/>
-        <v>61259.5</v>
+        <v>61359.5</v>
       </c>
       <c r="AI9" s="9">
         <f t="shared" si="4"/>
-        <v>53259.5</v>
+        <v>53159.5</v>
       </c>
       <c r="AJ9" s="10">
         <f t="shared" si="5"/>
@@ -1801,7 +1804,7 @@
         <v>44</v>
       </c>
       <c r="D10" s="1">
-        <v>15500</v>
+        <v>15700</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
@@ -1870,7 +1873,7 @@
       <c r="AB10" s="6"/>
       <c r="AC10" s="1">
         <f t="shared" si="0"/>
-        <v>153400</v>
+        <v>153600</v>
       </c>
       <c r="AD10" s="7">
         <f t="shared" si="1"/>
@@ -1888,11 +1891,11 @@
       </c>
       <c r="AH10" s="8">
         <f t="shared" si="3"/>
-        <v>69200</v>
+        <v>69300</v>
       </c>
       <c r="AI10" s="9">
         <f t="shared" si="4"/>
-        <v>61200</v>
+        <v>61100</v>
       </c>
       <c r="AJ10" s="10">
         <f t="shared" si="5"/>
@@ -2142,9 +2145,9 @@
         <f>IF(Junio!C32&gt;0,Junio!C32,"")</f>
         <v/>
       </c>
-      <c r="D15" s="1" t="str">
+      <c r="D15" s="1">
         <f>IF(Junio!D32&gt;0,Junio!D32,"")</f>
-        <v/>
+        <v>15540.52</v>
       </c>
       <c r="E15" s="1">
         <f>IF(Junio!E32&gt;0,Junio!E32,"")</f>
@@ -2152,11 +2155,11 @@
       </c>
       <c r="F15" s="1">
         <f>IF(Junio!F32&gt;0,Junio!F32,"")</f>
-        <v>17944</v>
-      </c>
-      <c r="G15" s="1" t="str">
+        <v>26054</v>
+      </c>
+      <c r="G15" s="1">
         <f>IF(Junio!G32&gt;0,Junio!G32,"")</f>
-        <v/>
+        <v>1015</v>
       </c>
       <c r="H15" s="1">
         <f>IF(Junio!H32&gt;0,Junio!H32,"")</f>
@@ -2200,11 +2203,11 @@
       </c>
       <c r="R15" s="1">
         <f>IF(Junio!R32&gt;0,Junio!R32,"")</f>
-        <v>11114.54</v>
-      </c>
-      <c r="S15" s="1" t="str">
+        <v>12236.69</v>
+      </c>
+      <c r="S15" s="1">
         <f>IF(Junio!S32&gt;0,Junio!S32,"")</f>
-        <v/>
+        <v>276.39</v>
       </c>
       <c r="T15" s="1" t="str">
         <f>IF(Junio!T32&gt;0,Junio!T32,"")</f>
@@ -2236,7 +2239,7 @@
       </c>
       <c r="AA15" s="1">
         <f>IF(Junio!AA32&gt;0,Junio!AA32,"")</f>
-        <v>4925.57</v>
+        <v>16845.239999999998</v>
       </c>
       <c r="AC15" s="1" t="str">
         <f>IF(Junio!AB32&gt;0,Junio!AB32,"")</f>
@@ -3164,9 +3167,9 @@
         <f>IF(ISNUMBER(Junio!C32),C4-Junio!C32,"")</f>
         <v/>
       </c>
-      <c r="D26" s="1" t="str">
+      <c r="D26" s="1">
         <f>IF(ISNUMBER(Junio!D32),D4-Junio!D32,"")</f>
-        <v/>
+        <v>9.4799999999995634</v>
       </c>
       <c r="E26" s="1">
         <f>IF(ISNUMBER(Junio!E32),E4-Junio!E32,"")</f>
@@ -3174,11 +3177,11 @@
       </c>
       <c r="F26" s="1">
         <f>IF(ISNUMBER(Junio!F32),F4-Junio!F32,"")</f>
-        <v>17556</v>
-      </c>
-      <c r="G26" s="1" t="str">
+        <v>9446</v>
+      </c>
+      <c r="G26" s="1">
         <f>IF(ISNUMBER(Junio!G32),G4-Junio!G32,"")</f>
-        <v/>
+        <v>-15</v>
       </c>
       <c r="H26" s="1">
         <f>IF(ISNUMBER(Junio!H32),H4-Junio!H32,"")</f>
@@ -3222,11 +3225,11 @@
       </c>
       <c r="R26" s="1">
         <f>IF(ISNUMBER(Junio!R32),R4-Junio!R32,"")</f>
-        <v>8885.4599999999991</v>
-      </c>
-      <c r="S26" s="1" t="str">
+        <v>7763.3099999999995</v>
+      </c>
+      <c r="S26" s="1">
         <f>IF(ISNUMBER(Junio!S32),S4-Junio!S32,"")</f>
-        <v/>
+        <v>2223.61</v>
       </c>
       <c r="T26" s="1" t="str">
         <f>IF(ISNUMBER(Junio!T32),T4-Junio!T32,"")</f>
@@ -3258,11 +3261,11 @@
       </c>
       <c r="AA26" s="1">
         <f>IF(ISNUMBER(Junio!AA32),AA4-Junio!AA32,"")</f>
-        <v>74.430000000000291</v>
+        <v>-11845.239999999998</v>
       </c>
       <c r="AC26" s="12">
         <f t="shared" si="7"/>
-        <v>26854.78</v>
+        <v>7921.0500000000029</v>
       </c>
     </row>
     <row r="27" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3957,7 +3960,7 @@
       </c>
       <c r="D33" s="12">
         <f t="shared" si="8"/>
-        <v>47.229999999999563</v>
+        <v>56.709999999999127</v>
       </c>
       <c r="E33" s="12">
         <f t="shared" si="8"/>
@@ -3965,11 +3968,11 @@
       </c>
       <c r="F33" s="12">
         <f t="shared" si="8"/>
-        <v>17602</v>
+        <v>9492</v>
       </c>
       <c r="G33" s="12">
         <f t="shared" si="8"/>
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H33" s="12">
         <f t="shared" si="8"/>
@@ -4013,11 +4016,11 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>9266.2499999999964</v>
+        <v>8144.0999999999967</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
-        <v>1689</v>
+        <v>3912.61</v>
       </c>
       <c r="T33" s="12">
         <f t="shared" si="8"/>
@@ -4049,11 +4052,11 @@
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="8"/>
-        <v>368.86000000000058</v>
+        <v>-11550.809999999998</v>
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>39021.75</v>
+        <v>20088.019999999997</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5840,6 +5843,7 @@
     <col min="27" max="27" width="13" customWidth="1"/>
     <col min="28" max="28" width="14" customWidth="1"/>
     <col min="29" max="29" width="25" customWidth="1"/>
+    <col min="30" max="30" width="28.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6303,7 +6307,10 @@
       <c r="O10" s="35"/>
       <c r="P10" s="35"/>
       <c r="Q10" s="35"/>
-      <c r="R10" s="35"/>
+      <c r="R10" s="35">
+        <f>582-9.99</f>
+        <v>572.01</v>
+      </c>
       <c r="S10" s="35"/>
       <c r="T10" s="35"/>
       <c r="U10" s="35"/>
@@ -6312,13 +6319,18 @@
       <c r="X10" s="35"/>
       <c r="Y10" s="35"/>
       <c r="Z10" s="35"/>
-      <c r="AA10" s="35"/>
+      <c r="AA10" s="35">
+        <f>7700+4290-70.33</f>
+        <v>11919.67</v>
+      </c>
       <c r="AB10" s="36"/>
       <c r="AC10" s="35">
         <f t="shared" si="0"/>
-        <v>9690.8900000000012</v>
-      </c>
-      <c r="AD10" s="35"/>
+        <v>22182.57</v>
+      </c>
+      <c r="AD10" s="35" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="11" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="34">
@@ -6326,10 +6338,16 @@
       </c>
       <c r="B11" s="35"/>
       <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
+      <c r="D11" s="35">
+        <v>15540.52</v>
+      </c>
       <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
+      <c r="F11" s="35">
+        <v>8110</v>
+      </c>
+      <c r="G11" s="35">
+        <v>1015</v>
+      </c>
       <c r="H11" s="35"/>
       <c r="I11" s="35"/>
       <c r="J11" s="35">
@@ -6346,8 +6364,14 @@
         <v>1800</v>
       </c>
       <c r="Q11" s="35"/>
-      <c r="R11" s="35"/>
-      <c r="S11" s="35"/>
+      <c r="R11" s="35">
+        <f>560-9.86</f>
+        <v>550.14</v>
+      </c>
+      <c r="S11" s="35">
+        <f>281-4.61</f>
+        <v>276.39</v>
+      </c>
       <c r="T11" s="35"/>
       <c r="U11" s="35"/>
       <c r="V11" s="35"/>
@@ -6359,7 +6383,7 @@
       <c r="AB11" s="36"/>
       <c r="AC11" s="35">
         <f t="shared" si="0"/>
-        <v>3610</v>
+        <v>29102.05</v>
       </c>
       <c r="AD11" s="35"/>
     </row>
@@ -7115,9 +7139,9 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="D32" s="12">
+        <f t="shared" si="1"/>
+        <v>15540.52</v>
       </c>
       <c r="E32" s="12">
         <f t="shared" si="1"/>
@@ -7125,11 +7149,11 @@
       </c>
       <c r="F32" s="12">
         <f t="shared" si="1"/>
-        <v>17944</v>
-      </c>
-      <c r="G32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+        <v>26054</v>
+      </c>
+      <c r="G32" s="12">
+        <f t="shared" si="1"/>
+        <v>1015</v>
       </c>
       <c r="H32" s="12">
         <f t="shared" si="1"/>
@@ -7173,11 +7197,11 @@
       </c>
       <c r="R32" s="12">
         <f t="shared" si="1"/>
-        <v>11114.54</v>
-      </c>
-      <c r="S32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+        <v>12236.69</v>
+      </c>
+      <c r="S32" s="12">
+        <f t="shared" si="1"/>
+        <v>276.39</v>
       </c>
       <c r="T32" s="12" t="str">
         <f t="shared" si="1"/>
@@ -7209,7 +7233,7 @@
       </c>
       <c r="AA32" s="12">
         <f t="shared" si="1"/>
-        <v>4925.57</v>
+        <v>16845.239999999998</v>
       </c>
       <c r="AB32" s="38" t="str">
         <f t="shared" si="1"/>
@@ -7217,7 +7241,7 @@
       </c>
       <c r="AC32" s="12">
         <f t="shared" si="1"/>
-        <v>65695.22</v>
+        <v>103678.95000000001</v>
       </c>
       <c r="AD32" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F93048B-105C-409B-8E81-B96472EA3D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD7B11D-0CCD-44CD-86B3-C04B1A1E2947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -2181,9 +2181,9 @@
         <f>IF(Junio!L32&gt;0,Junio!L32,"")</f>
         <v>9690.8900000000012</v>
       </c>
-      <c r="M15" s="1" t="str">
+      <c r="M15" s="1">
         <f>IF(Junio!M32&gt;0,Junio!M32,"")</f>
-        <v/>
+        <v>21668.69</v>
       </c>
       <c r="N15" s="1">
         <f>IF(Junio!N32&gt;0,Junio!N32,"")</f>
@@ -3203,9 +3203,9 @@
         <f>IF(ISNUMBER(Junio!L32),L4-Junio!L32,"")</f>
         <v>309.10999999999876</v>
       </c>
-      <c r="M26" s="1" t="str">
+      <c r="M26" s="1">
         <f>IF(ISNUMBER(Junio!M32),M4-Junio!M32,"")</f>
-        <v/>
+        <v>-13668.689999999999</v>
       </c>
       <c r="N26" s="1">
         <f>IF(ISNUMBER(Junio!N32),N4-Junio!N32,"")</f>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="AC26" s="12">
         <f t="shared" si="7"/>
-        <v>7921.0500000000029</v>
+        <v>-5747.6399999999976</v>
       </c>
     </row>
     <row r="27" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="M33" s="12">
         <f t="shared" si="8"/>
-        <v>72.319999999999709</v>
+        <v>-13596.369999999999</v>
       </c>
       <c r="N33" s="12">
         <f t="shared" si="8"/>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>20088.019999999997</v>
+        <v>6419.3299999999945</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6402,7 +6402,9 @@
       <c r="J12" s="35"/>
       <c r="K12" s="35"/>
       <c r="L12" s="35"/>
-      <c r="M12" s="35"/>
+      <c r="M12" s="35">
+        <v>21668.69</v>
+      </c>
       <c r="N12" s="35"/>
       <c r="O12" s="35"/>
       <c r="P12" s="35"/>
@@ -6420,7 +6422,7 @@
       <c r="AB12" s="36"/>
       <c r="AC12" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>21668.69</v>
       </c>
       <c r="AD12" s="35"/>
     </row>
@@ -7175,9 +7177,9 @@
         <f t="shared" si="1"/>
         <v>9690.8900000000012</v>
       </c>
-      <c r="M32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="M32" s="12">
+        <f t="shared" si="1"/>
+        <v>21668.69</v>
       </c>
       <c r="N32" s="12">
         <f t="shared" si="1"/>
@@ -7241,7 +7243,7 @@
       </c>
       <c r="AC32" s="12">
         <f t="shared" si="1"/>
-        <v>103678.95000000001</v>
+        <v>125347.64000000001</v>
       </c>
       <c r="AD32" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD7B11D-0CCD-44CD-86B3-C04B1A1E2947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F8CFC9A-3AA3-4E1D-80AF-02569476C3C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -2241,9 +2241,9 @@
         <f>IF(Junio!AA32&gt;0,Junio!AA32,"")</f>
         <v>16845.239999999998</v>
       </c>
-      <c r="AC15" s="1" t="str">
+      <c r="AC15" s="1">
         <f>IF(Junio!AB32&gt;0,Junio!AB32,"")</f>
-        <v/>
+        <v>973.77</v>
       </c>
     </row>
     <row r="16" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6419,7 +6419,10 @@
       <c r="Y12" s="35"/>
       <c r="Z12" s="35"/>
       <c r="AA12" s="35"/>
-      <c r="AB12" s="36"/>
+      <c r="AB12" s="36">
+        <f>990-16.23</f>
+        <v>973.77</v>
+      </c>
       <c r="AC12" s="35">
         <f t="shared" si="0"/>
         <v>21668.69</v>
@@ -7237,9 +7240,9 @@
         <f t="shared" si="1"/>
         <v>16845.239999999998</v>
       </c>
-      <c r="AB32" s="38" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="AB32" s="38">
+        <f t="shared" si="1"/>
+        <v>973.77</v>
       </c>
       <c r="AC32" s="12">
         <f t="shared" si="1"/>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F8CFC9A-3AA3-4E1D-80AF-02569476C3C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD62829-3EC2-499E-84CE-1A4636831C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="R15" s="1">
         <f>IF(Junio!R32&gt;0,Junio!R32,"")</f>
-        <v>12236.69</v>
+        <v>13360.970000000001</v>
       </c>
       <c r="S15" s="1">
         <f>IF(Junio!S32&gt;0,Junio!S32,"")</f>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="R26" s="1">
         <f>IF(ISNUMBER(Junio!R32),R4-Junio!R32,"")</f>
-        <v>7763.3099999999995</v>
+        <v>6639.0299999999988</v>
       </c>
       <c r="S26" s="1">
         <f>IF(ISNUMBER(Junio!S32),S4-Junio!S32,"")</f>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="AC26" s="12">
         <f t="shared" si="7"/>
-        <v>-5747.6399999999976</v>
+        <v>-6871.9199999999983</v>
       </c>
     </row>
     <row r="27" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>8144.0999999999967</v>
+        <v>7019.8199999999961</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>6419.3299999999945</v>
+        <v>5295.0499999999956</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6449,7 +6449,10 @@
       <c r="O13" s="35"/>
       <c r="P13" s="35"/>
       <c r="Q13" s="35"/>
-      <c r="R13" s="35"/>
+      <c r="R13" s="35">
+        <f>817.79+327-14.87-5.64</f>
+        <v>1124.28</v>
+      </c>
       <c r="S13" s="35"/>
       <c r="T13" s="35"/>
       <c r="U13" s="35"/>
@@ -6462,7 +6465,7 @@
       <c r="AB13" s="36"/>
       <c r="AC13" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1124.28</v>
       </c>
       <c r="AD13" s="35"/>
     </row>
@@ -7202,7 +7205,7 @@
       </c>
       <c r="R32" s="12">
         <f t="shared" si="1"/>
-        <v>12236.69</v>
+        <v>13360.970000000001</v>
       </c>
       <c r="S32" s="12">
         <f t="shared" si="1"/>
@@ -7246,7 +7249,7 @@
       </c>
       <c r="AC32" s="12">
         <f t="shared" si="1"/>
-        <v>125347.64000000001</v>
+        <v>126471.92000000001</v>
       </c>
       <c r="AD32" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD62829-3EC2-499E-84CE-1A4636831C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D943259F-5544-4350-81EF-2ED5765947A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="78">
   <si>
     <t>Presupuesto</t>
   </si>
@@ -275,6 +275,9 @@
   </si>
   <si>
     <t>materiales almohadones</t>
+  </si>
+  <si>
+    <t>seña salon</t>
   </si>
 </sst>
 </file>
@@ -2243,7 +2246,7 @@
       </c>
       <c r="AC15" s="1">
         <f>IF(Junio!AB32&gt;0,Junio!AB32,"")</f>
-        <v>973.77</v>
+        <v>1473.77</v>
       </c>
     </row>
     <row r="16" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6499,12 +6502,16 @@
       <c r="Y14" s="35"/>
       <c r="Z14" s="35"/>
       <c r="AA14" s="35"/>
-      <c r="AB14" s="36"/>
+      <c r="AB14" s="36">
+        <v>500</v>
+      </c>
       <c r="AC14" s="35">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AD14" s="35"/>
+      <c r="AD14" s="35" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="15" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="34">
@@ -7245,7 +7252,7 @@
       </c>
       <c r="AB32" s="38">
         <f t="shared" si="1"/>
-        <v>973.77</v>
+        <v>1473.77</v>
       </c>
       <c r="AC32" s="12">
         <f t="shared" si="1"/>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D943259F-5544-4350-81EF-2ED5765947A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EA6A7EA-E09E-48FA-B30A-8098071A3AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="79">
   <si>
     <t>Presupuesto</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t>seña salon</t>
+  </si>
+  <si>
+    <t>tortera y mac fiestas</t>
   </si>
 </sst>
 </file>
@@ -2206,11 +2209,11 @@
       </c>
       <c r="R15" s="1">
         <f>IF(Junio!R32&gt;0,Junio!R32,"")</f>
-        <v>13360.970000000001</v>
+        <v>16741.82</v>
       </c>
       <c r="S15" s="1">
         <f>IF(Junio!S32&gt;0,Junio!S32,"")</f>
-        <v>276.39</v>
+        <v>1378.1999999999998</v>
       </c>
       <c r="T15" s="1" t="str">
         <f>IF(Junio!T32&gt;0,Junio!T32,"")</f>
@@ -2228,13 +2231,13 @@
         <f>IF(Junio!W32&gt;0,Junio!W32,"")</f>
         <v/>
       </c>
-      <c r="X15" s="1" t="str">
+      <c r="X15" s="1">
         <f>IF(Junio!X32&gt;0,Junio!X32,"")</f>
-        <v/>
-      </c>
-      <c r="Y15" s="1" t="str">
+        <v>215</v>
+      </c>
+      <c r="Y15" s="1">
         <f>IF(Junio!Y32&gt;0,Junio!Y32,"")</f>
-        <v/>
+        <v>719.51</v>
       </c>
       <c r="Z15" s="1" t="str">
         <f>IF(Junio!Z32&gt;0,Junio!Z32,"")</f>
@@ -2246,7 +2249,7 @@
       </c>
       <c r="AC15" s="1">
         <f>IF(Junio!AB32&gt;0,Junio!AB32,"")</f>
-        <v>1473.77</v>
+        <v>3738.28</v>
       </c>
     </row>
     <row r="16" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3228,11 +3231,11 @@
       </c>
       <c r="R26" s="1">
         <f>IF(ISNUMBER(Junio!R32),R4-Junio!R32,"")</f>
-        <v>6639.0299999999988</v>
+        <v>3258.1800000000003</v>
       </c>
       <c r="S26" s="1">
         <f>IF(ISNUMBER(Junio!S32),S4-Junio!S32,"")</f>
-        <v>2223.61</v>
+        <v>1121.8000000000002</v>
       </c>
       <c r="T26" s="1" t="str">
         <f>IF(ISNUMBER(Junio!T32),T4-Junio!T32,"")</f>
@@ -3250,13 +3253,13 @@
         <f>IF(ISNUMBER(Junio!W32),W4-Junio!W32,"")</f>
         <v/>
       </c>
-      <c r="X26" s="1" t="str">
+      <c r="X26" s="1">
         <f>IF(ISNUMBER(Junio!X32),X4-Junio!X32,"")</f>
-        <v/>
-      </c>
-      <c r="Y26" s="1" t="str">
+        <v>1285</v>
+      </c>
+      <c r="Y26" s="1">
         <f>IF(ISNUMBER(Junio!Y32),Y4-Junio!Y32,"")</f>
-        <v/>
+        <v>1280.49</v>
       </c>
       <c r="Z26" s="1" t="str">
         <f>IF(ISNUMBER(Junio!Z32),Z4-Junio!Z32,"")</f>
@@ -3268,7 +3271,7 @@
       </c>
       <c r="AC26" s="12">
         <f t="shared" si="7"/>
-        <v>-6871.9199999999983</v>
+        <v>-8789.0899999999965</v>
       </c>
     </row>
     <row r="27" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4019,11 +4022,11 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>7019.8199999999961</v>
+        <v>3638.9699999999975</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
-        <v>3912.61</v>
+        <v>2810.8</v>
       </c>
       <c r="T33" s="12">
         <f t="shared" si="8"/>
@@ -4043,11 +4046,11 @@
       </c>
       <c r="X33" s="12">
         <f t="shared" si="8"/>
-        <v>790.91000000000008</v>
+        <v>2075.91</v>
       </c>
       <c r="Y33" s="12">
         <f t="shared" si="8"/>
-        <v>219.67000000000007</v>
+        <v>1500.16</v>
       </c>
       <c r="Z33" s="12">
         <f t="shared" si="8"/>
@@ -4059,7 +4062,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>5295.0499999999956</v>
+        <v>3377.8799999999974</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6453,8 +6456,8 @@
       <c r="P13" s="35"/>
       <c r="Q13" s="35"/>
       <c r="R13" s="35">
-        <f>817.79+327-14.87-5.64</f>
-        <v>1124.28</v>
+        <f>817.79+327-14.87-5.64+428-19.04</f>
+        <v>1533.24</v>
       </c>
       <c r="S13" s="35"/>
       <c r="T13" s="35"/>
@@ -6468,7 +6471,7 @@
       <c r="AB13" s="36"/>
       <c r="AC13" s="35">
         <f t="shared" si="0"/>
-        <v>1124.28</v>
+        <v>1533.24</v>
       </c>
       <c r="AD13" s="35"/>
     </row>
@@ -6498,8 +6501,13 @@
       <c r="U14" s="35"/>
       <c r="V14" s="35"/>
       <c r="W14" s="35"/>
-      <c r="X14" s="35"/>
-      <c r="Y14" s="35"/>
+      <c r="X14" s="35">
+        <v>215</v>
+      </c>
+      <c r="Y14" s="35">
+        <f>30-0.49</f>
+        <v>29.51</v>
+      </c>
       <c r="Z14" s="35"/>
       <c r="AA14" s="35"/>
       <c r="AB14" s="36">
@@ -6507,7 +6515,7 @@
       </c>
       <c r="AC14" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>244.51</v>
       </c>
       <c r="AD14" s="35" t="s">
         <v>77</v>
@@ -6533,22 +6541,32 @@
       <c r="O15" s="35"/>
       <c r="P15" s="35"/>
       <c r="Q15" s="35"/>
-      <c r="R15" s="35"/>
+      <c r="R15" s="35">
+        <f>685-11.82</f>
+        <v>673.18</v>
+      </c>
       <c r="S15" s="35"/>
       <c r="T15" s="35"/>
       <c r="U15" s="35"/>
       <c r="V15" s="35"/>
       <c r="W15" s="35"/>
       <c r="X15" s="35"/>
-      <c r="Y15" s="35"/>
+      <c r="Y15" s="35">
+        <v>690</v>
+      </c>
       <c r="Z15" s="35"/>
       <c r="AA15" s="35"/>
-      <c r="AB15" s="36"/>
+      <c r="AB15" s="36">
+        <f>1515-24+84+701-11.49</f>
+        <v>2264.5100000000002</v>
+      </c>
       <c r="AC15" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD15" s="35"/>
+        <v>1363.1799999999998</v>
+      </c>
+      <c r="AD15" s="35" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="16" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="34">
@@ -6570,8 +6588,14 @@
       <c r="O16" s="35"/>
       <c r="P16" s="35"/>
       <c r="Q16" s="35"/>
-      <c r="R16" s="35"/>
-      <c r="S16" s="35"/>
+      <c r="R16" s="35">
+        <f>1917.73-7.02+388</f>
+        <v>2298.71</v>
+      </c>
+      <c r="S16" s="35">
+        <f>1135-33.19</f>
+        <v>1101.81</v>
+      </c>
       <c r="T16" s="35"/>
       <c r="U16" s="35"/>
       <c r="V16" s="35"/>
@@ -6583,7 +6607,7 @@
       <c r="AB16" s="36"/>
       <c r="AC16" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3400.52</v>
       </c>
       <c r="AD16" s="35"/>
     </row>
@@ -7212,11 +7236,11 @@
       </c>
       <c r="R32" s="12">
         <f t="shared" si="1"/>
-        <v>13360.970000000001</v>
+        <v>16741.82</v>
       </c>
       <c r="S32" s="12">
         <f t="shared" si="1"/>
-        <v>276.39</v>
+        <v>1378.1999999999998</v>
       </c>
       <c r="T32" s="12" t="str">
         <f t="shared" si="1"/>
@@ -7234,13 +7258,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Y32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="X32" s="12">
+        <f t="shared" si="1"/>
+        <v>215</v>
+      </c>
+      <c r="Y32" s="12">
+        <f t="shared" si="1"/>
+        <v>719.51</v>
       </c>
       <c r="Z32" s="12" t="str">
         <f t="shared" si="1"/>
@@ -7252,11 +7276,11 @@
       </c>
       <c r="AB32" s="38">
         <f t="shared" si="1"/>
-        <v>1473.77</v>
+        <v>3738.28</v>
       </c>
       <c r="AC32" s="12">
         <f t="shared" si="1"/>
-        <v>126471.92000000001</v>
+        <v>131889.09</v>
       </c>
       <c r="AD32" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EA6A7EA-E09E-48FA-B30A-8098071A3AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7981962B-350B-44DC-BF22-9ED0B8A9F759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="79">
   <si>
     <t>Presupuesto</t>
   </si>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="R15" s="1">
         <f>IF(Junio!R32&gt;0,Junio!R32,"")</f>
-        <v>16741.82</v>
+        <v>18235.61</v>
       </c>
       <c r="S15" s="1">
         <f>IF(Junio!S32&gt;0,Junio!S32,"")</f>
@@ -2239,16 +2239,16 @@
         <f>IF(Junio!Y32&gt;0,Junio!Y32,"")</f>
         <v>719.51</v>
       </c>
-      <c r="Z15" s="1" t="str">
-        <f>IF(Junio!Z32&gt;0,Junio!Z32,"")</f>
-        <v/>
+      <c r="Z15" s="1">
+        <f>IF(Junio!AA32&gt;0,Junio!AA32,"")</f>
+        <v>5500</v>
       </c>
       <c r="AA15" s="1">
-        <f>IF(Junio!AA32&gt;0,Junio!AA32,"")</f>
+        <f>IF(Junio!AB32&gt;0,Junio!AB32,"")</f>
         <v>16845.239999999998</v>
       </c>
       <c r="AC15" s="1">
-        <f>IF(Junio!AB32&gt;0,Junio!AB32,"")</f>
+        <f>IF(Junio!AC32&gt;0,Junio!AC32,"")</f>
         <v>3738.28</v>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="R26" s="1">
         <f>IF(ISNUMBER(Junio!R32),R4-Junio!R32,"")</f>
-        <v>3258.1800000000003</v>
+        <v>1764.3899999999994</v>
       </c>
       <c r="S26" s="1">
         <f>IF(ISNUMBER(Junio!S32),S4-Junio!S32,"")</f>
@@ -3261,17 +3261,17 @@
         <f>IF(ISNUMBER(Junio!Y32),Y4-Junio!Y32,"")</f>
         <v>1280.49</v>
       </c>
-      <c r="Z26" s="1" t="str">
-        <f>IF(ISNUMBER(Junio!Z32),Z4-Junio!Z32,"")</f>
-        <v/>
+      <c r="Z26" s="1">
+        <f>IF(ISNUMBER(Junio!AA32),Z4-Junio!AA32,"")</f>
+        <v>-1650</v>
       </c>
       <c r="AA26" s="1">
-        <f>IF(ISNUMBER(Junio!AA32),AA4-Junio!AA32,"")</f>
+        <f>IF(ISNUMBER(Junio!AB32),AA4-Junio!AB32,"")</f>
         <v>-11845.239999999998</v>
       </c>
       <c r="AC26" s="12">
         <f t="shared" si="7"/>
-        <v>-8789.0899999999965</v>
+        <v>-11932.879999999997</v>
       </c>
     </row>
     <row r="27" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>3638.9699999999975</v>
+        <v>2145.1799999999967</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="Z33" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>-1650</v>
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="8"/>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>3377.8799999999974</v>
+        <v>234.08999999999651</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5828,7 +5828,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AD32"/>
+  <dimension ref="A1:AE32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -5845,14 +5845,14 @@
     <col min="22" max="23" width="13" customWidth="1"/>
     <col min="24" max="24" width="21" customWidth="1"/>
     <col min="25" max="25" width="13" customWidth="1"/>
-    <col min="26" max="26" width="21.42578125" customWidth="1"/>
-    <col min="27" max="27" width="13" customWidth="1"/>
-    <col min="28" max="28" width="14" customWidth="1"/>
-    <col min="29" max="29" width="25" customWidth="1"/>
-    <col min="30" max="30" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="21.42578125" customWidth="1"/>
+    <col min="28" max="28" width="13" customWidth="1"/>
+    <col min="29" max="29" width="14" customWidth="1"/>
+    <col min="30" max="30" width="25" customWidth="1"/>
+    <col min="31" max="31" width="28.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="33" t="s">
         <v>1</v>
       </c>
@@ -5932,19 +5932,22 @@
         <v>71</v>
       </c>
       <c r="AA1" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AC1" s="33" t="s">
+      <c r="AD1" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="AD1" s="33" t="s">
+      <c r="AE1" s="33" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="34">
         <v>1</v>
       </c>
@@ -5976,20 +5979,21 @@
       <c r="X2" s="35"/>
       <c r="Y2" s="35"/>
       <c r="Z2" s="35"/>
-      <c r="AA2" s="35">
+      <c r="AA2" s="35"/>
+      <c r="AB2" s="35">
         <f>208-3.41</f>
         <v>204.59</v>
       </c>
-      <c r="AB2" s="36"/>
-      <c r="AC2" s="35">
-        <f t="shared" ref="AC2:AC31" si="0">SUM(B2:AA2)</f>
+      <c r="AC2" s="36"/>
+      <c r="AD2" s="35">
+        <f>SUM(B2:AB2)</f>
         <v>6638.9299999999994</v>
       </c>
-      <c r="AD2" s="35" t="s">
+      <c r="AE2" s="35" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="34">
         <v>2</v>
       </c>
@@ -6030,14 +6034,15 @@
       <c r="Y3" s="35"/>
       <c r="Z3" s="35"/>
       <c r="AA3" s="35"/>
-      <c r="AB3" s="36"/>
-      <c r="AC3" s="35">
-        <f t="shared" si="0"/>
+      <c r="AB3" s="35"/>
+      <c r="AC3" s="36"/>
+      <c r="AD3" s="35">
+        <f>SUM(B3:AB3)</f>
         <v>17515.509999999998</v>
       </c>
-      <c r="AD3" s="35"/>
-    </row>
-    <row r="4" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AE3" s="35"/>
+    </row>
+    <row r="4" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="34">
         <v>3</v>
       </c>
@@ -6070,14 +6075,15 @@
       <c r="Y4" s="35"/>
       <c r="Z4" s="35"/>
       <c r="AA4" s="35"/>
-      <c r="AB4" s="36"/>
-      <c r="AC4" s="35">
-        <f t="shared" si="0"/>
+      <c r="AB4" s="35"/>
+      <c r="AC4" s="36"/>
+      <c r="AD4" s="35">
+        <f>SUM(B4:AB4)</f>
         <v>628.97</v>
       </c>
-      <c r="AD4" s="35"/>
-    </row>
-    <row r="5" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AE4" s="35"/>
+    </row>
+    <row r="5" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="34">
         <v>4</v>
       </c>
@@ -6109,20 +6115,21 @@
       <c r="X5" s="35"/>
       <c r="Y5" s="35"/>
       <c r="Z5" s="35"/>
-      <c r="AA5" s="35">
+      <c r="AA5" s="35"/>
+      <c r="AB5" s="35">
         <f>980+500+256-8.2-4.2</f>
         <v>1723.6</v>
       </c>
-      <c r="AB5" s="36"/>
-      <c r="AC5" s="35">
-        <f t="shared" si="0"/>
+      <c r="AC5" s="36"/>
+      <c r="AD5" s="35">
+        <f>SUM(B5:AB5)</f>
         <v>2121.42</v>
       </c>
-      <c r="AD5" s="35" t="s">
+      <c r="AE5" s="35" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="34">
         <v>5</v>
       </c>
@@ -6156,20 +6163,21 @@
       <c r="X6" s="35"/>
       <c r="Y6" s="35"/>
       <c r="Z6" s="35"/>
-      <c r="AA6" s="35">
+      <c r="AA6" s="35"/>
+      <c r="AB6" s="35">
         <f>99-1.62</f>
         <v>97.38</v>
       </c>
-      <c r="AB6" s="36"/>
-      <c r="AC6" s="35">
-        <f t="shared" si="0"/>
+      <c r="AC6" s="36"/>
+      <c r="AD6" s="35">
+        <f>SUM(B6:AB6)</f>
         <v>19998.63</v>
       </c>
-      <c r="AD6" s="35" t="s">
+      <c r="AE6" s="35" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="34">
         <v>6</v>
       </c>
@@ -6199,14 +6207,15 @@
       <c r="Y7" s="35"/>
       <c r="Z7" s="35"/>
       <c r="AA7" s="35"/>
-      <c r="AB7" s="36"/>
-      <c r="AC7" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD7" s="35"/>
-    </row>
-    <row r="8" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB7" s="35"/>
+      <c r="AC7" s="36"/>
+      <c r="AD7" s="35">
+        <f>SUM(B7:AB7)</f>
+        <v>0</v>
+      </c>
+      <c r="AE7" s="35"/>
+    </row>
+    <row r="8" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="34">
         <v>7</v>
       </c>
@@ -6239,14 +6248,15 @@
       <c r="Y8" s="35"/>
       <c r="Z8" s="35"/>
       <c r="AA8" s="35"/>
-      <c r="AB8" s="36"/>
-      <c r="AC8" s="35">
-        <f t="shared" si="0"/>
+      <c r="AB8" s="35"/>
+      <c r="AC8" s="36"/>
+      <c r="AD8" s="35">
+        <f>SUM(B8:AB8)</f>
         <v>1304.6799999999998</v>
       </c>
-      <c r="AD8" s="35"/>
-    </row>
-    <row r="9" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AE8" s="35"/>
+    </row>
+    <row r="9" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="34">
         <v>8</v>
       </c>
@@ -6278,19 +6288,20 @@
       <c r="X9" s="35"/>
       <c r="Y9" s="35"/>
       <c r="Z9" s="35"/>
-      <c r="AA9" s="35">
+      <c r="AA9" s="35"/>
+      <c r="AB9" s="35">
         <v>2900</v>
       </c>
-      <c r="AB9" s="36"/>
-      <c r="AC9" s="35">
-        <f t="shared" si="0"/>
+      <c r="AC9" s="36"/>
+      <c r="AD9" s="35">
+        <f>SUM(B9:AB9)</f>
         <v>4186.1900000000005</v>
       </c>
-      <c r="AD9" s="35" t="s">
+      <c r="AE9" s="35" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="34">
         <v>9</v>
       </c>
@@ -6325,20 +6336,21 @@
       <c r="X10" s="35"/>
       <c r="Y10" s="35"/>
       <c r="Z10" s="35"/>
-      <c r="AA10" s="35">
+      <c r="AA10" s="35"/>
+      <c r="AB10" s="35">
         <f>7700+4290-70.33</f>
         <v>11919.67</v>
       </c>
-      <c r="AB10" s="36"/>
-      <c r="AC10" s="35">
-        <f t="shared" si="0"/>
+      <c r="AC10" s="36"/>
+      <c r="AD10" s="35">
+        <f>SUM(B10:AB10)</f>
         <v>22182.57</v>
       </c>
-      <c r="AD10" s="35" t="s">
+      <c r="AE10" s="35" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="34">
         <v>10</v>
       </c>
@@ -6386,14 +6398,15 @@
       <c r="Y11" s="35"/>
       <c r="Z11" s="35"/>
       <c r="AA11" s="35"/>
-      <c r="AB11" s="36"/>
-      <c r="AC11" s="35">
-        <f t="shared" si="0"/>
+      <c r="AB11" s="35"/>
+      <c r="AC11" s="36"/>
+      <c r="AD11" s="35">
+        <f>SUM(B11:AB11)</f>
         <v>29102.05</v>
       </c>
-      <c r="AD11" s="35"/>
-    </row>
-    <row r="12" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AE11" s="35"/>
+    </row>
+    <row r="12" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="34">
         <v>11</v>
       </c>
@@ -6425,17 +6438,18 @@
       <c r="Y12" s="35"/>
       <c r="Z12" s="35"/>
       <c r="AA12" s="35"/>
-      <c r="AB12" s="36">
+      <c r="AB12" s="35"/>
+      <c r="AC12" s="36">
         <f>990-16.23</f>
         <v>973.77</v>
       </c>
-      <c r="AC12" s="35">
-        <f t="shared" si="0"/>
+      <c r="AD12" s="35">
+        <f>SUM(B12:AB12)</f>
         <v>21668.69</v>
       </c>
-      <c r="AD12" s="35"/>
-    </row>
-    <row r="13" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AE12" s="35"/>
+    </row>
+    <row r="13" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="34">
         <v>12</v>
       </c>
@@ -6468,14 +6482,15 @@
       <c r="Y13" s="35"/>
       <c r="Z13" s="35"/>
       <c r="AA13" s="35"/>
-      <c r="AB13" s="36"/>
-      <c r="AC13" s="35">
-        <f t="shared" si="0"/>
+      <c r="AB13" s="35"/>
+      <c r="AC13" s="36"/>
+      <c r="AD13" s="35">
+        <f>SUM(B13:AB13)</f>
         <v>1533.24</v>
       </c>
-      <c r="AD13" s="35"/>
-    </row>
-    <row r="14" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AE13" s="35"/>
+    </row>
+    <row r="14" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="34">
         <v>13</v>
       </c>
@@ -6510,18 +6525,19 @@
       </c>
       <c r="Z14" s="35"/>
       <c r="AA14" s="35"/>
-      <c r="AB14" s="36">
+      <c r="AB14" s="35"/>
+      <c r="AC14" s="36">
         <v>500</v>
       </c>
-      <c r="AC14" s="35">
-        <f t="shared" si="0"/>
+      <c r="AD14" s="35">
+        <f>SUM(B14:AB14)</f>
         <v>244.51</v>
       </c>
-      <c r="AD14" s="35" t="s">
+      <c r="AE14" s="35" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="34">
         <v>14</v>
       </c>
@@ -6556,19 +6572,20 @@
       </c>
       <c r="Z15" s="35"/>
       <c r="AA15" s="35"/>
-      <c r="AB15" s="36">
+      <c r="AB15" s="35"/>
+      <c r="AC15" s="36">
         <f>1515-24+84+701-11.49</f>
         <v>2264.5100000000002</v>
       </c>
-      <c r="AC15" s="35">
-        <f t="shared" si="0"/>
+      <c r="AD15" s="35">
+        <f>SUM(B15:AB15)</f>
         <v>1363.1799999999998</v>
       </c>
-      <c r="AD15" s="35" t="s">
+      <c r="AE15" s="35" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="34">
         <v>15</v>
       </c>
@@ -6604,14 +6621,15 @@
       <c r="Y16" s="35"/>
       <c r="Z16" s="35"/>
       <c r="AA16" s="35"/>
-      <c r="AB16" s="36"/>
-      <c r="AC16" s="35">
-        <f t="shared" si="0"/>
+      <c r="AB16" s="35"/>
+      <c r="AC16" s="36"/>
+      <c r="AD16" s="35">
+        <f>SUM(B16:AB16)</f>
         <v>3400.52</v>
       </c>
-      <c r="AD16" s="35"/>
-    </row>
-    <row r="17" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AE16" s="35"/>
+    </row>
+    <row r="17" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="34">
         <v>16</v>
       </c>
@@ -6631,7 +6649,10 @@
       <c r="O17" s="35"/>
       <c r="P17" s="35"/>
       <c r="Q17" s="35"/>
-      <c r="R17" s="35"/>
+      <c r="R17" s="35">
+        <f>351.7+897+270-5.77-14.71-4.43</f>
+        <v>1493.79</v>
+      </c>
       <c r="S17" s="35"/>
       <c r="T17" s="35"/>
       <c r="U17" s="35"/>
@@ -6640,15 +6661,18 @@
       <c r="X17" s="35"/>
       <c r="Y17" s="35"/>
       <c r="Z17" s="35"/>
-      <c r="AA17" s="35"/>
-      <c r="AB17" s="36"/>
-      <c r="AC17" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD17" s="35"/>
-    </row>
-    <row r="18" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AA17" s="35">
+        <v>5500</v>
+      </c>
+      <c r="AB17" s="35"/>
+      <c r="AC17" s="36"/>
+      <c r="AD17" s="35">
+        <f>SUM(B17:AB17)</f>
+        <v>6993.79</v>
+      </c>
+      <c r="AE17" s="35"/>
+    </row>
+    <row r="18" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="34">
         <v>17</v>
       </c>
@@ -6678,14 +6702,15 @@
       <c r="Y18" s="35"/>
       <c r="Z18" s="35"/>
       <c r="AA18" s="35"/>
-      <c r="AB18" s="36"/>
-      <c r="AC18" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD18" s="35"/>
-    </row>
-    <row r="19" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB18" s="35"/>
+      <c r="AC18" s="36"/>
+      <c r="AD18" s="35">
+        <f>SUM(B18:AB18)</f>
+        <v>0</v>
+      </c>
+      <c r="AE18" s="35"/>
+    </row>
+    <row r="19" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="34">
         <v>18</v>
       </c>
@@ -6715,14 +6740,15 @@
       <c r="Y19" s="35"/>
       <c r="Z19" s="35"/>
       <c r="AA19" s="35"/>
-      <c r="AB19" s="36"/>
-      <c r="AC19" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD19" s="35"/>
-    </row>
-    <row r="20" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB19" s="35"/>
+      <c r="AC19" s="36"/>
+      <c r="AD19" s="35">
+        <f>SUM(B19:AB19)</f>
+        <v>0</v>
+      </c>
+      <c r="AE19" s="35"/>
+    </row>
+    <row r="20" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="34">
         <v>19</v>
       </c>
@@ -6752,14 +6778,15 @@
       <c r="Y20" s="35"/>
       <c r="Z20" s="35"/>
       <c r="AA20" s="35"/>
-      <c r="AB20" s="36"/>
-      <c r="AC20" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD20" s="35"/>
-    </row>
-    <row r="21" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB20" s="35"/>
+      <c r="AC20" s="36"/>
+      <c r="AD20" s="35">
+        <f>SUM(B20:AB20)</f>
+        <v>0</v>
+      </c>
+      <c r="AE20" s="35"/>
+    </row>
+    <row r="21" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="34">
         <v>20</v>
       </c>
@@ -6789,14 +6816,15 @@
       <c r="Y21" s="35"/>
       <c r="Z21" s="35"/>
       <c r="AA21" s="35"/>
-      <c r="AB21" s="36"/>
-      <c r="AC21" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD21" s="35"/>
-    </row>
-    <row r="22" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB21" s="35"/>
+      <c r="AC21" s="36"/>
+      <c r="AD21" s="35">
+        <f>SUM(B21:AB21)</f>
+        <v>0</v>
+      </c>
+      <c r="AE21" s="35"/>
+    </row>
+    <row r="22" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="34">
         <v>21</v>
       </c>
@@ -6826,14 +6854,15 @@
       <c r="Y22" s="35"/>
       <c r="Z22" s="35"/>
       <c r="AA22" s="35"/>
-      <c r="AB22" s="36"/>
-      <c r="AC22" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD22" s="35"/>
-    </row>
-    <row r="23" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB22" s="35"/>
+      <c r="AC22" s="36"/>
+      <c r="AD22" s="35">
+        <f>SUM(B22:AB22)</f>
+        <v>0</v>
+      </c>
+      <c r="AE22" s="35"/>
+    </row>
+    <row r="23" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="34">
         <v>22</v>
       </c>
@@ -6863,14 +6892,15 @@
       <c r="Y23" s="35"/>
       <c r="Z23" s="35"/>
       <c r="AA23" s="35"/>
-      <c r="AB23" s="36"/>
-      <c r="AC23" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD23" s="35"/>
-    </row>
-    <row r="24" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB23" s="35"/>
+      <c r="AC23" s="36"/>
+      <c r="AD23" s="35">
+        <f>SUM(B23:AB23)</f>
+        <v>0</v>
+      </c>
+      <c r="AE23" s="35"/>
+    </row>
+    <row r="24" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="34">
         <v>23</v>
       </c>
@@ -6900,14 +6930,15 @@
       <c r="Y24" s="35"/>
       <c r="Z24" s="35"/>
       <c r="AA24" s="35"/>
-      <c r="AB24" s="36"/>
-      <c r="AC24" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD24" s="35"/>
-    </row>
-    <row r="25" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB24" s="35"/>
+      <c r="AC24" s="36"/>
+      <c r="AD24" s="35">
+        <f>SUM(B24:AB24)</f>
+        <v>0</v>
+      </c>
+      <c r="AE24" s="35"/>
+    </row>
+    <row r="25" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="34">
         <v>24</v>
       </c>
@@ -6937,14 +6968,15 @@
       <c r="Y25" s="35"/>
       <c r="Z25" s="35"/>
       <c r="AA25" s="35"/>
-      <c r="AB25" s="36"/>
-      <c r="AC25" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD25" s="35"/>
-    </row>
-    <row r="26" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB25" s="35"/>
+      <c r="AC25" s="36"/>
+      <c r="AD25" s="35">
+        <f>SUM(B25:AB25)</f>
+        <v>0</v>
+      </c>
+      <c r="AE25" s="35"/>
+    </row>
+    <row r="26" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="34">
         <v>25</v>
       </c>
@@ -6974,14 +7006,15 @@
       <c r="Y26" s="35"/>
       <c r="Z26" s="35"/>
       <c r="AA26" s="35"/>
-      <c r="AB26" s="36"/>
-      <c r="AC26" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD26" s="35"/>
-    </row>
-    <row r="27" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB26" s="35"/>
+      <c r="AC26" s="36"/>
+      <c r="AD26" s="35">
+        <f>SUM(B26:AB26)</f>
+        <v>0</v>
+      </c>
+      <c r="AE26" s="35"/>
+    </row>
+    <row r="27" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="34">
         <v>26</v>
       </c>
@@ -7011,14 +7044,15 @@
       <c r="Y27" s="35"/>
       <c r="Z27" s="35"/>
       <c r="AA27" s="35"/>
-      <c r="AB27" s="36"/>
-      <c r="AC27" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD27" s="35"/>
-    </row>
-    <row r="28" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB27" s="35"/>
+      <c r="AC27" s="36"/>
+      <c r="AD27" s="35">
+        <f>SUM(B27:AB27)</f>
+        <v>0</v>
+      </c>
+      <c r="AE27" s="35"/>
+    </row>
+    <row r="28" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="34">
         <v>27</v>
       </c>
@@ -7048,14 +7082,15 @@
       <c r="Y28" s="35"/>
       <c r="Z28" s="35"/>
       <c r="AA28" s="35"/>
-      <c r="AB28" s="36"/>
-      <c r="AC28" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD28" s="35"/>
-    </row>
-    <row r="29" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB28" s="35"/>
+      <c r="AC28" s="36"/>
+      <c r="AD28" s="35">
+        <f>SUM(B28:AB28)</f>
+        <v>0</v>
+      </c>
+      <c r="AE28" s="35"/>
+    </row>
+    <row r="29" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="34">
         <v>28</v>
       </c>
@@ -7085,14 +7120,15 @@
       <c r="Y29" s="35"/>
       <c r="Z29" s="35"/>
       <c r="AA29" s="35"/>
-      <c r="AB29" s="36"/>
-      <c r="AC29" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD29" s="35"/>
-    </row>
-    <row r="30" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB29" s="35"/>
+      <c r="AC29" s="36"/>
+      <c r="AD29" s="35">
+        <f>SUM(B29:AB29)</f>
+        <v>0</v>
+      </c>
+      <c r="AE29" s="35"/>
+    </row>
+    <row r="30" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="34">
         <v>29</v>
       </c>
@@ -7122,14 +7158,15 @@
       <c r="Y30" s="35"/>
       <c r="Z30" s="35"/>
       <c r="AA30" s="35"/>
-      <c r="AB30" s="36"/>
-      <c r="AC30" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD30" s="35"/>
-    </row>
-    <row r="31" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB30" s="35"/>
+      <c r="AC30" s="36"/>
+      <c r="AD30" s="35">
+        <f>SUM(B30:AB30)</f>
+        <v>0</v>
+      </c>
+      <c r="AE30" s="35"/>
+    </row>
+    <row r="31" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="34">
         <v>30</v>
       </c>
@@ -7159,130 +7196,135 @@
       <c r="Y31" s="35"/>
       <c r="Z31" s="35"/>
       <c r="AA31" s="35"/>
-      <c r="AB31" s="36"/>
-      <c r="AC31" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD31" s="35"/>
-    </row>
-    <row r="32" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB31" s="35"/>
+      <c r="AC31" s="36"/>
+      <c r="AD31" s="35">
+        <f>SUM(B31:AB31)</f>
+        <v>0</v>
+      </c>
+      <c r="AE31" s="35"/>
+    </row>
+    <row r="32" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
         <v>53</v>
       </c>
       <c r="B32" s="12" t="str">
-        <f t="shared" ref="B32:AC32" si="1">IF(COUNTA(B2:B31)&gt;0,SUM(B2:B31),"")</f>
+        <f t="shared" ref="B32:AD32" si="0">IF(COUNTA(B2:B31)&gt;0,SUM(B2:B31),"")</f>
         <v/>
       </c>
       <c r="C32" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="D32" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>15540.52</v>
       </c>
       <c r="E32" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>10990.82</v>
       </c>
       <c r="F32" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>26054</v>
       </c>
       <c r="G32" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1015</v>
       </c>
       <c r="H32" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3291.56</v>
       </c>
       <c r="I32" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2841.65</v>
       </c>
       <c r="J32" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1000</v>
       </c>
       <c r="K32" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1286.19</v>
       </c>
       <c r="L32" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>9690.8900000000012</v>
       </c>
       <c r="M32" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>21668.69</v>
       </c>
       <c r="N32" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>810</v>
       </c>
       <c r="O32" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="P32" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1800</v>
       </c>
       <c r="Q32" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="R32" s="12">
-        <f t="shared" si="1"/>
-        <v>16741.82</v>
+        <f t="shared" si="0"/>
+        <v>18235.61</v>
       </c>
       <c r="S32" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1378.1999999999998</v>
       </c>
       <c r="T32" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="U32" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="V32" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="W32" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="X32" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>215</v>
       </c>
       <c r="Y32" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>719.51</v>
       </c>
       <c r="Z32" s="12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="AA32" s="12">
-        <f t="shared" si="1"/>
+        <f>SUM(AA2:AA31)</f>
+        <v>5500</v>
+      </c>
+      <c r="AB32" s="12">
+        <f t="shared" si="0"/>
         <v>16845.239999999998</v>
       </c>
-      <c r="AB32" s="38">
-        <f t="shared" si="1"/>
+      <c r="AC32" s="38">
+        <f t="shared" si="0"/>
         <v>3738.28</v>
       </c>
-      <c r="AC32" s="12">
-        <f t="shared" si="1"/>
-        <v>131889.09</v>
-      </c>
-      <c r="AD32" s="39"/>
+      <c r="AD32" s="12">
+        <f t="shared" si="0"/>
+        <v>138882.88</v>
+      </c>
+      <c r="AE32" s="39"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7981962B-350B-44DC-BF22-9ED0B8A9F759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70D08AFA-A64D-4639-A1F6-007DA2DB903C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="80">
   <si>
     <t>Presupuesto</t>
   </si>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t>tortera y mac fiestas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Almohadones </t>
   </si>
 </sst>
 </file>
@@ -2161,7 +2164,7 @@
       </c>
       <c r="F15" s="1">
         <f>IF(Junio!F32&gt;0,Junio!F32,"")</f>
-        <v>26054</v>
+        <v>37432</v>
       </c>
       <c r="G15" s="1">
         <f>IF(Junio!G32&gt;0,Junio!G32,"")</f>
@@ -2209,7 +2212,7 @@
       </c>
       <c r="R15" s="1">
         <f>IF(Junio!R32&gt;0,Junio!R32,"")</f>
-        <v>18235.61</v>
+        <v>19225.12</v>
       </c>
       <c r="S15" s="1">
         <f>IF(Junio!S32&gt;0,Junio!S32,"")</f>
@@ -2237,7 +2240,7 @@
       </c>
       <c r="Y15" s="1">
         <f>IF(Junio!Y32&gt;0,Junio!Y32,"")</f>
-        <v>719.51</v>
+        <v>2432.9499999999998</v>
       </c>
       <c r="Z15" s="1">
         <f>IF(Junio!AA32&gt;0,Junio!AA32,"")</f>
@@ -2245,7 +2248,7 @@
       </c>
       <c r="AA15" s="1">
         <f>IF(Junio!AB32&gt;0,Junio!AB32,"")</f>
-        <v>16845.239999999998</v>
+        <v>21845.239999999998</v>
       </c>
       <c r="AC15" s="1">
         <f>IF(Junio!AC32&gt;0,Junio!AC32,"")</f>
@@ -3183,7 +3186,7 @@
       </c>
       <c r="F26" s="1">
         <f>IF(ISNUMBER(Junio!F32),F4-Junio!F32,"")</f>
-        <v>9446</v>
+        <v>-1932</v>
       </c>
       <c r="G26" s="1">
         <f>IF(ISNUMBER(Junio!G32),G4-Junio!G32,"")</f>
@@ -3231,7 +3234,7 @@
       </c>
       <c r="R26" s="1">
         <f>IF(ISNUMBER(Junio!R32),R4-Junio!R32,"")</f>
-        <v>1764.3899999999994</v>
+        <v>774.88000000000102</v>
       </c>
       <c r="S26" s="1">
         <f>IF(ISNUMBER(Junio!S32),S4-Junio!S32,"")</f>
@@ -3259,7 +3262,7 @@
       </c>
       <c r="Y26" s="1">
         <f>IF(ISNUMBER(Junio!Y32),Y4-Junio!Y32,"")</f>
-        <v>1280.49</v>
+        <v>-432.94999999999982</v>
       </c>
       <c r="Z26" s="1">
         <f>IF(ISNUMBER(Junio!AA32),Z4-Junio!AA32,"")</f>
@@ -3267,11 +3270,11 @@
       </c>
       <c r="AA26" s="1">
         <f>IF(ISNUMBER(Junio!AB32),AA4-Junio!AB32,"")</f>
-        <v>-11845.239999999998</v>
+        <v>-16845.239999999998</v>
       </c>
       <c r="AC26" s="12">
         <f t="shared" si="7"/>
-        <v>-11932.879999999997</v>
+        <v>-31013.829999999998</v>
       </c>
     </row>
     <row r="27" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3974,7 +3977,7 @@
       </c>
       <c r="F33" s="12">
         <f t="shared" si="8"/>
-        <v>9492</v>
+        <v>-1886</v>
       </c>
       <c r="G33" s="12">
         <f t="shared" si="8"/>
@@ -4022,7 +4025,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>2145.1799999999967</v>
+        <v>1155.6699999999983</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
@@ -4050,7 +4053,7 @@
       </c>
       <c r="Y33" s="12">
         <f t="shared" si="8"/>
-        <v>1500.16</v>
+        <v>-213.27999999999975</v>
       </c>
       <c r="Z33" s="12">
         <f t="shared" si="8"/>
@@ -4058,11 +4061,11 @@
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="8"/>
-        <v>-11550.809999999998</v>
+        <v>-16550.809999999998</v>
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>234.08999999999651</v>
+        <v>-18846.86</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5986,7 +5989,7 @@
       </c>
       <c r="AC2" s="36"/>
       <c r="AD2" s="35">
-        <f>SUM(B2:AB2)</f>
+        <f t="shared" ref="AD2:AD31" si="0">SUM(B2:AB2)</f>
         <v>6638.9299999999994</v>
       </c>
       <c r="AE2" s="35" t="s">
@@ -6037,7 +6040,7 @@
       <c r="AB3" s="35"/>
       <c r="AC3" s="36"/>
       <c r="AD3" s="35">
-        <f>SUM(B3:AB3)</f>
+        <f t="shared" si="0"/>
         <v>17515.509999999998</v>
       </c>
       <c r="AE3" s="35"/>
@@ -6078,7 +6081,7 @@
       <c r="AB4" s="35"/>
       <c r="AC4" s="36"/>
       <c r="AD4" s="35">
-        <f>SUM(B4:AB4)</f>
+        <f t="shared" si="0"/>
         <v>628.97</v>
       </c>
       <c r="AE4" s="35"/>
@@ -6122,7 +6125,7 @@
       </c>
       <c r="AC5" s="36"/>
       <c r="AD5" s="35">
-        <f>SUM(B5:AB5)</f>
+        <f t="shared" si="0"/>
         <v>2121.42</v>
       </c>
       <c r="AE5" s="35" t="s">
@@ -6170,7 +6173,7 @@
       </c>
       <c r="AC6" s="36"/>
       <c r="AD6" s="35">
-        <f>SUM(B6:AB6)</f>
+        <f t="shared" si="0"/>
         <v>19998.63</v>
       </c>
       <c r="AE6" s="35" t="s">
@@ -6210,7 +6213,7 @@
       <c r="AB7" s="35"/>
       <c r="AC7" s="36"/>
       <c r="AD7" s="35">
-        <f>SUM(B7:AB7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE7" s="35"/>
@@ -6251,7 +6254,7 @@
       <c r="AB8" s="35"/>
       <c r="AC8" s="36"/>
       <c r="AD8" s="35">
-        <f>SUM(B8:AB8)</f>
+        <f t="shared" si="0"/>
         <v>1304.6799999999998</v>
       </c>
       <c r="AE8" s="35"/>
@@ -6294,7 +6297,7 @@
       </c>
       <c r="AC9" s="36"/>
       <c r="AD9" s="35">
-        <f>SUM(B9:AB9)</f>
+        <f t="shared" si="0"/>
         <v>4186.1900000000005</v>
       </c>
       <c r="AE9" s="35" t="s">
@@ -6343,7 +6346,7 @@
       </c>
       <c r="AC10" s="36"/>
       <c r="AD10" s="35">
-        <f>SUM(B10:AB10)</f>
+        <f t="shared" si="0"/>
         <v>22182.57</v>
       </c>
       <c r="AE10" s="35" t="s">
@@ -6401,7 +6404,7 @@
       <c r="AB11" s="35"/>
       <c r="AC11" s="36"/>
       <c r="AD11" s="35">
-        <f>SUM(B11:AB11)</f>
+        <f t="shared" si="0"/>
         <v>29102.05</v>
       </c>
       <c r="AE11" s="35"/>
@@ -6444,7 +6447,7 @@
         <v>973.77</v>
       </c>
       <c r="AD12" s="35">
-        <f>SUM(B12:AB12)</f>
+        <f t="shared" si="0"/>
         <v>21668.69</v>
       </c>
       <c r="AE12" s="35"/>
@@ -6485,7 +6488,7 @@
       <c r="AB13" s="35"/>
       <c r="AC13" s="36"/>
       <c r="AD13" s="35">
-        <f>SUM(B13:AB13)</f>
+        <f t="shared" si="0"/>
         <v>1533.24</v>
       </c>
       <c r="AE13" s="35"/>
@@ -6530,7 +6533,7 @@
         <v>500</v>
       </c>
       <c r="AD14" s="35">
-        <f>SUM(B14:AB14)</f>
+        <f t="shared" si="0"/>
         <v>244.51</v>
       </c>
       <c r="AE14" s="35" t="s">
@@ -6578,7 +6581,7 @@
         <v>2264.5100000000002</v>
       </c>
       <c r="AD15" s="35">
-        <f>SUM(B15:AB15)</f>
+        <f t="shared" si="0"/>
         <v>1363.1799999999998</v>
       </c>
       <c r="AE15" s="35" t="s">
@@ -6624,7 +6627,7 @@
       <c r="AB16" s="35"/>
       <c r="AC16" s="36"/>
       <c r="AD16" s="35">
-        <f>SUM(B16:AB16)</f>
+        <f t="shared" si="0"/>
         <v>3400.52</v>
       </c>
       <c r="AE16" s="35"/>
@@ -6667,7 +6670,7 @@
       <c r="AB17" s="35"/>
       <c r="AC17" s="36"/>
       <c r="AD17" s="35">
-        <f>SUM(B17:AB17)</f>
+        <f t="shared" si="0"/>
         <v>6993.79</v>
       </c>
       <c r="AE17" s="35"/>
@@ -6680,7 +6683,9 @@
       <c r="C18" s="35"/>
       <c r="D18" s="35"/>
       <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
+      <c r="F18" s="35">
+        <v>11378</v>
+      </c>
       <c r="G18" s="35"/>
       <c r="H18" s="35"/>
       <c r="I18" s="35"/>
@@ -6692,7 +6697,10 @@
       <c r="O18" s="35"/>
       <c r="P18" s="35"/>
       <c r="Q18" s="35"/>
-      <c r="R18" s="35"/>
+      <c r="R18" s="35">
+        <f>1006-16.49</f>
+        <v>989.51</v>
+      </c>
       <c r="S18" s="35"/>
       <c r="T18" s="35"/>
       <c r="U18" s="35"/>
@@ -6705,8 +6713,8 @@
       <c r="AB18" s="35"/>
       <c r="AC18" s="36"/>
       <c r="AD18" s="35">
-        <f>SUM(B18:AB18)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>12367.51</v>
       </c>
       <c r="AE18" s="35"/>
     </row>
@@ -6737,16 +6745,23 @@
       <c r="V19" s="35"/>
       <c r="W19" s="35"/>
       <c r="X19" s="35"/>
-      <c r="Y19" s="35"/>
+      <c r="Y19" s="35">
+        <f>965+66+711-15.82-1.08-11.66</f>
+        <v>1713.44</v>
+      </c>
       <c r="Z19" s="35"/>
       <c r="AA19" s="35"/>
-      <c r="AB19" s="35"/>
+      <c r="AB19" s="35">
+        <v>5000</v>
+      </c>
       <c r="AC19" s="36"/>
       <c r="AD19" s="35">
-        <f>SUM(B19:AB19)</f>
-        <v>0</v>
-      </c>
-      <c r="AE19" s="35"/>
+        <f t="shared" si="0"/>
+        <v>6713.4400000000005</v>
+      </c>
+      <c r="AE19" s="35" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="20" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="34">
@@ -6781,7 +6796,7 @@
       <c r="AB20" s="35"/>
       <c r="AC20" s="36"/>
       <c r="AD20" s="35">
-        <f>SUM(B20:AB20)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE20" s="35"/>
@@ -6819,7 +6834,7 @@
       <c r="AB21" s="35"/>
       <c r="AC21" s="36"/>
       <c r="AD21" s="35">
-        <f>SUM(B21:AB21)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE21" s="35"/>
@@ -6857,7 +6872,7 @@
       <c r="AB22" s="35"/>
       <c r="AC22" s="36"/>
       <c r="AD22" s="35">
-        <f>SUM(B22:AB22)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE22" s="35"/>
@@ -6895,7 +6910,7 @@
       <c r="AB23" s="35"/>
       <c r="AC23" s="36"/>
       <c r="AD23" s="35">
-        <f>SUM(B23:AB23)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE23" s="35"/>
@@ -6933,7 +6948,7 @@
       <c r="AB24" s="35"/>
       <c r="AC24" s="36"/>
       <c r="AD24" s="35">
-        <f>SUM(B24:AB24)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE24" s="35"/>
@@ -6971,7 +6986,7 @@
       <c r="AB25" s="35"/>
       <c r="AC25" s="36"/>
       <c r="AD25" s="35">
-        <f>SUM(B25:AB25)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE25" s="35"/>
@@ -7009,7 +7024,7 @@
       <c r="AB26" s="35"/>
       <c r="AC26" s="36"/>
       <c r="AD26" s="35">
-        <f>SUM(B26:AB26)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE26" s="35"/>
@@ -7047,7 +7062,7 @@
       <c r="AB27" s="35"/>
       <c r="AC27" s="36"/>
       <c r="AD27" s="35">
-        <f>SUM(B27:AB27)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE27" s="35"/>
@@ -7085,7 +7100,7 @@
       <c r="AB28" s="35"/>
       <c r="AC28" s="36"/>
       <c r="AD28" s="35">
-        <f>SUM(B28:AB28)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE28" s="35"/>
@@ -7123,7 +7138,7 @@
       <c r="AB29" s="35"/>
       <c r="AC29" s="36"/>
       <c r="AD29" s="35">
-        <f>SUM(B29:AB29)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE29" s="35"/>
@@ -7161,7 +7176,7 @@
       <c r="AB30" s="35"/>
       <c r="AC30" s="36"/>
       <c r="AD30" s="35">
-        <f>SUM(B30:AB30)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE30" s="35"/>
@@ -7199,7 +7214,7 @@
       <c r="AB31" s="35"/>
       <c r="AC31" s="36"/>
       <c r="AD31" s="35">
-        <f>SUM(B31:AB31)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE31" s="35"/>
@@ -7209,103 +7224,103 @@
         <v>53</v>
       </c>
       <c r="B32" s="12" t="str">
-        <f t="shared" ref="B32:AD32" si="0">IF(COUNTA(B2:B31)&gt;0,SUM(B2:B31),"")</f>
+        <f t="shared" ref="B32:AD32" si="1">IF(COUNTA(B2:B31)&gt;0,SUM(B2:B31),"")</f>
         <v/>
       </c>
       <c r="C32" s="12" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="D32" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>15540.52</v>
       </c>
       <c r="E32" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10990.82</v>
       </c>
       <c r="F32" s="12">
-        <f t="shared" si="0"/>
-        <v>26054</v>
+        <f t="shared" si="1"/>
+        <v>37432</v>
       </c>
       <c r="G32" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1015</v>
       </c>
       <c r="H32" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3291.56</v>
       </c>
       <c r="I32" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2841.65</v>
       </c>
       <c r="J32" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1000</v>
       </c>
       <c r="K32" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1286.19</v>
       </c>
       <c r="L32" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9690.8900000000012</v>
       </c>
       <c r="M32" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>21668.69</v>
       </c>
       <c r="N32" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>810</v>
       </c>
       <c r="O32" s="12" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P32" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1800</v>
       </c>
       <c r="Q32" s="12" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="R32" s="12">
-        <f t="shared" si="0"/>
-        <v>18235.61</v>
+        <f t="shared" si="1"/>
+        <v>19225.12</v>
       </c>
       <c r="S32" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1378.1999999999998</v>
       </c>
       <c r="T32" s="12" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="U32" s="12" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="V32" s="12" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="W32" s="12" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X32" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>215</v>
       </c>
       <c r="Y32" s="12">
-        <f t="shared" si="0"/>
-        <v>719.51</v>
+        <f t="shared" si="1"/>
+        <v>2432.9499999999998</v>
       </c>
       <c r="Z32" s="12" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AA32" s="12">
@@ -7313,16 +7328,16 @@
         <v>5500</v>
       </c>
       <c r="AB32" s="12">
-        <f t="shared" si="0"/>
-        <v>16845.239999999998</v>
+        <f t="shared" si="1"/>
+        <v>21845.239999999998</v>
       </c>
       <c r="AC32" s="38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3738.28</v>
       </c>
       <c r="AD32" s="12">
-        <f t="shared" si="0"/>
-        <v>138882.88</v>
+        <f t="shared" si="1"/>
+        <v>157963.83000000002</v>
       </c>
       <c r="AE32" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70D08AFA-A64D-4639-A1F6-007DA2DB903C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C192F2E-E1A7-4DE8-96C6-46A816A8FA90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -2198,9 +2198,9 @@
         <f>IF(Junio!N32&gt;0,Junio!N32,"")</f>
         <v>810</v>
       </c>
-      <c r="O15" s="1" t="str">
+      <c r="O15" s="1">
         <f>IF(Junio!O32&gt;0,Junio!O32,"")</f>
-        <v/>
+        <v>804.4</v>
       </c>
       <c r="P15" s="1">
         <f>IF(Junio!P32&gt;0,Junio!P32,"")</f>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="AC15" s="1">
         <f>IF(Junio!AC32&gt;0,Junio!AC32,"")</f>
-        <v>3738.28</v>
+        <v>16813.899999999998</v>
       </c>
     </row>
     <row r="16" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3220,9 +3220,9 @@
         <f>IF(ISNUMBER(Junio!N32),N4-Junio!N32,"")</f>
         <v>40</v>
       </c>
-      <c r="O26" s="1" t="str">
+      <c r="O26" s="1">
         <f>IF(ISNUMBER(Junio!O32),O4-Junio!O32,"")</f>
-        <v/>
+        <v>10195.6</v>
       </c>
       <c r="P26" s="1">
         <f>IF(ISNUMBER(Junio!P32),P4-Junio!P32,"")</f>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AC26" s="12">
         <f t="shared" si="7"/>
-        <v>-31013.829999999998</v>
+        <v>-20818.229999999996</v>
       </c>
     </row>
     <row r="27" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="O33" s="12">
         <f t="shared" si="8"/>
-        <v>1219.2399999999998</v>
+        <v>11414.84</v>
       </c>
       <c r="P33" s="12">
         <f t="shared" si="8"/>
@@ -4065,7 +4065,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>-18846.86</v>
+        <v>-8651.260000000002</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6818,7 +6818,9 @@
       <c r="L21" s="35"/>
       <c r="M21" s="35"/>
       <c r="N21" s="35"/>
-      <c r="O21" s="35"/>
+      <c r="O21" s="35">
+        <v>1001</v>
+      </c>
       <c r="P21" s="35"/>
       <c r="Q21" s="35"/>
       <c r="R21" s="35"/>
@@ -6835,7 +6837,7 @@
       <c r="AC21" s="36"/>
       <c r="AD21" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="AE21" s="35"/>
     </row>
@@ -6856,7 +6858,9 @@
       <c r="L22" s="35"/>
       <c r="M22" s="35"/>
       <c r="N22" s="35"/>
-      <c r="O22" s="35"/>
+      <c r="O22" s="35">
+        <v>-196.6</v>
+      </c>
       <c r="P22" s="35"/>
       <c r="Q22" s="35"/>
       <c r="R22" s="35"/>
@@ -6870,10 +6874,13 @@
       <c r="Z22" s="35"/>
       <c r="AA22" s="35"/>
       <c r="AB22" s="35"/>
-      <c r="AC22" s="36"/>
+      <c r="AC22" s="36">
+        <f>1780-29.18+462-8.26+394-6.46+815-13.36+983+370-6.07+1052+1264-21.22+909-14.9+2461-40.34+1500-24.59+1250</f>
+        <v>13075.619999999999</v>
+      </c>
       <c r="AD22" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-196.6</v>
       </c>
       <c r="AE22" s="35"/>
     </row>
@@ -7275,9 +7282,9 @@
         <f t="shared" si="1"/>
         <v>810</v>
       </c>
-      <c r="O32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="O32" s="12">
+        <f t="shared" si="1"/>
+        <v>804.4</v>
       </c>
       <c r="P32" s="12">
         <f t="shared" si="1"/>
@@ -7333,11 +7340,11 @@
       </c>
       <c r="AC32" s="38">
         <f t="shared" si="1"/>
-        <v>3738.28</v>
+        <v>16813.899999999998</v>
       </c>
       <c r="AD32" s="12">
         <f t="shared" si="1"/>
-        <v>157963.83000000002</v>
+        <v>158768.23000000001</v>
       </c>
       <c r="AE32" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C192F2E-E1A7-4DE8-96C6-46A816A8FA90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5906D3B1-D698-490F-8207-47A429822B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2212,11 +2212,11 @@
       </c>
       <c r="R15" s="1">
         <f>IF(Junio!R32&gt;0,Junio!R32,"")</f>
-        <v>19225.12</v>
+        <v>19626.129999999997</v>
       </c>
       <c r="S15" s="1">
         <f>IF(Junio!S32&gt;0,Junio!S32,"")</f>
-        <v>1378.1999999999998</v>
+        <v>2295.1999999999998</v>
       </c>
       <c r="T15" s="1" t="str">
         <f>IF(Junio!T32&gt;0,Junio!T32,"")</f>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="AC15" s="1">
         <f>IF(Junio!AC32&gt;0,Junio!AC32,"")</f>
-        <v>16813.899999999998</v>
+        <v>17322.899999999998</v>
       </c>
     </row>
     <row r="16" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3234,11 +3234,11 @@
       </c>
       <c r="R26" s="1">
         <f>IF(ISNUMBER(Junio!R32),R4-Junio!R32,"")</f>
-        <v>774.88000000000102</v>
+        <v>373.87000000000262</v>
       </c>
       <c r="S26" s="1">
         <f>IF(ISNUMBER(Junio!S32),S4-Junio!S32,"")</f>
-        <v>1121.8000000000002</v>
+        <v>204.80000000000018</v>
       </c>
       <c r="T26" s="1" t="str">
         <f>IF(ISNUMBER(Junio!T32),T4-Junio!T32,"")</f>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AC26" s="12">
         <f t="shared" si="7"/>
-        <v>-20818.229999999996</v>
+        <v>-22136.239999999994</v>
       </c>
     </row>
     <row r="27" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4025,11 +4025,11 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>1155.6699999999983</v>
+        <v>754.65999999999985</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
-        <v>2810.8</v>
+        <v>1893.8000000000002</v>
       </c>
       <c r="T33" s="12">
         <f t="shared" si="8"/>
@@ -4065,7 +4065,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>-8651.260000000002</v>
+        <v>-9969.27</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6980,8 +6980,13 @@
       <c r="O25" s="35"/>
       <c r="P25" s="35"/>
       <c r="Q25" s="35"/>
-      <c r="R25" s="35"/>
-      <c r="S25" s="35"/>
+      <c r="R25" s="35">
+        <f>1340.91-S25-22.9</f>
+        <v>401.0100000000001</v>
+      </c>
+      <c r="S25" s="35">
+        <v>917</v>
+      </c>
       <c r="T25" s="35"/>
       <c r="U25" s="35"/>
       <c r="V25" s="35"/>
@@ -6991,10 +6996,12 @@
       <c r="Z25" s="35"/>
       <c r="AA25" s="35"/>
       <c r="AB25" s="35"/>
-      <c r="AC25" s="36"/>
+      <c r="AC25" s="36">
+        <v>509</v>
+      </c>
       <c r="AD25" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1318.0100000000002</v>
       </c>
       <c r="AE25" s="35"/>
     </row>
@@ -7296,11 +7303,11 @@
       </c>
       <c r="R32" s="12">
         <f t="shared" si="1"/>
-        <v>19225.12</v>
+        <v>19626.129999999997</v>
       </c>
       <c r="S32" s="12">
         <f t="shared" si="1"/>
-        <v>1378.1999999999998</v>
+        <v>2295.1999999999998</v>
       </c>
       <c r="T32" s="12" t="str">
         <f t="shared" si="1"/>
@@ -7340,11 +7347,11 @@
       </c>
       <c r="AC32" s="38">
         <f t="shared" si="1"/>
-        <v>16813.899999999998</v>
+        <v>17322.899999999998</v>
       </c>
       <c r="AD32" s="12">
         <f t="shared" si="1"/>
-        <v>158768.23000000001</v>
+        <v>160086.24000000002</v>
       </c>
       <c r="AE32" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Nico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5906D3B1-D698-490F-8207-47A429822B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -23,7 +22,7 @@
     <sheet name="Noviembre" sheetId="8" r:id="rId8"/>
     <sheet name="Diciembre" sheetId="9" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -289,7 +288,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
@@ -902,7 +901,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AJ54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1404,7 +1403,7 @@
         <v>26100</v>
       </c>
       <c r="G6" s="1">
-        <v>1000</v>
+        <v>1015</v>
       </c>
       <c r="H6" s="1">
         <v>3500</v>
@@ -1416,20 +1415,19 @@
         <v>1000</v>
       </c>
       <c r="K6" s="1">
-        <f t="shared" si="6"/>
-        <v>17700</v>
+        <v>18000</v>
       </c>
       <c r="L6" s="1">
-        <v>7500</v>
+        <v>12000</v>
       </c>
       <c r="M6" s="1">
-        <v>7500</v>
+        <v>17000</v>
       </c>
       <c r="N6" s="1">
-        <v>850</v>
+        <v>810</v>
       </c>
       <c r="O6" s="1">
-        <v>4400</v>
+        <v>8000</v>
       </c>
       <c r="P6" s="1">
         <v>1800</v>
@@ -1455,13 +1453,16 @@
       <c r="Y6" s="1">
         <v>2000</v>
       </c>
+      <c r="Z6" s="1">
+        <v>1000</v>
+      </c>
       <c r="AA6" s="1">
         <v>5000</v>
       </c>
       <c r="AB6" s="6"/>
       <c r="AC6" s="1">
-        <f t="shared" si="0"/>
-        <v>131450</v>
+        <f>SUM(B6:AB6)</f>
+        <v>150325</v>
       </c>
       <c r="AD6" s="7">
         <f t="shared" si="1"/>
@@ -1479,15 +1480,15 @@
       </c>
       <c r="AH6" s="8">
         <f t="shared" si="3"/>
-        <v>58225</v>
+        <v>58162.5</v>
       </c>
       <c r="AI6" s="9">
         <f t="shared" si="4"/>
-        <v>50125</v>
+        <v>59562.5</v>
       </c>
       <c r="AJ6" s="10">
         <f t="shared" si="5"/>
-        <v>108350</v>
+        <v>117725</v>
       </c>
     </row>
     <row r="7" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1510,7 +1511,7 @@
         <v>26100</v>
       </c>
       <c r="G7" s="1">
-        <v>1000</v>
+        <v>1015</v>
       </c>
       <c r="H7" s="1">
         <v>3500</v>
@@ -1522,17 +1523,16 @@
         <v>1000</v>
       </c>
       <c r="K7" s="1">
-        <f t="shared" si="6"/>
-        <v>17700</v>
+        <v>18000</v>
       </c>
       <c r="L7" s="1">
-        <v>7500</v>
+        <v>10000</v>
       </c>
       <c r="M7" s="1">
         <v>7500</v>
       </c>
       <c r="N7" s="1">
-        <v>850</v>
+        <v>810</v>
       </c>
       <c r="O7" s="1">
         <v>4400</v>
@@ -1552,6 +1552,9 @@
       <c r="T7" s="1">
         <v>5000</v>
       </c>
+      <c r="U7" s="1">
+        <v>12000</v>
+      </c>
       <c r="W7" s="1">
         <v>3000</v>
       </c>
@@ -1561,16 +1564,13 @@
       <c r="Y7" s="1">
         <v>2000</v>
       </c>
-      <c r="Z7" s="1">
-        <v>1350</v>
-      </c>
       <c r="AA7" s="1">
         <v>5000</v>
       </c>
       <c r="AB7" s="6"/>
       <c r="AC7" s="1">
         <f t="shared" si="0"/>
-        <v>162219</v>
+        <v>175644</v>
       </c>
       <c r="AD7" s="7">
         <f t="shared" si="1"/>
@@ -1588,15 +1588,15 @@
       </c>
       <c r="AH7" s="8">
         <f t="shared" si="3"/>
-        <v>73609.5</v>
+        <v>80322</v>
       </c>
       <c r="AI7" s="9">
         <f t="shared" si="4"/>
-        <v>65459.5</v>
+        <v>72172</v>
       </c>
       <c r="AJ7" s="10">
         <f t="shared" si="5"/>
-        <v>139069</v>
+        <v>152494</v>
       </c>
     </row>
     <row r="8" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1613,7 +1613,7 @@
         <v>26100</v>
       </c>
       <c r="G8" s="1">
-        <v>1000</v>
+        <v>1015</v>
       </c>
       <c r="H8" s="1">
         <v>3500</v>
@@ -1625,17 +1625,16 @@
         <v>1000</v>
       </c>
       <c r="K8" s="1">
-        <f t="shared" si="6"/>
-        <v>17700</v>
+        <v>18000</v>
       </c>
       <c r="L8" s="1">
-        <v>7500</v>
+        <v>10000</v>
       </c>
       <c r="M8" s="1">
         <v>7500</v>
       </c>
       <c r="N8" s="1">
-        <v>850</v>
+        <v>810</v>
       </c>
       <c r="O8" s="1">
         <v>4400</v>
@@ -1655,9 +1654,6 @@
       <c r="T8" s="1">
         <v>5000</v>
       </c>
-      <c r="U8" s="1">
-        <v>12000</v>
-      </c>
       <c r="V8" s="1">
         <v>1500</v>
       </c>
@@ -1676,7 +1672,7 @@
       <c r="AB8" s="6"/>
       <c r="AC8" s="1">
         <f t="shared" si="0"/>
-        <v>146800</v>
+        <v>137575</v>
       </c>
       <c r="AD8" s="7">
         <f t="shared" si="1"/>
@@ -1694,15 +1690,15 @@
       </c>
       <c r="AH8" s="8">
         <f t="shared" si="3"/>
-        <v>65900</v>
+        <v>61287.5</v>
       </c>
       <c r="AI8" s="9">
         <f t="shared" si="4"/>
-        <v>57750</v>
+        <v>53137.5</v>
       </c>
       <c r="AJ8" s="10">
         <f t="shared" si="5"/>
-        <v>123650</v>
+        <v>114425</v>
       </c>
     </row>
     <row r="9" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1722,7 +1718,7 @@
         <v>26100</v>
       </c>
       <c r="G9" s="1">
-        <v>1000</v>
+        <v>1015</v>
       </c>
       <c r="H9" s="1">
         <v>3500</v>
@@ -1734,17 +1730,16 @@
         <v>1000</v>
       </c>
       <c r="K9" s="1">
-        <f t="shared" si="6"/>
-        <v>17700</v>
+        <v>18000</v>
       </c>
       <c r="L9" s="1">
-        <v>7500</v>
+        <v>10000</v>
       </c>
       <c r="M9" s="1">
         <v>7500</v>
       </c>
       <c r="N9" s="1">
-        <v>850</v>
+        <v>810</v>
       </c>
       <c r="O9" s="1">
         <v>4400</v>
@@ -1779,7 +1774,7 @@
       <c r="AB9" s="6"/>
       <c r="AC9" s="1">
         <f t="shared" si="0"/>
-        <v>137719</v>
+        <v>140494</v>
       </c>
       <c r="AD9" s="7">
         <f t="shared" si="1"/>
@@ -1797,15 +1792,15 @@
       </c>
       <c r="AH9" s="8">
         <f t="shared" si="3"/>
-        <v>61359.5</v>
+        <v>62747</v>
       </c>
       <c r="AI9" s="9">
         <f t="shared" si="4"/>
-        <v>53159.5</v>
+        <v>54547</v>
       </c>
       <c r="AJ9" s="10">
         <f t="shared" si="5"/>
-        <v>114519</v>
+        <v>117294</v>
       </c>
     </row>
     <row r="10" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1822,7 +1817,7 @@
         <v>45000</v>
       </c>
       <c r="G10" s="1">
-        <v>1000</v>
+        <v>1015</v>
       </c>
       <c r="H10" s="1">
         <v>3500</v>
@@ -1834,17 +1829,16 @@
         <v>1000</v>
       </c>
       <c r="K10" s="1">
-        <f t="shared" si="6"/>
-        <v>17700</v>
+        <v>18000</v>
       </c>
       <c r="L10" s="1">
-        <v>7500</v>
+        <v>10000</v>
       </c>
       <c r="M10" s="1">
         <v>7500</v>
       </c>
       <c r="N10" s="1">
-        <v>850</v>
+        <v>810</v>
       </c>
       <c r="O10" s="1">
         <v>4400</v>
@@ -1882,7 +1876,7 @@
       <c r="AB10" s="6"/>
       <c r="AC10" s="1">
         <f t="shared" si="0"/>
-        <v>153600</v>
+        <v>156375</v>
       </c>
       <c r="AD10" s="7">
         <f t="shared" si="1"/>
@@ -1900,15 +1894,15 @@
       </c>
       <c r="AH10" s="8">
         <f t="shared" si="3"/>
-        <v>69300</v>
+        <v>70687.5</v>
       </c>
       <c r="AI10" s="9">
         <f t="shared" si="4"/>
-        <v>61100</v>
+        <v>62487.5</v>
       </c>
       <c r="AJ10" s="10">
         <f t="shared" si="5"/>
-        <v>130400</v>
+        <v>133175</v>
       </c>
     </row>
     <row r="12" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4261,7 +4255,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AD33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5830,7 +5824,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AE32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7362,7 +7356,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AD33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8736,7 +8730,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AD33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -10110,7 +10104,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AD32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -11447,7 +11441,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AD33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -12821,7 +12815,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AD32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -14158,7 +14152,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AD33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -2257,105 +2257,105 @@
         <f>IF(Julio!B33&gt;0,Julio!B33,"")</f>
         <v/>
       </c>
-      <c r="C16" s="1" t="str">
+      <c r="C16" s="1">
         <f>IF(Julio!C33&gt;0,Julio!C33,"")</f>
-        <v/>
-      </c>
-      <c r="D16" s="1" t="str">
+        <v>4369</v>
+      </c>
+      <c r="D16" s="1">
         <f>IF(Julio!D33&gt;0,Julio!D33,"")</f>
-        <v/>
+        <v>15600</v>
       </c>
       <c r="E16" s="1" t="str">
         <f>IF(Julio!E33&gt;0,Julio!E33,"")</f>
         <v/>
       </c>
-      <c r="F16" s="1" t="str">
+      <c r="F16" s="1">
         <f>IF(Julio!F33&gt;0,Julio!F33,"")</f>
-        <v/>
-      </c>
-      <c r="G16" s="1" t="str">
+        <v>26100</v>
+      </c>
+      <c r="G16" s="1">
         <f>IF(Julio!G33&gt;0,Julio!G33,"")</f>
-        <v/>
-      </c>
-      <c r="H16" s="1" t="str">
+        <v>1000</v>
+      </c>
+      <c r="H16" s="1">
         <f>IF(Julio!H33&gt;0,Julio!H33,"")</f>
-        <v/>
-      </c>
-      <c r="I16" s="1" t="str">
+        <v>3500</v>
+      </c>
+      <c r="I16" s="1">
         <f>IF(Julio!I33&gt;0,Julio!I33,"")</f>
-        <v/>
-      </c>
-      <c r="J16" s="1" t="str">
+        <v>3000</v>
+      </c>
+      <c r="J16" s="1">
         <f>IF(Julio!J33&gt;0,Julio!J33,"")</f>
-        <v/>
-      </c>
-      <c r="K16" s="1" t="str">
+        <v>1000</v>
+      </c>
+      <c r="K16" s="1">
         <f>IF(Julio!K33&gt;0,Julio!K33,"")</f>
-        <v/>
-      </c>
-      <c r="L16" s="1" t="str">
+        <v>17700</v>
+      </c>
+      <c r="L16" s="1">
         <f>IF(Julio!L33&gt;0,Julio!L33,"")</f>
-        <v/>
-      </c>
-      <c r="M16" s="1" t="str">
+        <v>7500</v>
+      </c>
+      <c r="M16" s="1">
         <f>IF(Julio!M33&gt;0,Julio!M33,"")</f>
-        <v/>
-      </c>
-      <c r="N16" s="1" t="str">
+        <v>7500</v>
+      </c>
+      <c r="N16" s="1">
         <f>IF(Julio!N33&gt;0,Julio!N33,"")</f>
-        <v/>
-      </c>
-      <c r="O16" s="1" t="str">
+        <v>850</v>
+      </c>
+      <c r="O16" s="1">
         <f>IF(Julio!O33&gt;0,Julio!O33,"")</f>
-        <v/>
-      </c>
-      <c r="P16" s="1" t="str">
+        <v>4400</v>
+      </c>
+      <c r="P16" s="1">
         <f>IF(Julio!P33&gt;0,Julio!P33,"")</f>
-        <v/>
-      </c>
-      <c r="Q16" s="1" t="str">
+        <v>1800</v>
+      </c>
+      <c r="Q16" s="1">
         <f>IF(Julio!Q33&gt;0,Julio!Q33,"")</f>
-        <v/>
-      </c>
-      <c r="R16" s="1" t="str">
+        <v>2500</v>
+      </c>
+      <c r="R16" s="1">
         <f>IF(Julio!R33&gt;0,Julio!R33,"")</f>
-        <v/>
-      </c>
-      <c r="S16" s="1" t="str">
+        <v>20000</v>
+      </c>
+      <c r="S16" s="1">
         <f>IF(Julio!S33&gt;0,Julio!S33,"")</f>
-        <v/>
-      </c>
-      <c r="T16" s="1" t="str">
+        <v>2500</v>
+      </c>
+      <c r="T16" s="1">
         <f>IF(Julio!T33&gt;0,Julio!T33,"")</f>
-        <v/>
+        <v>5000</v>
       </c>
       <c r="U16" s="1" t="str">
         <f>IF(Julio!U33&gt;0,Julio!U33,"")</f>
         <v/>
       </c>
-      <c r="V16" s="1" t="str">
+      <c r="V16" s="1">
         <f>IF(Julio!V33&gt;0,Julio!V33,"")</f>
-        <v/>
-      </c>
-      <c r="W16" s="1" t="str">
+        <v>1500</v>
+      </c>
+      <c r="W16" s="1">
         <f>IF(Julio!W33&gt;0,Julio!W33,"")</f>
-        <v/>
-      </c>
-      <c r="X16" s="1" t="str">
+        <v>3000</v>
+      </c>
+      <c r="X16" s="1">
         <f>IF(Julio!X33&gt;0,Julio!X33,"")</f>
-        <v/>
-      </c>
-      <c r="Y16" s="1" t="str">
+        <v>1500</v>
+      </c>
+      <c r="Y16" s="1">
         <f>IF(Julio!Y33&gt;0,Julio!Y33,"")</f>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="Z16" s="1" t="str">
         <f>IF(Julio!Z33&gt;0,Julio!Z33,"")</f>
         <v/>
       </c>
-      <c r="AA16" s="1" t="str">
+      <c r="AA16" s="1">
         <f>IF(Julio!AA33&gt;0,Julio!AA33,"")</f>
-        <v/>
+        <v>5000</v>
       </c>
       <c r="AC16" s="1" t="str">
         <f>IF(Julio!AB33&gt;0,Julio!AB33,"")</f>
@@ -3279,105 +3279,105 @@
         <f>IF(ISNUMBER(Julio!B33),B5-Julio!B33,"")</f>
         <v/>
       </c>
-      <c r="C27" s="1" t="str">
+      <c r="C27" s="1">
         <f>IF(ISNUMBER(Julio!C33),C5-Julio!C33,"")</f>
-        <v/>
-      </c>
-      <c r="D27" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="D27" s="1">
         <f>IF(ISNUMBER(Julio!D33),D5-Julio!D33,"")</f>
-        <v/>
-      </c>
-      <c r="E27" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="E27" s="1">
         <f>IF(ISNUMBER(Julio!E33),E5-Julio!E33,"")</f>
-        <v/>
-      </c>
-      <c r="F27" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="F27" s="1">
         <f>IF(ISNUMBER(Julio!F33),F5-Julio!F33,"")</f>
-        <v/>
-      </c>
-      <c r="G27" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1">
         <f>IF(ISNUMBER(Julio!G33),G5-Julio!G33,"")</f>
-        <v/>
-      </c>
-      <c r="H27" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1">
         <f>IF(ISNUMBER(Julio!H33),H5-Julio!H33,"")</f>
-        <v/>
-      </c>
-      <c r="I27" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="I27" s="1">
         <f>IF(ISNUMBER(Julio!I33),I5-Julio!I33,"")</f>
-        <v/>
-      </c>
-      <c r="J27" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="J27" s="1">
         <f>IF(ISNUMBER(Julio!J33),J5-Julio!J33,"")</f>
-        <v/>
-      </c>
-      <c r="K27" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="K27" s="1">
         <f>IF(ISNUMBER(Julio!K33),K5-Julio!K33,"")</f>
-        <v/>
-      </c>
-      <c r="L27" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="L27" s="1">
         <f>IF(ISNUMBER(Julio!L33),L5-Julio!L33,"")</f>
-        <v/>
-      </c>
-      <c r="M27" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="M27" s="1">
         <f>IF(ISNUMBER(Julio!M33),M5-Julio!M33,"")</f>
-        <v/>
-      </c>
-      <c r="N27" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="N27" s="1">
         <f>IF(ISNUMBER(Julio!N33),N5-Julio!N33,"")</f>
-        <v/>
-      </c>
-      <c r="O27" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="O27" s="1">
         <f>IF(ISNUMBER(Julio!O33),O5-Julio!O33,"")</f>
-        <v/>
-      </c>
-      <c r="P27" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="P27" s="1">
         <f>IF(ISNUMBER(Julio!P33),P5-Julio!P33,"")</f>
-        <v/>
-      </c>
-      <c r="Q27" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="1">
         <f>IF(ISNUMBER(Julio!Q33),Q5-Julio!Q33,"")</f>
-        <v/>
-      </c>
-      <c r="R27" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="R27" s="1">
         <f>IF(ISNUMBER(Julio!R33),R5-Julio!R33,"")</f>
-        <v/>
-      </c>
-      <c r="S27" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="S27" s="1">
         <f>IF(ISNUMBER(Julio!S33),S5-Julio!S33,"")</f>
-        <v/>
-      </c>
-      <c r="T27" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="T27" s="1">
         <f>IF(ISNUMBER(Julio!T33),T5-Julio!T33,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U27" s="1" t="str">
         <f>IF(ISNUMBER(Julio!U33),U5-Julio!U33,"")</f>
         <v/>
       </c>
-      <c r="V27" s="1" t="str">
+      <c r="V27" s="1">
         <f>IF(ISNUMBER(Julio!V33),V5-Julio!V33,"")</f>
-        <v/>
-      </c>
-      <c r="W27" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="W27" s="1">
         <f>IF(ISNUMBER(Julio!W33),W5-Julio!W33,"")</f>
-        <v/>
-      </c>
-      <c r="X27" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="X27" s="1">
         <f>IF(ISNUMBER(Julio!X33),X5-Julio!X33,"")</f>
-        <v/>
-      </c>
-      <c r="Y27" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="1">
         <f>IF(ISNUMBER(Julio!Y33),Y5-Julio!Y33,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Z27" s="1" t="str">
         <f>IF(ISNUMBER(Julio!Z33),Z5-Julio!Z33,"")</f>
         <v/>
       </c>
-      <c r="AA27" s="1" t="str">
+      <c r="AA27" s="1">
         <f>IF(ISNUMBER(Julio!AA33),AA5-Julio!AA33,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC27" s="12">
         <f t="shared" si="7"/>
@@ -8573,35 +8573,81 @@
         <v>31</v>
       </c>
       <c r="B32" s="35"/>
-      <c r="C32" s="35"/>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="35"/>
-      <c r="I32" s="35"/>
-      <c r="J32" s="35"/>
-      <c r="K32" s="35"/>
-      <c r="L32" s="35"/>
-      <c r="M32" s="35"/>
-      <c r="N32" s="35"/>
-      <c r="O32" s="35"/>
-      <c r="P32" s="35"/>
-      <c r="Q32" s="35"/>
-      <c r="R32" s="35"/>
-      <c r="S32" s="35"/>
-      <c r="T32" s="35"/>
+      <c r="C32" s="35">
+        <v>4369</v>
+      </c>
+      <c r="D32" s="35">
+        <v>15600</v>
+      </c>
+      <c r="E32" s="35">
+        <v>0</v>
+      </c>
+      <c r="F32" s="35">
+        <v>26100</v>
+      </c>
+      <c r="G32" s="35">
+        <v>1000</v>
+      </c>
+      <c r="H32" s="35">
+        <v>3500</v>
+      </c>
+      <c r="I32" s="35">
+        <v>3000</v>
+      </c>
+      <c r="J32" s="35">
+        <v>1000</v>
+      </c>
+      <c r="K32" s="35">
+        <v>17700</v>
+      </c>
+      <c r="L32" s="35">
+        <v>7500</v>
+      </c>
+      <c r="M32" s="35">
+        <v>7500</v>
+      </c>
+      <c r="N32" s="35">
+        <v>850</v>
+      </c>
+      <c r="O32" s="35">
+        <v>4400</v>
+      </c>
+      <c r="P32" s="35">
+        <v>1800</v>
+      </c>
+      <c r="Q32" s="35">
+        <v>2500</v>
+      </c>
+      <c r="R32" s="35">
+        <v>20000</v>
+      </c>
+      <c r="S32" s="35">
+        <v>2500</v>
+      </c>
+      <c r="T32" s="35">
+        <v>5000</v>
+      </c>
       <c r="U32" s="35"/>
-      <c r="V32" s="35"/>
-      <c r="W32" s="35"/>
-      <c r="X32" s="35"/>
-      <c r="Y32" s="35"/>
+      <c r="V32" s="35">
+        <v>1500</v>
+      </c>
+      <c r="W32" s="35">
+        <v>3000</v>
+      </c>
+      <c r="X32" s="35">
+        <v>1500</v>
+      </c>
+      <c r="Y32" s="35">
+        <v>2000</v>
+      </c>
       <c r="Z32" s="35"/>
-      <c r="AA32" s="35"/>
+      <c r="AA32" s="35">
+        <v>5000</v>
+      </c>
       <c r="AB32" s="36"/>
       <c r="AC32" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>137319</v>
       </c>
       <c r="AD32" s="35"/>
     </row>
@@ -8613,105 +8659,105 @@
         <f t="shared" ref="B33:AC33" si="1">IF(COUNTA(B2:B32)&gt;0,SUM(B2:B32),"")</f>
         <v/>
       </c>
-      <c r="C33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="D33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="E33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="L33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="N33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Q33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="R33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="C33" s="12">
+        <f t="shared" si="1"/>
+        <v>4369</v>
+      </c>
+      <c r="D33" s="12">
+        <f t="shared" si="1"/>
+        <v>15600</v>
+      </c>
+      <c r="E33" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F33" s="12">
+        <f t="shared" si="1"/>
+        <v>26100</v>
+      </c>
+      <c r="G33" s="12">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="H33" s="12">
+        <f t="shared" si="1"/>
+        <v>3500</v>
+      </c>
+      <c r="I33" s="12">
+        <f t="shared" si="1"/>
+        <v>3000</v>
+      </c>
+      <c r="J33" s="12">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="K33" s="12">
+        <f t="shared" si="1"/>
+        <v>17700</v>
+      </c>
+      <c r="L33" s="12">
+        <f t="shared" si="1"/>
+        <v>7500</v>
+      </c>
+      <c r="M33" s="12">
+        <f t="shared" si="1"/>
+        <v>7500</v>
+      </c>
+      <c r="N33" s="12">
+        <f t="shared" si="1"/>
+        <v>850</v>
+      </c>
+      <c r="O33" s="12">
+        <f t="shared" si="1"/>
+        <v>4400</v>
+      </c>
+      <c r="P33" s="12">
+        <f t="shared" si="1"/>
+        <v>1800</v>
+      </c>
+      <c r="Q33" s="12">
+        <f t="shared" si="1"/>
+        <v>2500</v>
+      </c>
+      <c r="R33" s="12">
+        <f t="shared" si="1"/>
+        <v>20000</v>
+      </c>
+      <c r="S33" s="12">
+        <f t="shared" si="1"/>
+        <v>2500</v>
+      </c>
+      <c r="T33" s="12">
+        <f t="shared" si="1"/>
+        <v>5000</v>
       </c>
       <c r="U33" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="V33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="X33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Y33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="V33" s="12">
+        <f t="shared" si="1"/>
+        <v>1500</v>
+      </c>
+      <c r="W33" s="12">
+        <f t="shared" si="1"/>
+        <v>3000</v>
+      </c>
+      <c r="X33" s="12">
+        <f t="shared" si="1"/>
+        <v>1500</v>
+      </c>
+      <c r="Y33" s="12">
+        <f t="shared" si="1"/>
+        <v>2000</v>
       </c>
       <c r="Z33" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AA33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="AA33" s="12">
+        <f t="shared" si="1"/>
+        <v>5000</v>
       </c>
       <c r="AB33" s="38" t="str">
         <f t="shared" si="1"/>
@@ -8719,7 +8765,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>137319</v>
       </c>
       <c r="AD33" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -1312,7 +1312,7 @@
         <v>1000</v>
       </c>
       <c r="K5" s="1">
-        <f t="shared" ref="K5:K10" si="6">1300+9800+6600</f>
+        <f t="shared" ref="K5" si="6">1300+9800+6600</f>
         <v>17700</v>
       </c>
       <c r="L5" s="1">
@@ -2418,9 +2418,9 @@
         <f>IF(Agosto!N33&gt;0,Agosto!N33,"")</f>
         <v/>
       </c>
-      <c r="O17" s="1" t="str">
+      <c r="O17" s="1">
         <f>IF(Agosto!O33&gt;0,Agosto!O33,"")</f>
-        <v/>
+        <v>491.81</v>
       </c>
       <c r="P17" s="1" t="str">
         <f>IF(Agosto!P33&gt;0,Agosto!P33,"")</f>
@@ -2430,9 +2430,9 @@
         <f>IF(Agosto!Q33&gt;0,Agosto!Q33,"")</f>
         <v/>
       </c>
-      <c r="R17" s="1" t="str">
+      <c r="R17" s="1">
         <f>IF(Agosto!R33&gt;0,Agosto!R33,"")</f>
-        <v/>
+        <v>1219.6400000000001</v>
       </c>
       <c r="S17" s="1" t="str">
         <f>IF(Agosto!S33&gt;0,Agosto!S33,"")</f>
@@ -2454,9 +2454,9 @@
         <f>IF(Agosto!W33&gt;0,Agosto!W33,"")</f>
         <v/>
       </c>
-      <c r="X17" s="1" t="str">
+      <c r="X17" s="1">
         <f>IF(Agosto!X33&gt;0,Agosto!X33,"")</f>
-        <v/>
+        <v>181.21</v>
       </c>
       <c r="Y17" s="1" t="str">
         <f>IF(Agosto!Y33&gt;0,Agosto!Y33,"")</f>
@@ -3440,9 +3440,9 @@
         <f>IF(ISNUMBER(Agosto!N33),N6-Agosto!N33,"")</f>
         <v/>
       </c>
-      <c r="O28" s="1" t="str">
+      <c r="O28" s="1">
         <f>IF(ISNUMBER(Agosto!O33),O6-Agosto!O33,"")</f>
-        <v/>
+        <v>7508.19</v>
       </c>
       <c r="P28" s="1" t="str">
         <f>IF(ISNUMBER(Agosto!P33),P6-Agosto!P33,"")</f>
@@ -3452,9 +3452,9 @@
         <f>IF(ISNUMBER(Agosto!Q33),Q6-Agosto!Q33,"")</f>
         <v/>
       </c>
-      <c r="R28" s="1" t="str">
+      <c r="R28" s="1">
         <f>IF(ISNUMBER(Agosto!R33),R6-Agosto!R33,"")</f>
-        <v/>
+        <v>18780.36</v>
       </c>
       <c r="S28" s="1" t="str">
         <f>IF(ISNUMBER(Agosto!S33),S6-Agosto!S33,"")</f>
@@ -3476,9 +3476,9 @@
         <f>IF(ISNUMBER(Agosto!W33),W6-Agosto!W33,"")</f>
         <v/>
       </c>
-      <c r="X28" s="1" t="str">
+      <c r="X28" s="1">
         <f>IF(ISNUMBER(Agosto!X33),X6-Agosto!X33,"")</f>
-        <v/>
+        <v>1318.79</v>
       </c>
       <c r="Y28" s="1" t="str">
         <f>IF(ISNUMBER(Agosto!Y33),Y6-Agosto!Y33,"")</f>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="AC28" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>27607.34</v>
       </c>
     </row>
     <row r="29" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="O33" s="12">
         <f t="shared" si="8"/>
-        <v>11414.84</v>
+        <v>18923.03</v>
       </c>
       <c r="P33" s="12">
         <f t="shared" si="8"/>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>754.65999999999985</v>
+        <v>19535.02</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="X33" s="12">
         <f t="shared" si="8"/>
-        <v>2075.91</v>
+        <v>3394.7</v>
       </c>
       <c r="Y33" s="12">
         <f t="shared" si="8"/>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>-9969.27</v>
+        <v>17638.07</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8781,12 +8781,31 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="27" width="13" customWidth="1"/>
+    <col min="2" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="9" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.42578125" customWidth="1"/>
+    <col min="10" max="10" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="15" max="15" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="20" width="13" customWidth="1"/>
+    <col min="21" max="21" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="13" customWidth="1"/>
+    <col min="24" max="24" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13" customWidth="1"/>
+    <col min="26" max="26" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13" customWidth="1"/>
     <col min="28" max="28" width="14" customWidth="1"/>
     <col min="29" max="29" width="25" customWidth="1"/>
+    <col min="30" max="30" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A1" s="33" t="s">
         <v>1</v>
       </c>
@@ -8935,20 +8954,26 @@
       <c r="O3" s="35"/>
       <c r="P3" s="35"/>
       <c r="Q3" s="35"/>
-      <c r="R3" s="35"/>
+      <c r="R3" s="35">
+        <f>194-3.53</f>
+        <v>190.47</v>
+      </c>
       <c r="S3" s="35"/>
       <c r="T3" s="35"/>
       <c r="U3" s="35"/>
       <c r="V3" s="35"/>
       <c r="W3" s="35"/>
-      <c r="X3" s="35"/>
+      <c r="X3" s="35">
+        <f>120.81+60.4</f>
+        <v>181.21</v>
+      </c>
       <c r="Y3" s="35"/>
       <c r="Z3" s="35"/>
       <c r="AA3" s="35"/>
       <c r="AB3" s="36"/>
       <c r="AC3" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>371.68</v>
       </c>
       <c r="AD3" s="35"/>
     </row>
@@ -8969,10 +8994,16 @@
       <c r="L4" s="35"/>
       <c r="M4" s="35"/>
       <c r="N4" s="35"/>
-      <c r="O4" s="35"/>
+      <c r="O4" s="35">
+        <f>500-8.19</f>
+        <v>491.81</v>
+      </c>
       <c r="P4" s="35"/>
       <c r="Q4" s="35"/>
-      <c r="R4" s="35"/>
+      <c r="R4" s="35">
+        <f>1047-17.83</f>
+        <v>1029.17</v>
+      </c>
       <c r="S4" s="35"/>
       <c r="T4" s="35"/>
       <c r="U4" s="35"/>
@@ -8985,7 +9016,7 @@
       <c r="AB4" s="36"/>
       <c r="AC4" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1520.98</v>
       </c>
       <c r="AD4" s="35"/>
     </row>
@@ -10081,9 +10112,9 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="O33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="O33" s="12">
+        <f t="shared" si="1"/>
+        <v>491.81</v>
       </c>
       <c r="P33" s="12" t="str">
         <f t="shared" si="1"/>
@@ -10093,9 +10124,9 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="R33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="R33" s="12">
+        <f t="shared" si="1"/>
+        <v>1219.6400000000001</v>
       </c>
       <c r="S33" s="12" t="str">
         <f t="shared" si="1"/>
@@ -10117,9 +10148,9 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="X33" s="12">
+        <f t="shared" si="1"/>
+        <v>181.21</v>
       </c>
       <c r="Y33" s="12" t="str">
         <f t="shared" si="1"/>
@@ -10139,7 +10170,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1892.66</v>
       </c>
       <c r="AD33" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="81">
   <si>
     <t>Presupuesto</t>
   </si>
@@ -283,6 +283,9 @@
   </si>
   <si>
     <t xml:space="preserve">Almohadones </t>
+  </si>
+  <si>
+    <t>luces spot</t>
   </si>
 </sst>
 </file>
@@ -2432,7 +2435,7 @@
       </c>
       <c r="R17" s="1">
         <f>IF(Agosto!R33&gt;0,Agosto!R33,"")</f>
-        <v>1219.6400000000001</v>
+        <v>2860.71</v>
       </c>
       <c r="S17" s="1" t="str">
         <f>IF(Agosto!S33&gt;0,Agosto!S33,"")</f>
@@ -2466,9 +2469,9 @@
         <f>IF(Agosto!Z33&gt;0,Agosto!Z33,"")</f>
         <v/>
       </c>
-      <c r="AA17" s="1" t="str">
+      <c r="AA17" s="1">
         <f>IF(Agosto!AA33&gt;0,Agosto!AA33,"")</f>
-        <v/>
+        <v>879.34</v>
       </c>
       <c r="AC17" s="1" t="str">
         <f>IF(Agosto!AB33&gt;0,Agosto!AB33,"")</f>
@@ -3454,7 +3457,7 @@
       </c>
       <c r="R28" s="1">
         <f>IF(ISNUMBER(Agosto!R33),R6-Agosto!R33,"")</f>
-        <v>18780.36</v>
+        <v>17139.29</v>
       </c>
       <c r="S28" s="1" t="str">
         <f>IF(ISNUMBER(Agosto!S33),S6-Agosto!S33,"")</f>
@@ -3488,13 +3491,13 @@
         <f>IF(ISNUMBER(Agosto!Z33),Z6-Agosto!Z33,"")</f>
         <v/>
       </c>
-      <c r="AA28" s="1" t="str">
+      <c r="AA28" s="1">
         <f>IF(ISNUMBER(Agosto!AA33),AA6-Agosto!AA33,"")</f>
-        <v/>
+        <v>4120.66</v>
       </c>
       <c r="AC28" s="12">
         <f t="shared" si="7"/>
-        <v>27607.34</v>
+        <v>30086.93</v>
       </c>
     </row>
     <row r="29" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4019,7 +4022,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>19535.02</v>
+        <v>17893.95</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
@@ -4055,11 +4058,11 @@
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="8"/>
-        <v>-16550.809999999998</v>
+        <v>-12430.149999999998</v>
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>17638.07</v>
+        <v>20117.66</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9040,7 +9043,10 @@
       <c r="O5" s="35"/>
       <c r="P5" s="35"/>
       <c r="Q5" s="35"/>
-      <c r="R5" s="35"/>
+      <c r="R5" s="35">
+        <f>637.58+338-11.38-5.54+694-11.59</f>
+        <v>1641.0700000000002</v>
+      </c>
       <c r="S5" s="35"/>
       <c r="T5" s="35"/>
       <c r="U5" s="35"/>
@@ -9049,13 +9055,18 @@
       <c r="X5" s="35"/>
       <c r="Y5" s="35"/>
       <c r="Z5" s="35"/>
-      <c r="AA5" s="35"/>
+      <c r="AA5" s="35">
+        <f>894-14.66</f>
+        <v>879.34</v>
+      </c>
       <c r="AB5" s="36"/>
       <c r="AC5" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD5" s="35"/>
+        <v>2520.4100000000003</v>
+      </c>
+      <c r="AD5" s="35" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="6" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="34">
@@ -10126,7 +10137,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="1"/>
-        <v>1219.6400000000001</v>
+        <v>2860.71</v>
       </c>
       <c r="S33" s="12" t="str">
         <f t="shared" si="1"/>
@@ -10160,9 +10171,9 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AA33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="AA33" s="12">
+        <f t="shared" si="1"/>
+        <v>879.34</v>
       </c>
       <c r="AB33" s="38" t="str">
         <f t="shared" si="1"/>
@@ -10170,7 +10181,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="1"/>
-        <v>1892.66</v>
+        <v>4413.0700000000006</v>
       </c>
       <c r="AD33" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="82">
   <si>
     <t>Presupuesto</t>
   </si>
@@ -286,6 +286,9 @@
   </si>
   <si>
     <t>luces spot</t>
+  </si>
+  <si>
+    <t>comepa</t>
   </si>
 </sst>
 </file>
@@ -2385,21 +2388,21 @@
         <f>IF(Agosto!E33&gt;0,Agosto!E33,"")</f>
         <v/>
       </c>
-      <c r="F17" s="1" t="str">
+      <c r="F17" s="1">
         <f>IF(Agosto!F33&gt;0,Agosto!F33,"")</f>
-        <v/>
-      </c>
-      <c r="G17" s="1" t="str">
+        <v>19744</v>
+      </c>
+      <c r="G17" s="1">
         <f>IF(Agosto!G33&gt;0,Agosto!G33,"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="1" t="str">
+        <v>1185</v>
+      </c>
+      <c r="H17" s="1">
         <f>IF(Agosto!H33&gt;0,Agosto!H33,"")</f>
-        <v/>
-      </c>
-      <c r="I17" s="1" t="str">
+        <v>3291.56</v>
+      </c>
+      <c r="I17" s="1">
         <f>IF(Agosto!I33&gt;0,Agosto!I33,"")</f>
-        <v/>
+        <v>3335.41</v>
       </c>
       <c r="J17" s="1" t="str">
         <f>IF(Agosto!J33&gt;0,Agosto!J33,"")</f>
@@ -2409,9 +2412,9 @@
         <f>IF(Agosto!K33&gt;0,Agosto!K33,"")</f>
         <v/>
       </c>
-      <c r="L17" s="1" t="str">
+      <c r="L17" s="1">
         <f>IF(Agosto!L33&gt;0,Agosto!L33,"")</f>
-        <v/>
+        <v>13997.56</v>
       </c>
       <c r="M17" s="1" t="str">
         <f>IF(Agosto!M33&gt;0,Agosto!M33,"")</f>
@@ -2435,7 +2438,7 @@
       </c>
       <c r="R17" s="1">
         <f>IF(Agosto!R33&gt;0,Agosto!R33,"")</f>
-        <v>2860.71</v>
+        <v>3186.5</v>
       </c>
       <c r="S17" s="1" t="str">
         <f>IF(Agosto!S33&gt;0,Agosto!S33,"")</f>
@@ -2471,7 +2474,7 @@
       </c>
       <c r="AA17" s="1">
         <f>IF(Agosto!AA33&gt;0,Agosto!AA33,"")</f>
-        <v>879.34</v>
+        <v>1229.01</v>
       </c>
       <c r="AC17" s="1" t="str">
         <f>IF(Agosto!AB33&gt;0,Agosto!AB33,"")</f>
@@ -3407,21 +3410,21 @@
         <f>IF(ISNUMBER(Agosto!E33),E6-Agosto!E33,"")</f>
         <v/>
       </c>
-      <c r="F28" s="1" t="str">
+      <c r="F28" s="1">
         <f>IF(ISNUMBER(Agosto!F33),F6-Agosto!F33,"")</f>
-        <v/>
-      </c>
-      <c r="G28" s="1" t="str">
+        <v>6356</v>
+      </c>
+      <c r="G28" s="1">
         <f>IF(ISNUMBER(Agosto!G33),G6-Agosto!G33,"")</f>
-        <v/>
-      </c>
-      <c r="H28" s="1" t="str">
+        <v>-170</v>
+      </c>
+      <c r="H28" s="1">
         <f>IF(ISNUMBER(Agosto!H33),H6-Agosto!H33,"")</f>
-        <v/>
-      </c>
-      <c r="I28" s="1" t="str">
+        <v>208.44000000000005</v>
+      </c>
+      <c r="I28" s="1">
         <f>IF(ISNUMBER(Agosto!I33),I6-Agosto!I33,"")</f>
-        <v/>
+        <v>-335.40999999999985</v>
       </c>
       <c r="J28" s="1" t="str">
         <f>IF(ISNUMBER(Agosto!J33),J6-Agosto!J33,"")</f>
@@ -3431,9 +3434,9 @@
         <f>IF(ISNUMBER(Agosto!K33),K6-Agosto!K33,"")</f>
         <v/>
       </c>
-      <c r="L28" s="1" t="str">
+      <c r="L28" s="1">
         <f>IF(ISNUMBER(Agosto!L33),L6-Agosto!L33,"")</f>
-        <v/>
+        <v>-1997.5599999999995</v>
       </c>
       <c r="M28" s="1" t="str">
         <f>IF(ISNUMBER(Agosto!M33),M6-Agosto!M33,"")</f>
@@ -3457,7 +3460,7 @@
       </c>
       <c r="R28" s="1">
         <f>IF(ISNUMBER(Agosto!R33),R6-Agosto!R33,"")</f>
-        <v>17139.29</v>
+        <v>16813.5</v>
       </c>
       <c r="S28" s="1" t="str">
         <f>IF(ISNUMBER(Agosto!S33),S6-Agosto!S33,"")</f>
@@ -3493,11 +3496,11 @@
       </c>
       <c r="AA28" s="1">
         <f>IF(ISNUMBER(Agosto!AA33),AA6-Agosto!AA33,"")</f>
-        <v>4120.66</v>
+        <v>3770.99</v>
       </c>
       <c r="AC28" s="12">
         <f t="shared" si="7"/>
-        <v>30086.93</v>
+        <v>33472.94</v>
       </c>
     </row>
     <row r="29" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3974,19 +3977,19 @@
       </c>
       <c r="F33" s="12">
         <f t="shared" si="8"/>
-        <v>-1886</v>
+        <v>4470</v>
       </c>
       <c r="G33" s="12">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>-165</v>
       </c>
       <c r="H33" s="12">
         <f t="shared" si="8"/>
-        <v>416.88000000000011</v>
+        <v>625.32000000000016</v>
       </c>
       <c r="I33" s="12">
         <f t="shared" si="8"/>
-        <v>1014.0899999999997</v>
+        <v>678.67999999999984</v>
       </c>
       <c r="J33" s="12">
         <f t="shared" si="8"/>
@@ -3998,7 +4001,7 @@
       </c>
       <c r="L33" s="12">
         <f t="shared" si="8"/>
-        <v>327.09999999999673</v>
+        <v>-1670.4600000000028</v>
       </c>
       <c r="M33" s="12">
         <f t="shared" si="8"/>
@@ -4022,7 +4025,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>17893.95</v>
+        <v>17568.16</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
@@ -4058,11 +4061,11 @@
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="8"/>
-        <v>-12430.149999999998</v>
+        <v>-12779.819999999998</v>
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>20117.66</v>
+        <v>23503.669999999991</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9088,7 +9091,10 @@
       <c r="O6" s="35"/>
       <c r="P6" s="35"/>
       <c r="Q6" s="35"/>
-      <c r="R6" s="35"/>
+      <c r="R6" s="35">
+        <f>161-2.64</f>
+        <v>158.36000000000001</v>
+      </c>
       <c r="S6" s="35"/>
       <c r="T6" s="35"/>
       <c r="U6" s="35"/>
@@ -9101,7 +9107,7 @@
       <c r="AB6" s="36"/>
       <c r="AC6" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>158.36000000000001</v>
       </c>
       <c r="AD6" s="35"/>
     </row>
@@ -9113,19 +9119,35 @@
       <c r="C7" s="35"/>
       <c r="D7" s="35"/>
       <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="35"/>
+      <c r="F7" s="35">
+        <v>19744</v>
+      </c>
+      <c r="G7" s="35">
+        <v>1185</v>
+      </c>
+      <c r="H7" s="35">
+        <f>3327-35.44</f>
+        <v>3291.56</v>
+      </c>
+      <c r="I7" s="35">
+        <f>3391-55.59</f>
+        <v>3335.41</v>
+      </c>
       <c r="J7" s="35"/>
       <c r="K7" s="35"/>
-      <c r="L7" s="35"/>
+      <c r="L7" s="35">
+        <f>256.98+13740.58</f>
+        <v>13997.56</v>
+      </c>
       <c r="M7" s="35"/>
       <c r="N7" s="35"/>
       <c r="O7" s="35"/>
       <c r="P7" s="35"/>
       <c r="Q7" s="35"/>
-      <c r="R7" s="35"/>
+      <c r="R7" s="35">
+        <f>170-2.57</f>
+        <v>167.43</v>
+      </c>
       <c r="S7" s="35"/>
       <c r="T7" s="35"/>
       <c r="U7" s="35"/>
@@ -9134,13 +9156,18 @@
       <c r="X7" s="35"/>
       <c r="Y7" s="35"/>
       <c r="Z7" s="35"/>
-      <c r="AA7" s="35"/>
+      <c r="AA7" s="35">
+        <f>353-3.33</f>
+        <v>349.67</v>
+      </c>
       <c r="AB7" s="36"/>
       <c r="AC7" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD7" s="35"/>
+        <v>42070.63</v>
+      </c>
+      <c r="AD7" s="35" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="8" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="34">
@@ -10087,21 +10114,21 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="F33" s="12">
+        <f t="shared" si="1"/>
+        <v>19744</v>
+      </c>
+      <c r="G33" s="12">
+        <f t="shared" si="1"/>
+        <v>1185</v>
+      </c>
+      <c r="H33" s="12">
+        <f t="shared" si="1"/>
+        <v>3291.56</v>
+      </c>
+      <c r="I33" s="12">
+        <f t="shared" si="1"/>
+        <v>3335.41</v>
       </c>
       <c r="J33" s="12" t="str">
         <f t="shared" si="1"/>
@@ -10111,9 +10138,9 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="L33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="L33" s="12">
+        <f t="shared" si="1"/>
+        <v>13997.56</v>
       </c>
       <c r="M33" s="12" t="str">
         <f t="shared" si="1"/>
@@ -10137,7 +10164,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="1"/>
-        <v>2860.71</v>
+        <v>3186.5</v>
       </c>
       <c r="S33" s="12" t="str">
         <f t="shared" si="1"/>
@@ -10173,7 +10200,7 @@
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="1"/>
-        <v>879.34</v>
+        <v>1229.01</v>
       </c>
       <c r="AB33" s="38" t="str">
         <f t="shared" si="1"/>
@@ -10181,7 +10208,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="1"/>
-        <v>4413.0700000000006</v>
+        <v>46642.06</v>
       </c>
       <c r="AD33" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -2408,9 +2408,9 @@
         <f>IF(Agosto!J33&gt;0,Agosto!J33,"")</f>
         <v/>
       </c>
-      <c r="K17" s="1" t="str">
+      <c r="K17" s="1">
         <f>IF(Agosto!K33&gt;0,Agosto!K33,"")</f>
-        <v/>
+        <v>17999.740000000002</v>
       </c>
       <c r="L17" s="1">
         <f>IF(Agosto!L33&gt;0,Agosto!L33,"")</f>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="O17" s="1">
         <f>IF(Agosto!O33&gt;0,Agosto!O33,"")</f>
-        <v>491.81</v>
+        <v>983.62</v>
       </c>
       <c r="P17" s="1" t="str">
         <f>IF(Agosto!P33&gt;0,Agosto!P33,"")</f>
@@ -2438,15 +2438,15 @@
       </c>
       <c r="R17" s="1">
         <f>IF(Agosto!R33&gt;0,Agosto!R33,"")</f>
-        <v>3186.5</v>
+        <v>3456.99</v>
       </c>
       <c r="S17" s="1" t="str">
         <f>IF(Agosto!S33&gt;0,Agosto!S33,"")</f>
         <v/>
       </c>
-      <c r="T17" s="1" t="str">
+      <c r="T17" s="1">
         <f>IF(Agosto!T33&gt;0,Agosto!T33,"")</f>
-        <v/>
+        <v>1882.2299999999998</v>
       </c>
       <c r="U17" s="1" t="str">
         <f>IF(Agosto!U33&gt;0,Agosto!U33,"")</f>
@@ -3430,9 +3430,9 @@
         <f>IF(ISNUMBER(Agosto!J33),J6-Agosto!J33,"")</f>
         <v/>
       </c>
-      <c r="K28" s="1" t="str">
+      <c r="K28" s="1">
         <f>IF(ISNUMBER(Agosto!K33),K6-Agosto!K33,"")</f>
-        <v/>
+        <v>0.25999999999839929</v>
       </c>
       <c r="L28" s="1">
         <f>IF(ISNUMBER(Agosto!L33),L6-Agosto!L33,"")</f>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="O28" s="1">
         <f>IF(ISNUMBER(Agosto!O33),O6-Agosto!O33,"")</f>
-        <v>7508.19</v>
+        <v>7016.38</v>
       </c>
       <c r="P28" s="1" t="str">
         <f>IF(ISNUMBER(Agosto!P33),P6-Agosto!P33,"")</f>
@@ -3460,15 +3460,15 @@
       </c>
       <c r="R28" s="1">
         <f>IF(ISNUMBER(Agosto!R33),R6-Agosto!R33,"")</f>
-        <v>16813.5</v>
+        <v>16543.010000000002</v>
       </c>
       <c r="S28" s="1" t="str">
         <f>IF(ISNUMBER(Agosto!S33),S6-Agosto!S33,"")</f>
         <v/>
       </c>
-      <c r="T28" s="1" t="str">
+      <c r="T28" s="1">
         <f>IF(ISNUMBER(Agosto!T33),T6-Agosto!T33,"")</f>
-        <v/>
+        <v>3117.7700000000004</v>
       </c>
       <c r="U28" s="1" t="str">
         <f>IF(ISNUMBER(Agosto!U33),U6-Agosto!U33,"")</f>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="AC28" s="12">
         <f t="shared" si="7"/>
-        <v>33472.94</v>
+        <v>35828.670000000006</v>
       </c>
     </row>
     <row r="29" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="K33" s="12">
         <f t="shared" si="8"/>
-        <v>13.809999999999945</v>
+        <v>14.069999999998345</v>
       </c>
       <c r="L33" s="12">
         <f t="shared" si="8"/>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="O33" s="12">
         <f t="shared" si="8"/>
-        <v>18923.03</v>
+        <v>18431.22</v>
       </c>
       <c r="P33" s="12">
         <f t="shared" si="8"/>
@@ -4025,7 +4025,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>17568.16</v>
+        <v>17297.670000000002</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="T33" s="12">
         <f t="shared" si="8"/>
-        <v>1738.5</v>
+        <v>4856.2700000000004</v>
       </c>
       <c r="U33" s="12">
         <f t="shared" si="8"/>
@@ -4065,7 +4065,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>23503.669999999991</v>
+        <v>25859.399999999994</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9226,9 +9226,15 @@
       <c r="O9" s="35"/>
       <c r="P9" s="35"/>
       <c r="Q9" s="35"/>
-      <c r="R9" s="35"/>
+      <c r="R9" s="35">
+        <f>275-4.51</f>
+        <v>270.49</v>
+      </c>
       <c r="S9" s="35"/>
-      <c r="T9" s="35"/>
+      <c r="T9" s="35">
+        <f>303.5-4.98</f>
+        <v>298.52</v>
+      </c>
       <c r="U9" s="35"/>
       <c r="V9" s="35"/>
       <c r="W9" s="35"/>
@@ -9239,7 +9245,7 @@
       <c r="AB9" s="36"/>
       <c r="AC9" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>569.01</v>
       </c>
       <c r="AD9" s="35"/>
     </row>
@@ -9265,7 +9271,10 @@
       <c r="Q10" s="35"/>
       <c r="R10" s="35"/>
       <c r="S10" s="35"/>
-      <c r="T10" s="35"/>
+      <c r="T10" s="35">
+        <f>1107.87-18.16</f>
+        <v>1089.7099999999998</v>
+      </c>
       <c r="U10" s="35"/>
       <c r="V10" s="35"/>
       <c r="W10" s="35"/>
@@ -9276,7 +9285,7 @@
       <c r="AB10" s="36"/>
       <c r="AC10" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1089.7099999999998</v>
       </c>
       <c r="AD10" s="35"/>
     </row>
@@ -9293,16 +9302,23 @@
       <c r="H11" s="35"/>
       <c r="I11" s="35"/>
       <c r="J11" s="35"/>
-      <c r="K11" s="35"/>
+      <c r="K11" s="35">
+        <v>17999.740000000002</v>
+      </c>
       <c r="L11" s="35"/>
       <c r="M11" s="35"/>
       <c r="N11" s="35"/>
-      <c r="O11" s="35"/>
+      <c r="O11" s="35">
+        <f>500-8.19</f>
+        <v>491.81</v>
+      </c>
       <c r="P11" s="35"/>
       <c r="Q11" s="35"/>
       <c r="R11" s="35"/>
       <c r="S11" s="35"/>
-      <c r="T11" s="35"/>
+      <c r="T11" s="35">
+        <v>494</v>
+      </c>
       <c r="U11" s="35"/>
       <c r="V11" s="35"/>
       <c r="W11" s="35"/>
@@ -9313,7 +9329,7 @@
       <c r="AB11" s="36"/>
       <c r="AC11" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>18985.550000000003</v>
       </c>
       <c r="AD11" s="35"/>
     </row>
@@ -10134,9 +10150,9 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="K33" s="12">
+        <f t="shared" si="1"/>
+        <v>17999.740000000002</v>
       </c>
       <c r="L33" s="12">
         <f t="shared" si="1"/>
@@ -10152,7 +10168,7 @@
       </c>
       <c r="O33" s="12">
         <f t="shared" si="1"/>
-        <v>491.81</v>
+        <v>983.62</v>
       </c>
       <c r="P33" s="12" t="str">
         <f t="shared" si="1"/>
@@ -10164,15 +10180,15 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="1"/>
-        <v>3186.5</v>
+        <v>3456.99</v>
       </c>
       <c r="S33" s="12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="T33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="T33" s="12">
+        <f t="shared" si="1"/>
+        <v>1882.2299999999998</v>
       </c>
       <c r="U33" s="12" t="str">
         <f t="shared" si="1"/>
@@ -10208,7 +10224,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="1"/>
-        <v>46642.06</v>
+        <v>67286.33</v>
       </c>
       <c r="AD33" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -1400,34 +1400,34 @@
         <v>40</v>
       </c>
       <c r="D6" s="1">
-        <v>15600</v>
+        <v>15690.71</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
       </c>
       <c r="F6" s="1">
-        <v>26100</v>
+        <v>28611</v>
       </c>
       <c r="G6" s="1">
-        <v>1015</v>
+        <v>1185</v>
       </c>
       <c r="H6" s="1">
-        <v>3500</v>
+        <v>3291.56</v>
       </c>
       <c r="I6" s="1">
-        <v>3000</v>
+        <v>3335.41</v>
       </c>
       <c r="J6" s="1">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="K6" s="1">
         <v>18000</v>
       </c>
       <c r="L6" s="1">
-        <v>12000</v>
+        <v>14000</v>
       </c>
       <c r="M6" s="1">
-        <v>17000</v>
+        <v>19000</v>
       </c>
       <c r="N6" s="1">
         <v>810</v>
@@ -1439,7 +1439,7 @@
         <v>1800</v>
       </c>
       <c r="Q6" s="1">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="R6" s="1">
         <v>20000</v>
@@ -1450,17 +1450,11 @@
       <c r="T6" s="1">
         <v>5000</v>
       </c>
-      <c r="W6" s="1">
-        <v>3000</v>
-      </c>
       <c r="X6" s="1">
         <v>1500</v>
       </c>
       <c r="Y6" s="1">
-        <v>2000</v>
-      </c>
-      <c r="Z6" s="1">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="AA6" s="1">
         <v>5000</v>
@@ -1468,7 +1462,7 @@
       <c r="AB6" s="6"/>
       <c r="AC6" s="1">
         <f>SUM(B6:AB6)</f>
-        <v>150325</v>
+        <v>152423.67999999999</v>
       </c>
       <c r="AD6" s="7">
         <f t="shared" si="1"/>
@@ -1486,15 +1480,15 @@
       </c>
       <c r="AH6" s="8">
         <f t="shared" si="3"/>
-        <v>58162.5</v>
+        <v>57211.839999999997</v>
       </c>
       <c r="AI6" s="9">
         <f t="shared" si="4"/>
-        <v>59562.5</v>
+        <v>60521.13</v>
       </c>
       <c r="AJ6" s="10">
         <f t="shared" si="5"/>
-        <v>117725</v>
+        <v>117732.97</v>
       </c>
     </row>
     <row r="7" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1508,7 +1502,7 @@
         <v>4369</v>
       </c>
       <c r="D7" s="1">
-        <v>15650</v>
+        <v>15750</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
@@ -1526,7 +1520,7 @@
         <v>3000</v>
       </c>
       <c r="J7" s="1">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="K7" s="1">
         <v>18000</v>
@@ -1576,7 +1570,7 @@
       <c r="AB7" s="6"/>
       <c r="AC7" s="1">
         <f t="shared" si="0"/>
-        <v>175644</v>
+        <v>175444</v>
       </c>
       <c r="AD7" s="7">
         <f t="shared" si="1"/>
@@ -1594,15 +1588,15 @@
       </c>
       <c r="AH7" s="8">
         <f t="shared" si="3"/>
-        <v>80322</v>
+        <v>80222</v>
       </c>
       <c r="AI7" s="9">
         <f t="shared" si="4"/>
-        <v>72172</v>
+        <v>71972</v>
       </c>
       <c r="AJ7" s="10">
         <f t="shared" si="5"/>
-        <v>152494</v>
+        <v>152194</v>
       </c>
     </row>
     <row r="8" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1610,7 +1604,7 @@
         <v>42</v>
       </c>
       <c r="D8" s="1">
-        <v>15650</v>
+        <v>15750</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
@@ -1628,7 +1622,7 @@
         <v>3000</v>
       </c>
       <c r="J8" s="1">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="K8" s="1">
         <v>18000</v>
@@ -1678,7 +1672,7 @@
       <c r="AB8" s="6"/>
       <c r="AC8" s="1">
         <f t="shared" si="0"/>
-        <v>137575</v>
+        <v>137375</v>
       </c>
       <c r="AD8" s="7">
         <f t="shared" si="1"/>
@@ -1696,15 +1690,15 @@
       </c>
       <c r="AH8" s="8">
         <f t="shared" si="3"/>
-        <v>61287.5</v>
+        <v>61187.5</v>
       </c>
       <c r="AI8" s="9">
         <f t="shared" si="4"/>
-        <v>53137.5</v>
+        <v>52937.5</v>
       </c>
       <c r="AJ8" s="10">
         <f t="shared" si="5"/>
-        <v>114425</v>
+        <v>114125</v>
       </c>
     </row>
     <row r="9" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1715,7 +1709,7 @@
         <v>4369</v>
       </c>
       <c r="D9" s="1">
-        <v>15700</v>
+        <v>15800</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
@@ -1733,7 +1727,7 @@
         <v>3000</v>
       </c>
       <c r="J9" s="1">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="K9" s="1">
         <v>18000</v>
@@ -1780,7 +1774,7 @@
       <c r="AB9" s="6"/>
       <c r="AC9" s="1">
         <f t="shared" si="0"/>
-        <v>140494</v>
+        <v>140294</v>
       </c>
       <c r="AD9" s="7">
         <f t="shared" si="1"/>
@@ -1798,15 +1792,15 @@
       </c>
       <c r="AH9" s="8">
         <f t="shared" si="3"/>
-        <v>62747</v>
+        <v>62647</v>
       </c>
       <c r="AI9" s="9">
         <f t="shared" si="4"/>
-        <v>54547</v>
+        <v>54347</v>
       </c>
       <c r="AJ9" s="10">
         <f t="shared" si="5"/>
-        <v>117294</v>
+        <v>116994</v>
       </c>
     </row>
     <row r="10" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1814,7 +1808,7 @@
         <v>44</v>
       </c>
       <c r="D10" s="1">
-        <v>15700</v>
+        <v>15800</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
@@ -1832,7 +1826,7 @@
         <v>3000</v>
       </c>
       <c r="J10" s="1">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="K10" s="1">
         <v>18000</v>
@@ -1882,7 +1876,7 @@
       <c r="AB10" s="6"/>
       <c r="AC10" s="1">
         <f t="shared" si="0"/>
-        <v>156375</v>
+        <v>156175</v>
       </c>
       <c r="AD10" s="7">
         <f t="shared" si="1"/>
@@ -1900,15 +1894,15 @@
       </c>
       <c r="AH10" s="8">
         <f t="shared" si="3"/>
-        <v>70687.5</v>
+        <v>70587.5</v>
       </c>
       <c r="AI10" s="9">
         <f t="shared" si="4"/>
-        <v>62487.5</v>
+        <v>62287.5</v>
       </c>
       <c r="AJ10" s="10">
         <f t="shared" si="5"/>
-        <v>133175</v>
+        <v>132875</v>
       </c>
     </row>
     <row r="12" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2390,7 +2384,7 @@
       </c>
       <c r="F17" s="1">
         <f>IF(Agosto!F33&gt;0,Agosto!F33,"")</f>
-        <v>19744</v>
+        <v>28611</v>
       </c>
       <c r="G17" s="1">
         <f>IF(Agosto!G33&gt;0,Agosto!G33,"")</f>
@@ -2426,7 +2420,7 @@
       </c>
       <c r="O17" s="1">
         <f>IF(Agosto!O33&gt;0,Agosto!O33,"")</f>
-        <v>983.62</v>
+        <v>4041.22</v>
       </c>
       <c r="P17" s="1" t="str">
         <f>IF(Agosto!P33&gt;0,Agosto!P33,"")</f>
@@ -2438,7 +2432,7 @@
       </c>
       <c r="R17" s="1">
         <f>IF(Agosto!R33&gt;0,Agosto!R33,"")</f>
-        <v>3456.99</v>
+        <v>5674.48</v>
       </c>
       <c r="S17" s="1" t="str">
         <f>IF(Agosto!S33&gt;0,Agosto!S33,"")</f>
@@ -3412,19 +3406,19 @@
       </c>
       <c r="F28" s="1">
         <f>IF(ISNUMBER(Agosto!F33),F6-Agosto!F33,"")</f>
-        <v>6356</v>
+        <v>0</v>
       </c>
       <c r="G28" s="1">
         <f>IF(ISNUMBER(Agosto!G33),G6-Agosto!G33,"")</f>
-        <v>-170</v>
+        <v>0</v>
       </c>
       <c r="H28" s="1">
         <f>IF(ISNUMBER(Agosto!H33),H6-Agosto!H33,"")</f>
-        <v>208.44000000000005</v>
+        <v>0</v>
       </c>
       <c r="I28" s="1">
         <f>IF(ISNUMBER(Agosto!I33),I6-Agosto!I33,"")</f>
-        <v>-335.40999999999985</v>
+        <v>0</v>
       </c>
       <c r="J28" s="1" t="str">
         <f>IF(ISNUMBER(Agosto!J33),J6-Agosto!J33,"")</f>
@@ -3436,7 +3430,7 @@
       </c>
       <c r="L28" s="1">
         <f>IF(ISNUMBER(Agosto!L33),L6-Agosto!L33,"")</f>
-        <v>-1997.5599999999995</v>
+        <v>2.4400000000005093</v>
       </c>
       <c r="M28" s="1" t="str">
         <f>IF(ISNUMBER(Agosto!M33),M6-Agosto!M33,"")</f>
@@ -3448,7 +3442,7 @@
       </c>
       <c r="O28" s="1">
         <f>IF(ISNUMBER(Agosto!O33),O6-Agosto!O33,"")</f>
-        <v>7016.38</v>
+        <v>3958.78</v>
       </c>
       <c r="P28" s="1" t="str">
         <f>IF(ISNUMBER(Agosto!P33),P6-Agosto!P33,"")</f>
@@ -3460,7 +3454,7 @@
       </c>
       <c r="R28" s="1">
         <f>IF(ISNUMBER(Agosto!R33),R6-Agosto!R33,"")</f>
-        <v>16543.010000000002</v>
+        <v>14325.52</v>
       </c>
       <c r="S28" s="1" t="str">
         <f>IF(ISNUMBER(Agosto!S33),S6-Agosto!S33,"")</f>
@@ -3500,7 +3494,7 @@
       </c>
       <c r="AC28" s="12">
         <f t="shared" si="7"/>
-        <v>35828.670000000006</v>
+        <v>26494.550000000003</v>
       </c>
     </row>
     <row r="29" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3977,19 +3971,19 @@
       </c>
       <c r="F33" s="12">
         <f t="shared" si="8"/>
-        <v>4470</v>
+        <v>-1886</v>
       </c>
       <c r="G33" s="12">
         <f t="shared" si="8"/>
-        <v>-165</v>
+        <v>5</v>
       </c>
       <c r="H33" s="12">
         <f t="shared" si="8"/>
-        <v>625.32000000000016</v>
+        <v>416.88000000000011</v>
       </c>
       <c r="I33" s="12">
         <f t="shared" si="8"/>
-        <v>678.67999999999984</v>
+        <v>1014.0899999999997</v>
       </c>
       <c r="J33" s="12">
         <f t="shared" si="8"/>
@@ -4001,7 +3995,7 @@
       </c>
       <c r="L33" s="12">
         <f t="shared" si="8"/>
-        <v>-1670.4600000000028</v>
+        <v>329.53999999999724</v>
       </c>
       <c r="M33" s="12">
         <f t="shared" si="8"/>
@@ -4013,7 +4007,7 @@
       </c>
       <c r="O33" s="12">
         <f t="shared" si="8"/>
-        <v>18431.22</v>
+        <v>15373.62</v>
       </c>
       <c r="P33" s="12">
         <f t="shared" si="8"/>
@@ -4025,7 +4019,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>17297.670000000002</v>
+        <v>15080.18</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
@@ -4065,7 +4059,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>25859.399999999994</v>
+        <v>16525.28</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9269,7 +9263,10 @@
       <c r="O10" s="35"/>
       <c r="P10" s="35"/>
       <c r="Q10" s="35"/>
-      <c r="R10" s="35"/>
+      <c r="R10" s="35">
+        <f>442+715-7.35-11.72-4.76+523-9.18+267</f>
+        <v>1913.99</v>
+      </c>
       <c r="S10" s="35"/>
       <c r="T10" s="35">
         <f>1107.87-18.16</f>
@@ -9285,7 +9282,7 @@
       <c r="AB10" s="36"/>
       <c r="AC10" s="35">
         <f t="shared" si="0"/>
-        <v>1089.7099999999998</v>
+        <v>3003.7</v>
       </c>
       <c r="AD10" s="35"/>
     </row>
@@ -9297,7 +9294,9 @@
       <c r="C11" s="35"/>
       <c r="D11" s="35"/>
       <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
+      <c r="F11" s="35">
+        <v>8345</v>
+      </c>
       <c r="G11" s="35"/>
       <c r="H11" s="35"/>
       <c r="I11" s="35"/>
@@ -9314,7 +9313,9 @@
       </c>
       <c r="P11" s="35"/>
       <c r="Q11" s="35"/>
-      <c r="R11" s="35"/>
+      <c r="R11" s="35">
+        <v>303.5</v>
+      </c>
       <c r="S11" s="35"/>
       <c r="T11" s="35">
         <v>494</v>
@@ -9329,7 +9330,7 @@
       <c r="AB11" s="36"/>
       <c r="AC11" s="35">
         <f t="shared" si="0"/>
-        <v>18985.550000000003</v>
+        <v>27634.050000000003</v>
       </c>
       <c r="AD11" s="35"/>
     </row>
@@ -9341,7 +9342,9 @@
       <c r="C12" s="35"/>
       <c r="D12" s="35"/>
       <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
+      <c r="F12" s="35">
+        <v>522</v>
+      </c>
       <c r="G12" s="35"/>
       <c r="H12" s="35"/>
       <c r="I12" s="35"/>
@@ -9350,7 +9353,9 @@
       <c r="L12" s="35"/>
       <c r="M12" s="35"/>
       <c r="N12" s="35"/>
-      <c r="O12" s="35"/>
+      <c r="O12" s="35">
+        <v>3920</v>
+      </c>
       <c r="P12" s="35"/>
       <c r="Q12" s="35"/>
       <c r="R12" s="35"/>
@@ -9366,7 +9371,7 @@
       <c r="AB12" s="36"/>
       <c r="AC12" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4442</v>
       </c>
       <c r="AD12" s="35"/>
     </row>
@@ -9387,7 +9392,9 @@
       <c r="L13" s="35"/>
       <c r="M13" s="35"/>
       <c r="N13" s="35"/>
-      <c r="O13" s="35"/>
+      <c r="O13" s="35">
+        <v>-862.4</v>
+      </c>
       <c r="P13" s="35"/>
       <c r="Q13" s="35"/>
       <c r="R13" s="35"/>
@@ -9403,7 +9410,7 @@
       <c r="AB13" s="36"/>
       <c r="AC13" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-862.4</v>
       </c>
       <c r="AD13" s="35"/>
     </row>
@@ -10132,7 +10139,7 @@
       </c>
       <c r="F33" s="12">
         <f t="shared" si="1"/>
-        <v>19744</v>
+        <v>28611</v>
       </c>
       <c r="G33" s="12">
         <f t="shared" si="1"/>
@@ -10168,7 +10175,7 @@
       </c>
       <c r="O33" s="12">
         <f t="shared" si="1"/>
-        <v>983.62</v>
+        <v>4041.22</v>
       </c>
       <c r="P33" s="12" t="str">
         <f t="shared" si="1"/>
@@ -10180,7 +10187,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="1"/>
-        <v>3456.99</v>
+        <v>5674.48</v>
       </c>
       <c r="S33" s="12" t="str">
         <f t="shared" si="1"/>
@@ -10224,7 +10231,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="1"/>
-        <v>67286.33</v>
+        <v>81428.420000000013</v>
       </c>
       <c r="AD33" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -2374,9 +2374,9 @@
         <f>IF(Agosto!C33&gt;0,Agosto!C33,"")</f>
         <v/>
       </c>
-      <c r="D17" s="1" t="str">
+      <c r="D17" s="1">
         <f>IF(Agosto!D33&gt;0,Agosto!D33,"")</f>
-        <v/>
+        <v>15691</v>
       </c>
       <c r="E17" s="1" t="str">
         <f>IF(Agosto!E33&gt;0,Agosto!E33,"")</f>
@@ -2410,9 +2410,9 @@
         <f>IF(Agosto!L33&gt;0,Agosto!L33,"")</f>
         <v>13997.56</v>
       </c>
-      <c r="M17" s="1" t="str">
+      <c r="M17" s="1">
         <f>IF(Agosto!M33&gt;0,Agosto!M33,"")</f>
-        <v/>
+        <v>19000</v>
       </c>
       <c r="N17" s="1" t="str">
         <f>IF(Agosto!N33&gt;0,Agosto!N33,"")</f>
@@ -3396,9 +3396,9 @@
         <f>IF(ISNUMBER(Agosto!C33),C6-Agosto!C33,"")</f>
         <v/>
       </c>
-      <c r="D28" s="1" t="str">
+      <c r="D28" s="1">
         <f>IF(ISNUMBER(Agosto!D33),D6-Agosto!D33,"")</f>
-        <v/>
+        <v>-0.29000000000087311</v>
       </c>
       <c r="E28" s="1" t="str">
         <f>IF(ISNUMBER(Agosto!E33),E6-Agosto!E33,"")</f>
@@ -3432,9 +3432,9 @@
         <f>IF(ISNUMBER(Agosto!L33),L6-Agosto!L33,"")</f>
         <v>2.4400000000005093</v>
       </c>
-      <c r="M28" s="1" t="str">
+      <c r="M28" s="1">
         <f>IF(ISNUMBER(Agosto!M33),M6-Agosto!M33,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N28" s="1" t="str">
         <f>IF(ISNUMBER(Agosto!N33),N6-Agosto!N33,"")</f>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="AC28" s="12">
         <f t="shared" si="7"/>
-        <v>26494.550000000003</v>
+        <v>26494.260000000002</v>
       </c>
     </row>
     <row r="29" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="D33" s="12">
         <f t="shared" si="8"/>
-        <v>56.709999999999127</v>
+        <v>56.419999999998254</v>
       </c>
       <c r="E33" s="12">
         <f t="shared" si="8"/>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>16525.28</v>
+        <v>16524.989999999998</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9292,7 +9292,9 @@
       </c>
       <c r="B11" s="35"/>
       <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
+      <c r="D11" s="35">
+        <v>15691</v>
+      </c>
       <c r="E11" s="35"/>
       <c r="F11" s="35">
         <v>8345</v>
@@ -9305,7 +9307,9 @@
         <v>17999.740000000002</v>
       </c>
       <c r="L11" s="35"/>
-      <c r="M11" s="35"/>
+      <c r="M11" s="35">
+        <v>19000</v>
+      </c>
       <c r="N11" s="35"/>
       <c r="O11" s="35">
         <f>500-8.19</f>
@@ -9330,7 +9334,7 @@
       <c r="AB11" s="36"/>
       <c r="AC11" s="35">
         <f t="shared" si="0"/>
-        <v>27634.050000000003</v>
+        <v>62325.05</v>
       </c>
       <c r="AD11" s="35"/>
     </row>
@@ -10129,9 +10133,9 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="D33" s="12">
+        <f t="shared" si="1"/>
+        <v>15691</v>
       </c>
       <c r="E33" s="12" t="str">
         <f t="shared" si="1"/>
@@ -10165,9 +10169,9 @@
         <f t="shared" si="1"/>
         <v>13997.56</v>
       </c>
-      <c r="M33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="M33" s="12">
+        <f t="shared" si="1"/>
+        <v>19000</v>
       </c>
       <c r="N33" s="12" t="str">
         <f t="shared" si="1"/>
@@ -10231,7 +10235,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="1"/>
-        <v>81428.420000000013</v>
+        <v>116119.42000000001</v>
       </c>
       <c r="AD33" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -1400,7 +1400,7 @@
         <v>40</v>
       </c>
       <c r="D6" s="1">
-        <v>15690.71</v>
+        <v>15691</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
@@ -1462,7 +1462,7 @@
       <c r="AB6" s="6"/>
       <c r="AC6" s="1">
         <f>SUM(B6:AB6)</f>
-        <v>152423.67999999999</v>
+        <v>152423.97</v>
       </c>
       <c r="AD6" s="7">
         <f t="shared" si="1"/>
@@ -1480,11 +1480,11 @@
       </c>
       <c r="AH6" s="8">
         <f t="shared" si="3"/>
-        <v>57211.839999999997</v>
+        <v>57211.985000000001</v>
       </c>
       <c r="AI6" s="9">
         <f t="shared" si="4"/>
-        <v>60521.13</v>
+        <v>60520.985000000001</v>
       </c>
       <c r="AJ6" s="10">
         <f t="shared" si="5"/>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="D28" s="1">
         <f>IF(ISNUMBER(Agosto!D33),D6-Agosto!D33,"")</f>
-        <v>-0.29000000000087311</v>
+        <v>0</v>
       </c>
       <c r="E28" s="1" t="str">
         <f>IF(ISNUMBER(Agosto!E33),E6-Agosto!E33,"")</f>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="AC28" s="12">
         <f t="shared" si="7"/>
-        <v>26494.260000000002</v>
+        <v>26494.550000000003</v>
       </c>
     </row>
     <row r="29" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="D33" s="12">
         <f t="shared" si="8"/>
-        <v>56.419999999998254</v>
+        <v>56.709999999999127</v>
       </c>
       <c r="E33" s="12">
         <f t="shared" si="8"/>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>16524.989999999998</v>
+        <v>16525.28</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -1508,13 +1508,13 @@
         <v>0</v>
       </c>
       <c r="F7" s="1">
-        <v>26100</v>
+        <v>27000</v>
       </c>
       <c r="G7" s="1">
-        <v>1015</v>
+        <v>1100</v>
       </c>
       <c r="H7" s="1">
-        <v>3500</v>
+        <v>3300</v>
       </c>
       <c r="I7" s="1">
         <v>3000</v>
@@ -1570,7 +1570,7 @@
       <c r="AB7" s="6"/>
       <c r="AC7" s="1">
         <f t="shared" si="0"/>
-        <v>175444</v>
+        <v>176229</v>
       </c>
       <c r="AD7" s="7">
         <f t="shared" si="1"/>
@@ -1588,15 +1588,15 @@
       </c>
       <c r="AH7" s="8">
         <f t="shared" si="3"/>
-        <v>80222</v>
+        <v>80614.5</v>
       </c>
       <c r="AI7" s="9">
         <f t="shared" si="4"/>
-        <v>71972</v>
+        <v>72364.5</v>
       </c>
       <c r="AJ7" s="10">
         <f t="shared" si="5"/>
-        <v>152194</v>
+        <v>152979</v>
       </c>
     </row>
     <row r="8" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1610,13 +1610,13 @@
         <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>26100</v>
+        <v>27000</v>
       </c>
       <c r="G8" s="1">
-        <v>1015</v>
+        <v>1100</v>
       </c>
       <c r="H8" s="1">
-        <v>3500</v>
+        <v>3300</v>
       </c>
       <c r="I8" s="1">
         <v>3000</v>
@@ -1672,7 +1672,7 @@
       <c r="AB8" s="6"/>
       <c r="AC8" s="1">
         <f t="shared" si="0"/>
-        <v>137375</v>
+        <v>138160</v>
       </c>
       <c r="AD8" s="7">
         <f t="shared" si="1"/>
@@ -1690,15 +1690,15 @@
       </c>
       <c r="AH8" s="8">
         <f t="shared" si="3"/>
-        <v>61187.5</v>
+        <v>61580</v>
       </c>
       <c r="AI8" s="9">
         <f t="shared" si="4"/>
-        <v>52937.5</v>
+        <v>53330</v>
       </c>
       <c r="AJ8" s="10">
         <f t="shared" si="5"/>
-        <v>114125</v>
+        <v>114910</v>
       </c>
     </row>
     <row r="9" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1715,13 +1715,13 @@
         <v>0</v>
       </c>
       <c r="F9" s="1">
-        <v>26100</v>
+        <v>27000</v>
       </c>
       <c r="G9" s="1">
-        <v>1015</v>
+        <v>1100</v>
       </c>
       <c r="H9" s="1">
-        <v>3500</v>
+        <v>3300</v>
       </c>
       <c r="I9" s="1">
         <v>3000</v>
@@ -1774,7 +1774,7 @@
       <c r="AB9" s="6"/>
       <c r="AC9" s="1">
         <f t="shared" si="0"/>
-        <v>140294</v>
+        <v>141079</v>
       </c>
       <c r="AD9" s="7">
         <f t="shared" si="1"/>
@@ -1792,15 +1792,15 @@
       </c>
       <c r="AH9" s="8">
         <f t="shared" si="3"/>
-        <v>62647</v>
+        <v>63039.5</v>
       </c>
       <c r="AI9" s="9">
         <f t="shared" si="4"/>
-        <v>54347</v>
+        <v>54739.5</v>
       </c>
       <c r="AJ9" s="10">
         <f t="shared" si="5"/>
-        <v>116994</v>
+        <v>117779</v>
       </c>
     </row>
     <row r="10" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1817,10 +1817,10 @@
         <v>45000</v>
       </c>
       <c r="G10" s="1">
-        <v>1015</v>
+        <v>1100</v>
       </c>
       <c r="H10" s="1">
-        <v>3500</v>
+        <v>3300</v>
       </c>
       <c r="I10" s="1">
         <v>3000</v>
@@ -1876,7 +1876,7 @@
       <c r="AB10" s="6"/>
       <c r="AC10" s="1">
         <f t="shared" si="0"/>
-        <v>156175</v>
+        <v>156060</v>
       </c>
       <c r="AD10" s="7">
         <f t="shared" si="1"/>
@@ -1894,15 +1894,15 @@
       </c>
       <c r="AH10" s="8">
         <f t="shared" si="3"/>
-        <v>70587.5</v>
+        <v>70530</v>
       </c>
       <c r="AI10" s="9">
         <f t="shared" si="4"/>
-        <v>62287.5</v>
+        <v>62230</v>
       </c>
       <c r="AJ10" s="10">
         <f t="shared" si="5"/>
-        <v>132875</v>
+        <v>132760</v>
       </c>
     </row>
     <row r="12" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2398,9 +2398,9 @@
         <f>IF(Agosto!I33&gt;0,Agosto!I33,"")</f>
         <v>3335.41</v>
       </c>
-      <c r="J17" s="1" t="str">
+      <c r="J17" s="1">
         <f>IF(Agosto!J33&gt;0,Agosto!J33,"")</f>
-        <v/>
+        <v>700</v>
       </c>
       <c r="K17" s="1">
         <f>IF(Agosto!K33&gt;0,Agosto!K33,"")</f>
@@ -2414,17 +2414,17 @@
         <f>IF(Agosto!M33&gt;0,Agosto!M33,"")</f>
         <v>19000</v>
       </c>
-      <c r="N17" s="1" t="str">
+      <c r="N17" s="1">
         <f>IF(Agosto!N33&gt;0,Agosto!N33,"")</f>
-        <v/>
+        <v>810</v>
       </c>
       <c r="O17" s="1">
         <f>IF(Agosto!O33&gt;0,Agosto!O33,"")</f>
         <v>4041.22</v>
       </c>
-      <c r="P17" s="1" t="str">
+      <c r="P17" s="1">
         <f>IF(Agosto!P33&gt;0,Agosto!P33,"")</f>
-        <v/>
+        <v>1800</v>
       </c>
       <c r="Q17" s="1" t="str">
         <f>IF(Agosto!Q33&gt;0,Agosto!Q33,"")</f>
@@ -3420,9 +3420,9 @@
         <f>IF(ISNUMBER(Agosto!I33),I6-Agosto!I33,"")</f>
         <v>0</v>
       </c>
-      <c r="J28" s="1" t="str">
+      <c r="J28" s="1">
         <f>IF(ISNUMBER(Agosto!J33),J6-Agosto!J33,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
         <f>IF(ISNUMBER(Agosto!K33),K6-Agosto!K33,"")</f>
@@ -3436,17 +3436,17 @@
         <f>IF(ISNUMBER(Agosto!M33),M6-Agosto!M33,"")</f>
         <v>0</v>
       </c>
-      <c r="N28" s="1" t="str">
+      <c r="N28" s="1">
         <f>IF(ISNUMBER(Agosto!N33),N6-Agosto!N33,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O28" s="1">
         <f>IF(ISNUMBER(Agosto!O33),O6-Agosto!O33,"")</f>
         <v>3958.78</v>
       </c>
-      <c r="P28" s="1" t="str">
+      <c r="P28" s="1">
         <f>IF(ISNUMBER(Agosto!P33),P6-Agosto!P33,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q28" s="1" t="str">
         <f>IF(ISNUMBER(Agosto!Q33),Q6-Agosto!Q33,"")</f>
@@ -9430,13 +9430,19 @@
       <c r="G14" s="35"/>
       <c r="H14" s="35"/>
       <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
+      <c r="J14" s="35">
+        <v>700</v>
+      </c>
       <c r="K14" s="35"/>
       <c r="L14" s="35"/>
       <c r="M14" s="35"/>
-      <c r="N14" s="35"/>
+      <c r="N14" s="35">
+        <v>810</v>
+      </c>
       <c r="O14" s="35"/>
-      <c r="P14" s="35"/>
+      <c r="P14" s="35">
+        <v>1800</v>
+      </c>
       <c r="Q14" s="35"/>
       <c r="R14" s="35"/>
       <c r="S14" s="35"/>
@@ -9451,7 +9457,7 @@
       <c r="AB14" s="36"/>
       <c r="AC14" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3310</v>
       </c>
       <c r="AD14" s="35"/>
     </row>
@@ -10157,9 +10163,9 @@
         <f t="shared" si="1"/>
         <v>3335.41</v>
       </c>
-      <c r="J33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="J33" s="12">
+        <f t="shared" si="1"/>
+        <v>700</v>
       </c>
       <c r="K33" s="12">
         <f t="shared" si="1"/>
@@ -10173,17 +10179,17 @@
         <f t="shared" si="1"/>
         <v>19000</v>
       </c>
-      <c r="N33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="N33" s="12">
+        <f t="shared" si="1"/>
+        <v>810</v>
       </c>
       <c r="O33" s="12">
         <f t="shared" si="1"/>
         <v>4041.22</v>
       </c>
-      <c r="P33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="P33" s="12">
+        <f t="shared" si="1"/>
+        <v>1800</v>
       </c>
       <c r="Q33" s="12" t="str">
         <f t="shared" si="1"/>
@@ -10235,7 +10241,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="1"/>
-        <v>116119.42000000001</v>
+        <v>119429.42000000001</v>
       </c>
       <c r="AD33" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="R17" s="1">
         <f>IF(Agosto!R33&gt;0,Agosto!R33,"")</f>
-        <v>5674.48</v>
+        <v>7253.99</v>
       </c>
       <c r="S17" s="1" t="str">
         <f>IF(Agosto!S33&gt;0,Agosto!S33,"")</f>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="X17" s="1">
         <f>IF(Agosto!X33&gt;0,Agosto!X33,"")</f>
-        <v>181.21</v>
+        <v>396.21000000000004</v>
       </c>
       <c r="Y17" s="1" t="str">
         <f>IF(Agosto!Y33&gt;0,Agosto!Y33,"")</f>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="R28" s="1">
         <f>IF(ISNUMBER(Agosto!R33),R6-Agosto!R33,"")</f>
-        <v>14325.52</v>
+        <v>12746.01</v>
       </c>
       <c r="S28" s="1" t="str">
         <f>IF(ISNUMBER(Agosto!S33),S6-Agosto!S33,"")</f>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="X28" s="1">
         <f>IF(ISNUMBER(Agosto!X33),X6-Agosto!X33,"")</f>
-        <v>1318.79</v>
+        <v>1103.79</v>
       </c>
       <c r="Y28" s="1" t="str">
         <f>IF(ISNUMBER(Agosto!Y33),Y6-Agosto!Y33,"")</f>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="AC28" s="12">
         <f t="shared" si="7"/>
-        <v>26494.550000000003</v>
+        <v>24700.04</v>
       </c>
     </row>
     <row r="29" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>15080.18</v>
+        <v>13500.67</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="X33" s="12">
         <f t="shared" si="8"/>
-        <v>3394.7</v>
+        <v>3179.7</v>
       </c>
       <c r="Y33" s="12">
         <f t="shared" si="8"/>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>16525.28</v>
+        <v>14730.769999999999</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9444,7 +9444,9 @@
         <v>1800</v>
       </c>
       <c r="Q14" s="35"/>
-      <c r="R14" s="35"/>
+      <c r="R14" s="35">
+        <v>650</v>
+      </c>
       <c r="S14" s="35"/>
       <c r="T14" s="35"/>
       <c r="U14" s="35"/>
@@ -9457,7 +9459,7 @@
       <c r="AB14" s="36"/>
       <c r="AC14" s="35">
         <f t="shared" si="0"/>
-        <v>3310</v>
+        <v>3960</v>
       </c>
       <c r="AD14" s="35"/>
     </row>
@@ -9481,20 +9483,25 @@
       <c r="O15" s="35"/>
       <c r="P15" s="35"/>
       <c r="Q15" s="35"/>
-      <c r="R15" s="35"/>
+      <c r="R15" s="35">
+        <f>945-15.49</f>
+        <v>929.51</v>
+      </c>
       <c r="S15" s="35"/>
       <c r="T15" s="35"/>
       <c r="U15" s="35"/>
       <c r="V15" s="35"/>
       <c r="W15" s="35"/>
-      <c r="X15" s="35"/>
+      <c r="X15" s="35">
+        <v>215</v>
+      </c>
       <c r="Y15" s="35"/>
       <c r="Z15" s="35"/>
       <c r="AA15" s="35"/>
       <c r="AB15" s="36"/>
       <c r="AC15" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1144.51</v>
       </c>
       <c r="AD15" s="35"/>
     </row>
@@ -10197,7 +10204,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="1"/>
-        <v>5674.48</v>
+        <v>7253.99</v>
       </c>
       <c r="S33" s="12" t="str">
         <f t="shared" si="1"/>
@@ -10221,7 +10228,7 @@
       </c>
       <c r="X33" s="12">
         <f t="shared" si="1"/>
-        <v>181.21</v>
+        <v>396.21000000000004</v>
       </c>
       <c r="Y33" s="12" t="str">
         <f t="shared" si="1"/>
@@ -10241,7 +10248,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="1"/>
-        <v>119429.42000000001</v>
+        <v>121223.93000000001</v>
       </c>
       <c r="AD33" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="83">
   <si>
     <t>Presupuesto</t>
   </si>
@@ -289,6 +289,9 @@
   </si>
   <si>
     <t>comepa</t>
+  </si>
+  <si>
+    <t>resistencia calefon</t>
   </si>
 </sst>
 </file>
@@ -2432,7 +2435,7 @@
       </c>
       <c r="R17" s="1">
         <f>IF(Agosto!R33&gt;0,Agosto!R33,"")</f>
-        <v>7253.99</v>
+        <v>9641.69</v>
       </c>
       <c r="S17" s="1" t="str">
         <f>IF(Agosto!S33&gt;0,Agosto!S33,"")</f>
@@ -2458,9 +2461,9 @@
         <f>IF(Agosto!X33&gt;0,Agosto!X33,"")</f>
         <v>396.21000000000004</v>
       </c>
-      <c r="Y17" s="1" t="str">
+      <c r="Y17" s="1">
         <f>IF(Agosto!Y33&gt;0,Agosto!Y33,"")</f>
-        <v/>
+        <v>747.54</v>
       </c>
       <c r="Z17" s="1" t="str">
         <f>IF(Agosto!Z33&gt;0,Agosto!Z33,"")</f>
@@ -2468,7 +2471,7 @@
       </c>
       <c r="AA17" s="1">
         <f>IF(Agosto!AA33&gt;0,Agosto!AA33,"")</f>
-        <v>1229.01</v>
+        <v>1706.06</v>
       </c>
       <c r="AC17" s="1" t="str">
         <f>IF(Agosto!AB33&gt;0,Agosto!AB33,"")</f>
@@ -3454,7 +3457,7 @@
       </c>
       <c r="R28" s="1">
         <f>IF(ISNUMBER(Agosto!R33),R6-Agosto!R33,"")</f>
-        <v>12746.01</v>
+        <v>10358.31</v>
       </c>
       <c r="S28" s="1" t="str">
         <f>IF(ISNUMBER(Agosto!S33),S6-Agosto!S33,"")</f>
@@ -3480,9 +3483,9 @@
         <f>IF(ISNUMBER(Agosto!X33),X6-Agosto!X33,"")</f>
         <v>1103.79</v>
       </c>
-      <c r="Y28" s="1" t="str">
+      <c r="Y28" s="1">
         <f>IF(ISNUMBER(Agosto!Y33),Y6-Agosto!Y33,"")</f>
-        <v/>
+        <v>3252.46</v>
       </c>
       <c r="Z28" s="1" t="str">
         <f>IF(ISNUMBER(Agosto!Z33),Z6-Agosto!Z33,"")</f>
@@ -3490,11 +3493,11 @@
       </c>
       <c r="AA28" s="1">
         <f>IF(ISNUMBER(Agosto!AA33),AA6-Agosto!AA33,"")</f>
-        <v>3770.99</v>
+        <v>3293.94</v>
       </c>
       <c r="AC28" s="12">
         <f t="shared" si="7"/>
-        <v>24700.04</v>
+        <v>25087.749999999996</v>
       </c>
     </row>
     <row r="29" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4019,7 +4022,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>13500.67</v>
+        <v>11112.97</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
@@ -4047,7 +4050,7 @@
       </c>
       <c r="Y33" s="12">
         <f t="shared" si="8"/>
-        <v>-213.27999999999975</v>
+        <v>3039.1800000000003</v>
       </c>
       <c r="Z33" s="12">
         <f t="shared" si="8"/>
@@ -4055,11 +4058,11 @@
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="8"/>
-        <v>-12779.819999999998</v>
+        <v>-13256.869999999997</v>
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>14730.769999999999</v>
+        <v>15118.479999999998</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8802,7 +8805,7 @@
     <col min="27" max="27" width="13" customWidth="1"/>
     <col min="28" max="28" width="14" customWidth="1"/>
     <col min="29" max="29" width="25" customWidth="1"/>
-    <col min="30" max="30" width="16.7109375" customWidth="1"/>
+    <col min="30" max="30" width="17.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="28.5" x14ac:dyDescent="0.25">
@@ -9525,20 +9528,26 @@
       <c r="O16" s="35"/>
       <c r="P16" s="35"/>
       <c r="Q16" s="35"/>
-      <c r="R16" s="35"/>
+      <c r="R16" s="35">
+        <f>858+235+873-15.74-63.3-3.85</f>
+        <v>1883.1100000000001</v>
+      </c>
       <c r="S16" s="35"/>
       <c r="T16" s="35"/>
       <c r="U16" s="35"/>
       <c r="V16" s="35"/>
       <c r="W16" s="35"/>
       <c r="X16" s="35"/>
-      <c r="Y16" s="35"/>
+      <c r="Y16" s="35">
+        <f>760-12.46</f>
+        <v>747.54</v>
+      </c>
       <c r="Z16" s="35"/>
       <c r="AA16" s="35"/>
       <c r="AB16" s="36"/>
       <c r="AC16" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2630.65</v>
       </c>
       <c r="AD16" s="35"/>
     </row>
@@ -9562,7 +9571,10 @@
       <c r="O17" s="35"/>
       <c r="P17" s="35"/>
       <c r="Q17" s="35"/>
-      <c r="R17" s="35"/>
+      <c r="R17" s="35">
+        <f>513-8.41</f>
+        <v>504.59</v>
+      </c>
       <c r="S17" s="35"/>
       <c r="T17" s="35"/>
       <c r="U17" s="35"/>
@@ -9571,13 +9583,18 @@
       <c r="X17" s="35"/>
       <c r="Y17" s="35"/>
       <c r="Z17" s="35"/>
-      <c r="AA17" s="35"/>
+      <c r="AA17" s="35">
+        <f>485-7.95</f>
+        <v>477.05</v>
+      </c>
       <c r="AB17" s="36"/>
       <c r="AC17" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD17" s="35"/>
+        <v>981.64</v>
+      </c>
+      <c r="AD17" s="35" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="18" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="34">
@@ -10204,7 +10221,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="1"/>
-        <v>7253.99</v>
+        <v>9641.69</v>
       </c>
       <c r="S33" s="12" t="str">
         <f t="shared" si="1"/>
@@ -10230,9 +10247,9 @@
         <f t="shared" si="1"/>
         <v>396.21000000000004</v>
       </c>
-      <c r="Y33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="Y33" s="12">
+        <f t="shared" si="1"/>
+        <v>747.54</v>
       </c>
       <c r="Z33" s="12" t="str">
         <f t="shared" si="1"/>
@@ -10240,7 +10257,7 @@
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="1"/>
-        <v>1229.01</v>
+        <v>1706.06</v>
       </c>
       <c r="AB33" s="38" t="str">
         <f t="shared" si="1"/>
@@ -10248,7 +10265,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="1"/>
-        <v>121223.93000000001</v>
+        <v>124836.22</v>
       </c>
       <c r="AD33" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="87">
   <si>
     <t>Presupuesto</t>
   </si>
@@ -293,6 +293,18 @@
   <si>
     <t>resistencia calefon</t>
   </si>
+  <si>
+    <t>Cena Berni</t>
+  </si>
+  <si>
+    <t>3 comepa</t>
+  </si>
+  <si>
+    <t>envio zartenes</t>
+  </si>
+  <si>
+    <t>regalo lolo</t>
+  </si>
 </sst>
 </file>
 
@@ -402,7 +414,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -505,6 +517,12 @@
         <bgColor rgb="FF4472C4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -533,7 +551,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -616,6 +634,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1498,9 +1517,6 @@
       <c r="A7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="1">
-        <v>25000</v>
-      </c>
       <c r="C7" s="1">
         <v>4369</v>
       </c>
@@ -1573,7 +1589,7 @@
       <c r="AB7" s="6"/>
       <c r="AC7" s="1">
         <f t="shared" si="0"/>
-        <v>176229</v>
+        <v>151229</v>
       </c>
       <c r="AD7" s="7">
         <f t="shared" si="1"/>
@@ -1591,21 +1607,24 @@
       </c>
       <c r="AH7" s="8">
         <f t="shared" si="3"/>
-        <v>80614.5</v>
+        <v>68114.5</v>
       </c>
       <c r="AI7" s="9">
         <f t="shared" si="4"/>
-        <v>72364.5</v>
+        <v>59864.5</v>
       </c>
       <c r="AJ7" s="10">
         <f t="shared" si="5"/>
-        <v>152979</v>
+        <v>127979</v>
       </c>
     </row>
     <row r="8" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>42</v>
       </c>
+      <c r="B8" s="1">
+        <v>25000</v>
+      </c>
       <c r="D8" s="1">
         <v>15750</v>
       </c>
@@ -1674,8 +1693,8 @@
       </c>
       <c r="AB8" s="6"/>
       <c r="AC8" s="1">
-        <f t="shared" si="0"/>
-        <v>138160</v>
+        <f>SUM(B8:AB8)</f>
+        <v>163160</v>
       </c>
       <c r="AD8" s="7">
         <f t="shared" si="1"/>
@@ -1693,15 +1712,15 @@
       </c>
       <c r="AH8" s="8">
         <f t="shared" si="3"/>
-        <v>61580</v>
+        <v>74080</v>
       </c>
       <c r="AI8" s="9">
         <f t="shared" si="4"/>
-        <v>53330</v>
+        <v>65830</v>
       </c>
       <c r="AJ8" s="10">
         <f t="shared" si="5"/>
-        <v>114910</v>
+        <v>139910</v>
       </c>
     </row>
     <row r="9" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2423,7 +2442,7 @@
       </c>
       <c r="O17" s="1">
         <f>IF(Agosto!O33&gt;0,Agosto!O33,"")</f>
-        <v>4041.22</v>
+        <v>7575.0299999999988</v>
       </c>
       <c r="P17" s="1">
         <f>IF(Agosto!P33&gt;0,Agosto!P33,"")</f>
@@ -2435,15 +2454,15 @@
       </c>
       <c r="R17" s="1">
         <f>IF(Agosto!R33&gt;0,Agosto!R33,"")</f>
-        <v>9641.69</v>
-      </c>
-      <c r="S17" s="1" t="str">
+        <v>11378.37</v>
+      </c>
+      <c r="S17" s="1">
         <f>IF(Agosto!S33&gt;0,Agosto!S33,"")</f>
-        <v/>
+        <v>858.12</v>
       </c>
       <c r="T17" s="1">
         <f>IF(Agosto!T33&gt;0,Agosto!T33,"")</f>
-        <v>1882.2299999999998</v>
+        <v>3841.8099999999995</v>
       </c>
       <c r="U17" s="1" t="str">
         <f>IF(Agosto!U33&gt;0,Agosto!U33,"")</f>
@@ -2463,7 +2482,7 @@
       </c>
       <c r="Y17" s="1">
         <f>IF(Agosto!Y33&gt;0,Agosto!Y33,"")</f>
-        <v>747.54</v>
+        <v>1190.1599999999999</v>
       </c>
       <c r="Z17" s="1" t="str">
         <f>IF(Agosto!Z33&gt;0,Agosto!Z33,"")</f>
@@ -2471,7 +2490,7 @@
       </c>
       <c r="AA17" s="1">
         <f>IF(Agosto!AA33&gt;0,Agosto!AA33,"")</f>
-        <v>1706.06</v>
+        <v>4723.9800000000005</v>
       </c>
       <c r="AC17" s="1" t="str">
         <f>IF(Agosto!AB33&gt;0,Agosto!AB33,"")</f>
@@ -3445,7 +3464,7 @@
       </c>
       <c r="O28" s="1">
         <f>IF(ISNUMBER(Agosto!O33),O6-Agosto!O33,"")</f>
-        <v>3958.78</v>
+        <v>424.97000000000116</v>
       </c>
       <c r="P28" s="1">
         <f>IF(ISNUMBER(Agosto!P33),P6-Agosto!P33,"")</f>
@@ -3457,15 +3476,15 @@
       </c>
       <c r="R28" s="1">
         <f>IF(ISNUMBER(Agosto!R33),R6-Agosto!R33,"")</f>
-        <v>10358.31</v>
-      </c>
-      <c r="S28" s="1" t="str">
+        <v>8621.6299999999992</v>
+      </c>
+      <c r="S28" s="1">
         <f>IF(ISNUMBER(Agosto!S33),S6-Agosto!S33,"")</f>
-        <v/>
+        <v>1641.88</v>
       </c>
       <c r="T28" s="1">
         <f>IF(ISNUMBER(Agosto!T33),T6-Agosto!T33,"")</f>
-        <v>3117.7700000000004</v>
+        <v>1158.1900000000005</v>
       </c>
       <c r="U28" s="1" t="str">
         <f>IF(ISNUMBER(Agosto!U33),U6-Agosto!U33,"")</f>
@@ -3485,7 +3504,7 @@
       </c>
       <c r="Y28" s="1">
         <f>IF(ISNUMBER(Agosto!Y33),Y6-Agosto!Y33,"")</f>
-        <v>3252.46</v>
+        <v>2809.84</v>
       </c>
       <c r="Z28" s="1" t="str">
         <f>IF(ISNUMBER(Agosto!Z33),Z6-Agosto!Z33,"")</f>
@@ -3493,11 +3512,11 @@
       </c>
       <c r="AA28" s="1">
         <f>IF(ISNUMBER(Agosto!AA33),AA6-Agosto!AA33,"")</f>
-        <v>3293.94</v>
+        <v>276.01999999999953</v>
       </c>
       <c r="AC28" s="12">
         <f t="shared" si="7"/>
-        <v>25087.749999999996</v>
+        <v>16039.02</v>
       </c>
     </row>
     <row r="29" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3505,7 +3524,7 @@
         <v>41</v>
       </c>
       <c r="B29" s="1" t="str">
-        <f>IF(ISNUMBER(Setiembre!B32),B7-Setiembre!B32,"")</f>
+        <f>IF(ISNUMBER(Setiembre!B32),B8-Setiembre!B32,"")</f>
         <v/>
       </c>
       <c r="C29" s="1" t="str">
@@ -3618,7 +3637,7 @@
         <v>42</v>
       </c>
       <c r="B30" s="1" t="str">
-        <f>IF(ISNUMBER(Octubre!B33),B8-Octubre!B33,"")</f>
+        <f>IF(ISNUMBER(Octubre!B33),#REF!-Octubre!B33,"")</f>
         <v/>
       </c>
       <c r="C30" s="1" t="str">
@@ -4010,7 +4029,7 @@
       </c>
       <c r="O33" s="12">
         <f t="shared" si="8"/>
-        <v>15373.62</v>
+        <v>11839.810000000001</v>
       </c>
       <c r="P33" s="12">
         <f t="shared" si="8"/>
@@ -4022,15 +4041,15 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>11112.97</v>
+        <v>9376.2899999999991</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
-        <v>1893.8000000000002</v>
+        <v>3535.6800000000003</v>
       </c>
       <c r="T33" s="12">
         <f t="shared" si="8"/>
-        <v>4856.2700000000004</v>
+        <v>2896.6900000000005</v>
       </c>
       <c r="U33" s="12">
         <f t="shared" si="8"/>
@@ -4050,7 +4069,7 @@
       </c>
       <c r="Y33" s="12">
         <f t="shared" si="8"/>
-        <v>3039.1800000000003</v>
+        <v>2596.5600000000004</v>
       </c>
       <c r="Z33" s="12">
         <f t="shared" si="8"/>
@@ -4058,11 +4077,11 @@
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="8"/>
-        <v>-13256.869999999997</v>
+        <v>-16274.789999999997</v>
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>15118.479999999998</v>
+        <v>6069.75</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9625,13 +9644,17 @@
       <c r="X18" s="35"/>
       <c r="Y18" s="35"/>
       <c r="Z18" s="35"/>
-      <c r="AA18" s="35"/>
+      <c r="AA18" s="44">
+        <v>1584</v>
+      </c>
       <c r="AB18" s="36"/>
       <c r="AC18" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD18" s="35"/>
+        <v>1584</v>
+      </c>
+      <c r="AD18" s="35" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="19" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="34">
@@ -9650,7 +9673,10 @@
       <c r="L19" s="35"/>
       <c r="M19" s="35"/>
       <c r="N19" s="35"/>
-      <c r="O19" s="35"/>
+      <c r="O19" s="35">
+        <f>500-8.19</f>
+        <v>491.81</v>
+      </c>
       <c r="P19" s="35"/>
       <c r="Q19" s="35"/>
       <c r="R19" s="35"/>
@@ -9662,13 +9688,18 @@
       <c r="X19" s="35"/>
       <c r="Y19" s="35"/>
       <c r="Z19" s="35"/>
-      <c r="AA19" s="35"/>
+      <c r="AA19" s="35">
+        <f>352+470+353-8.54-5.6-3.33</f>
+        <v>1157.5300000000002</v>
+      </c>
       <c r="AB19" s="36"/>
       <c r="AC19" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD19" s="35"/>
+        <v>1649.3400000000001</v>
+      </c>
+      <c r="AD19" s="35" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="20" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="34">
@@ -9687,11 +9718,19 @@
       <c r="L20" s="35"/>
       <c r="M20" s="35"/>
       <c r="N20" s="35"/>
-      <c r="O20" s="35"/>
+      <c r="O20" s="35">
+        <v>3900</v>
+      </c>
       <c r="P20" s="35"/>
       <c r="Q20" s="35"/>
-      <c r="R20" s="35"/>
-      <c r="S20" s="35"/>
+      <c r="R20" s="35">
+        <f>1040.99-18.39</f>
+        <v>1022.6</v>
+      </c>
+      <c r="S20" s="35">
+        <f>874-15.88</f>
+        <v>858.12</v>
+      </c>
       <c r="T20" s="35"/>
       <c r="U20" s="35"/>
       <c r="V20" s="35"/>
@@ -9699,13 +9738,18 @@
       <c r="X20" s="35"/>
       <c r="Y20" s="35"/>
       <c r="Z20" s="35"/>
-      <c r="AA20" s="35"/>
+      <c r="AA20" s="35">
+        <f>281-4.61</f>
+        <v>276.39</v>
+      </c>
       <c r="AB20" s="36"/>
       <c r="AC20" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD20" s="35"/>
+        <v>6057.1100000000006</v>
+      </c>
+      <c r="AD20" s="35" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="21" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="34">
@@ -9724,25 +9768,38 @@
       <c r="L21" s="35"/>
       <c r="M21" s="35"/>
       <c r="N21" s="35"/>
-      <c r="O21" s="35"/>
+      <c r="O21" s="35">
+        <v>-858</v>
+      </c>
       <c r="P21" s="35"/>
       <c r="Q21" s="35"/>
-      <c r="R21" s="35"/>
+      <c r="R21" s="35">
+        <f>727-12.92</f>
+        <v>714.08</v>
+      </c>
       <c r="S21" s="35"/>
-      <c r="T21" s="35"/>
+      <c r="T21" s="35">
+        <f>70+1080-0.66+269.46-19.88+570-9.34</f>
+        <v>1959.58</v>
+      </c>
       <c r="U21" s="35"/>
       <c r="V21" s="35"/>
       <c r="W21" s="35"/>
       <c r="X21" s="35"/>
-      <c r="Y21" s="35"/>
+      <c r="Y21" s="35">
+        <f>450-7.38</f>
+        <v>442.62</v>
+      </c>
       <c r="Z21" s="35"/>
       <c r="AA21" s="35"/>
       <c r="AB21" s="36"/>
       <c r="AC21" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD21" s="35"/>
+        <v>2258.2799999999997</v>
+      </c>
+      <c r="AD21" s="35" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="22" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="34">
@@ -10209,7 +10266,7 @@
       </c>
       <c r="O33" s="12">
         <f t="shared" si="1"/>
-        <v>4041.22</v>
+        <v>7575.0299999999988</v>
       </c>
       <c r="P33" s="12">
         <f t="shared" si="1"/>
@@ -10221,15 +10278,15 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="1"/>
-        <v>9641.69</v>
-      </c>
-      <c r="S33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+        <v>11378.37</v>
+      </c>
+      <c r="S33" s="12">
+        <f t="shared" si="1"/>
+        <v>858.12</v>
       </c>
       <c r="T33" s="12">
         <f t="shared" si="1"/>
-        <v>1882.2299999999998</v>
+        <v>3841.8099999999995</v>
       </c>
       <c r="U33" s="12" t="str">
         <f t="shared" si="1"/>
@@ -10249,7 +10306,7 @@
       </c>
       <c r="Y33" s="12">
         <f t="shared" si="1"/>
-        <v>747.54</v>
+        <v>1190.1599999999999</v>
       </c>
       <c r="Z33" s="12" t="str">
         <f t="shared" si="1"/>
@@ -10257,7 +10314,7 @@
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="1"/>
-        <v>1706.06</v>
+        <v>4723.9800000000005</v>
       </c>
       <c r="AB33" s="38" t="str">
         <f t="shared" si="1"/>
@@ -10265,7 +10322,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="1"/>
-        <v>124836.22</v>
+        <v>136384.94999999998</v>
       </c>
       <c r="AD33" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="88">
   <si>
     <t>Presupuesto</t>
   </si>
@@ -305,6 +305,9 @@
   <si>
     <t>regalo lolo</t>
   </si>
+  <si>
+    <t>farmacia</t>
+  </si>
 </sst>
 </file>
 
@@ -414,7 +417,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -523,6 +526,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -551,7 +560,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -625,6 +634,7 @@
     <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -634,7 +644,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -960,36 +970,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
-      <c r="S1" s="41"/>
-      <c r="T1" s="41"/>
-      <c r="U1" s="41"/>
-      <c r="V1" s="41"/>
-      <c r="W1" s="41"/>
-      <c r="X1" s="41"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="41"/>
-      <c r="AA1" s="41"/>
-      <c r="AB1" s="41"/>
+      <c r="A1" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="42"/>
+      <c r="Q1" s="42"/>
+      <c r="R1" s="42"/>
+      <c r="S1" s="42"/>
+      <c r="T1" s="42"/>
+      <c r="U1" s="42"/>
+      <c r="V1" s="42"/>
+      <c r="W1" s="42"/>
+      <c r="X1" s="42"/>
+      <c r="Y1" s="42"/>
+      <c r="Z1" s="42"/>
+      <c r="AA1" s="42"/>
+      <c r="AB1" s="42"/>
     </row>
     <row r="2" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1928,36 +1938,36 @@
       </c>
     </row>
     <row r="12" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="42"/>
-      <c r="K12" s="42"/>
-      <c r="L12" s="42"/>
-      <c r="M12" s="42"/>
-      <c r="N12" s="42"/>
-      <c r="O12" s="42"/>
-      <c r="P12" s="42"/>
-      <c r="Q12" s="42"/>
-      <c r="R12" s="42"/>
-      <c r="S12" s="42"/>
-      <c r="T12" s="42"/>
-      <c r="U12" s="42"/>
-      <c r="V12" s="42"/>
-      <c r="W12" s="42"/>
-      <c r="X12" s="42"/>
-      <c r="Y12" s="42"/>
-      <c r="Z12" s="42"/>
-      <c r="AA12" s="42"/>
-      <c r="AB12" s="42"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="43"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="43"/>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="43"/>
+      <c r="R12" s="43"/>
+      <c r="S12" s="43"/>
+      <c r="T12" s="43"/>
+      <c r="U12" s="43"/>
+      <c r="V12" s="43"/>
+      <c r="W12" s="43"/>
+      <c r="X12" s="43"/>
+      <c r="Y12" s="43"/>
+      <c r="Z12" s="43"/>
+      <c r="AA12" s="43"/>
+      <c r="AB12" s="43"/>
     </row>
     <row r="13" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -2442,7 +2452,7 @@
       </c>
       <c r="O17" s="1">
         <f>IF(Agosto!O33&gt;0,Agosto!O33,"")</f>
-        <v>7575.0299999999988</v>
+        <v>10325.029999999999</v>
       </c>
       <c r="P17" s="1">
         <f>IF(Agosto!P33&gt;0,Agosto!P33,"")</f>
@@ -2454,11 +2464,11 @@
       </c>
       <c r="R17" s="1">
         <f>IF(Agosto!R33&gt;0,Agosto!R33,"")</f>
-        <v>11378.37</v>
+        <v>16436.79</v>
       </c>
       <c r="S17" s="1">
         <f>IF(Agosto!S33&gt;0,Agosto!S33,"")</f>
-        <v>858.12</v>
+        <v>2458.12</v>
       </c>
       <c r="T17" s="1">
         <f>IF(Agosto!T33&gt;0,Agosto!T33,"")</f>
@@ -2490,7 +2500,7 @@
       </c>
       <c r="AA17" s="1">
         <f>IF(Agosto!AA33&gt;0,Agosto!AA33,"")</f>
-        <v>4723.9800000000005</v>
+        <v>5873.9800000000005</v>
       </c>
       <c r="AC17" s="1" t="str">
         <f>IF(Agosto!AB33&gt;0,Agosto!AB33,"")</f>
@@ -2950,36 +2960,36 @@
       </c>
     </row>
     <row r="23" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="43" t="s">
+      <c r="A23" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="43"/>
-      <c r="C23" s="43"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="43"/>
-      <c r="H23" s="43"/>
-      <c r="I23" s="43"/>
-      <c r="J23" s="43"/>
-      <c r="K23" s="43"/>
-      <c r="L23" s="43"/>
-      <c r="M23" s="43"/>
-      <c r="N23" s="43"/>
-      <c r="O23" s="43"/>
-      <c r="P23" s="43"/>
-      <c r="Q23" s="43"/>
-      <c r="R23" s="43"/>
-      <c r="S23" s="43"/>
-      <c r="T23" s="43"/>
-      <c r="U23" s="43"/>
-      <c r="V23" s="43"/>
-      <c r="W23" s="43"/>
-      <c r="X23" s="43"/>
-      <c r="Y23" s="43"/>
-      <c r="Z23" s="43"/>
-      <c r="AA23" s="43"/>
-      <c r="AB23" s="43"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="44"/>
+      <c r="K23" s="44"/>
+      <c r="L23" s="44"/>
+      <c r="M23" s="44"/>
+      <c r="N23" s="44"/>
+      <c r="O23" s="44"/>
+      <c r="P23" s="44"/>
+      <c r="Q23" s="44"/>
+      <c r="R23" s="44"/>
+      <c r="S23" s="44"/>
+      <c r="T23" s="44"/>
+      <c r="U23" s="44"/>
+      <c r="V23" s="44"/>
+      <c r="W23" s="44"/>
+      <c r="X23" s="44"/>
+      <c r="Y23" s="44"/>
+      <c r="Z23" s="44"/>
+      <c r="AA23" s="44"/>
+      <c r="AB23" s="44"/>
     </row>
     <row r="24" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
@@ -3464,7 +3474,7 @@
       </c>
       <c r="O28" s="1">
         <f>IF(ISNUMBER(Agosto!O33),O6-Agosto!O33,"")</f>
-        <v>424.97000000000116</v>
+        <v>-2325.0299999999988</v>
       </c>
       <c r="P28" s="1">
         <f>IF(ISNUMBER(Agosto!P33),P6-Agosto!P33,"")</f>
@@ -3476,23 +3486,23 @@
       </c>
       <c r="R28" s="1">
         <f>IF(ISNUMBER(Agosto!R33),R6-Agosto!R33,"")</f>
-        <v>8621.6299999999992</v>
+        <v>3563.2099999999991</v>
       </c>
       <c r="S28" s="1">
         <f>IF(ISNUMBER(Agosto!S33),S6-Agosto!S33,"")</f>
-        <v>1641.88</v>
+        <v>41.880000000000109</v>
       </c>
       <c r="T28" s="1">
         <f>IF(ISNUMBER(Agosto!T33),T6-Agosto!T33,"")</f>
         <v>1158.1900000000005</v>
       </c>
-      <c r="U28" s="1" t="str">
+      <c r="U28" s="1">
         <f>IF(ISNUMBER(Agosto!U33),U6-Agosto!U33,"")</f>
-        <v/>
-      </c>
-      <c r="V28" s="1" t="str">
+        <v>0</v>
+      </c>
+      <c r="V28" s="1">
         <f>IF(ISNUMBER(Agosto!V33),V6-Agosto!V33,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W28" s="1" t="str">
         <f>IF(ISNUMBER(Agosto!W33),W6-Agosto!W33,"")</f>
@@ -3512,11 +3522,11 @@
       </c>
       <c r="AA28" s="1">
         <f>IF(ISNUMBER(Agosto!AA33),AA6-Agosto!AA33,"")</f>
-        <v>276.01999999999953</v>
+        <v>-873.98000000000047</v>
       </c>
       <c r="AC28" s="12">
         <f t="shared" si="7"/>
-        <v>16039.02</v>
+        <v>5480.5999999999995</v>
       </c>
     </row>
     <row r="29" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4029,7 +4039,7 @@
       </c>
       <c r="O33" s="12">
         <f t="shared" si="8"/>
-        <v>11839.810000000001</v>
+        <v>9089.8100000000013</v>
       </c>
       <c r="P33" s="12">
         <f t="shared" si="8"/>
@@ -4041,11 +4051,11 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>9376.2899999999991</v>
+        <v>4317.869999999999</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
-        <v>3535.6800000000003</v>
+        <v>1935.6800000000003</v>
       </c>
       <c r="T33" s="12">
         <f t="shared" si="8"/>
@@ -4077,11 +4087,11 @@
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="8"/>
-        <v>-16274.789999999997</v>
+        <v>-17424.789999999997</v>
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>6069.75</v>
+        <v>-4488.6700000000019</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9644,7 +9654,7 @@
       <c r="X18" s="35"/>
       <c r="Y18" s="35"/>
       <c r="Z18" s="35"/>
-      <c r="AA18" s="44">
+      <c r="AA18" s="41">
         <v>1584</v>
       </c>
       <c r="AB18" s="36"/>
@@ -9818,11 +9828,17 @@
       <c r="L22" s="35"/>
       <c r="M22" s="35"/>
       <c r="N22" s="35"/>
-      <c r="O22" s="35"/>
+      <c r="O22" s="45">
+        <v>150</v>
+      </c>
       <c r="P22" s="35"/>
       <c r="Q22" s="35"/>
-      <c r="R22" s="35"/>
-      <c r="S22" s="35"/>
+      <c r="R22" s="45">
+        <v>800</v>
+      </c>
+      <c r="S22" s="45">
+        <v>1600</v>
+      </c>
       <c r="T22" s="35"/>
       <c r="U22" s="35"/>
       <c r="V22" s="35"/>
@@ -9830,13 +9846,17 @@
       <c r="X22" s="35"/>
       <c r="Y22" s="35"/>
       <c r="Z22" s="35"/>
-      <c r="AA22" s="35"/>
+      <c r="AA22" s="45">
+        <v>1150</v>
+      </c>
       <c r="AB22" s="36"/>
       <c r="AC22" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD22" s="35"/>
+        <v>3700</v>
+      </c>
+      <c r="AD22" s="35" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="23" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="34">
@@ -9855,10 +9875,14 @@
       <c r="L23" s="35"/>
       <c r="M23" s="35"/>
       <c r="N23" s="35"/>
-      <c r="O23" s="35"/>
+      <c r="O23" s="45">
+        <v>2600</v>
+      </c>
       <c r="P23" s="35"/>
       <c r="Q23" s="35"/>
-      <c r="R23" s="35"/>
+      <c r="R23" s="45">
+        <v>1500</v>
+      </c>
       <c r="S23" s="35"/>
       <c r="T23" s="35"/>
       <c r="U23" s="35"/>
@@ -9871,7 +9895,7 @@
       <c r="AB23" s="36"/>
       <c r="AC23" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="AD23" s="35"/>
     </row>
@@ -9895,7 +9919,10 @@
       <c r="O24" s="35"/>
       <c r="P24" s="35"/>
       <c r="Q24" s="35"/>
-      <c r="R24" s="35"/>
+      <c r="R24" s="35">
+        <f>310-5.08</f>
+        <v>304.92</v>
+      </c>
       <c r="S24" s="35"/>
       <c r="T24" s="35"/>
       <c r="U24" s="35"/>
@@ -9908,7 +9935,7 @@
       <c r="AB24" s="36"/>
       <c r="AC24" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>304.92</v>
       </c>
       <c r="AD24" s="35"/>
     </row>
@@ -10006,7 +10033,10 @@
       <c r="O27" s="35"/>
       <c r="P27" s="35"/>
       <c r="Q27" s="35"/>
-      <c r="R27" s="35"/>
+      <c r="R27" s="35">
+        <f>1437.41+331+728-5.43-24.91-12.57</f>
+        <v>2453.5</v>
+      </c>
       <c r="S27" s="35"/>
       <c r="T27" s="35"/>
       <c r="U27" s="35"/>
@@ -10019,7 +10049,7 @@
       <c r="AB27" s="36"/>
       <c r="AC27" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2453.5</v>
       </c>
       <c r="AD27" s="35"/>
     </row>
@@ -10194,8 +10224,12 @@
       <c r="R32" s="35"/>
       <c r="S32" s="35"/>
       <c r="T32" s="35"/>
-      <c r="U32" s="35"/>
-      <c r="V32" s="35"/>
+      <c r="U32" s="35">
+        <v>0</v>
+      </c>
+      <c r="V32" s="35">
+        <v>0</v>
+      </c>
       <c r="W32" s="35"/>
       <c r="X32" s="35"/>
       <c r="Y32" s="35"/>
@@ -10266,7 +10300,7 @@
       </c>
       <c r="O33" s="12">
         <f t="shared" si="1"/>
-        <v>7575.0299999999988</v>
+        <v>10325.029999999999</v>
       </c>
       <c r="P33" s="12">
         <f t="shared" si="1"/>
@@ -10278,23 +10312,23 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="1"/>
-        <v>11378.37</v>
+        <v>16436.79</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="1"/>
-        <v>858.12</v>
+        <v>2458.12</v>
       </c>
       <c r="T33" s="12">
         <f t="shared" si="1"/>
         <v>3841.8099999999995</v>
       </c>
-      <c r="U33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="V33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="U33" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="W33" s="12" t="str">
         <f t="shared" si="1"/>
@@ -10314,7 +10348,7 @@
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="1"/>
-        <v>4723.9800000000005</v>
+        <v>5873.9800000000005</v>
       </c>
       <c r="AB33" s="38" t="str">
         <f t="shared" si="1"/>
@@ -10322,7 +10356,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="1"/>
-        <v>136384.94999999998</v>
+        <v>146943.37</v>
       </c>
       <c r="AD33" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="89">
   <si>
     <t>Presupuesto</t>
   </si>
@@ -307,6 +307,9 @@
   </si>
   <si>
     <t>farmacia</t>
+  </si>
+  <si>
+    <t>disfraces roci</t>
   </si>
 </sst>
 </file>
@@ -635,6 +638,7 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -644,7 +648,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -970,36 +973,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="42"/>
-      <c r="W1" s="42"/>
-      <c r="X1" s="42"/>
-      <c r="Y1" s="42"/>
-      <c r="Z1" s="42"/>
-      <c r="AA1" s="42"/>
-      <c r="AB1" s="42"/>
+      <c r="A1" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="43"/>
+      <c r="Q1" s="43"/>
+      <c r="R1" s="43"/>
+      <c r="S1" s="43"/>
+      <c r="T1" s="43"/>
+      <c r="U1" s="43"/>
+      <c r="V1" s="43"/>
+      <c r="W1" s="43"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="43"/>
+      <c r="Z1" s="43"/>
+      <c r="AA1" s="43"/>
+      <c r="AB1" s="43"/>
     </row>
     <row r="2" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1938,36 +1941,36 @@
       </c>
     </row>
     <row r="12" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="43" t="s">
+      <c r="A12" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="43"/>
-      <c r="K12" s="43"/>
-      <c r="L12" s="43"/>
-      <c r="M12" s="43"/>
-      <c r="N12" s="43"/>
-      <c r="O12" s="43"/>
-      <c r="P12" s="43"/>
-      <c r="Q12" s="43"/>
-      <c r="R12" s="43"/>
-      <c r="S12" s="43"/>
-      <c r="T12" s="43"/>
-      <c r="U12" s="43"/>
-      <c r="V12" s="43"/>
-      <c r="W12" s="43"/>
-      <c r="X12" s="43"/>
-      <c r="Y12" s="43"/>
-      <c r="Z12" s="43"/>
-      <c r="AA12" s="43"/>
-      <c r="AB12" s="43"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="44"/>
+      <c r="L12" s="44"/>
+      <c r="M12" s="44"/>
+      <c r="N12" s="44"/>
+      <c r="O12" s="44"/>
+      <c r="P12" s="44"/>
+      <c r="Q12" s="44"/>
+      <c r="R12" s="44"/>
+      <c r="S12" s="44"/>
+      <c r="T12" s="44"/>
+      <c r="U12" s="44"/>
+      <c r="V12" s="44"/>
+      <c r="W12" s="44"/>
+      <c r="X12" s="44"/>
+      <c r="Y12" s="44"/>
+      <c r="Z12" s="44"/>
+      <c r="AA12" s="44"/>
+      <c r="AB12" s="44"/>
     </row>
     <row r="13" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -2500,7 +2503,7 @@
       </c>
       <c r="AA17" s="1">
         <f>IF(Agosto!AA33&gt;0,Agosto!AA33,"")</f>
-        <v>5873.9800000000005</v>
+        <v>6388.06</v>
       </c>
       <c r="AC17" s="1" t="str">
         <f>IF(Agosto!AB33&gt;0,Agosto!AB33,"")</f>
@@ -2960,36 +2963,36 @@
       </c>
     </row>
     <row r="23" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="44" t="s">
+      <c r="A23" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="44"/>
-      <c r="C23" s="44"/>
-      <c r="D23" s="44"/>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="44"/>
-      <c r="J23" s="44"/>
-      <c r="K23" s="44"/>
-      <c r="L23" s="44"/>
-      <c r="M23" s="44"/>
-      <c r="N23" s="44"/>
-      <c r="O23" s="44"/>
-      <c r="P23" s="44"/>
-      <c r="Q23" s="44"/>
-      <c r="R23" s="44"/>
-      <c r="S23" s="44"/>
-      <c r="T23" s="44"/>
-      <c r="U23" s="44"/>
-      <c r="V23" s="44"/>
-      <c r="W23" s="44"/>
-      <c r="X23" s="44"/>
-      <c r="Y23" s="44"/>
-      <c r="Z23" s="44"/>
-      <c r="AA23" s="44"/>
-      <c r="AB23" s="44"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="45"/>
+      <c r="L23" s="45"/>
+      <c r="M23" s="45"/>
+      <c r="N23" s="45"/>
+      <c r="O23" s="45"/>
+      <c r="P23" s="45"/>
+      <c r="Q23" s="45"/>
+      <c r="R23" s="45"/>
+      <c r="S23" s="45"/>
+      <c r="T23" s="45"/>
+      <c r="U23" s="45"/>
+      <c r="V23" s="45"/>
+      <c r="W23" s="45"/>
+      <c r="X23" s="45"/>
+      <c r="Y23" s="45"/>
+      <c r="Z23" s="45"/>
+      <c r="AA23" s="45"/>
+      <c r="AB23" s="45"/>
     </row>
     <row r="24" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
@@ -3522,11 +3525,11 @@
       </c>
       <c r="AA28" s="1">
         <f>IF(ISNUMBER(Agosto!AA33),AA6-Agosto!AA33,"")</f>
-        <v>-873.98000000000047</v>
+        <v>-1388.0600000000004</v>
       </c>
       <c r="AC28" s="12">
         <f t="shared" si="7"/>
-        <v>5480.5999999999995</v>
+        <v>4966.5199999999995</v>
       </c>
     </row>
     <row r="29" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4087,11 +4090,11 @@
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="8"/>
-        <v>-17424.789999999997</v>
+        <v>-17938.87</v>
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>-4488.6700000000019</v>
+        <v>-5002.7500000000036</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9828,15 +9831,15 @@
       <c r="L22" s="35"/>
       <c r="M22" s="35"/>
       <c r="N22" s="35"/>
-      <c r="O22" s="45">
+      <c r="O22" s="42">
         <v>150</v>
       </c>
       <c r="P22" s="35"/>
       <c r="Q22" s="35"/>
-      <c r="R22" s="45">
+      <c r="R22" s="42">
         <v>800</v>
       </c>
-      <c r="S22" s="45">
+      <c r="S22" s="42">
         <v>1600</v>
       </c>
       <c r="T22" s="35"/>
@@ -9846,7 +9849,7 @@
       <c r="X22" s="35"/>
       <c r="Y22" s="35"/>
       <c r="Z22" s="35"/>
-      <c r="AA22" s="45">
+      <c r="AA22" s="42">
         <v>1150</v>
       </c>
       <c r="AB22" s="36"/>
@@ -9875,12 +9878,12 @@
       <c r="L23" s="35"/>
       <c r="M23" s="35"/>
       <c r="N23" s="35"/>
-      <c r="O23" s="45">
+      <c r="O23" s="42">
         <v>2600</v>
       </c>
       <c r="P23" s="35"/>
       <c r="Q23" s="35"/>
-      <c r="R23" s="45">
+      <c r="R23" s="42">
         <v>1500</v>
       </c>
       <c r="S23" s="35"/>
@@ -10082,13 +10085,18 @@
       <c r="X28" s="35"/>
       <c r="Y28" s="35"/>
       <c r="Z28" s="35"/>
-      <c r="AA28" s="35"/>
+      <c r="AA28" s="35">
+        <f>117-1.92+399</f>
+        <v>514.08000000000004</v>
+      </c>
       <c r="AB28" s="36"/>
       <c r="AC28" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD28" s="35"/>
+        <v>514.08000000000004</v>
+      </c>
+      <c r="AD28" s="35" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="29" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="34">
@@ -10348,7 +10356,7 @@
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="1"/>
-        <v>5873.9800000000005</v>
+        <v>6388.06</v>
       </c>
       <c r="AB33" s="38" t="str">
         <f t="shared" si="1"/>
@@ -10356,7 +10364,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="1"/>
-        <v>146943.37</v>
+        <v>147457.44999999998</v>
       </c>
       <c r="AD33" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -2455,7 +2455,7 @@
       </c>
       <c r="O17" s="1">
         <f>IF(Agosto!O33&gt;0,Agosto!O33,"")</f>
-        <v>10325.029999999999</v>
+        <v>13308.64</v>
       </c>
       <c r="P17" s="1">
         <f>IF(Agosto!P33&gt;0,Agosto!P33,"")</f>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="T17" s="1">
         <f>IF(Agosto!T33&gt;0,Agosto!T33,"")</f>
-        <v>3841.8099999999995</v>
+        <v>5511.4699999999993</v>
       </c>
       <c r="U17" s="1" t="str">
         <f>IF(Agosto!U33&gt;0,Agosto!U33,"")</f>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="Y17" s="1">
         <f>IF(Agosto!Y33&gt;0,Agosto!Y33,"")</f>
-        <v>1190.1599999999999</v>
+        <v>3019.08</v>
       </c>
       <c r="Z17" s="1" t="str">
         <f>IF(Agosto!Z33&gt;0,Agosto!Z33,"")</f>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="O28" s="1">
         <f>IF(ISNUMBER(Agosto!O33),O6-Agosto!O33,"")</f>
-        <v>-2325.0299999999988</v>
+        <v>-5308.6399999999994</v>
       </c>
       <c r="P28" s="1">
         <f>IF(ISNUMBER(Agosto!P33),P6-Agosto!P33,"")</f>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="T28" s="1">
         <f>IF(ISNUMBER(Agosto!T33),T6-Agosto!T33,"")</f>
-        <v>1158.1900000000005</v>
+        <v>-511.46999999999935</v>
       </c>
       <c r="U28" s="1">
         <f>IF(ISNUMBER(Agosto!U33),U6-Agosto!U33,"")</f>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="Y28" s="1">
         <f>IF(ISNUMBER(Agosto!Y33),Y6-Agosto!Y33,"")</f>
-        <v>2809.84</v>
+        <v>980.92000000000007</v>
       </c>
       <c r="Z28" s="1" t="str">
         <f>IF(ISNUMBER(Agosto!Z33),Z6-Agosto!Z33,"")</f>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="AC28" s="12">
         <f t="shared" si="7"/>
-        <v>4966.5199999999995</v>
+        <v>-1515.670000000001</v>
       </c>
     </row>
     <row r="29" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="O33" s="12">
         <f t="shared" si="8"/>
-        <v>9089.8100000000013</v>
+        <v>6106.2000000000007</v>
       </c>
       <c r="P33" s="12">
         <f t="shared" si="8"/>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="T33" s="12">
         <f t="shared" si="8"/>
-        <v>2896.6900000000005</v>
+        <v>1227.0300000000007</v>
       </c>
       <c r="U33" s="12">
         <f t="shared" si="8"/>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="Y33" s="12">
         <f t="shared" si="8"/>
-        <v>2596.5600000000004</v>
+        <v>767.64000000000033</v>
       </c>
       <c r="Z33" s="12">
         <f t="shared" si="8"/>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>-5002.7500000000036</v>
+        <v>-11484.940000000004</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10189,12 +10189,18 @@
       <c r="L31" s="35"/>
       <c r="M31" s="35"/>
       <c r="N31" s="35"/>
-      <c r="O31" s="35"/>
+      <c r="O31" s="35">
+        <f>1000-16.39</f>
+        <v>983.61</v>
+      </c>
       <c r="P31" s="35"/>
       <c r="Q31" s="35"/>
       <c r="R31" s="35"/>
       <c r="S31" s="35"/>
-      <c r="T31" s="35"/>
+      <c r="T31" s="35">
+        <f>271+387-6.34+260</f>
+        <v>911.66</v>
+      </c>
       <c r="U31" s="35"/>
       <c r="V31" s="35"/>
       <c r="W31" s="35"/>
@@ -10205,7 +10211,7 @@
       <c r="AB31" s="36"/>
       <c r="AC31" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1895.27</v>
       </c>
       <c r="AD31" s="35"/>
     </row>
@@ -10226,12 +10232,16 @@
       <c r="L32" s="35"/>
       <c r="M32" s="35"/>
       <c r="N32" s="35"/>
-      <c r="O32" s="35"/>
+      <c r="O32" s="35">
+        <v>2000</v>
+      </c>
       <c r="P32" s="35"/>
       <c r="Q32" s="35"/>
       <c r="R32" s="35"/>
       <c r="S32" s="35"/>
-      <c r="T32" s="35"/>
+      <c r="T32" s="35">
+        <v>758</v>
+      </c>
       <c r="U32" s="35">
         <v>0</v>
       </c>
@@ -10240,13 +10250,16 @@
       </c>
       <c r="W32" s="35"/>
       <c r="X32" s="35"/>
-      <c r="Y32" s="35"/>
+      <c r="Y32" s="35">
+        <f>1860-31.08</f>
+        <v>1828.92</v>
+      </c>
       <c r="Z32" s="35"/>
       <c r="AA32" s="35"/>
       <c r="AB32" s="36"/>
       <c r="AC32" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4586.92</v>
       </c>
       <c r="AD32" s="35"/>
     </row>
@@ -10308,7 +10321,7 @@
       </c>
       <c r="O33" s="12">
         <f t="shared" si="1"/>
-        <v>10325.029999999999</v>
+        <v>13308.64</v>
       </c>
       <c r="P33" s="12">
         <f t="shared" si="1"/>
@@ -10328,7 +10341,7 @@
       </c>
       <c r="T33" s="12">
         <f t="shared" si="1"/>
-        <v>3841.8099999999995</v>
+        <v>5511.4699999999993</v>
       </c>
       <c r="U33" s="12">
         <f t="shared" si="1"/>
@@ -10348,7 +10361,7 @@
       </c>
       <c r="Y33" s="12">
         <f t="shared" si="1"/>
-        <v>1190.1599999999999</v>
+        <v>3019.08</v>
       </c>
       <c r="Z33" s="12" t="str">
         <f t="shared" si="1"/>
@@ -10364,7 +10377,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="1"/>
-        <v>147457.44999999998</v>
+        <v>153939.63999999998</v>
       </c>
       <c r="AD33" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -1534,7 +1534,7 @@
         <v>4369</v>
       </c>
       <c r="D7" s="1">
-        <v>15750</v>
+        <v>15700</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
@@ -1549,25 +1549,25 @@
         <v>3300</v>
       </c>
       <c r="I7" s="1">
-        <v>3000</v>
+        <v>3750</v>
       </c>
       <c r="J7" s="1">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="K7" s="1">
-        <v>18000</v>
+        <v>23200</v>
       </c>
       <c r="L7" s="1">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="M7" s="1">
-        <v>7500</v>
+        <v>20000</v>
       </c>
       <c r="N7" s="1">
         <v>810</v>
       </c>
       <c r="O7" s="1">
-        <v>4400</v>
+        <v>8000</v>
       </c>
       <c r="P7" s="1">
         <v>1800</v>
@@ -1576,22 +1576,25 @@
         <v>2500</v>
       </c>
       <c r="R7" s="1">
-        <v>20000</v>
+        <v>19000</v>
       </c>
       <c r="S7" s="1">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="T7" s="1">
         <v>5000</v>
       </c>
       <c r="U7" s="1">
-        <v>12000</v>
+        <v>12500</v>
+      </c>
+      <c r="V7" s="1">
+        <v>1500</v>
       </c>
       <c r="W7" s="1">
         <v>3000</v>
       </c>
       <c r="X7" s="1">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="Y7" s="1">
         <v>2000</v>
@@ -1602,7 +1605,7 @@
       <c r="AB7" s="6"/>
       <c r="AC7" s="1">
         <f t="shared" si="0"/>
-        <v>151229</v>
+        <v>171329</v>
       </c>
       <c r="AD7" s="7">
         <f t="shared" si="1"/>
@@ -1620,15 +1623,15 @@
       </c>
       <c r="AH7" s="8">
         <f t="shared" si="3"/>
-        <v>68114.5</v>
+        <v>65664.5</v>
       </c>
       <c r="AI7" s="9">
         <f t="shared" si="4"/>
-        <v>59864.5</v>
+        <v>69964.5</v>
       </c>
       <c r="AJ7" s="10">
         <f t="shared" si="5"/>
-        <v>127979</v>
+        <v>135629</v>
       </c>
     </row>
     <row r="8" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1681,22 +1684,19 @@
         <v>2500</v>
       </c>
       <c r="R8" s="1">
-        <v>20000</v>
+        <v>19000</v>
       </c>
       <c r="S8" s="1">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="T8" s="1">
         <v>5000</v>
       </c>
-      <c r="V8" s="1">
-        <v>1500</v>
-      </c>
       <c r="W8" s="1">
         <v>3000</v>
       </c>
       <c r="X8" s="1">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="Y8" s="1">
         <v>2000</v>
@@ -1707,7 +1707,7 @@
       <c r="AB8" s="6"/>
       <c r="AC8" s="1">
         <f>SUM(B8:AB8)</f>
-        <v>163160</v>
+        <v>159460</v>
       </c>
       <c r="AD8" s="7">
         <f t="shared" si="1"/>
@@ -1725,15 +1725,15 @@
       </c>
       <c r="AH8" s="8">
         <f t="shared" si="3"/>
-        <v>74080</v>
+        <v>72230</v>
       </c>
       <c r="AI8" s="9">
         <f t="shared" si="4"/>
-        <v>65830</v>
+        <v>63980</v>
       </c>
       <c r="AJ8" s="10">
         <f t="shared" si="5"/>
-        <v>139910</v>
+        <v>136210</v>
       </c>
     </row>
     <row r="9" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1786,10 +1786,10 @@
         <v>2500</v>
       </c>
       <c r="R9" s="1">
-        <v>20000</v>
+        <v>19000</v>
       </c>
       <c r="S9" s="1">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="T9" s="1">
         <v>5000</v>
@@ -1798,7 +1798,7 @@
         <v>3000</v>
       </c>
       <c r="X9" s="1">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="Y9" s="1">
         <v>2000</v>
@@ -1809,7 +1809,7 @@
       <c r="AB9" s="6"/>
       <c r="AC9" s="1">
         <f t="shared" si="0"/>
-        <v>141079</v>
+        <v>138879</v>
       </c>
       <c r="AD9" s="7">
         <f t="shared" si="1"/>
@@ -1827,15 +1827,15 @@
       </c>
       <c r="AH9" s="8">
         <f t="shared" si="3"/>
-        <v>63039.5</v>
+        <v>61939.5</v>
       </c>
       <c r="AI9" s="9">
         <f t="shared" si="4"/>
-        <v>54739.5</v>
+        <v>53639.5</v>
       </c>
       <c r="AJ9" s="10">
         <f t="shared" si="5"/>
-        <v>117779</v>
+        <v>115579</v>
       </c>
     </row>
     <row r="10" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1885,10 +1885,10 @@
         <v>2500</v>
       </c>
       <c r="R10" s="1">
-        <v>20000</v>
+        <v>19000</v>
       </c>
       <c r="S10" s="1">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="T10" s="1">
         <v>5000</v>
@@ -1897,21 +1897,18 @@
         <v>3000</v>
       </c>
       <c r="X10" s="1">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="Y10" s="1">
         <v>2000</v>
       </c>
-      <c r="Z10" s="1">
-        <v>1350</v>
-      </c>
       <c r="AA10" s="1">
         <v>5000</v>
       </c>
       <c r="AB10" s="6"/>
       <c r="AC10" s="1">
         <f t="shared" si="0"/>
-        <v>156060</v>
+        <v>152510</v>
       </c>
       <c r="AD10" s="7">
         <f t="shared" si="1"/>
@@ -1929,15 +1926,15 @@
       </c>
       <c r="AH10" s="8">
         <f t="shared" si="3"/>
-        <v>70530</v>
+        <v>68755</v>
       </c>
       <c r="AI10" s="9">
         <f t="shared" si="4"/>
-        <v>62230</v>
+        <v>60455</v>
       </c>
       <c r="AJ10" s="10">
         <f t="shared" si="5"/>
-        <v>132760</v>
+        <v>129210</v>
       </c>
     </row>
     <row r="12" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2578,9 +2575,9 @@
         <f>IF(Setiembre!Q32&gt;0,Setiembre!Q32,"")</f>
         <v/>
       </c>
-      <c r="R18" s="1" t="str">
+      <c r="R18" s="1">
         <f>IF(Setiembre!R32&gt;0,Setiembre!R32,"")</f>
-        <v/>
+        <v>846.29</v>
       </c>
       <c r="S18" s="1" t="str">
         <f>IF(Setiembre!S32&gt;0,Setiembre!S32,"")</f>
@@ -3600,9 +3597,9 @@
         <f>IF(ISNUMBER(Setiembre!Q32),Q7-Setiembre!Q32,"")</f>
         <v/>
       </c>
-      <c r="R29" s="1" t="str">
+      <c r="R29" s="1">
         <f>IF(ISNUMBER(Setiembre!R32),R7-Setiembre!R32,"")</f>
-        <v/>
+        <v>18153.71</v>
       </c>
       <c r="S29" s="1" t="str">
         <f>IF(ISNUMBER(Setiembre!S32),S7-Setiembre!S32,"")</f>
@@ -3642,7 +3639,7 @@
       </c>
       <c r="AC29" s="12">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>18153.71</v>
       </c>
     </row>
     <row r="30" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4054,7 +4051,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>4317.869999999999</v>
+        <v>22471.579999999998</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
@@ -4094,7 +4091,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>-11484.940000000004</v>
+        <v>6668.7699999999968</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10393,6 +10390,2722 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="27" width="13" customWidth="1"/>
+    <col min="28" max="28" width="14" customWidth="1"/>
+    <col min="29" max="29" width="25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:30" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="O1" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="P1" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q1" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="R1" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="S1" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="T1" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="U1" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="V1" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="W1" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="X1" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y1" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z1" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA1" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC1" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD1" s="33" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="34">
+        <v>1</v>
+      </c>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35">
+        <f>859.68-13.39</f>
+        <v>846.29</v>
+      </c>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="35"/>
+      <c r="Y2" s="35"/>
+      <c r="Z2" s="35"/>
+      <c r="AA2" s="35"/>
+      <c r="AB2" s="36"/>
+      <c r="AC2" s="35">
+        <f t="shared" ref="AC2:AC31" si="0">SUM(B2:AA2)</f>
+        <v>846.29</v>
+      </c>
+      <c r="AD2" s="35"/>
+    </row>
+    <row r="3" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="34">
+        <v>2</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="35"/>
+      <c r="N3" s="35"/>
+      <c r="O3" s="35"/>
+      <c r="P3" s="35"/>
+      <c r="Q3" s="35"/>
+      <c r="R3" s="35"/>
+      <c r="S3" s="35"/>
+      <c r="T3" s="35"/>
+      <c r="U3" s="35"/>
+      <c r="V3" s="35"/>
+      <c r="W3" s="35"/>
+      <c r="X3" s="35"/>
+      <c r="Y3" s="35"/>
+      <c r="Z3" s="35"/>
+      <c r="AA3" s="35"/>
+      <c r="AB3" s="36"/>
+      <c r="AC3" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD3" s="35"/>
+    </row>
+    <row r="4" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="34">
+        <v>3</v>
+      </c>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="35"/>
+      <c r="N4" s="35"/>
+      <c r="O4" s="35"/>
+      <c r="P4" s="35"/>
+      <c r="Q4" s="35"/>
+      <c r="R4" s="35"/>
+      <c r="S4" s="35"/>
+      <c r="T4" s="35"/>
+      <c r="U4" s="35"/>
+      <c r="V4" s="35"/>
+      <c r="W4" s="35"/>
+      <c r="X4" s="35"/>
+      <c r="Y4" s="35"/>
+      <c r="Z4" s="35"/>
+      <c r="AA4" s="35"/>
+      <c r="AB4" s="36"/>
+      <c r="AC4" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD4" s="35"/>
+    </row>
+    <row r="5" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="34">
+        <v>4</v>
+      </c>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
+      <c r="L5" s="35"/>
+      <c r="M5" s="35"/>
+      <c r="N5" s="35"/>
+      <c r="O5" s="35"/>
+      <c r="P5" s="35"/>
+      <c r="Q5" s="35"/>
+      <c r="R5" s="35"/>
+      <c r="S5" s="35"/>
+      <c r="T5" s="35"/>
+      <c r="U5" s="35"/>
+      <c r="V5" s="35"/>
+      <c r="W5" s="35"/>
+      <c r="X5" s="35"/>
+      <c r="Y5" s="35"/>
+      <c r="Z5" s="35"/>
+      <c r="AA5" s="35"/>
+      <c r="AB5" s="36"/>
+      <c r="AC5" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD5" s="35"/>
+    </row>
+    <row r="6" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="34">
+        <v>5</v>
+      </c>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="35"/>
+      <c r="N6" s="35"/>
+      <c r="O6" s="35"/>
+      <c r="P6" s="35"/>
+      <c r="Q6" s="35"/>
+      <c r="R6" s="35"/>
+      <c r="S6" s="35"/>
+      <c r="T6" s="35"/>
+      <c r="U6" s="35"/>
+      <c r="V6" s="35"/>
+      <c r="W6" s="35"/>
+      <c r="X6" s="35"/>
+      <c r="Y6" s="35"/>
+      <c r="Z6" s="35"/>
+      <c r="AA6" s="35"/>
+      <c r="AB6" s="36"/>
+      <c r="AC6" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD6" s="35"/>
+    </row>
+    <row r="7" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="34">
+        <v>6</v>
+      </c>
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="35"/>
+      <c r="L7" s="35"/>
+      <c r="M7" s="35"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="35"/>
+      <c r="P7" s="35"/>
+      <c r="Q7" s="35"/>
+      <c r="R7" s="35"/>
+      <c r="S7" s="35"/>
+      <c r="T7" s="35"/>
+      <c r="U7" s="35"/>
+      <c r="V7" s="35"/>
+      <c r="W7" s="35"/>
+      <c r="X7" s="35"/>
+      <c r="Y7" s="35"/>
+      <c r="Z7" s="35"/>
+      <c r="AA7" s="35"/>
+      <c r="AB7" s="36"/>
+      <c r="AC7" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD7" s="35"/>
+    </row>
+    <row r="8" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="34">
+        <v>7</v>
+      </c>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="35"/>
+      <c r="L8" s="35"/>
+      <c r="M8" s="35"/>
+      <c r="N8" s="35"/>
+      <c r="O8" s="35"/>
+      <c r="P8" s="35"/>
+      <c r="Q8" s="35"/>
+      <c r="R8" s="35"/>
+      <c r="S8" s="35"/>
+      <c r="T8" s="35"/>
+      <c r="U8" s="35"/>
+      <c r="V8" s="35"/>
+      <c r="W8" s="35"/>
+      <c r="X8" s="35"/>
+      <c r="Y8" s="35"/>
+      <c r="Z8" s="35"/>
+      <c r="AA8" s="35"/>
+      <c r="AB8" s="36"/>
+      <c r="AC8" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD8" s="35"/>
+    </row>
+    <row r="9" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="34">
+        <v>8</v>
+      </c>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="35"/>
+      <c r="L9" s="35"/>
+      <c r="M9" s="35"/>
+      <c r="N9" s="35"/>
+      <c r="O9" s="35"/>
+      <c r="P9" s="35"/>
+      <c r="Q9" s="35"/>
+      <c r="R9" s="35"/>
+      <c r="S9" s="35"/>
+      <c r="T9" s="35"/>
+      <c r="U9" s="35"/>
+      <c r="V9" s="35"/>
+      <c r="W9" s="35"/>
+      <c r="X9" s="35"/>
+      <c r="Y9" s="35"/>
+      <c r="Z9" s="35"/>
+      <c r="AA9" s="35"/>
+      <c r="AB9" s="36"/>
+      <c r="AC9" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD9" s="35"/>
+    </row>
+    <row r="10" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="34">
+        <v>9</v>
+      </c>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="35"/>
+      <c r="L10" s="35"/>
+      <c r="M10" s="35"/>
+      <c r="N10" s="35"/>
+      <c r="O10" s="35"/>
+      <c r="P10" s="35"/>
+      <c r="Q10" s="35"/>
+      <c r="R10" s="35"/>
+      <c r="S10" s="35"/>
+      <c r="T10" s="35"/>
+      <c r="U10" s="35"/>
+      <c r="V10" s="35"/>
+      <c r="W10" s="35"/>
+      <c r="X10" s="35"/>
+      <c r="Y10" s="35"/>
+      <c r="Z10" s="35"/>
+      <c r="AA10" s="35"/>
+      <c r="AB10" s="36"/>
+      <c r="AC10" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD10" s="35"/>
+    </row>
+    <row r="11" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="34">
+        <v>10</v>
+      </c>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="35"/>
+      <c r="J11" s="35"/>
+      <c r="K11" s="35"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="35"/>
+      <c r="N11" s="35"/>
+      <c r="O11" s="35"/>
+      <c r="P11" s="35"/>
+      <c r="Q11" s="35"/>
+      <c r="R11" s="35"/>
+      <c r="S11" s="35"/>
+      <c r="T11" s="35"/>
+      <c r="U11" s="35"/>
+      <c r="V11" s="35"/>
+      <c r="W11" s="35"/>
+      <c r="X11" s="35"/>
+      <c r="Y11" s="35"/>
+      <c r="Z11" s="35"/>
+      <c r="AA11" s="35"/>
+      <c r="AB11" s="36"/>
+      <c r="AC11" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD11" s="35"/>
+    </row>
+    <row r="12" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="34">
+        <v>11</v>
+      </c>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="35"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="35"/>
+      <c r="N12" s="35"/>
+      <c r="O12" s="35"/>
+      <c r="P12" s="35"/>
+      <c r="Q12" s="35"/>
+      <c r="R12" s="35"/>
+      <c r="S12" s="35"/>
+      <c r="T12" s="35"/>
+      <c r="U12" s="35"/>
+      <c r="V12" s="35"/>
+      <c r="W12" s="35"/>
+      <c r="X12" s="35"/>
+      <c r="Y12" s="35"/>
+      <c r="Z12" s="35"/>
+      <c r="AA12" s="35"/>
+      <c r="AB12" s="36"/>
+      <c r="AC12" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD12" s="35"/>
+    </row>
+    <row r="13" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="34">
+        <v>12</v>
+      </c>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="35"/>
+      <c r="K13" s="35"/>
+      <c r="L13" s="35"/>
+      <c r="M13" s="35"/>
+      <c r="N13" s="35"/>
+      <c r="O13" s="35"/>
+      <c r="P13" s="35"/>
+      <c r="Q13" s="35"/>
+      <c r="R13" s="35"/>
+      <c r="S13" s="35"/>
+      <c r="T13" s="35"/>
+      <c r="U13" s="35"/>
+      <c r="V13" s="35"/>
+      <c r="W13" s="35"/>
+      <c r="X13" s="35"/>
+      <c r="Y13" s="35"/>
+      <c r="Z13" s="35"/>
+      <c r="AA13" s="35"/>
+      <c r="AB13" s="36"/>
+      <c r="AC13" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD13" s="35"/>
+    </row>
+    <row r="14" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="34">
+        <v>13</v>
+      </c>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="35"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="35"/>
+      <c r="N14" s="35"/>
+      <c r="O14" s="35"/>
+      <c r="P14" s="35"/>
+      <c r="Q14" s="35"/>
+      <c r="R14" s="35"/>
+      <c r="S14" s="35"/>
+      <c r="T14" s="35"/>
+      <c r="U14" s="35"/>
+      <c r="V14" s="35"/>
+      <c r="W14" s="35"/>
+      <c r="X14" s="35"/>
+      <c r="Y14" s="35"/>
+      <c r="Z14" s="35"/>
+      <c r="AA14" s="35"/>
+      <c r="AB14" s="36"/>
+      <c r="AC14" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD14" s="35"/>
+    </row>
+    <row r="15" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="34">
+        <v>14</v>
+      </c>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="35"/>
+      <c r="L15" s="35"/>
+      <c r="M15" s="35"/>
+      <c r="N15" s="35"/>
+      <c r="O15" s="35"/>
+      <c r="P15" s="35"/>
+      <c r="Q15" s="35"/>
+      <c r="R15" s="35"/>
+      <c r="S15" s="35"/>
+      <c r="T15" s="35"/>
+      <c r="U15" s="35"/>
+      <c r="V15" s="35"/>
+      <c r="W15" s="35"/>
+      <c r="X15" s="35"/>
+      <c r="Y15" s="35"/>
+      <c r="Z15" s="35"/>
+      <c r="AA15" s="35"/>
+      <c r="AB15" s="36"/>
+      <c r="AC15" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD15" s="35"/>
+    </row>
+    <row r="16" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="34">
+        <v>15</v>
+      </c>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="35"/>
+      <c r="L16" s="35"/>
+      <c r="M16" s="35"/>
+      <c r="N16" s="35"/>
+      <c r="O16" s="35"/>
+      <c r="P16" s="35"/>
+      <c r="Q16" s="35"/>
+      <c r="R16" s="35"/>
+      <c r="S16" s="35"/>
+      <c r="T16" s="35"/>
+      <c r="U16" s="35"/>
+      <c r="V16" s="35"/>
+      <c r="W16" s="35"/>
+      <c r="X16" s="35"/>
+      <c r="Y16" s="35"/>
+      <c r="Z16" s="35"/>
+      <c r="AA16" s="35"/>
+      <c r="AB16" s="36"/>
+      <c r="AC16" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD16" s="35"/>
+    </row>
+    <row r="17" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="34">
+        <v>16</v>
+      </c>
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="35"/>
+      <c r="L17" s="35"/>
+      <c r="M17" s="35"/>
+      <c r="N17" s="35"/>
+      <c r="O17" s="35"/>
+      <c r="P17" s="35"/>
+      <c r="Q17" s="35"/>
+      <c r="R17" s="35"/>
+      <c r="S17" s="35"/>
+      <c r="T17" s="35"/>
+      <c r="U17" s="35"/>
+      <c r="V17" s="35"/>
+      <c r="W17" s="35"/>
+      <c r="X17" s="35"/>
+      <c r="Y17" s="35"/>
+      <c r="Z17" s="35"/>
+      <c r="AA17" s="35"/>
+      <c r="AB17" s="36"/>
+      <c r="AC17" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD17" s="35"/>
+    </row>
+    <row r="18" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="34">
+        <v>17</v>
+      </c>
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="35"/>
+      <c r="K18" s="35"/>
+      <c r="L18" s="35"/>
+      <c r="M18" s="35"/>
+      <c r="N18" s="35"/>
+      <c r="O18" s="35"/>
+      <c r="P18" s="35"/>
+      <c r="Q18" s="35"/>
+      <c r="R18" s="35"/>
+      <c r="S18" s="35"/>
+      <c r="T18" s="35"/>
+      <c r="U18" s="35"/>
+      <c r="V18" s="35"/>
+      <c r="W18" s="35"/>
+      <c r="X18" s="35"/>
+      <c r="Y18" s="35"/>
+      <c r="Z18" s="35"/>
+      <c r="AA18" s="35"/>
+      <c r="AB18" s="36"/>
+      <c r="AC18" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD18" s="35"/>
+    </row>
+    <row r="19" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="34">
+        <v>18</v>
+      </c>
+      <c r="B19" s="35"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="35"/>
+      <c r="P19" s="35"/>
+      <c r="Q19" s="35"/>
+      <c r="R19" s="35"/>
+      <c r="S19" s="35"/>
+      <c r="T19" s="35"/>
+      <c r="U19" s="35"/>
+      <c r="V19" s="35"/>
+      <c r="W19" s="35"/>
+      <c r="X19" s="35"/>
+      <c r="Y19" s="35"/>
+      <c r="Z19" s="35"/>
+      <c r="AA19" s="35"/>
+      <c r="AB19" s="36"/>
+      <c r="AC19" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD19" s="35"/>
+    </row>
+    <row r="20" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="34">
+        <v>19</v>
+      </c>
+      <c r="B20" s="35"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="35"/>
+      <c r="L20" s="35"/>
+      <c r="M20" s="35"/>
+      <c r="N20" s="35"/>
+      <c r="O20" s="35"/>
+      <c r="P20" s="35"/>
+      <c r="Q20" s="35"/>
+      <c r="R20" s="35"/>
+      <c r="S20" s="35"/>
+      <c r="T20" s="35"/>
+      <c r="U20" s="35"/>
+      <c r="V20" s="35"/>
+      <c r="W20" s="35"/>
+      <c r="X20" s="35"/>
+      <c r="Y20" s="35"/>
+      <c r="Z20" s="35"/>
+      <c r="AA20" s="35"/>
+      <c r="AB20" s="36"/>
+      <c r="AC20" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD20" s="35"/>
+    </row>
+    <row r="21" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="34">
+        <v>20</v>
+      </c>
+      <c r="B21" s="35"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="35"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="35"/>
+      <c r="M21" s="35"/>
+      <c r="N21" s="35"/>
+      <c r="O21" s="35"/>
+      <c r="P21" s="35"/>
+      <c r="Q21" s="35"/>
+      <c r="R21" s="35"/>
+      <c r="S21" s="35"/>
+      <c r="T21" s="35"/>
+      <c r="U21" s="35"/>
+      <c r="V21" s="35"/>
+      <c r="W21" s="35"/>
+      <c r="X21" s="35"/>
+      <c r="Y21" s="35"/>
+      <c r="Z21" s="35"/>
+      <c r="AA21" s="35"/>
+      <c r="AB21" s="36"/>
+      <c r="AC21" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD21" s="35"/>
+    </row>
+    <row r="22" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="34">
+        <v>21</v>
+      </c>
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="35"/>
+      <c r="N22" s="35"/>
+      <c r="O22" s="35"/>
+      <c r="P22" s="35"/>
+      <c r="Q22" s="35"/>
+      <c r="R22" s="35"/>
+      <c r="S22" s="35"/>
+      <c r="T22" s="35"/>
+      <c r="U22" s="35"/>
+      <c r="V22" s="35"/>
+      <c r="W22" s="35"/>
+      <c r="X22" s="35"/>
+      <c r="Y22" s="35"/>
+      <c r="Z22" s="35"/>
+      <c r="AA22" s="35"/>
+      <c r="AB22" s="36"/>
+      <c r="AC22" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD22" s="35"/>
+    </row>
+    <row r="23" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="34">
+        <v>22</v>
+      </c>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="35"/>
+      <c r="L23" s="35"/>
+      <c r="M23" s="35"/>
+      <c r="N23" s="35"/>
+      <c r="O23" s="35"/>
+      <c r="P23" s="35"/>
+      <c r="Q23" s="35"/>
+      <c r="R23" s="35"/>
+      <c r="S23" s="35"/>
+      <c r="T23" s="35"/>
+      <c r="U23" s="35"/>
+      <c r="V23" s="35"/>
+      <c r="W23" s="35"/>
+      <c r="X23" s="35"/>
+      <c r="Y23" s="35"/>
+      <c r="Z23" s="35"/>
+      <c r="AA23" s="35"/>
+      <c r="AB23" s="36"/>
+      <c r="AC23" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD23" s="35"/>
+    </row>
+    <row r="24" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="34">
+        <v>23</v>
+      </c>
+      <c r="B24" s="35"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="35"/>
+      <c r="I24" s="35"/>
+      <c r="J24" s="35"/>
+      <c r="K24" s="35"/>
+      <c r="L24" s="35"/>
+      <c r="M24" s="35"/>
+      <c r="N24" s="35"/>
+      <c r="O24" s="35"/>
+      <c r="P24" s="35"/>
+      <c r="Q24" s="35"/>
+      <c r="R24" s="35"/>
+      <c r="S24" s="35"/>
+      <c r="T24" s="35"/>
+      <c r="U24" s="35"/>
+      <c r="V24" s="35"/>
+      <c r="W24" s="35"/>
+      <c r="X24" s="35"/>
+      <c r="Y24" s="35"/>
+      <c r="Z24" s="35"/>
+      <c r="AA24" s="35"/>
+      <c r="AB24" s="36"/>
+      <c r="AC24" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD24" s="35"/>
+    </row>
+    <row r="25" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="34">
+        <v>24</v>
+      </c>
+      <c r="B25" s="35"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="35"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="35"/>
+      <c r="K25" s="35"/>
+      <c r="L25" s="35"/>
+      <c r="M25" s="35"/>
+      <c r="N25" s="35"/>
+      <c r="O25" s="35"/>
+      <c r="P25" s="35"/>
+      <c r="Q25" s="35"/>
+      <c r="R25" s="35"/>
+      <c r="S25" s="35"/>
+      <c r="T25" s="35"/>
+      <c r="U25" s="35"/>
+      <c r="V25" s="35"/>
+      <c r="W25" s="35"/>
+      <c r="X25" s="35"/>
+      <c r="Y25" s="35"/>
+      <c r="Z25" s="35"/>
+      <c r="AA25" s="35"/>
+      <c r="AB25" s="36"/>
+      <c r="AC25" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD25" s="35"/>
+    </row>
+    <row r="26" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="34">
+        <v>25</v>
+      </c>
+      <c r="B26" s="35"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="35"/>
+      <c r="I26" s="35"/>
+      <c r="J26" s="35"/>
+      <c r="K26" s="35"/>
+      <c r="L26" s="35"/>
+      <c r="M26" s="35"/>
+      <c r="N26" s="35"/>
+      <c r="O26" s="35"/>
+      <c r="P26" s="35"/>
+      <c r="Q26" s="35"/>
+      <c r="R26" s="35"/>
+      <c r="S26" s="35"/>
+      <c r="T26" s="35"/>
+      <c r="U26" s="35"/>
+      <c r="V26" s="35"/>
+      <c r="W26" s="35"/>
+      <c r="X26" s="35"/>
+      <c r="Y26" s="35"/>
+      <c r="Z26" s="35"/>
+      <c r="AA26" s="35"/>
+      <c r="AB26" s="36"/>
+      <c r="AC26" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD26" s="35"/>
+    </row>
+    <row r="27" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="34">
+        <v>26</v>
+      </c>
+      <c r="B27" s="35"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="35"/>
+      <c r="I27" s="35"/>
+      <c r="J27" s="35"/>
+      <c r="K27" s="35"/>
+      <c r="L27" s="35"/>
+      <c r="M27" s="35"/>
+      <c r="N27" s="35"/>
+      <c r="O27" s="35"/>
+      <c r="P27" s="35"/>
+      <c r="Q27" s="35"/>
+      <c r="R27" s="35"/>
+      <c r="S27" s="35"/>
+      <c r="T27" s="35"/>
+      <c r="U27" s="35"/>
+      <c r="V27" s="35"/>
+      <c r="W27" s="35"/>
+      <c r="X27" s="35"/>
+      <c r="Y27" s="35"/>
+      <c r="Z27" s="35"/>
+      <c r="AA27" s="35"/>
+      <c r="AB27" s="36"/>
+      <c r="AC27" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD27" s="35"/>
+    </row>
+    <row r="28" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="34">
+        <v>27</v>
+      </c>
+      <c r="B28" s="35"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="35"/>
+      <c r="I28" s="35"/>
+      <c r="J28" s="35"/>
+      <c r="K28" s="35"/>
+      <c r="L28" s="35"/>
+      <c r="M28" s="35"/>
+      <c r="N28" s="35"/>
+      <c r="O28" s="35"/>
+      <c r="P28" s="35"/>
+      <c r="Q28" s="35"/>
+      <c r="R28" s="35"/>
+      <c r="S28" s="35"/>
+      <c r="T28" s="35"/>
+      <c r="U28" s="35"/>
+      <c r="V28" s="35"/>
+      <c r="W28" s="35"/>
+      <c r="X28" s="35"/>
+      <c r="Y28" s="35"/>
+      <c r="Z28" s="35"/>
+      <c r="AA28" s="35"/>
+      <c r="AB28" s="36"/>
+      <c r="AC28" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD28" s="35"/>
+    </row>
+    <row r="29" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="34">
+        <v>28</v>
+      </c>
+      <c r="B29" s="35"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="35"/>
+      <c r="I29" s="35"/>
+      <c r="J29" s="35"/>
+      <c r="K29" s="35"/>
+      <c r="L29" s="35"/>
+      <c r="M29" s="35"/>
+      <c r="N29" s="35"/>
+      <c r="O29" s="35"/>
+      <c r="P29" s="35"/>
+      <c r="Q29" s="35"/>
+      <c r="R29" s="35"/>
+      <c r="S29" s="35"/>
+      <c r="T29" s="35"/>
+      <c r="U29" s="35"/>
+      <c r="V29" s="35"/>
+      <c r="W29" s="35"/>
+      <c r="X29" s="35"/>
+      <c r="Y29" s="35"/>
+      <c r="Z29" s="35"/>
+      <c r="AA29" s="35"/>
+      <c r="AB29" s="36"/>
+      <c r="AC29" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD29" s="35"/>
+    </row>
+    <row r="30" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="34">
+        <v>29</v>
+      </c>
+      <c r="B30" s="35"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="35"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="35"/>
+      <c r="I30" s="35"/>
+      <c r="J30" s="35"/>
+      <c r="K30" s="35"/>
+      <c r="L30" s="35"/>
+      <c r="M30" s="35"/>
+      <c r="N30" s="35"/>
+      <c r="O30" s="35"/>
+      <c r="P30" s="35"/>
+      <c r="Q30" s="35"/>
+      <c r="R30" s="35"/>
+      <c r="S30" s="35"/>
+      <c r="T30" s="35"/>
+      <c r="U30" s="35"/>
+      <c r="V30" s="35"/>
+      <c r="W30" s="35"/>
+      <c r="X30" s="35"/>
+      <c r="Y30" s="35"/>
+      <c r="Z30" s="35"/>
+      <c r="AA30" s="35"/>
+      <c r="AB30" s="36"/>
+      <c r="AC30" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD30" s="35"/>
+    </row>
+    <row r="31" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="34">
+        <v>30</v>
+      </c>
+      <c r="B31" s="35"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="35"/>
+      <c r="I31" s="35"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="35"/>
+      <c r="L31" s="35"/>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
+      <c r="O31" s="35"/>
+      <c r="P31" s="35"/>
+      <c r="Q31" s="35"/>
+      <c r="R31" s="35"/>
+      <c r="S31" s="35"/>
+      <c r="T31" s="35"/>
+      <c r="U31" s="35"/>
+      <c r="V31" s="35"/>
+      <c r="W31" s="35"/>
+      <c r="X31" s="35"/>
+      <c r="Y31" s="35"/>
+      <c r="Z31" s="35"/>
+      <c r="AA31" s="35"/>
+      <c r="AB31" s="36"/>
+      <c r="AC31" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD31" s="35"/>
+    </row>
+    <row r="32" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" s="12" t="str">
+        <f t="shared" ref="B32:AC32" si="1">IF(COUNTA(B2:B31)&gt;0,SUM(B2:B31),"")</f>
+        <v/>
+      </c>
+      <c r="C32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="D32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="E32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="G32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="M32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="N32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="O32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="P32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Q32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="R32" s="12">
+        <f t="shared" si="1"/>
+        <v>846.29</v>
+      </c>
+      <c r="S32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="T32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="U32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="V32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="X32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Y32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Z32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AA32" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AB32" s="38" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AC32" s="12">
+        <f t="shared" si="1"/>
+        <v>846.29</v>
+      </c>
+      <c r="AD32" s="39"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AD33"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="27" width="13" customWidth="1"/>
+    <col min="28" max="28" width="14" customWidth="1"/>
+    <col min="29" max="29" width="25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:30" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="O1" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="P1" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q1" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="R1" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="S1" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="T1" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="U1" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="V1" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="W1" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="X1" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y1" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z1" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA1" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC1" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD1" s="33" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="34">
+        <v>1</v>
+      </c>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="35"/>
+      <c r="Y2" s="35"/>
+      <c r="Z2" s="35"/>
+      <c r="AA2" s="35"/>
+      <c r="AB2" s="36"/>
+      <c r="AC2" s="35">
+        <f t="shared" ref="AC2:AC32" si="0">SUM(B2:AA2)</f>
+        <v>0</v>
+      </c>
+      <c r="AD2" s="35"/>
+    </row>
+    <row r="3" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="34">
+        <v>2</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="35"/>
+      <c r="N3" s="35"/>
+      <c r="O3" s="35"/>
+      <c r="P3" s="35"/>
+      <c r="Q3" s="35"/>
+      <c r="R3" s="35"/>
+      <c r="S3" s="35"/>
+      <c r="T3" s="35"/>
+      <c r="U3" s="35"/>
+      <c r="V3" s="35"/>
+      <c r="W3" s="35"/>
+      <c r="X3" s="35"/>
+      <c r="Y3" s="35"/>
+      <c r="Z3" s="35"/>
+      <c r="AA3" s="35"/>
+      <c r="AB3" s="36"/>
+      <c r="AC3" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD3" s="35"/>
+    </row>
+    <row r="4" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="34">
+        <v>3</v>
+      </c>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="35"/>
+      <c r="N4" s="35"/>
+      <c r="O4" s="35"/>
+      <c r="P4" s="35"/>
+      <c r="Q4" s="35"/>
+      <c r="R4" s="35"/>
+      <c r="S4" s="35"/>
+      <c r="T4" s="35"/>
+      <c r="U4" s="35"/>
+      <c r="V4" s="35"/>
+      <c r="W4" s="35"/>
+      <c r="X4" s="35"/>
+      <c r="Y4" s="35"/>
+      <c r="Z4" s="35"/>
+      <c r="AA4" s="35"/>
+      <c r="AB4" s="36"/>
+      <c r="AC4" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD4" s="35"/>
+    </row>
+    <row r="5" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="34">
+        <v>4</v>
+      </c>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
+      <c r="L5" s="35"/>
+      <c r="M5" s="35"/>
+      <c r="N5" s="35"/>
+      <c r="O5" s="35"/>
+      <c r="P5" s="35"/>
+      <c r="Q5" s="35"/>
+      <c r="R5" s="35"/>
+      <c r="S5" s="35"/>
+      <c r="T5" s="35"/>
+      <c r="U5" s="35"/>
+      <c r="V5" s="35"/>
+      <c r="W5" s="35"/>
+      <c r="X5" s="35"/>
+      <c r="Y5" s="35"/>
+      <c r="Z5" s="35"/>
+      <c r="AA5" s="35"/>
+      <c r="AB5" s="36"/>
+      <c r="AC5" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD5" s="35"/>
+    </row>
+    <row r="6" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="34">
+        <v>5</v>
+      </c>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="35"/>
+      <c r="N6" s="35"/>
+      <c r="O6" s="35"/>
+      <c r="P6" s="35"/>
+      <c r="Q6" s="35"/>
+      <c r="R6" s="35"/>
+      <c r="S6" s="35"/>
+      <c r="T6" s="35"/>
+      <c r="U6" s="35"/>
+      <c r="V6" s="35"/>
+      <c r="W6" s="35"/>
+      <c r="X6" s="35"/>
+      <c r="Y6" s="35"/>
+      <c r="Z6" s="35"/>
+      <c r="AA6" s="35"/>
+      <c r="AB6" s="36"/>
+      <c r="AC6" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD6" s="35"/>
+    </row>
+    <row r="7" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="34">
+        <v>6</v>
+      </c>
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="35"/>
+      <c r="L7" s="35"/>
+      <c r="M7" s="35"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="35"/>
+      <c r="P7" s="35"/>
+      <c r="Q7" s="35"/>
+      <c r="R7" s="35"/>
+      <c r="S7" s="35"/>
+      <c r="T7" s="35"/>
+      <c r="U7" s="35"/>
+      <c r="V7" s="35"/>
+      <c r="W7" s="35"/>
+      <c r="X7" s="35"/>
+      <c r="Y7" s="35"/>
+      <c r="Z7" s="35"/>
+      <c r="AA7" s="35"/>
+      <c r="AB7" s="36"/>
+      <c r="AC7" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD7" s="35"/>
+    </row>
+    <row r="8" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="34">
+        <v>7</v>
+      </c>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="35"/>
+      <c r="L8" s="35"/>
+      <c r="M8" s="35"/>
+      <c r="N8" s="35"/>
+      <c r="O8" s="35"/>
+      <c r="P8" s="35"/>
+      <c r="Q8" s="35"/>
+      <c r="R8" s="35"/>
+      <c r="S8" s="35"/>
+      <c r="T8" s="35"/>
+      <c r="U8" s="35"/>
+      <c r="V8" s="35"/>
+      <c r="W8" s="35"/>
+      <c r="X8" s="35"/>
+      <c r="Y8" s="35"/>
+      <c r="Z8" s="35"/>
+      <c r="AA8" s="35"/>
+      <c r="AB8" s="36"/>
+      <c r="AC8" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD8" s="35"/>
+    </row>
+    <row r="9" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="34">
+        <v>8</v>
+      </c>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="35"/>
+      <c r="L9" s="35"/>
+      <c r="M9" s="35"/>
+      <c r="N9" s="35"/>
+      <c r="O9" s="35"/>
+      <c r="P9" s="35"/>
+      <c r="Q9" s="35"/>
+      <c r="R9" s="35"/>
+      <c r="S9" s="35"/>
+      <c r="T9" s="35"/>
+      <c r="U9" s="35"/>
+      <c r="V9" s="35"/>
+      <c r="W9" s="35"/>
+      <c r="X9" s="35"/>
+      <c r="Y9" s="35"/>
+      <c r="Z9" s="35"/>
+      <c r="AA9" s="35"/>
+      <c r="AB9" s="36"/>
+      <c r="AC9" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD9" s="35"/>
+    </row>
+    <row r="10" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="34">
+        <v>9</v>
+      </c>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="35"/>
+      <c r="L10" s="35"/>
+      <c r="M10" s="35"/>
+      <c r="N10" s="35"/>
+      <c r="O10" s="35"/>
+      <c r="P10" s="35"/>
+      <c r="Q10" s="35"/>
+      <c r="R10" s="35"/>
+      <c r="S10" s="35"/>
+      <c r="T10" s="35"/>
+      <c r="U10" s="35"/>
+      <c r="V10" s="35"/>
+      <c r="W10" s="35"/>
+      <c r="X10" s="35"/>
+      <c r="Y10" s="35"/>
+      <c r="Z10" s="35"/>
+      <c r="AA10" s="35"/>
+      <c r="AB10" s="36"/>
+      <c r="AC10" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD10" s="35"/>
+    </row>
+    <row r="11" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="34">
+        <v>10</v>
+      </c>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="35"/>
+      <c r="J11" s="35"/>
+      <c r="K11" s="35"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="35"/>
+      <c r="N11" s="35"/>
+      <c r="O11" s="35"/>
+      <c r="P11" s="35"/>
+      <c r="Q11" s="35"/>
+      <c r="R11" s="35"/>
+      <c r="S11" s="35"/>
+      <c r="T11" s="35"/>
+      <c r="U11" s="35"/>
+      <c r="V11" s="35"/>
+      <c r="W11" s="35"/>
+      <c r="X11" s="35"/>
+      <c r="Y11" s="35"/>
+      <c r="Z11" s="35"/>
+      <c r="AA11" s="35"/>
+      <c r="AB11" s="36"/>
+      <c r="AC11" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD11" s="35"/>
+    </row>
+    <row r="12" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="34">
+        <v>11</v>
+      </c>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="35"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="35"/>
+      <c r="N12" s="35"/>
+      <c r="O12" s="35"/>
+      <c r="P12" s="35"/>
+      <c r="Q12" s="35"/>
+      <c r="R12" s="35"/>
+      <c r="S12" s="35"/>
+      <c r="T12" s="35"/>
+      <c r="U12" s="35"/>
+      <c r="V12" s="35"/>
+      <c r="W12" s="35"/>
+      <c r="X12" s="35"/>
+      <c r="Y12" s="35"/>
+      <c r="Z12" s="35"/>
+      <c r="AA12" s="35"/>
+      <c r="AB12" s="36"/>
+      <c r="AC12" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD12" s="35"/>
+    </row>
+    <row r="13" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="34">
+        <v>12</v>
+      </c>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="35"/>
+      <c r="K13" s="35"/>
+      <c r="L13" s="35"/>
+      <c r="M13" s="35"/>
+      <c r="N13" s="35"/>
+      <c r="O13" s="35"/>
+      <c r="P13" s="35"/>
+      <c r="Q13" s="35"/>
+      <c r="R13" s="35"/>
+      <c r="S13" s="35"/>
+      <c r="T13" s="35"/>
+      <c r="U13" s="35"/>
+      <c r="V13" s="35"/>
+      <c r="W13" s="35"/>
+      <c r="X13" s="35"/>
+      <c r="Y13" s="35"/>
+      <c r="Z13" s="35"/>
+      <c r="AA13" s="35"/>
+      <c r="AB13" s="36"/>
+      <c r="AC13" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD13" s="35"/>
+    </row>
+    <row r="14" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="34">
+        <v>13</v>
+      </c>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="35"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="35"/>
+      <c r="N14" s="35"/>
+      <c r="O14" s="35"/>
+      <c r="P14" s="35"/>
+      <c r="Q14" s="35"/>
+      <c r="R14" s="35"/>
+      <c r="S14" s="35"/>
+      <c r="T14" s="35"/>
+      <c r="U14" s="35"/>
+      <c r="V14" s="35"/>
+      <c r="W14" s="35"/>
+      <c r="X14" s="35"/>
+      <c r="Y14" s="35"/>
+      <c r="Z14" s="35"/>
+      <c r="AA14" s="35"/>
+      <c r="AB14" s="36"/>
+      <c r="AC14" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD14" s="35"/>
+    </row>
+    <row r="15" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="34">
+        <v>14</v>
+      </c>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="35"/>
+      <c r="L15" s="35"/>
+      <c r="M15" s="35"/>
+      <c r="N15" s="35"/>
+      <c r="O15" s="35"/>
+      <c r="P15" s="35"/>
+      <c r="Q15" s="35"/>
+      <c r="R15" s="35"/>
+      <c r="S15" s="35"/>
+      <c r="T15" s="35"/>
+      <c r="U15" s="35"/>
+      <c r="V15" s="35"/>
+      <c r="W15" s="35"/>
+      <c r="X15" s="35"/>
+      <c r="Y15" s="35"/>
+      <c r="Z15" s="35"/>
+      <c r="AA15" s="35"/>
+      <c r="AB15" s="36"/>
+      <c r="AC15" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD15" s="35"/>
+    </row>
+    <row r="16" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="34">
+        <v>15</v>
+      </c>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="35"/>
+      <c r="L16" s="35"/>
+      <c r="M16" s="35"/>
+      <c r="N16" s="35"/>
+      <c r="O16" s="35"/>
+      <c r="P16" s="35"/>
+      <c r="Q16" s="35"/>
+      <c r="R16" s="35"/>
+      <c r="S16" s="35"/>
+      <c r="T16" s="35"/>
+      <c r="U16" s="35"/>
+      <c r="V16" s="35"/>
+      <c r="W16" s="35"/>
+      <c r="X16" s="35"/>
+      <c r="Y16" s="35"/>
+      <c r="Z16" s="35"/>
+      <c r="AA16" s="35"/>
+      <c r="AB16" s="36"/>
+      <c r="AC16" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD16" s="35"/>
+    </row>
+    <row r="17" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="34">
+        <v>16</v>
+      </c>
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="35"/>
+      <c r="L17" s="35"/>
+      <c r="M17" s="35"/>
+      <c r="N17" s="35"/>
+      <c r="O17" s="35"/>
+      <c r="P17" s="35"/>
+      <c r="Q17" s="35"/>
+      <c r="R17" s="35"/>
+      <c r="S17" s="35"/>
+      <c r="T17" s="35"/>
+      <c r="U17" s="35"/>
+      <c r="V17" s="35"/>
+      <c r="W17" s="35"/>
+      <c r="X17" s="35"/>
+      <c r="Y17" s="35"/>
+      <c r="Z17" s="35"/>
+      <c r="AA17" s="35"/>
+      <c r="AB17" s="36"/>
+      <c r="AC17" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD17" s="35"/>
+    </row>
+    <row r="18" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="34">
+        <v>17</v>
+      </c>
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="35"/>
+      <c r="K18" s="35"/>
+      <c r="L18" s="35"/>
+      <c r="M18" s="35"/>
+      <c r="N18" s="35"/>
+      <c r="O18" s="35"/>
+      <c r="P18" s="35"/>
+      <c r="Q18" s="35"/>
+      <c r="R18" s="35"/>
+      <c r="S18" s="35"/>
+      <c r="T18" s="35"/>
+      <c r="U18" s="35"/>
+      <c r="V18" s="35"/>
+      <c r="W18" s="35"/>
+      <c r="X18" s="35"/>
+      <c r="Y18" s="35"/>
+      <c r="Z18" s="35"/>
+      <c r="AA18" s="35"/>
+      <c r="AB18" s="36"/>
+      <c r="AC18" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD18" s="35"/>
+    </row>
+    <row r="19" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="34">
+        <v>18</v>
+      </c>
+      <c r="B19" s="35"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="35"/>
+      <c r="P19" s="35"/>
+      <c r="Q19" s="35"/>
+      <c r="R19" s="35"/>
+      <c r="S19" s="35"/>
+      <c r="T19" s="35"/>
+      <c r="U19" s="35"/>
+      <c r="V19" s="35"/>
+      <c r="W19" s="35"/>
+      <c r="X19" s="35"/>
+      <c r="Y19" s="35"/>
+      <c r="Z19" s="35"/>
+      <c r="AA19" s="35"/>
+      <c r="AB19" s="36"/>
+      <c r="AC19" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD19" s="35"/>
+    </row>
+    <row r="20" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="34">
+        <v>19</v>
+      </c>
+      <c r="B20" s="35"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="35"/>
+      <c r="L20" s="35"/>
+      <c r="M20" s="35"/>
+      <c r="N20" s="35"/>
+      <c r="O20" s="35"/>
+      <c r="P20" s="35"/>
+      <c r="Q20" s="35"/>
+      <c r="R20" s="35"/>
+      <c r="S20" s="35"/>
+      <c r="T20" s="35"/>
+      <c r="U20" s="35"/>
+      <c r="V20" s="35"/>
+      <c r="W20" s="35"/>
+      <c r="X20" s="35"/>
+      <c r="Y20" s="35"/>
+      <c r="Z20" s="35"/>
+      <c r="AA20" s="35"/>
+      <c r="AB20" s="36"/>
+      <c r="AC20" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD20" s="35"/>
+    </row>
+    <row r="21" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="34">
+        <v>20</v>
+      </c>
+      <c r="B21" s="35"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="35"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="35"/>
+      <c r="M21" s="35"/>
+      <c r="N21" s="35"/>
+      <c r="O21" s="35"/>
+      <c r="P21" s="35"/>
+      <c r="Q21" s="35"/>
+      <c r="R21" s="35"/>
+      <c r="S21" s="35"/>
+      <c r="T21" s="35"/>
+      <c r="U21" s="35"/>
+      <c r="V21" s="35"/>
+      <c r="W21" s="35"/>
+      <c r="X21" s="35"/>
+      <c r="Y21" s="35"/>
+      <c r="Z21" s="35"/>
+      <c r="AA21" s="35"/>
+      <c r="AB21" s="36"/>
+      <c r="AC21" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD21" s="35"/>
+    </row>
+    <row r="22" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="34">
+        <v>21</v>
+      </c>
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="35"/>
+      <c r="N22" s="35"/>
+      <c r="O22" s="35"/>
+      <c r="P22" s="35"/>
+      <c r="Q22" s="35"/>
+      <c r="R22" s="35"/>
+      <c r="S22" s="35"/>
+      <c r="T22" s="35"/>
+      <c r="U22" s="35"/>
+      <c r="V22" s="35"/>
+      <c r="W22" s="35"/>
+      <c r="X22" s="35"/>
+      <c r="Y22" s="35"/>
+      <c r="Z22" s="35"/>
+      <c r="AA22" s="35"/>
+      <c r="AB22" s="36"/>
+      <c r="AC22" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD22" s="35"/>
+    </row>
+    <row r="23" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="34">
+        <v>22</v>
+      </c>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="35"/>
+      <c r="L23" s="35"/>
+      <c r="M23" s="35"/>
+      <c r="N23" s="35"/>
+      <c r="O23" s="35"/>
+      <c r="P23" s="35"/>
+      <c r="Q23" s="35"/>
+      <c r="R23" s="35"/>
+      <c r="S23" s="35"/>
+      <c r="T23" s="35"/>
+      <c r="U23" s="35"/>
+      <c r="V23" s="35"/>
+      <c r="W23" s="35"/>
+      <c r="X23" s="35"/>
+      <c r="Y23" s="35"/>
+      <c r="Z23" s="35"/>
+      <c r="AA23" s="35"/>
+      <c r="AB23" s="36"/>
+      <c r="AC23" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD23" s="35"/>
+    </row>
+    <row r="24" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="34">
+        <v>23</v>
+      </c>
+      <c r="B24" s="35"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="35"/>
+      <c r="I24" s="35"/>
+      <c r="J24" s="35"/>
+      <c r="K24" s="35"/>
+      <c r="L24" s="35"/>
+      <c r="M24" s="35"/>
+      <c r="N24" s="35"/>
+      <c r="O24" s="35"/>
+      <c r="P24" s="35"/>
+      <c r="Q24" s="35"/>
+      <c r="R24" s="35"/>
+      <c r="S24" s="35"/>
+      <c r="T24" s="35"/>
+      <c r="U24" s="35"/>
+      <c r="V24" s="35"/>
+      <c r="W24" s="35"/>
+      <c r="X24" s="35"/>
+      <c r="Y24" s="35"/>
+      <c r="Z24" s="35"/>
+      <c r="AA24" s="35"/>
+      <c r="AB24" s="36"/>
+      <c r="AC24" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD24" s="35"/>
+    </row>
+    <row r="25" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="34">
+        <v>24</v>
+      </c>
+      <c r="B25" s="35"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="35"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="35"/>
+      <c r="K25" s="35"/>
+      <c r="L25" s="35"/>
+      <c r="M25" s="35"/>
+      <c r="N25" s="35"/>
+      <c r="O25" s="35"/>
+      <c r="P25" s="35"/>
+      <c r="Q25" s="35"/>
+      <c r="R25" s="35"/>
+      <c r="S25" s="35"/>
+      <c r="T25" s="35"/>
+      <c r="U25" s="35"/>
+      <c r="V25" s="35"/>
+      <c r="W25" s="35"/>
+      <c r="X25" s="35"/>
+      <c r="Y25" s="35"/>
+      <c r="Z25" s="35"/>
+      <c r="AA25" s="35"/>
+      <c r="AB25" s="36"/>
+      <c r="AC25" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD25" s="35"/>
+    </row>
+    <row r="26" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="34">
+        <v>25</v>
+      </c>
+      <c r="B26" s="35"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="35"/>
+      <c r="I26" s="35"/>
+      <c r="J26" s="35"/>
+      <c r="K26" s="35"/>
+      <c r="L26" s="35"/>
+      <c r="M26" s="35"/>
+      <c r="N26" s="35"/>
+      <c r="O26" s="35"/>
+      <c r="P26" s="35"/>
+      <c r="Q26" s="35"/>
+      <c r="R26" s="35"/>
+      <c r="S26" s="35"/>
+      <c r="T26" s="35"/>
+      <c r="U26" s="35"/>
+      <c r="V26" s="35"/>
+      <c r="W26" s="35"/>
+      <c r="X26" s="35"/>
+      <c r="Y26" s="35"/>
+      <c r="Z26" s="35"/>
+      <c r="AA26" s="35"/>
+      <c r="AB26" s="36"/>
+      <c r="AC26" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD26" s="35"/>
+    </row>
+    <row r="27" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="34">
+        <v>26</v>
+      </c>
+      <c r="B27" s="35"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="35"/>
+      <c r="I27" s="35"/>
+      <c r="J27" s="35"/>
+      <c r="K27" s="35"/>
+      <c r="L27" s="35"/>
+      <c r="M27" s="35"/>
+      <c r="N27" s="35"/>
+      <c r="O27" s="35"/>
+      <c r="P27" s="35"/>
+      <c r="Q27" s="35"/>
+      <c r="R27" s="35"/>
+      <c r="S27" s="35"/>
+      <c r="T27" s="35"/>
+      <c r="U27" s="35"/>
+      <c r="V27" s="35"/>
+      <c r="W27" s="35"/>
+      <c r="X27" s="35"/>
+      <c r="Y27" s="35"/>
+      <c r="Z27" s="35"/>
+      <c r="AA27" s="35"/>
+      <c r="AB27" s="36"/>
+      <c r="AC27" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD27" s="35"/>
+    </row>
+    <row r="28" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="34">
+        <v>27</v>
+      </c>
+      <c r="B28" s="35"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="35"/>
+      <c r="I28" s="35"/>
+      <c r="J28" s="35"/>
+      <c r="K28" s="35"/>
+      <c r="L28" s="35"/>
+      <c r="M28" s="35"/>
+      <c r="N28" s="35"/>
+      <c r="O28" s="35"/>
+      <c r="P28" s="35"/>
+      <c r="Q28" s="35"/>
+      <c r="R28" s="35"/>
+      <c r="S28" s="35"/>
+      <c r="T28" s="35"/>
+      <c r="U28" s="35"/>
+      <c r="V28" s="35"/>
+      <c r="W28" s="35"/>
+      <c r="X28" s="35"/>
+      <c r="Y28" s="35"/>
+      <c r="Z28" s="35"/>
+      <c r="AA28" s="35"/>
+      <c r="AB28" s="36"/>
+      <c r="AC28" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD28" s="35"/>
+    </row>
+    <row r="29" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="34">
+        <v>28</v>
+      </c>
+      <c r="B29" s="35"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="35"/>
+      <c r="I29" s="35"/>
+      <c r="J29" s="35"/>
+      <c r="K29" s="35"/>
+      <c r="L29" s="35"/>
+      <c r="M29" s="35"/>
+      <c r="N29" s="35"/>
+      <c r="O29" s="35"/>
+      <c r="P29" s="35"/>
+      <c r="Q29" s="35"/>
+      <c r="R29" s="35"/>
+      <c r="S29" s="35"/>
+      <c r="T29" s="35"/>
+      <c r="U29" s="35"/>
+      <c r="V29" s="35"/>
+      <c r="W29" s="35"/>
+      <c r="X29" s="35"/>
+      <c r="Y29" s="35"/>
+      <c r="Z29" s="35"/>
+      <c r="AA29" s="35"/>
+      <c r="AB29" s="36"/>
+      <c r="AC29" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD29" s="35"/>
+    </row>
+    <row r="30" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="34">
+        <v>29</v>
+      </c>
+      <c r="B30" s="35"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="35"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="35"/>
+      <c r="I30" s="35"/>
+      <c r="J30" s="35"/>
+      <c r="K30" s="35"/>
+      <c r="L30" s="35"/>
+      <c r="M30" s="35"/>
+      <c r="N30" s="35"/>
+      <c r="O30" s="35"/>
+      <c r="P30" s="35"/>
+      <c r="Q30" s="35"/>
+      <c r="R30" s="35"/>
+      <c r="S30" s="35"/>
+      <c r="T30" s="35"/>
+      <c r="U30" s="35"/>
+      <c r="V30" s="35"/>
+      <c r="W30" s="35"/>
+      <c r="X30" s="35"/>
+      <c r="Y30" s="35"/>
+      <c r="Z30" s="35"/>
+      <c r="AA30" s="35"/>
+      <c r="AB30" s="36"/>
+      <c r="AC30" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD30" s="35"/>
+    </row>
+    <row r="31" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="34">
+        <v>30</v>
+      </c>
+      <c r="B31" s="35"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="35"/>
+      <c r="I31" s="35"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="35"/>
+      <c r="L31" s="35"/>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
+      <c r="O31" s="35"/>
+      <c r="P31" s="35"/>
+      <c r="Q31" s="35"/>
+      <c r="R31" s="35"/>
+      <c r="S31" s="35"/>
+      <c r="T31" s="35"/>
+      <c r="U31" s="35"/>
+      <c r="V31" s="35"/>
+      <c r="W31" s="35"/>
+      <c r="X31" s="35"/>
+      <c r="Y31" s="35"/>
+      <c r="Z31" s="35"/>
+      <c r="AA31" s="35"/>
+      <c r="AB31" s="36"/>
+      <c r="AC31" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD31" s="35"/>
+    </row>
+    <row r="32" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="34">
+        <v>31</v>
+      </c>
+      <c r="B32" s="35"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="35"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="35"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="35"/>
+      <c r="I32" s="35"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="35"/>
+      <c r="L32" s="35"/>
+      <c r="M32" s="35"/>
+      <c r="N32" s="35"/>
+      <c r="O32" s="35"/>
+      <c r="P32" s="35"/>
+      <c r="Q32" s="35"/>
+      <c r="R32" s="35"/>
+      <c r="S32" s="35"/>
+      <c r="T32" s="35"/>
+      <c r="U32" s="35"/>
+      <c r="V32" s="35"/>
+      <c r="W32" s="35"/>
+      <c r="X32" s="35"/>
+      <c r="Y32" s="35"/>
+      <c r="Z32" s="35"/>
+      <c r="AA32" s="35"/>
+      <c r="AB32" s="36"/>
+      <c r="AC32" s="35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AD32" s="35"/>
+    </row>
+    <row r="33" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" s="12" t="str">
+        <f t="shared" ref="B33:AC33" si="1">IF(COUNTA(B2:B32)&gt;0,SUM(B2:B32),"")</f>
+        <v/>
+      </c>
+      <c r="C33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="D33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="E33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="G33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="M33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="N33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="O33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="P33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Q33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="R33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="S33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="T33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="U33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="V33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="X33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Y33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Z33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AA33" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AB33" s="38" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AC33" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AD33" s="39"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AD32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="27" width="13" customWidth="1"/>
     <col min="28" max="28" width="14" customWidth="1"/>
     <col min="29" max="29" width="25" customWidth="1"/>
@@ -11724,7 +14437,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AD33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13096,2715 +15809,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="27" width="13" customWidth="1"/>
-    <col min="28" max="28" width="14" customWidth="1"/>
-    <col min="29" max="29" width="25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:30" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="33" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="33" t="s">
-        <v>12</v>
-      </c>
-      <c r="M1" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="O1" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="P1" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q1" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="R1" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="T1" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="U1" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="V1" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="W1" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="X1" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="Y1" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z1" s="33" t="s">
-        <v>71</v>
-      </c>
-      <c r="AA1" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC1" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD1" s="33" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="34">
-        <v>1</v>
-      </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
-      <c r="T2" s="35"/>
-      <c r="U2" s="35"/>
-      <c r="V2" s="35"/>
-      <c r="W2" s="35"/>
-      <c r="X2" s="35"/>
-      <c r="Y2" s="35"/>
-      <c r="Z2" s="35"/>
-      <c r="AA2" s="35"/>
-      <c r="AB2" s="36"/>
-      <c r="AC2" s="35">
-        <f t="shared" ref="AC2:AC31" si="0">SUM(B2:AA2)</f>
-        <v>0</v>
-      </c>
-      <c r="AD2" s="35"/>
-    </row>
-    <row r="3" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="34">
-        <v>2</v>
-      </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="35"/>
-      <c r="L3" s="35"/>
-      <c r="M3" s="35"/>
-      <c r="N3" s="35"/>
-      <c r="O3" s="35"/>
-      <c r="P3" s="35"/>
-      <c r="Q3" s="35"/>
-      <c r="R3" s="35"/>
-      <c r="S3" s="35"/>
-      <c r="T3" s="35"/>
-      <c r="U3" s="35"/>
-      <c r="V3" s="35"/>
-      <c r="W3" s="35"/>
-      <c r="X3" s="35"/>
-      <c r="Y3" s="35"/>
-      <c r="Z3" s="35"/>
-      <c r="AA3" s="35"/>
-      <c r="AB3" s="36"/>
-      <c r="AC3" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD3" s="35"/>
-    </row>
-    <row r="4" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="34">
-        <v>3</v>
-      </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="35"/>
-      <c r="M4" s="35"/>
-      <c r="N4" s="35"/>
-      <c r="O4" s="35"/>
-      <c r="P4" s="35"/>
-      <c r="Q4" s="35"/>
-      <c r="R4" s="35"/>
-      <c r="S4" s="35"/>
-      <c r="T4" s="35"/>
-      <c r="U4" s="35"/>
-      <c r="V4" s="35"/>
-      <c r="W4" s="35"/>
-      <c r="X4" s="35"/>
-      <c r="Y4" s="35"/>
-      <c r="Z4" s="35"/>
-      <c r="AA4" s="35"/>
-      <c r="AB4" s="36"/>
-      <c r="AC4" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD4" s="35"/>
-    </row>
-    <row r="5" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="34">
-        <v>4</v>
-      </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="35"/>
-      <c r="K5" s="35"/>
-      <c r="L5" s="35"/>
-      <c r="M5" s="35"/>
-      <c r="N5" s="35"/>
-      <c r="O5" s="35"/>
-      <c r="P5" s="35"/>
-      <c r="Q5" s="35"/>
-      <c r="R5" s="35"/>
-      <c r="S5" s="35"/>
-      <c r="T5" s="35"/>
-      <c r="U5" s="35"/>
-      <c r="V5" s="35"/>
-      <c r="W5" s="35"/>
-      <c r="X5" s="35"/>
-      <c r="Y5" s="35"/>
-      <c r="Z5" s="35"/>
-      <c r="AA5" s="35"/>
-      <c r="AB5" s="36"/>
-      <c r="AC5" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD5" s="35"/>
-    </row>
-    <row r="6" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="34">
-        <v>5</v>
-      </c>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="35"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="35"/>
-      <c r="N6" s="35"/>
-      <c r="O6" s="35"/>
-      <c r="P6" s="35"/>
-      <c r="Q6" s="35"/>
-      <c r="R6" s="35"/>
-      <c r="S6" s="35"/>
-      <c r="T6" s="35"/>
-      <c r="U6" s="35"/>
-      <c r="V6" s="35"/>
-      <c r="W6" s="35"/>
-      <c r="X6" s="35"/>
-      <c r="Y6" s="35"/>
-      <c r="Z6" s="35"/>
-      <c r="AA6" s="35"/>
-      <c r="AB6" s="36"/>
-      <c r="AC6" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD6" s="35"/>
-    </row>
-    <row r="7" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="34">
-        <v>6</v>
-      </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="35"/>
-      <c r="J7" s="35"/>
-      <c r="K7" s="35"/>
-      <c r="L7" s="35"/>
-      <c r="M7" s="35"/>
-      <c r="N7" s="35"/>
-      <c r="O7" s="35"/>
-      <c r="P7" s="35"/>
-      <c r="Q7" s="35"/>
-      <c r="R7" s="35"/>
-      <c r="S7" s="35"/>
-      <c r="T7" s="35"/>
-      <c r="U7" s="35"/>
-      <c r="V7" s="35"/>
-      <c r="W7" s="35"/>
-      <c r="X7" s="35"/>
-      <c r="Y7" s="35"/>
-      <c r="Z7" s="35"/>
-      <c r="AA7" s="35"/>
-      <c r="AB7" s="36"/>
-      <c r="AC7" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD7" s="35"/>
-    </row>
-    <row r="8" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="34">
-        <v>7</v>
-      </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="35"/>
-      <c r="J8" s="35"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="35"/>
-      <c r="M8" s="35"/>
-      <c r="N8" s="35"/>
-      <c r="O8" s="35"/>
-      <c r="P8" s="35"/>
-      <c r="Q8" s="35"/>
-      <c r="R8" s="35"/>
-      <c r="S8" s="35"/>
-      <c r="T8" s="35"/>
-      <c r="U8" s="35"/>
-      <c r="V8" s="35"/>
-      <c r="W8" s="35"/>
-      <c r="X8" s="35"/>
-      <c r="Y8" s="35"/>
-      <c r="Z8" s="35"/>
-      <c r="AA8" s="35"/>
-      <c r="AB8" s="36"/>
-      <c r="AC8" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD8" s="35"/>
-    </row>
-    <row r="9" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="34">
-        <v>8</v>
-      </c>
-      <c r="B9" s="35"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="35"/>
-      <c r="J9" s="35"/>
-      <c r="K9" s="35"/>
-      <c r="L9" s="35"/>
-      <c r="M9" s="35"/>
-      <c r="N9" s="35"/>
-      <c r="O9" s="35"/>
-      <c r="P9" s="35"/>
-      <c r="Q9" s="35"/>
-      <c r="R9" s="35"/>
-      <c r="S9" s="35"/>
-      <c r="T9" s="35"/>
-      <c r="U9" s="35"/>
-      <c r="V9" s="35"/>
-      <c r="W9" s="35"/>
-      <c r="X9" s="35"/>
-      <c r="Y9" s="35"/>
-      <c r="Z9" s="35"/>
-      <c r="AA9" s="35"/>
-      <c r="AB9" s="36"/>
-      <c r="AC9" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD9" s="35"/>
-    </row>
-    <row r="10" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="34">
-        <v>9</v>
-      </c>
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="35"/>
-      <c r="J10" s="35"/>
-      <c r="K10" s="35"/>
-      <c r="L10" s="35"/>
-      <c r="M10" s="35"/>
-      <c r="N10" s="35"/>
-      <c r="O10" s="35"/>
-      <c r="P10" s="35"/>
-      <c r="Q10" s="35"/>
-      <c r="R10" s="35"/>
-      <c r="S10" s="35"/>
-      <c r="T10" s="35"/>
-      <c r="U10" s="35"/>
-      <c r="V10" s="35"/>
-      <c r="W10" s="35"/>
-      <c r="X10" s="35"/>
-      <c r="Y10" s="35"/>
-      <c r="Z10" s="35"/>
-      <c r="AA10" s="35"/>
-      <c r="AB10" s="36"/>
-      <c r="AC10" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD10" s="35"/>
-    </row>
-    <row r="11" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="34">
-        <v>10</v>
-      </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="35"/>
-      <c r="J11" s="35"/>
-      <c r="K11" s="35"/>
-      <c r="L11" s="35"/>
-      <c r="M11" s="35"/>
-      <c r="N11" s="35"/>
-      <c r="O11" s="35"/>
-      <c r="P11" s="35"/>
-      <c r="Q11" s="35"/>
-      <c r="R11" s="35"/>
-      <c r="S11" s="35"/>
-      <c r="T11" s="35"/>
-      <c r="U11" s="35"/>
-      <c r="V11" s="35"/>
-      <c r="W11" s="35"/>
-      <c r="X11" s="35"/>
-      <c r="Y11" s="35"/>
-      <c r="Z11" s="35"/>
-      <c r="AA11" s="35"/>
-      <c r="AB11" s="36"/>
-      <c r="AC11" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD11" s="35"/>
-    </row>
-    <row r="12" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="34">
-        <v>11</v>
-      </c>
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="35"/>
-      <c r="J12" s="35"/>
-      <c r="K12" s="35"/>
-      <c r="L12" s="35"/>
-      <c r="M12" s="35"/>
-      <c r="N12" s="35"/>
-      <c r="O12" s="35"/>
-      <c r="P12" s="35"/>
-      <c r="Q12" s="35"/>
-      <c r="R12" s="35"/>
-      <c r="S12" s="35"/>
-      <c r="T12" s="35"/>
-      <c r="U12" s="35"/>
-      <c r="V12" s="35"/>
-      <c r="W12" s="35"/>
-      <c r="X12" s="35"/>
-      <c r="Y12" s="35"/>
-      <c r="Z12" s="35"/>
-      <c r="AA12" s="35"/>
-      <c r="AB12" s="36"/>
-      <c r="AC12" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD12" s="35"/>
-    </row>
-    <row r="13" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="34">
-        <v>12</v>
-      </c>
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="35"/>
-      <c r="K13" s="35"/>
-      <c r="L13" s="35"/>
-      <c r="M13" s="35"/>
-      <c r="N13" s="35"/>
-      <c r="O13" s="35"/>
-      <c r="P13" s="35"/>
-      <c r="Q13" s="35"/>
-      <c r="R13" s="35"/>
-      <c r="S13" s="35"/>
-      <c r="T13" s="35"/>
-      <c r="U13" s="35"/>
-      <c r="V13" s="35"/>
-      <c r="W13" s="35"/>
-      <c r="X13" s="35"/>
-      <c r="Y13" s="35"/>
-      <c r="Z13" s="35"/>
-      <c r="AA13" s="35"/>
-      <c r="AB13" s="36"/>
-      <c r="AC13" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD13" s="35"/>
-    </row>
-    <row r="14" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="34">
-        <v>13</v>
-      </c>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="35"/>
-      <c r="L14" s="35"/>
-      <c r="M14" s="35"/>
-      <c r="N14" s="35"/>
-      <c r="O14" s="35"/>
-      <c r="P14" s="35"/>
-      <c r="Q14" s="35"/>
-      <c r="R14" s="35"/>
-      <c r="S14" s="35"/>
-      <c r="T14" s="35"/>
-      <c r="U14" s="35"/>
-      <c r="V14" s="35"/>
-      <c r="W14" s="35"/>
-      <c r="X14" s="35"/>
-      <c r="Y14" s="35"/>
-      <c r="Z14" s="35"/>
-      <c r="AA14" s="35"/>
-      <c r="AB14" s="36"/>
-      <c r="AC14" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD14" s="35"/>
-    </row>
-    <row r="15" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="34">
-        <v>14</v>
-      </c>
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="35"/>
-      <c r="J15" s="35"/>
-      <c r="K15" s="35"/>
-      <c r="L15" s="35"/>
-      <c r="M15" s="35"/>
-      <c r="N15" s="35"/>
-      <c r="O15" s="35"/>
-      <c r="P15" s="35"/>
-      <c r="Q15" s="35"/>
-      <c r="R15" s="35"/>
-      <c r="S15" s="35"/>
-      <c r="T15" s="35"/>
-      <c r="U15" s="35"/>
-      <c r="V15" s="35"/>
-      <c r="W15" s="35"/>
-      <c r="X15" s="35"/>
-      <c r="Y15" s="35"/>
-      <c r="Z15" s="35"/>
-      <c r="AA15" s="35"/>
-      <c r="AB15" s="36"/>
-      <c r="AC15" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD15" s="35"/>
-    </row>
-    <row r="16" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="34">
-        <v>15</v>
-      </c>
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="35"/>
-      <c r="J16" s="35"/>
-      <c r="K16" s="35"/>
-      <c r="L16" s="35"/>
-      <c r="M16" s="35"/>
-      <c r="N16" s="35"/>
-      <c r="O16" s="35"/>
-      <c r="P16" s="35"/>
-      <c r="Q16" s="35"/>
-      <c r="R16" s="35"/>
-      <c r="S16" s="35"/>
-      <c r="T16" s="35"/>
-      <c r="U16" s="35"/>
-      <c r="V16" s="35"/>
-      <c r="W16" s="35"/>
-      <c r="X16" s="35"/>
-      <c r="Y16" s="35"/>
-      <c r="Z16" s="35"/>
-      <c r="AA16" s="35"/>
-      <c r="AB16" s="36"/>
-      <c r="AC16" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD16" s="35"/>
-    </row>
-    <row r="17" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="34">
-        <v>16</v>
-      </c>
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="35"/>
-      <c r="J17" s="35"/>
-      <c r="K17" s="35"/>
-      <c r="L17" s="35"/>
-      <c r="M17" s="35"/>
-      <c r="N17" s="35"/>
-      <c r="O17" s="35"/>
-      <c r="P17" s="35"/>
-      <c r="Q17" s="35"/>
-      <c r="R17" s="35"/>
-      <c r="S17" s="35"/>
-      <c r="T17" s="35"/>
-      <c r="U17" s="35"/>
-      <c r="V17" s="35"/>
-      <c r="W17" s="35"/>
-      <c r="X17" s="35"/>
-      <c r="Y17" s="35"/>
-      <c r="Z17" s="35"/>
-      <c r="AA17" s="35"/>
-      <c r="AB17" s="36"/>
-      <c r="AC17" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD17" s="35"/>
-    </row>
-    <row r="18" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="34">
-        <v>17</v>
-      </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="35"/>
-      <c r="J18" s="35"/>
-      <c r="K18" s="35"/>
-      <c r="L18" s="35"/>
-      <c r="M18" s="35"/>
-      <c r="N18" s="35"/>
-      <c r="O18" s="35"/>
-      <c r="P18" s="35"/>
-      <c r="Q18" s="35"/>
-      <c r="R18" s="35"/>
-      <c r="S18" s="35"/>
-      <c r="T18" s="35"/>
-      <c r="U18" s="35"/>
-      <c r="V18" s="35"/>
-      <c r="W18" s="35"/>
-      <c r="X18" s="35"/>
-      <c r="Y18" s="35"/>
-      <c r="Z18" s="35"/>
-      <c r="AA18" s="35"/>
-      <c r="AB18" s="36"/>
-      <c r="AC18" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD18" s="35"/>
-    </row>
-    <row r="19" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="34">
-        <v>18</v>
-      </c>
-      <c r="B19" s="35"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="35"/>
-      <c r="I19" s="35"/>
-      <c r="J19" s="35"/>
-      <c r="K19" s="35"/>
-      <c r="L19" s="35"/>
-      <c r="M19" s="35"/>
-      <c r="N19" s="35"/>
-      <c r="O19" s="35"/>
-      <c r="P19" s="35"/>
-      <c r="Q19" s="35"/>
-      <c r="R19" s="35"/>
-      <c r="S19" s="35"/>
-      <c r="T19" s="35"/>
-      <c r="U19" s="35"/>
-      <c r="V19" s="35"/>
-      <c r="W19" s="35"/>
-      <c r="X19" s="35"/>
-      <c r="Y19" s="35"/>
-      <c r="Z19" s="35"/>
-      <c r="AA19" s="35"/>
-      <c r="AB19" s="36"/>
-      <c r="AC19" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD19" s="35"/>
-    </row>
-    <row r="20" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="34">
-        <v>19</v>
-      </c>
-      <c r="B20" s="35"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="35"/>
-      <c r="J20" s="35"/>
-      <c r="K20" s="35"/>
-      <c r="L20" s="35"/>
-      <c r="M20" s="35"/>
-      <c r="N20" s="35"/>
-      <c r="O20" s="35"/>
-      <c r="P20" s="35"/>
-      <c r="Q20" s="35"/>
-      <c r="R20" s="35"/>
-      <c r="S20" s="35"/>
-      <c r="T20" s="35"/>
-      <c r="U20" s="35"/>
-      <c r="V20" s="35"/>
-      <c r="W20" s="35"/>
-      <c r="X20" s="35"/>
-      <c r="Y20" s="35"/>
-      <c r="Z20" s="35"/>
-      <c r="AA20" s="35"/>
-      <c r="AB20" s="36"/>
-      <c r="AC20" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD20" s="35"/>
-    </row>
-    <row r="21" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="34">
-        <v>20</v>
-      </c>
-      <c r="B21" s="35"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="35"/>
-      <c r="J21" s="35"/>
-      <c r="K21" s="35"/>
-      <c r="L21" s="35"/>
-      <c r="M21" s="35"/>
-      <c r="N21" s="35"/>
-      <c r="O21" s="35"/>
-      <c r="P21" s="35"/>
-      <c r="Q21" s="35"/>
-      <c r="R21" s="35"/>
-      <c r="S21" s="35"/>
-      <c r="T21" s="35"/>
-      <c r="U21" s="35"/>
-      <c r="V21" s="35"/>
-      <c r="W21" s="35"/>
-      <c r="X21" s="35"/>
-      <c r="Y21" s="35"/>
-      <c r="Z21" s="35"/>
-      <c r="AA21" s="35"/>
-      <c r="AB21" s="36"/>
-      <c r="AC21" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD21" s="35"/>
-    </row>
-    <row r="22" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="34">
-        <v>21</v>
-      </c>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="35"/>
-      <c r="L22" s="35"/>
-      <c r="M22" s="35"/>
-      <c r="N22" s="35"/>
-      <c r="O22" s="35"/>
-      <c r="P22" s="35"/>
-      <c r="Q22" s="35"/>
-      <c r="R22" s="35"/>
-      <c r="S22" s="35"/>
-      <c r="T22" s="35"/>
-      <c r="U22" s="35"/>
-      <c r="V22" s="35"/>
-      <c r="W22" s="35"/>
-      <c r="X22" s="35"/>
-      <c r="Y22" s="35"/>
-      <c r="Z22" s="35"/>
-      <c r="AA22" s="35"/>
-      <c r="AB22" s="36"/>
-      <c r="AC22" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD22" s="35"/>
-    </row>
-    <row r="23" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="34">
-        <v>22</v>
-      </c>
-      <c r="B23" s="35"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="35"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="35"/>
-      <c r="J23" s="35"/>
-      <c r="K23" s="35"/>
-      <c r="L23" s="35"/>
-      <c r="M23" s="35"/>
-      <c r="N23" s="35"/>
-      <c r="O23" s="35"/>
-      <c r="P23" s="35"/>
-      <c r="Q23" s="35"/>
-      <c r="R23" s="35"/>
-      <c r="S23" s="35"/>
-      <c r="T23" s="35"/>
-      <c r="U23" s="35"/>
-      <c r="V23" s="35"/>
-      <c r="W23" s="35"/>
-      <c r="X23" s="35"/>
-      <c r="Y23" s="35"/>
-      <c r="Z23" s="35"/>
-      <c r="AA23" s="35"/>
-      <c r="AB23" s="36"/>
-      <c r="AC23" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD23" s="35"/>
-    </row>
-    <row r="24" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="34">
-        <v>23</v>
-      </c>
-      <c r="B24" s="35"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="35"/>
-      <c r="J24" s="35"/>
-      <c r="K24" s="35"/>
-      <c r="L24" s="35"/>
-      <c r="M24" s="35"/>
-      <c r="N24" s="35"/>
-      <c r="O24" s="35"/>
-      <c r="P24" s="35"/>
-      <c r="Q24" s="35"/>
-      <c r="R24" s="35"/>
-      <c r="S24" s="35"/>
-      <c r="T24" s="35"/>
-      <c r="U24" s="35"/>
-      <c r="V24" s="35"/>
-      <c r="W24" s="35"/>
-      <c r="X24" s="35"/>
-      <c r="Y24" s="35"/>
-      <c r="Z24" s="35"/>
-      <c r="AA24" s="35"/>
-      <c r="AB24" s="36"/>
-      <c r="AC24" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD24" s="35"/>
-    </row>
-    <row r="25" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="34">
-        <v>24</v>
-      </c>
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="35"/>
-      <c r="J25" s="35"/>
-      <c r="K25" s="35"/>
-      <c r="L25" s="35"/>
-      <c r="M25" s="35"/>
-      <c r="N25" s="35"/>
-      <c r="O25" s="35"/>
-      <c r="P25" s="35"/>
-      <c r="Q25" s="35"/>
-      <c r="R25" s="35"/>
-      <c r="S25" s="35"/>
-      <c r="T25" s="35"/>
-      <c r="U25" s="35"/>
-      <c r="V25" s="35"/>
-      <c r="W25" s="35"/>
-      <c r="X25" s="35"/>
-      <c r="Y25" s="35"/>
-      <c r="Z25" s="35"/>
-      <c r="AA25" s="35"/>
-      <c r="AB25" s="36"/>
-      <c r="AC25" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD25" s="35"/>
-    </row>
-    <row r="26" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="34">
-        <v>25</v>
-      </c>
-      <c r="B26" s="35"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="35"/>
-      <c r="J26" s="35"/>
-      <c r="K26" s="35"/>
-      <c r="L26" s="35"/>
-      <c r="M26" s="35"/>
-      <c r="N26" s="35"/>
-      <c r="O26" s="35"/>
-      <c r="P26" s="35"/>
-      <c r="Q26" s="35"/>
-      <c r="R26" s="35"/>
-      <c r="S26" s="35"/>
-      <c r="T26" s="35"/>
-      <c r="U26" s="35"/>
-      <c r="V26" s="35"/>
-      <c r="W26" s="35"/>
-      <c r="X26" s="35"/>
-      <c r="Y26" s="35"/>
-      <c r="Z26" s="35"/>
-      <c r="AA26" s="35"/>
-      <c r="AB26" s="36"/>
-      <c r="AC26" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD26" s="35"/>
-    </row>
-    <row r="27" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="34">
-        <v>26</v>
-      </c>
-      <c r="B27" s="35"/>
-      <c r="C27" s="35"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="35"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="35"/>
-      <c r="J27" s="35"/>
-      <c r="K27" s="35"/>
-      <c r="L27" s="35"/>
-      <c r="M27" s="35"/>
-      <c r="N27" s="35"/>
-      <c r="O27" s="35"/>
-      <c r="P27" s="35"/>
-      <c r="Q27" s="35"/>
-      <c r="R27" s="35"/>
-      <c r="S27" s="35"/>
-      <c r="T27" s="35"/>
-      <c r="U27" s="35"/>
-      <c r="V27" s="35"/>
-      <c r="W27" s="35"/>
-      <c r="X27" s="35"/>
-      <c r="Y27" s="35"/>
-      <c r="Z27" s="35"/>
-      <c r="AA27" s="35"/>
-      <c r="AB27" s="36"/>
-      <c r="AC27" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD27" s="35"/>
-    </row>
-    <row r="28" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="34">
-        <v>27</v>
-      </c>
-      <c r="B28" s="35"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="35"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="35"/>
-      <c r="J28" s="35"/>
-      <c r="K28" s="35"/>
-      <c r="L28" s="35"/>
-      <c r="M28" s="35"/>
-      <c r="N28" s="35"/>
-      <c r="O28" s="35"/>
-      <c r="P28" s="35"/>
-      <c r="Q28" s="35"/>
-      <c r="R28" s="35"/>
-      <c r="S28" s="35"/>
-      <c r="T28" s="35"/>
-      <c r="U28" s="35"/>
-      <c r="V28" s="35"/>
-      <c r="W28" s="35"/>
-      <c r="X28" s="35"/>
-      <c r="Y28" s="35"/>
-      <c r="Z28" s="35"/>
-      <c r="AA28" s="35"/>
-      <c r="AB28" s="36"/>
-      <c r="AC28" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD28" s="35"/>
-    </row>
-    <row r="29" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="34">
-        <v>28</v>
-      </c>
-      <c r="B29" s="35"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="35"/>
-      <c r="I29" s="35"/>
-      <c r="J29" s="35"/>
-      <c r="K29" s="35"/>
-      <c r="L29" s="35"/>
-      <c r="M29" s="35"/>
-      <c r="N29" s="35"/>
-      <c r="O29" s="35"/>
-      <c r="P29" s="35"/>
-      <c r="Q29" s="35"/>
-      <c r="R29" s="35"/>
-      <c r="S29" s="35"/>
-      <c r="T29" s="35"/>
-      <c r="U29" s="35"/>
-      <c r="V29" s="35"/>
-      <c r="W29" s="35"/>
-      <c r="X29" s="35"/>
-      <c r="Y29" s="35"/>
-      <c r="Z29" s="35"/>
-      <c r="AA29" s="35"/>
-      <c r="AB29" s="36"/>
-      <c r="AC29" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD29" s="35"/>
-    </row>
-    <row r="30" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="34">
-        <v>29</v>
-      </c>
-      <c r="B30" s="35"/>
-      <c r="C30" s="35"/>
-      <c r="D30" s="35"/>
-      <c r="E30" s="35"/>
-      <c r="F30" s="35"/>
-      <c r="G30" s="35"/>
-      <c r="H30" s="35"/>
-      <c r="I30" s="35"/>
-      <c r="J30" s="35"/>
-      <c r="K30" s="35"/>
-      <c r="L30" s="35"/>
-      <c r="M30" s="35"/>
-      <c r="N30" s="35"/>
-      <c r="O30" s="35"/>
-      <c r="P30" s="35"/>
-      <c r="Q30" s="35"/>
-      <c r="R30" s="35"/>
-      <c r="S30" s="35"/>
-      <c r="T30" s="35"/>
-      <c r="U30" s="35"/>
-      <c r="V30" s="35"/>
-      <c r="W30" s="35"/>
-      <c r="X30" s="35"/>
-      <c r="Y30" s="35"/>
-      <c r="Z30" s="35"/>
-      <c r="AA30" s="35"/>
-      <c r="AB30" s="36"/>
-      <c r="AC30" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD30" s="35"/>
-    </row>
-    <row r="31" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="34">
-        <v>30</v>
-      </c>
-      <c r="B31" s="35"/>
-      <c r="C31" s="35"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="35"/>
-      <c r="H31" s="35"/>
-      <c r="I31" s="35"/>
-      <c r="J31" s="35"/>
-      <c r="K31" s="35"/>
-      <c r="L31" s="35"/>
-      <c r="M31" s="35"/>
-      <c r="N31" s="35"/>
-      <c r="O31" s="35"/>
-      <c r="P31" s="35"/>
-      <c r="Q31" s="35"/>
-      <c r="R31" s="35"/>
-      <c r="S31" s="35"/>
-      <c r="T31" s="35"/>
-      <c r="U31" s="35"/>
-      <c r="V31" s="35"/>
-      <c r="W31" s="35"/>
-      <c r="X31" s="35"/>
-      <c r="Y31" s="35"/>
-      <c r="Z31" s="35"/>
-      <c r="AA31" s="35"/>
-      <c r="AB31" s="36"/>
-      <c r="AC31" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD31" s="35"/>
-    </row>
-    <row r="32" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="B32" s="12" t="str">
-        <f t="shared" ref="B32:AC32" si="1">IF(COUNTA(B2:B31)&gt;0,SUM(B2:B31),"")</f>
-        <v/>
-      </c>
-      <c r="C32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="D32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="E32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="L32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="N32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Q32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="R32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="U32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="V32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="X32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Y32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AA32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB32" s="38" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AC32" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AD32" s="39"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="27" width="13" customWidth="1"/>
-    <col min="28" max="28" width="14" customWidth="1"/>
-    <col min="29" max="29" width="25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:30" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="33" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="33" t="s">
-        <v>12</v>
-      </c>
-      <c r="M1" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="O1" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="P1" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q1" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="R1" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="T1" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="U1" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="V1" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="W1" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="X1" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="Y1" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z1" s="33" t="s">
-        <v>71</v>
-      </c>
-      <c r="AA1" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC1" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD1" s="33" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="34">
-        <v>1</v>
-      </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
-      <c r="T2" s="35"/>
-      <c r="U2" s="35"/>
-      <c r="V2" s="35"/>
-      <c r="W2" s="35"/>
-      <c r="X2" s="35"/>
-      <c r="Y2" s="35"/>
-      <c r="Z2" s="35"/>
-      <c r="AA2" s="35"/>
-      <c r="AB2" s="36"/>
-      <c r="AC2" s="35">
-        <f t="shared" ref="AC2:AC32" si="0">SUM(B2:AA2)</f>
-        <v>0</v>
-      </c>
-      <c r="AD2" s="35"/>
-    </row>
-    <row r="3" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="34">
-        <v>2</v>
-      </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="35"/>
-      <c r="L3" s="35"/>
-      <c r="M3" s="35"/>
-      <c r="N3" s="35"/>
-      <c r="O3" s="35"/>
-      <c r="P3" s="35"/>
-      <c r="Q3" s="35"/>
-      <c r="R3" s="35"/>
-      <c r="S3" s="35"/>
-      <c r="T3" s="35"/>
-      <c r="U3" s="35"/>
-      <c r="V3" s="35"/>
-      <c r="W3" s="35"/>
-      <c r="X3" s="35"/>
-      <c r="Y3" s="35"/>
-      <c r="Z3" s="35"/>
-      <c r="AA3" s="35"/>
-      <c r="AB3" s="36"/>
-      <c r="AC3" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD3" s="35"/>
-    </row>
-    <row r="4" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="34">
-        <v>3</v>
-      </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="35"/>
-      <c r="M4" s="35"/>
-      <c r="N4" s="35"/>
-      <c r="O4" s="35"/>
-      <c r="P4" s="35"/>
-      <c r="Q4" s="35"/>
-      <c r="R4" s="35"/>
-      <c r="S4" s="35"/>
-      <c r="T4" s="35"/>
-      <c r="U4" s="35"/>
-      <c r="V4" s="35"/>
-      <c r="W4" s="35"/>
-      <c r="X4" s="35"/>
-      <c r="Y4" s="35"/>
-      <c r="Z4" s="35"/>
-      <c r="AA4" s="35"/>
-      <c r="AB4" s="36"/>
-      <c r="AC4" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD4" s="35"/>
-    </row>
-    <row r="5" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="34">
-        <v>4</v>
-      </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="35"/>
-      <c r="K5" s="35"/>
-      <c r="L5" s="35"/>
-      <c r="M5" s="35"/>
-      <c r="N5" s="35"/>
-      <c r="O5" s="35"/>
-      <c r="P5" s="35"/>
-      <c r="Q5" s="35"/>
-      <c r="R5" s="35"/>
-      <c r="S5" s="35"/>
-      <c r="T5" s="35"/>
-      <c r="U5" s="35"/>
-      <c r="V5" s="35"/>
-      <c r="W5" s="35"/>
-      <c r="X5" s="35"/>
-      <c r="Y5" s="35"/>
-      <c r="Z5" s="35"/>
-      <c r="AA5" s="35"/>
-      <c r="AB5" s="36"/>
-      <c r="AC5" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD5" s="35"/>
-    </row>
-    <row r="6" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="34">
-        <v>5</v>
-      </c>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="35"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="35"/>
-      <c r="N6" s="35"/>
-      <c r="O6" s="35"/>
-      <c r="P6" s="35"/>
-      <c r="Q6" s="35"/>
-      <c r="R6" s="35"/>
-      <c r="S6" s="35"/>
-      <c r="T6" s="35"/>
-      <c r="U6" s="35"/>
-      <c r="V6" s="35"/>
-      <c r="W6" s="35"/>
-      <c r="X6" s="35"/>
-      <c r="Y6" s="35"/>
-      <c r="Z6" s="35"/>
-      <c r="AA6" s="35"/>
-      <c r="AB6" s="36"/>
-      <c r="AC6" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD6" s="35"/>
-    </row>
-    <row r="7" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="34">
-        <v>6</v>
-      </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="35"/>
-      <c r="J7" s="35"/>
-      <c r="K7" s="35"/>
-      <c r="L7" s="35"/>
-      <c r="M7" s="35"/>
-      <c r="N7" s="35"/>
-      <c r="O7" s="35"/>
-      <c r="P7" s="35"/>
-      <c r="Q7" s="35"/>
-      <c r="R7" s="35"/>
-      <c r="S7" s="35"/>
-      <c r="T7" s="35"/>
-      <c r="U7" s="35"/>
-      <c r="V7" s="35"/>
-      <c r="W7" s="35"/>
-      <c r="X7" s="35"/>
-      <c r="Y7" s="35"/>
-      <c r="Z7" s="35"/>
-      <c r="AA7" s="35"/>
-      <c r="AB7" s="36"/>
-      <c r="AC7" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD7" s="35"/>
-    </row>
-    <row r="8" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="34">
-        <v>7</v>
-      </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="35"/>
-      <c r="J8" s="35"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="35"/>
-      <c r="M8" s="35"/>
-      <c r="N8" s="35"/>
-      <c r="O8" s="35"/>
-      <c r="P8" s="35"/>
-      <c r="Q8" s="35"/>
-      <c r="R8" s="35"/>
-      <c r="S8" s="35"/>
-      <c r="T8" s="35"/>
-      <c r="U8" s="35"/>
-      <c r="V8" s="35"/>
-      <c r="W8" s="35"/>
-      <c r="X8" s="35"/>
-      <c r="Y8" s="35"/>
-      <c r="Z8" s="35"/>
-      <c r="AA8" s="35"/>
-      <c r="AB8" s="36"/>
-      <c r="AC8" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD8" s="35"/>
-    </row>
-    <row r="9" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="34">
-        <v>8</v>
-      </c>
-      <c r="B9" s="35"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="35"/>
-      <c r="J9" s="35"/>
-      <c r="K9" s="35"/>
-      <c r="L9" s="35"/>
-      <c r="M9" s="35"/>
-      <c r="N9" s="35"/>
-      <c r="O9" s="35"/>
-      <c r="P9" s="35"/>
-      <c r="Q9" s="35"/>
-      <c r="R9" s="35"/>
-      <c r="S9" s="35"/>
-      <c r="T9" s="35"/>
-      <c r="U9" s="35"/>
-      <c r="V9" s="35"/>
-      <c r="W9" s="35"/>
-      <c r="X9" s="35"/>
-      <c r="Y9" s="35"/>
-      <c r="Z9" s="35"/>
-      <c r="AA9" s="35"/>
-      <c r="AB9" s="36"/>
-      <c r="AC9" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD9" s="35"/>
-    </row>
-    <row r="10" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="34">
-        <v>9</v>
-      </c>
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="35"/>
-      <c r="J10" s="35"/>
-      <c r="K10" s="35"/>
-      <c r="L10" s="35"/>
-      <c r="M10" s="35"/>
-      <c r="N10" s="35"/>
-      <c r="O10" s="35"/>
-      <c r="P10" s="35"/>
-      <c r="Q10" s="35"/>
-      <c r="R10" s="35"/>
-      <c r="S10" s="35"/>
-      <c r="T10" s="35"/>
-      <c r="U10" s="35"/>
-      <c r="V10" s="35"/>
-      <c r="W10" s="35"/>
-      <c r="X10" s="35"/>
-      <c r="Y10" s="35"/>
-      <c r="Z10" s="35"/>
-      <c r="AA10" s="35"/>
-      <c r="AB10" s="36"/>
-      <c r="AC10" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD10" s="35"/>
-    </row>
-    <row r="11" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="34">
-        <v>10</v>
-      </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="35"/>
-      <c r="J11" s="35"/>
-      <c r="K11" s="35"/>
-      <c r="L11" s="35"/>
-      <c r="M11" s="35"/>
-      <c r="N11" s="35"/>
-      <c r="O11" s="35"/>
-      <c r="P11" s="35"/>
-      <c r="Q11" s="35"/>
-      <c r="R11" s="35"/>
-      <c r="S11" s="35"/>
-      <c r="T11" s="35"/>
-      <c r="U11" s="35"/>
-      <c r="V11" s="35"/>
-      <c r="W11" s="35"/>
-      <c r="X11" s="35"/>
-      <c r="Y11" s="35"/>
-      <c r="Z11" s="35"/>
-      <c r="AA11" s="35"/>
-      <c r="AB11" s="36"/>
-      <c r="AC11" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD11" s="35"/>
-    </row>
-    <row r="12" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="34">
-        <v>11</v>
-      </c>
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="35"/>
-      <c r="J12" s="35"/>
-      <c r="K12" s="35"/>
-      <c r="L12" s="35"/>
-      <c r="M12" s="35"/>
-      <c r="N12" s="35"/>
-      <c r="O12" s="35"/>
-      <c r="P12" s="35"/>
-      <c r="Q12" s="35"/>
-      <c r="R12" s="35"/>
-      <c r="S12" s="35"/>
-      <c r="T12" s="35"/>
-      <c r="U12" s="35"/>
-      <c r="V12" s="35"/>
-      <c r="W12" s="35"/>
-      <c r="X12" s="35"/>
-      <c r="Y12" s="35"/>
-      <c r="Z12" s="35"/>
-      <c r="AA12" s="35"/>
-      <c r="AB12" s="36"/>
-      <c r="AC12" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD12" s="35"/>
-    </row>
-    <row r="13" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="34">
-        <v>12</v>
-      </c>
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="35"/>
-      <c r="K13" s="35"/>
-      <c r="L13" s="35"/>
-      <c r="M13" s="35"/>
-      <c r="N13" s="35"/>
-      <c r="O13" s="35"/>
-      <c r="P13" s="35"/>
-      <c r="Q13" s="35"/>
-      <c r="R13" s="35"/>
-      <c r="S13" s="35"/>
-      <c r="T13" s="35"/>
-      <c r="U13" s="35"/>
-      <c r="V13" s="35"/>
-      <c r="W13" s="35"/>
-      <c r="X13" s="35"/>
-      <c r="Y13" s="35"/>
-      <c r="Z13" s="35"/>
-      <c r="AA13" s="35"/>
-      <c r="AB13" s="36"/>
-      <c r="AC13" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD13" s="35"/>
-    </row>
-    <row r="14" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="34">
-        <v>13</v>
-      </c>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="35"/>
-      <c r="L14" s="35"/>
-      <c r="M14" s="35"/>
-      <c r="N14" s="35"/>
-      <c r="O14" s="35"/>
-      <c r="P14" s="35"/>
-      <c r="Q14" s="35"/>
-      <c r="R14" s="35"/>
-      <c r="S14" s="35"/>
-      <c r="T14" s="35"/>
-      <c r="U14" s="35"/>
-      <c r="V14" s="35"/>
-      <c r="W14" s="35"/>
-      <c r="X14" s="35"/>
-      <c r="Y14" s="35"/>
-      <c r="Z14" s="35"/>
-      <c r="AA14" s="35"/>
-      <c r="AB14" s="36"/>
-      <c r="AC14" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD14" s="35"/>
-    </row>
-    <row r="15" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="34">
-        <v>14</v>
-      </c>
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="35"/>
-      <c r="J15" s="35"/>
-      <c r="K15" s="35"/>
-      <c r="L15" s="35"/>
-      <c r="M15" s="35"/>
-      <c r="N15" s="35"/>
-      <c r="O15" s="35"/>
-      <c r="P15" s="35"/>
-      <c r="Q15" s="35"/>
-      <c r="R15" s="35"/>
-      <c r="S15" s="35"/>
-      <c r="T15" s="35"/>
-      <c r="U15" s="35"/>
-      <c r="V15" s="35"/>
-      <c r="W15" s="35"/>
-      <c r="X15" s="35"/>
-      <c r="Y15" s="35"/>
-      <c r="Z15" s="35"/>
-      <c r="AA15" s="35"/>
-      <c r="AB15" s="36"/>
-      <c r="AC15" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD15" s="35"/>
-    </row>
-    <row r="16" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="34">
-        <v>15</v>
-      </c>
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="35"/>
-      <c r="J16" s="35"/>
-      <c r="K16" s="35"/>
-      <c r="L16" s="35"/>
-      <c r="M16" s="35"/>
-      <c r="N16" s="35"/>
-      <c r="O16" s="35"/>
-      <c r="P16" s="35"/>
-      <c r="Q16" s="35"/>
-      <c r="R16" s="35"/>
-      <c r="S16" s="35"/>
-      <c r="T16" s="35"/>
-      <c r="U16" s="35"/>
-      <c r="V16" s="35"/>
-      <c r="W16" s="35"/>
-      <c r="X16" s="35"/>
-      <c r="Y16" s="35"/>
-      <c r="Z16" s="35"/>
-      <c r="AA16" s="35"/>
-      <c r="AB16" s="36"/>
-      <c r="AC16" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD16" s="35"/>
-    </row>
-    <row r="17" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="34">
-        <v>16</v>
-      </c>
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="35"/>
-      <c r="J17" s="35"/>
-      <c r="K17" s="35"/>
-      <c r="L17" s="35"/>
-      <c r="M17" s="35"/>
-      <c r="N17" s="35"/>
-      <c r="O17" s="35"/>
-      <c r="P17" s="35"/>
-      <c r="Q17" s="35"/>
-      <c r="R17" s="35"/>
-      <c r="S17" s="35"/>
-      <c r="T17" s="35"/>
-      <c r="U17" s="35"/>
-      <c r="V17" s="35"/>
-      <c r="W17" s="35"/>
-      <c r="X17" s="35"/>
-      <c r="Y17" s="35"/>
-      <c r="Z17" s="35"/>
-      <c r="AA17" s="35"/>
-      <c r="AB17" s="36"/>
-      <c r="AC17" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD17" s="35"/>
-    </row>
-    <row r="18" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="34">
-        <v>17</v>
-      </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="35"/>
-      <c r="J18" s="35"/>
-      <c r="K18" s="35"/>
-      <c r="L18" s="35"/>
-      <c r="M18" s="35"/>
-      <c r="N18" s="35"/>
-      <c r="O18" s="35"/>
-      <c r="P18" s="35"/>
-      <c r="Q18" s="35"/>
-      <c r="R18" s="35"/>
-      <c r="S18" s="35"/>
-      <c r="T18" s="35"/>
-      <c r="U18" s="35"/>
-      <c r="V18" s="35"/>
-      <c r="W18" s="35"/>
-      <c r="X18" s="35"/>
-      <c r="Y18" s="35"/>
-      <c r="Z18" s="35"/>
-      <c r="AA18" s="35"/>
-      <c r="AB18" s="36"/>
-      <c r="AC18" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD18" s="35"/>
-    </row>
-    <row r="19" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="34">
-        <v>18</v>
-      </c>
-      <c r="B19" s="35"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="35"/>
-      <c r="I19" s="35"/>
-      <c r="J19" s="35"/>
-      <c r="K19" s="35"/>
-      <c r="L19" s="35"/>
-      <c r="M19" s="35"/>
-      <c r="N19" s="35"/>
-      <c r="O19" s="35"/>
-      <c r="P19" s="35"/>
-      <c r="Q19" s="35"/>
-      <c r="R19" s="35"/>
-      <c r="S19" s="35"/>
-      <c r="T19" s="35"/>
-      <c r="U19" s="35"/>
-      <c r="V19" s="35"/>
-      <c r="W19" s="35"/>
-      <c r="X19" s="35"/>
-      <c r="Y19" s="35"/>
-      <c r="Z19" s="35"/>
-      <c r="AA19" s="35"/>
-      <c r="AB19" s="36"/>
-      <c r="AC19" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD19" s="35"/>
-    </row>
-    <row r="20" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="34">
-        <v>19</v>
-      </c>
-      <c r="B20" s="35"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="35"/>
-      <c r="J20" s="35"/>
-      <c r="K20" s="35"/>
-      <c r="L20" s="35"/>
-      <c r="M20" s="35"/>
-      <c r="N20" s="35"/>
-      <c r="O20" s="35"/>
-      <c r="P20" s="35"/>
-      <c r="Q20" s="35"/>
-      <c r="R20" s="35"/>
-      <c r="S20" s="35"/>
-      <c r="T20" s="35"/>
-      <c r="U20" s="35"/>
-      <c r="V20" s="35"/>
-      <c r="W20" s="35"/>
-      <c r="X20" s="35"/>
-      <c r="Y20" s="35"/>
-      <c r="Z20" s="35"/>
-      <c r="AA20" s="35"/>
-      <c r="AB20" s="36"/>
-      <c r="AC20" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD20" s="35"/>
-    </row>
-    <row r="21" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="34">
-        <v>20</v>
-      </c>
-      <c r="B21" s="35"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="35"/>
-      <c r="J21" s="35"/>
-      <c r="K21" s="35"/>
-      <c r="L21" s="35"/>
-      <c r="M21" s="35"/>
-      <c r="N21" s="35"/>
-      <c r="O21" s="35"/>
-      <c r="P21" s="35"/>
-      <c r="Q21" s="35"/>
-      <c r="R21" s="35"/>
-      <c r="S21" s="35"/>
-      <c r="T21" s="35"/>
-      <c r="U21" s="35"/>
-      <c r="V21" s="35"/>
-      <c r="W21" s="35"/>
-      <c r="X21" s="35"/>
-      <c r="Y21" s="35"/>
-      <c r="Z21" s="35"/>
-      <c r="AA21" s="35"/>
-      <c r="AB21" s="36"/>
-      <c r="AC21" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD21" s="35"/>
-    </row>
-    <row r="22" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="34">
-        <v>21</v>
-      </c>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="35"/>
-      <c r="L22" s="35"/>
-      <c r="M22" s="35"/>
-      <c r="N22" s="35"/>
-      <c r="O22" s="35"/>
-      <c r="P22" s="35"/>
-      <c r="Q22" s="35"/>
-      <c r="R22" s="35"/>
-      <c r="S22" s="35"/>
-      <c r="T22" s="35"/>
-      <c r="U22" s="35"/>
-      <c r="V22" s="35"/>
-      <c r="W22" s="35"/>
-      <c r="X22" s="35"/>
-      <c r="Y22" s="35"/>
-      <c r="Z22" s="35"/>
-      <c r="AA22" s="35"/>
-      <c r="AB22" s="36"/>
-      <c r="AC22" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD22" s="35"/>
-    </row>
-    <row r="23" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="34">
-        <v>22</v>
-      </c>
-      <c r="B23" s="35"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="35"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="35"/>
-      <c r="J23" s="35"/>
-      <c r="K23" s="35"/>
-      <c r="L23" s="35"/>
-      <c r="M23" s="35"/>
-      <c r="N23" s="35"/>
-      <c r="O23" s="35"/>
-      <c r="P23" s="35"/>
-      <c r="Q23" s="35"/>
-      <c r="R23" s="35"/>
-      <c r="S23" s="35"/>
-      <c r="T23" s="35"/>
-      <c r="U23" s="35"/>
-      <c r="V23" s="35"/>
-      <c r="W23" s="35"/>
-      <c r="X23" s="35"/>
-      <c r="Y23" s="35"/>
-      <c r="Z23" s="35"/>
-      <c r="AA23" s="35"/>
-      <c r="AB23" s="36"/>
-      <c r="AC23" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD23" s="35"/>
-    </row>
-    <row r="24" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="34">
-        <v>23</v>
-      </c>
-      <c r="B24" s="35"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="35"/>
-      <c r="J24" s="35"/>
-      <c r="K24" s="35"/>
-      <c r="L24" s="35"/>
-      <c r="M24" s="35"/>
-      <c r="N24" s="35"/>
-      <c r="O24" s="35"/>
-      <c r="P24" s="35"/>
-      <c r="Q24" s="35"/>
-      <c r="R24" s="35"/>
-      <c r="S24" s="35"/>
-      <c r="T24" s="35"/>
-      <c r="U24" s="35"/>
-      <c r="V24" s="35"/>
-      <c r="W24" s="35"/>
-      <c r="X24" s="35"/>
-      <c r="Y24" s="35"/>
-      <c r="Z24" s="35"/>
-      <c r="AA24" s="35"/>
-      <c r="AB24" s="36"/>
-      <c r="AC24" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD24" s="35"/>
-    </row>
-    <row r="25" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="34">
-        <v>24</v>
-      </c>
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="35"/>
-      <c r="J25" s="35"/>
-      <c r="K25" s="35"/>
-      <c r="L25" s="35"/>
-      <c r="M25" s="35"/>
-      <c r="N25" s="35"/>
-      <c r="O25" s="35"/>
-      <c r="P25" s="35"/>
-      <c r="Q25" s="35"/>
-      <c r="R25" s="35"/>
-      <c r="S25" s="35"/>
-      <c r="T25" s="35"/>
-      <c r="U25" s="35"/>
-      <c r="V25" s="35"/>
-      <c r="W25" s="35"/>
-      <c r="X25" s="35"/>
-      <c r="Y25" s="35"/>
-      <c r="Z25" s="35"/>
-      <c r="AA25" s="35"/>
-      <c r="AB25" s="36"/>
-      <c r="AC25" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD25" s="35"/>
-    </row>
-    <row r="26" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="34">
-        <v>25</v>
-      </c>
-      <c r="B26" s="35"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="35"/>
-      <c r="J26" s="35"/>
-      <c r="K26" s="35"/>
-      <c r="L26" s="35"/>
-      <c r="M26" s="35"/>
-      <c r="N26" s="35"/>
-      <c r="O26" s="35"/>
-      <c r="P26" s="35"/>
-      <c r="Q26" s="35"/>
-      <c r="R26" s="35"/>
-      <c r="S26" s="35"/>
-      <c r="T26" s="35"/>
-      <c r="U26" s="35"/>
-      <c r="V26" s="35"/>
-      <c r="W26" s="35"/>
-      <c r="X26" s="35"/>
-      <c r="Y26" s="35"/>
-      <c r="Z26" s="35"/>
-      <c r="AA26" s="35"/>
-      <c r="AB26" s="36"/>
-      <c r="AC26" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD26" s="35"/>
-    </row>
-    <row r="27" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="34">
-        <v>26</v>
-      </c>
-      <c r="B27" s="35"/>
-      <c r="C27" s="35"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="35"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="35"/>
-      <c r="J27" s="35"/>
-      <c r="K27" s="35"/>
-      <c r="L27" s="35"/>
-      <c r="M27" s="35"/>
-      <c r="N27" s="35"/>
-      <c r="O27" s="35"/>
-      <c r="P27" s="35"/>
-      <c r="Q27" s="35"/>
-      <c r="R27" s="35"/>
-      <c r="S27" s="35"/>
-      <c r="T27" s="35"/>
-      <c r="U27" s="35"/>
-      <c r="V27" s="35"/>
-      <c r="W27" s="35"/>
-      <c r="X27" s="35"/>
-      <c r="Y27" s="35"/>
-      <c r="Z27" s="35"/>
-      <c r="AA27" s="35"/>
-      <c r="AB27" s="36"/>
-      <c r="AC27" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD27" s="35"/>
-    </row>
-    <row r="28" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="34">
-        <v>27</v>
-      </c>
-      <c r="B28" s="35"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="35"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="35"/>
-      <c r="J28" s="35"/>
-      <c r="K28" s="35"/>
-      <c r="L28" s="35"/>
-      <c r="M28" s="35"/>
-      <c r="N28" s="35"/>
-      <c r="O28" s="35"/>
-      <c r="P28" s="35"/>
-      <c r="Q28" s="35"/>
-      <c r="R28" s="35"/>
-      <c r="S28" s="35"/>
-      <c r="T28" s="35"/>
-      <c r="U28" s="35"/>
-      <c r="V28" s="35"/>
-      <c r="W28" s="35"/>
-      <c r="X28" s="35"/>
-      <c r="Y28" s="35"/>
-      <c r="Z28" s="35"/>
-      <c r="AA28" s="35"/>
-      <c r="AB28" s="36"/>
-      <c r="AC28" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD28" s="35"/>
-    </row>
-    <row r="29" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="34">
-        <v>28</v>
-      </c>
-      <c r="B29" s="35"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="35"/>
-      <c r="I29" s="35"/>
-      <c r="J29" s="35"/>
-      <c r="K29" s="35"/>
-      <c r="L29" s="35"/>
-      <c r="M29" s="35"/>
-      <c r="N29" s="35"/>
-      <c r="O29" s="35"/>
-      <c r="P29" s="35"/>
-      <c r="Q29" s="35"/>
-      <c r="R29" s="35"/>
-      <c r="S29" s="35"/>
-      <c r="T29" s="35"/>
-      <c r="U29" s="35"/>
-      <c r="V29" s="35"/>
-      <c r="W29" s="35"/>
-      <c r="X29" s="35"/>
-      <c r="Y29" s="35"/>
-      <c r="Z29" s="35"/>
-      <c r="AA29" s="35"/>
-      <c r="AB29" s="36"/>
-      <c r="AC29" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD29" s="35"/>
-    </row>
-    <row r="30" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="34">
-        <v>29</v>
-      </c>
-      <c r="B30" s="35"/>
-      <c r="C30" s="35"/>
-      <c r="D30" s="35"/>
-      <c r="E30" s="35"/>
-      <c r="F30" s="35"/>
-      <c r="G30" s="35"/>
-      <c r="H30" s="35"/>
-      <c r="I30" s="35"/>
-      <c r="J30" s="35"/>
-      <c r="K30" s="35"/>
-      <c r="L30" s="35"/>
-      <c r="M30" s="35"/>
-      <c r="N30" s="35"/>
-      <c r="O30" s="35"/>
-      <c r="P30" s="35"/>
-      <c r="Q30" s="35"/>
-      <c r="R30" s="35"/>
-      <c r="S30" s="35"/>
-      <c r="T30" s="35"/>
-      <c r="U30" s="35"/>
-      <c r="V30" s="35"/>
-      <c r="W30" s="35"/>
-      <c r="X30" s="35"/>
-      <c r="Y30" s="35"/>
-      <c r="Z30" s="35"/>
-      <c r="AA30" s="35"/>
-      <c r="AB30" s="36"/>
-      <c r="AC30" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD30" s="35"/>
-    </row>
-    <row r="31" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="34">
-        <v>30</v>
-      </c>
-      <c r="B31" s="35"/>
-      <c r="C31" s="35"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="35"/>
-      <c r="H31" s="35"/>
-      <c r="I31" s="35"/>
-      <c r="J31" s="35"/>
-      <c r="K31" s="35"/>
-      <c r="L31" s="35"/>
-      <c r="M31" s="35"/>
-      <c r="N31" s="35"/>
-      <c r="O31" s="35"/>
-      <c r="P31" s="35"/>
-      <c r="Q31" s="35"/>
-      <c r="R31" s="35"/>
-      <c r="S31" s="35"/>
-      <c r="T31" s="35"/>
-      <c r="U31" s="35"/>
-      <c r="V31" s="35"/>
-      <c r="W31" s="35"/>
-      <c r="X31" s="35"/>
-      <c r="Y31" s="35"/>
-      <c r="Z31" s="35"/>
-      <c r="AA31" s="35"/>
-      <c r="AB31" s="36"/>
-      <c r="AC31" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD31" s="35"/>
-    </row>
-    <row r="32" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="34">
-        <v>31</v>
-      </c>
-      <c r="B32" s="35"/>
-      <c r="C32" s="35"/>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="35"/>
-      <c r="I32" s="35"/>
-      <c r="J32" s="35"/>
-      <c r="K32" s="35"/>
-      <c r="L32" s="35"/>
-      <c r="M32" s="35"/>
-      <c r="N32" s="35"/>
-      <c r="O32" s="35"/>
-      <c r="P32" s="35"/>
-      <c r="Q32" s="35"/>
-      <c r="R32" s="35"/>
-      <c r="S32" s="35"/>
-      <c r="T32" s="35"/>
-      <c r="U32" s="35"/>
-      <c r="V32" s="35"/>
-      <c r="W32" s="35"/>
-      <c r="X32" s="35"/>
-      <c r="Y32" s="35"/>
-      <c r="Z32" s="35"/>
-      <c r="AA32" s="35"/>
-      <c r="AB32" s="36"/>
-      <c r="AC32" s="35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD32" s="35"/>
-    </row>
-    <row r="33" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="B33" s="12" t="str">
-        <f t="shared" ref="B33:AC33" si="1">IF(COUNTA(B2:B32)&gt;0,SUM(B2:B32),"")</f>
-        <v/>
-      </c>
-      <c r="C33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="D33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="E33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="L33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="N33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Q33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="R33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="S33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="U33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="V33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="X33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Y33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Z33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AA33" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB33" s="38" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AC33" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AD33" s="39"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
 </file>
--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -2523,13 +2523,13 @@
         <f>IF(Setiembre!D32&gt;0,Setiembre!D32,"")</f>
         <v/>
       </c>
-      <c r="E18" s="1" t="str">
+      <c r="E18" s="1">
         <f>IF(Setiembre!E32&gt;0,Setiembre!E32,"")</f>
-        <v/>
-      </c>
-      <c r="F18" s="1" t="str">
+        <v>498</v>
+      </c>
+      <c r="F18" s="1">
         <f>IF(Setiembre!F32&gt;0,Setiembre!F32,"")</f>
-        <v/>
+        <v>18447</v>
       </c>
       <c r="G18" s="1" t="str">
         <f>IF(Setiembre!G32&gt;0,Setiembre!G32,"")</f>
@@ -3545,13 +3545,13 @@
         <f>IF(ISNUMBER(Setiembre!D32),D7-Setiembre!D32,"")</f>
         <v/>
       </c>
-      <c r="E29" s="1" t="str">
+      <c r="E29" s="1">
         <f>IF(ISNUMBER(Setiembre!E32),E7-Setiembre!E32,"")</f>
-        <v/>
-      </c>
-      <c r="F29" s="1" t="str">
+        <v>-498</v>
+      </c>
+      <c r="F29" s="1">
         <f>IF(ISNUMBER(Setiembre!F32),F7-Setiembre!F32,"")</f>
-        <v/>
+        <v>8553</v>
       </c>
       <c r="G29" s="1" t="str">
         <f>IF(ISNUMBER(Setiembre!G32),G7-Setiembre!G32,"")</f>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="AC29" s="12">
         <f t="shared" si="7"/>
-        <v>18153.71</v>
+        <v>26208.71</v>
       </c>
     </row>
     <row r="30" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3999,11 +3999,11 @@
       </c>
       <c r="E33" s="12">
         <f t="shared" si="8"/>
-        <v>-360.81999999999971</v>
+        <v>-858.81999999999971</v>
       </c>
       <c r="F33" s="12">
         <f t="shared" si="8"/>
-        <v>-1886</v>
+        <v>6667</v>
       </c>
       <c r="G33" s="12">
         <f t="shared" si="8"/>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>6668.7699999999968</v>
+        <v>14723.769999999993</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10390,7 +10390,9 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="12" width="13" customWidth="1"/>
+    <col min="2" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" customWidth="1"/>
+    <col min="5" max="12" width="13" customWidth="1"/>
     <col min="13" max="13" width="15.7109375" customWidth="1"/>
     <col min="14" max="27" width="13" customWidth="1"/>
     <col min="28" max="28" width="14" customWidth="1"/>
@@ -10536,8 +10538,12 @@
       <c r="B3" s="35"/>
       <c r="C3" s="35"/>
       <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
+      <c r="E3" s="35">
+        <v>498</v>
+      </c>
+      <c r="F3" s="35">
+        <v>18447</v>
+      </c>
       <c r="G3" s="35"/>
       <c r="H3" s="35"/>
       <c r="I3" s="35"/>
@@ -10562,7 +10568,7 @@
       <c r="AB3" s="36"/>
       <c r="AC3" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>18945</v>
       </c>
       <c r="AD3" s="35"/>
     </row>
@@ -11618,13 +11624,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="E32" s="12">
+        <f t="shared" si="1"/>
+        <v>498</v>
+      </c>
+      <c r="F32" s="12">
+        <f t="shared" si="1"/>
+        <v>18447</v>
       </c>
       <c r="G32" s="12" t="str">
         <f t="shared" si="1"/>
@@ -11716,7 +11722,7 @@
       </c>
       <c r="AC32" s="12">
         <f t="shared" si="1"/>
-        <v>846.29</v>
+        <v>19791.29</v>
       </c>
       <c r="AD32" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -1558,10 +1558,10 @@
         <v>23200</v>
       </c>
       <c r="L7" s="1">
-        <v>8000</v>
+        <v>7500</v>
       </c>
       <c r="M7" s="1">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="N7" s="1">
         <v>810</v>
@@ -1605,7 +1605,7 @@
       <c r="AB7" s="6"/>
       <c r="AC7" s="1">
         <f t="shared" si="0"/>
-        <v>171329</v>
+        <v>175829</v>
       </c>
       <c r="AD7" s="7">
         <f t="shared" si="1"/>
@@ -1623,15 +1623,15 @@
       </c>
       <c r="AH7" s="8">
         <f t="shared" si="3"/>
-        <v>65664.5</v>
+        <v>62914.5</v>
       </c>
       <c r="AI7" s="9">
         <f t="shared" si="4"/>
-        <v>69964.5</v>
+        <v>72214.5</v>
       </c>
       <c r="AJ7" s="10">
         <f t="shared" si="5"/>
-        <v>135629</v>
+        <v>135129</v>
       </c>
     </row>
     <row r="8" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2535,13 +2535,13 @@
         <f>IF(Setiembre!G32&gt;0,Setiembre!G32,"")</f>
         <v/>
       </c>
-      <c r="H18" s="1" t="str">
+      <c r="H18" s="1">
         <f>IF(Setiembre!H32&gt;0,Setiembre!H32,"")</f>
-        <v/>
-      </c>
-      <c r="I18" s="1" t="str">
+        <v>3291.56</v>
+      </c>
+      <c r="I18" s="1">
         <f>IF(Setiembre!I32&gt;0,Setiembre!I32,"")</f>
-        <v/>
+        <v>3687.55</v>
       </c>
       <c r="J18" s="1" t="str">
         <f>IF(Setiembre!J32&gt;0,Setiembre!J32,"")</f>
@@ -2567,9 +2567,9 @@
         <f>IF(Setiembre!O32&gt;0,Setiembre!O32,"")</f>
         <v/>
       </c>
-      <c r="P18" s="1" t="str">
+      <c r="P18" s="1">
         <f>IF(Setiembre!P32&gt;0,Setiembre!P32,"")</f>
-        <v/>
+        <v>1800</v>
       </c>
       <c r="Q18" s="1" t="str">
         <f>IF(Setiembre!Q32&gt;0,Setiembre!Q32,"")</f>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="R18" s="1">
         <f>IF(Setiembre!R32&gt;0,Setiembre!R32,"")</f>
-        <v>846.29</v>
+        <v>1406.6399999999999</v>
       </c>
       <c r="S18" s="1" t="str">
         <f>IF(Setiembre!S32&gt;0,Setiembre!S32,"")</f>
@@ -3557,13 +3557,13 @@
         <f>IF(ISNUMBER(Setiembre!G32),G7-Setiembre!G32,"")</f>
         <v/>
       </c>
-      <c r="H29" s="1" t="str">
+      <c r="H29" s="1">
         <f>IF(ISNUMBER(Setiembre!H32),H7-Setiembre!H32,"")</f>
-        <v/>
-      </c>
-      <c r="I29" s="1" t="str">
+        <v>8.4400000000000546</v>
+      </c>
+      <c r="I29" s="1">
         <f>IF(ISNUMBER(Setiembre!I32),I7-Setiembre!I32,"")</f>
-        <v/>
+        <v>62.449999999999818</v>
       </c>
       <c r="J29" s="1" t="str">
         <f>IF(ISNUMBER(Setiembre!J32),J7-Setiembre!J32,"")</f>
@@ -3589,9 +3589,9 @@
         <f>IF(ISNUMBER(Setiembre!O32),O7-Setiembre!O32,"")</f>
         <v/>
       </c>
-      <c r="P29" s="1" t="str">
+      <c r="P29" s="1">
         <f>IF(ISNUMBER(Setiembre!P32),P7-Setiembre!P32,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q29" s="1" t="str">
         <f>IF(ISNUMBER(Setiembre!Q32),Q7-Setiembre!Q32,"")</f>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="R29" s="1">
         <f>IF(ISNUMBER(Setiembre!R32),R7-Setiembre!R32,"")</f>
-        <v>18153.71</v>
+        <v>17593.36</v>
       </c>
       <c r="S29" s="1" t="str">
         <f>IF(ISNUMBER(Setiembre!S32),S7-Setiembre!S32,"")</f>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="AC29" s="12">
         <f t="shared" si="7"/>
-        <v>26208.71</v>
+        <v>25719.25</v>
       </c>
     </row>
     <row r="30" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4011,11 +4011,11 @@
       </c>
       <c r="H33" s="12">
         <f t="shared" si="8"/>
-        <v>416.88000000000011</v>
+        <v>425.32000000000016</v>
       </c>
       <c r="I33" s="12">
         <f t="shared" si="8"/>
-        <v>1014.0899999999997</v>
+        <v>1076.5399999999995</v>
       </c>
       <c r="J33" s="12">
         <f t="shared" si="8"/>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>22471.579999999998</v>
+        <v>21911.23</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>14723.769999999993</v>
+        <v>14234.309999999994</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10394,7 +10394,9 @@
     <col min="4" max="4" width="15.28515625" customWidth="1"/>
     <col min="5" max="12" width="13" customWidth="1"/>
     <col min="13" max="13" width="15.7109375" customWidth="1"/>
-    <col min="14" max="27" width="13" customWidth="1"/>
+    <col min="14" max="25" width="13" customWidth="1"/>
+    <col min="26" max="26" width="16.140625" customWidth="1"/>
+    <col min="27" max="27" width="13" customWidth="1"/>
     <col min="28" max="28" width="14" customWidth="1"/>
     <col min="29" max="29" width="25" customWidth="1"/>
   </cols>
@@ -10555,7 +10557,10 @@
       <c r="O3" s="35"/>
       <c r="P3" s="35"/>
       <c r="Q3" s="35"/>
-      <c r="R3" s="35"/>
+      <c r="R3" s="35">
+        <f>605-44.65</f>
+        <v>560.35</v>
+      </c>
       <c r="S3" s="35"/>
       <c r="T3" s="35"/>
       <c r="U3" s="35"/>
@@ -10568,7 +10573,7 @@
       <c r="AB3" s="36"/>
       <c r="AC3" s="35">
         <f t="shared" si="0"/>
-        <v>18945</v>
+        <v>19505.349999999999</v>
       </c>
       <c r="AD3" s="35"/>
     </row>
@@ -10582,15 +10587,23 @@
       <c r="E4" s="35"/>
       <c r="F4" s="35"/>
       <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
+      <c r="H4" s="35">
+        <f>3327-35.44</f>
+        <v>3291.56</v>
+      </c>
+      <c r="I4" s="35">
+        <f>3749-61.45</f>
+        <v>3687.55</v>
+      </c>
       <c r="J4" s="35"/>
       <c r="K4" s="35"/>
       <c r="L4" s="35"/>
       <c r="M4" s="35"/>
       <c r="N4" s="35"/>
       <c r="O4" s="35"/>
-      <c r="P4" s="35"/>
+      <c r="P4" s="35">
+        <v>1800</v>
+      </c>
       <c r="Q4" s="35"/>
       <c r="R4" s="35"/>
       <c r="S4" s="35"/>
@@ -10605,7 +10618,7 @@
       <c r="AB4" s="36"/>
       <c r="AC4" s="35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8779.11</v>
       </c>
       <c r="AD4" s="35"/>
     </row>
@@ -11636,13 +11649,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="H32" s="12">
+        <f t="shared" si="1"/>
+        <v>3291.56</v>
+      </c>
+      <c r="I32" s="12">
+        <f t="shared" si="1"/>
+        <v>3687.55</v>
       </c>
       <c r="J32" s="12" t="str">
         <f t="shared" si="1"/>
@@ -11668,9 +11681,9 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="P32" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="P32" s="12">
+        <f t="shared" si="1"/>
+        <v>1800</v>
       </c>
       <c r="Q32" s="12" t="str">
         <f t="shared" si="1"/>
@@ -11678,7 +11691,7 @@
       </c>
       <c r="R32" s="12">
         <f t="shared" si="1"/>
-        <v>846.29</v>
+        <v>1406.6399999999999</v>
       </c>
       <c r="S32" s="12" t="str">
         <f t="shared" si="1"/>
@@ -11722,7 +11735,7 @@
       </c>
       <c r="AC32" s="12">
         <f t="shared" si="1"/>
-        <v>19791.29</v>
+        <v>29130.75</v>
       </c>
       <c r="AD32" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="F18" s="1">
         <f>IF(Setiembre!F32&gt;0,Setiembre!F32,"")</f>
-        <v>18447</v>
+        <v>26792</v>
       </c>
       <c r="G18" s="1" t="str">
         <f>IF(Setiembre!G32&gt;0,Setiembre!G32,"")</f>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="F29" s="1">
         <f>IF(ISNUMBER(Setiembre!F32),F7-Setiembre!F32,"")</f>
-        <v>8553</v>
+        <v>208</v>
       </c>
       <c r="G29" s="1" t="str">
         <f>IF(ISNUMBER(Setiembre!G32),G7-Setiembre!G32,"")</f>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="AC29" s="12">
         <f t="shared" si="7"/>
-        <v>25719.25</v>
+        <v>17374.25</v>
       </c>
     </row>
     <row r="30" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="F33" s="12">
         <f t="shared" si="8"/>
-        <v>6667</v>
+        <v>-1678</v>
       </c>
       <c r="G33" s="12">
         <f t="shared" si="8"/>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>14234.309999999994</v>
+        <v>5889.3099999999977</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10585,7 +10585,9 @@
       <c r="C4" s="35"/>
       <c r="D4" s="35"/>
       <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
+      <c r="F4" s="35">
+        <v>8345</v>
+      </c>
       <c r="G4" s="35"/>
       <c r="H4" s="35">
         <f>3327-35.44</f>
@@ -10618,7 +10620,7 @@
       <c r="AB4" s="36"/>
       <c r="AC4" s="35">
         <f t="shared" si="0"/>
-        <v>8779.11</v>
+        <v>17124.11</v>
       </c>
       <c r="AD4" s="35"/>
     </row>
@@ -11643,7 +11645,7 @@
       </c>
       <c r="F32" s="12">
         <f t="shared" si="1"/>
-        <v>18447</v>
+        <v>26792</v>
       </c>
       <c r="G32" s="12" t="str">
         <f t="shared" si="1"/>
@@ -11735,7 +11737,7 @@
       </c>
       <c r="AC32" s="12">
         <f t="shared" si="1"/>
-        <v>29130.75</v>
+        <v>37475.75</v>
       </c>
       <c r="AD32" s="39"/>
     </row>

--- a/Presupuesto_2026.xlsx
+++ b/Presupuesto_2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620" tabRatio="500" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="R18" s="1">
         <f>IF(Setiembre!R32&gt;0,Setiembre!R32,"")</f>
-        <v>1406.6399999999999</v>
+        <v>3616.7999999999997</v>
       </c>
       <c r="S18" s="1" t="str">
         <f>IF(Setiembre!S32&gt;0,Setiembre!S32,"")</f>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="R29" s="1">
         <f>IF(ISNUMBER(Setiembre!R32),R7-Setiembre!R32,"")</f>
-        <v>17593.36</v>
+        <v>15383.2</v>
       </c>
       <c r="S29" s="1" t="str">
         <f>IF(ISNUMBER(Setiembre!S32),S7-Setiembre!S32,"")</f>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="AC29" s="12">
         <f t="shared" si="7"/>
-        <v>17374.25</v>
+        <v>15164.09</v>
       </c>
     </row>
     <row r="30" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="R33" s="12">
         <f t="shared" si="8"/>
-        <v>21911.23</v>
+        <v>19701.07</v>
       </c>
       <c r="S33" s="12">
         <f t="shared" si="8"/>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="AC33" s="12">
         <f t="shared" si="7"/>
-        <v>5889.3099999999977</v>
+        <v>3679.1499999999978</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10607,7 +10607,10 @@
         <v>1800</v>
       </c>
       <c r="Q4" s="35"/>
-      <c r="R4" s="35"/>
+      <c r="R4" s="35">
+        <f>378+1112.2+742-15.61-6.43</f>
+        <v>2210.16</v>
+      </c>
       <c r="S4" s="35"/>
       <c r="T4" s="35"/>
       <c r="U4" s="35"/>
@@ -10620,7 +10623,7 @@
       <c r="AB4" s="36"/>
       <c r="AC4" s="35">
         <f t="shared" si="0"/>
-        <v>17124.11</v>
+        <v>19334.27</v>
       </c>
       <c r="AD4" s="35"/>
     </row>
@@ -11693,7 +11696,7 @@
       </c>
       <c r="R32" s="12">
         <f t="shared" si="1"/>
-        <v>1406.6399999999999</v>
+        <v>3616.7999999999997</v>
       </c>
       <c r="S32" s="12" t="str">
         <f t="shared" si="1"/>
@@ -11737,7 +11740,7 @@
       </c>
       <c r="AC32" s="12">
         <f t="shared" si="1"/>
-        <v>37475.75</v>
+        <v>39685.910000000003</v>
       </c>
       <c r="AD32" s="39"/>
     </row>
